--- a/testprocess/1-process/大对象测试/Testing_LOB.xlsx
+++ b/testprocess/1-process/大对象测试/Testing_LOB.xlsx
@@ -4,29 +4,32 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="8"/>
   </bookViews>
   <sheets>
-    <sheet name="Main" sheetId="1" r:id="rId1"/>
-    <sheet name="基本功能" sheetId="2" r:id="rId2"/>
-    <sheet name="相关功能" sheetId="3" r:id="rId3"/>
-    <sheet name="数据构造" sheetId="13" r:id="rId4"/>
-    <sheet name="并发" sheetId="7" r:id="rId5"/>
-    <sheet name="边界" sheetId="8" r:id="rId6"/>
-    <sheet name="约束" sheetId="9" r:id="rId7"/>
-    <sheet name="一致性" sheetId="4" r:id="rId8"/>
-    <sheet name="可靠性" sheetId="5" r:id="rId9"/>
-    <sheet name="均匀性" sheetId="10" r:id="rId10"/>
-    <sheet name="性能" sheetId="6" r:id="rId11"/>
-    <sheet name="部署" sheetId="11" r:id="rId12"/>
-    <sheet name="异常" sheetId="12" r:id="rId13"/>
+    <sheet name="测试主题" sheetId="14" r:id="rId1"/>
+    <sheet name="Main" sheetId="1" r:id="rId2"/>
+    <sheet name="基本功能" sheetId="2" r:id="rId3"/>
+    <sheet name="相关功能" sheetId="3" r:id="rId4"/>
+    <sheet name="数据构造" sheetId="13" r:id="rId5"/>
+    <sheet name="并发" sheetId="7" r:id="rId6"/>
+    <sheet name="边界" sheetId="8" r:id="rId7"/>
+    <sheet name="约束" sheetId="9" r:id="rId8"/>
+    <sheet name="一致性" sheetId="4" r:id="rId9"/>
+    <sheet name="可靠性" sheetId="5" r:id="rId10"/>
+    <sheet name="均匀性" sheetId="10" r:id="rId11"/>
+    <sheet name="性能" sheetId="6" r:id="rId12"/>
+    <sheet name="部署" sheetId="11" r:id="rId13"/>
+    <sheet name="异常" sheetId="12" r:id="rId14"/>
+    <sheet name="测试评审" sheetId="15" r:id="rId15"/>
+    <sheet name="测试报告" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="489">
   <si>
     <t>可靠性</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -344,14 +347,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>250K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>260K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>128M</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -384,18 +379,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>256K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>128M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4G</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>性能</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -437,14 +420,6 @@
   </si>
   <si>
     <t>大对象不被另一表访问</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>130M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>120M</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1491,10 +1466,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>128M(core大小?)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>大于256K</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2062,12 +2033,169 @@
     <t>写读删打开关闭</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>128M(存储文件的涨幅大小)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小于256K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大于128M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小于128M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等于256K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等于128M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>该表格用于填写测试项目基本信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大对象数据存储测试【如视频/音频/图片等文件】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*填写项目名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>起始时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*填写测试立项时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预计完成时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*填写预期测试结束时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负责人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡晓均</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*填写该项目的测试负责人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参与人员</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*填写参与该项目的测试人员。如果除负责人外无其它测试人员参与，那么填无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>难度系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*由测试主管根据测试任务难度填写。1.0为日常测试任务难度水平。难度越高，该系数越大。最大为2.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目背景：如何将存储视频、音频以及图片等文件存储到SequoiaDB。
+项目需求：将数据格式为视频、音频及图片的数据存入数据库。
+测试目标：1.大对象存储的数据准确无误；
+         2.大对象数据可进行基本的操作，增删改查、切分等等；
+         3.大对象数据对其它的数据库的其他操作没有影响。
+测试方式：手工测试+自动化用例测试
+实现方式：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*填写项目与测试相关情况。例如项目背景、项目需求、实现技术等等。同时说明测试目标（例如验证xxx功能、获取性能数据等等）、测试方式（黑箱/白箱）、实现方式（脚本/程序/工具）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与会者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>评审意见</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>评审人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>说明：该表格用于记录评审意见，在测试设计与测试点评审时记录。解决完成后将条目背景色改为绿色填充。见下图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已解决</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.测试结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.测试结论</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.产物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.总结与建议</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="10">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2149,8 +2277,43 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="18"/>
+      <color theme="10"/>
+      <name val="黑体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2215,8 +2378,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="45">
+  <borders count="52">
     <border>
       <left/>
       <right/>
@@ -2800,6 +2981,85 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2808,7 +3068,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3089,6 +3349,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3097,18 +3366,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3121,80 +3402,160 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="13" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="13" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="50" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="41" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3492,399 +3853,456 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
-    <tabColor rgb="FFFF0000"/>
+    <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="B1:L19"/>
+  <dimension ref="B1:D28"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="1.25" style="1" customWidth="1"/>
-    <col min="2" max="12" width="17.375" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="1.25" customWidth="1"/>
+    <col min="2" max="2" width="13.125" customWidth="1"/>
+    <col min="3" max="3" width="99.375" style="134" customWidth="1"/>
+    <col min="4" max="4" width="66.375" style="133" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="6" customHeight="1" thickBot="1"/>
-    <row r="2" spans="2:12" ht="39.75" customHeight="1" thickBot="1">
-      <c r="B2" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="H2" s="42" t="s">
-        <v>261</v>
-      </c>
-      <c r="I2" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="J2" s="79" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="L2" s="41" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" ht="24.95" customHeight="1">
-      <c r="B3" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>257</v>
-      </c>
-      <c r="F3" s="43">
-        <v>0</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="J3" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="K3" s="29" t="s">
-        <v>295</v>
-      </c>
-      <c r="L3" s="47" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="24.95" customHeight="1">
-      <c r="B4" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>258</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="30"/>
-      <c r="H4" s="23" t="s">
-        <v>438</v>
-      </c>
-      <c r="I4" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="J4" s="24"/>
-      <c r="K4" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="L4" s="48" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="24.95" customHeight="1">
-      <c r="B5" s="55" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>259</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="30"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="48"/>
-    </row>
-    <row r="6" spans="2:12" ht="24.95" customHeight="1">
-      <c r="B6" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="48"/>
-    </row>
-    <row r="7" spans="2:12" ht="24.95" customHeight="1">
-      <c r="B7" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="30"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="48"/>
-    </row>
-    <row r="8" spans="2:12" ht="24.95" customHeight="1">
-      <c r="B8" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="92" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="48"/>
-    </row>
-    <row r="9" spans="2:12" ht="24.95" customHeight="1">
-      <c r="B9" s="44"/>
-      <c r="C9" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="G9" s="30"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="48"/>
-    </row>
-    <row r="10" spans="2:12" ht="24.95" customHeight="1">
-      <c r="B10" s="44"/>
-      <c r="C10" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="23"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="30"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="48"/>
-    </row>
-    <row r="11" spans="2:12" ht="24.95" customHeight="1">
-      <c r="B11" s="45"/>
-      <c r="C11" s="78" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="49"/>
-    </row>
-    <row r="12" spans="2:12" ht="24.95" customHeight="1">
-      <c r="B12" s="45"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="49"/>
-    </row>
-    <row r="13" spans="2:12" ht="24.95" customHeight="1">
-      <c r="B13" s="45"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="49"/>
-    </row>
-    <row r="14" spans="2:12" ht="24.95" customHeight="1">
-      <c r="B14" s="45"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="49"/>
-    </row>
-    <row r="15" spans="2:12" ht="24.95" customHeight="1">
-      <c r="B15" s="45"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="49"/>
-    </row>
-    <row r="16" spans="2:12" ht="24.95" customHeight="1">
-      <c r="B16" s="45"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="49"/>
-    </row>
-    <row r="17" spans="2:12" ht="24.95" customHeight="1">
-      <c r="B17" s="45"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="49"/>
-    </row>
-    <row r="18" spans="2:12" ht="24.95" customHeight="1" thickBot="1">
-      <c r="B18" s="46"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="50"/>
-    </row>
-    <row r="19" spans="2:12" s="37" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="B19" s="34" t="s">
-        <v>443</v>
-      </c>
-      <c r="C19" s="37" t="s">
-        <v>441</v>
-      </c>
-      <c r="D19" s="54" t="s">
-        <v>444</v>
-      </c>
-      <c r="E19" s="37" t="s">
-        <v>440</v>
-      </c>
-      <c r="F19" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="37" t="s">
-        <v>439</v>
-      </c>
-      <c r="H19" s="93" t="s">
-        <v>445</v>
-      </c>
-      <c r="I19" s="37" t="s">
-        <v>442</v>
-      </c>
-      <c r="J19" s="94"/>
-      <c r="K19" s="67"/>
+    <row r="1" spans="2:4" ht="6" customHeight="1">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+    </row>
+    <row r="2" spans="2:4" ht="14.25" thickBot="1">
+      <c r="B2" s="132" t="s">
+        <v>457</v>
+      </c>
+      <c r="C2" s="132"/>
+    </row>
+    <row r="3" spans="2:4" ht="25.5">
+      <c r="B3" s="135" t="s">
+        <v>458</v>
+      </c>
+      <c r="C3" s="136" t="s">
+        <v>459</v>
+      </c>
+      <c r="D3" s="137" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" s="138" t="s">
+        <v>461</v>
+      </c>
+      <c r="C4" s="139">
+        <v>41849</v>
+      </c>
+      <c r="D4" s="137" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" s="138" t="s">
+        <v>463</v>
+      </c>
+      <c r="C5" s="139"/>
+      <c r="D5" s="137" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" s="138" t="s">
+        <v>465</v>
+      </c>
+      <c r="C6" s="140" t="s">
+        <v>466</v>
+      </c>
+      <c r="D6" s="137" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="13.5" customHeight="1">
+      <c r="B7" s="141" t="s">
+        <v>468</v>
+      </c>
+      <c r="C7" s="140"/>
+      <c r="D7" s="137" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" s="142" t="s">
+        <v>470</v>
+      </c>
+      <c r="C8" s="143"/>
+      <c r="D8" s="137" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="40.5" customHeight="1">
+      <c r="B9" s="144" t="s">
+        <v>472</v>
+      </c>
+      <c r="C9" s="145" t="s">
+        <v>473</v>
+      </c>
+      <c r="D9" s="146" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" s="147"/>
+      <c r="C10" s="148"/>
+      <c r="D10" s="146"/>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="B11" s="147"/>
+      <c r="C11" s="148"/>
+      <c r="D11" s="146"/>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" s="147"/>
+      <c r="C12" s="148"/>
+      <c r="D12" s="146"/>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" s="147"/>
+      <c r="C13" s="148"/>
+      <c r="D13" s="146"/>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" s="147"/>
+      <c r="C14" s="148"/>
+      <c r="D14" s="146"/>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15" s="147"/>
+      <c r="C15" s="148"/>
+      <c r="D15" s="146"/>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16" s="147"/>
+      <c r="C16" s="148"/>
+      <c r="D16" s="146"/>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="147"/>
+      <c r="C17" s="148"/>
+      <c r="D17" s="146"/>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="147"/>
+      <c r="C18" s="148"/>
+      <c r="D18" s="146"/>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" s="147"/>
+      <c r="C19" s="148"/>
+      <c r="D19" s="146"/>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" s="147"/>
+      <c r="C20" s="148"/>
+      <c r="D20" s="146"/>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" s="147"/>
+      <c r="C21" s="148"/>
+      <c r="D21" s="146"/>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" s="147"/>
+      <c r="C22" s="148"/>
+      <c r="D22" s="146"/>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" s="147"/>
+      <c r="C23" s="148"/>
+      <c r="D23" s="146"/>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" s="147"/>
+      <c r="C24" s="148"/>
+      <c r="D24" s="146"/>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" s="147"/>
+      <c r="C25" s="148"/>
+      <c r="D25" s="146"/>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" s="147"/>
+      <c r="C26" s="148"/>
+      <c r="D26" s="146"/>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" s="147"/>
+      <c r="C27" s="148"/>
+      <c r="D27" s="146"/>
+    </row>
+    <row r="28" spans="2:4" ht="14.25" thickBot="1">
+      <c r="B28" s="149"/>
+      <c r="C28" s="150"/>
+      <c r="D28" s="146"/>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B9:B28"/>
+    <mergeCell ref="C9:C28"/>
+    <mergeCell ref="D9:D28"/>
+    <mergeCell ref="B2:C2"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="E2" location="并发!A1" display="并发"/>
-    <hyperlink ref="B2" location="基本功能!A1" display="基本功能"/>
-    <hyperlink ref="F2" location="边界!A1" display="边界"/>
-    <hyperlink ref="L2" location="部署!A1" display="部署"/>
-    <hyperlink ref="K2" location="性能!A1" display="性能"/>
-    <hyperlink ref="D2" location="数据构造!A1" display="数据构造"/>
-    <hyperlink ref="C2" location="相关功能!A1" display="相关功能"/>
-    <hyperlink ref="G2" location="约束!A1" display="约束"/>
-    <hyperlink ref="H2" location="一致性!A1" display="一致性"/>
-    <hyperlink ref="I2" location="可靠性!A1" display="可靠性"/>
-    <hyperlink ref="J2" location="均匀性!A1" display="均匀性"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF0070C0"/>
+  </sheetPr>
+  <dimension ref="B1:M13"/>
+  <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="1.25" customWidth="1"/>
+    <col min="2" max="20" width="15.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" ht="6" customHeight="1" thickBot="1"/>
+    <row r="2" spans="2:13" ht="26.25" thickBot="1">
+      <c r="B2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="B3" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="B4" s="82" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B5" s="20"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+    </row>
+    <row r="7" spans="2:13" ht="26.25" customHeight="1">
+      <c r="B7" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="109" t="s">
+        <v>341</v>
+      </c>
+      <c r="E7" s="110"/>
+      <c r="F7" s="119" t="s">
+        <v>342</v>
+      </c>
+      <c r="G7" s="119"/>
+      <c r="H7" s="119"/>
+      <c r="I7" s="119"/>
+      <c r="J7" s="119"/>
+      <c r="K7" s="109" t="s">
+        <v>103</v>
+      </c>
+      <c r="L7" s="111"/>
+      <c r="M7" s="110"/>
+    </row>
+    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B8" s="104" t="s">
+        <v>321</v>
+      </c>
+      <c r="C8" s="74" t="s">
+        <v>322</v>
+      </c>
+      <c r="D8" s="98" t="s">
+        <v>325</v>
+      </c>
+      <c r="E8" s="100"/>
+      <c r="F8" s="112" t="s">
+        <v>324</v>
+      </c>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="112"/>
+      <c r="K8" s="108" t="s">
+        <v>338</v>
+      </c>
+      <c r="L8" s="108"/>
+      <c r="M8" s="108"/>
+    </row>
+    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B9" s="106"/>
+      <c r="C9" s="74" t="s">
+        <v>323</v>
+      </c>
+      <c r="D9" s="98" t="s">
+        <v>326</v>
+      </c>
+      <c r="E9" s="100"/>
+      <c r="F9" s="112" t="s">
+        <v>326</v>
+      </c>
+      <c r="G9" s="112"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="112"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="64"/>
+      <c r="M9" s="65"/>
+    </row>
+    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B10" s="107" t="s">
+        <v>327</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>322</v>
+      </c>
+      <c r="D10" s="98" t="s">
+        <v>329</v>
+      </c>
+      <c r="E10" s="100"/>
+      <c r="F10" s="112" t="s">
+        <v>331</v>
+      </c>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="112"/>
+      <c r="K10" s="98" t="s">
+        <v>336</v>
+      </c>
+      <c r="L10" s="99"/>
+      <c r="M10" s="100"/>
+    </row>
+    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B11" s="107"/>
+      <c r="C11" s="51" t="s">
+        <v>323</v>
+      </c>
+      <c r="D11" s="98" t="s">
+        <v>330</v>
+      </c>
+      <c r="E11" s="100"/>
+      <c r="F11" s="112" t="s">
+        <v>332</v>
+      </c>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="112"/>
+      <c r="K11" s="98" t="s">
+        <v>337</v>
+      </c>
+      <c r="L11" s="99"/>
+      <c r="M11" s="100"/>
+    </row>
+    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B12" s="107" t="s">
+        <v>328</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>322</v>
+      </c>
+      <c r="D12" s="108" t="s">
+        <v>333</v>
+      </c>
+      <c r="E12" s="108"/>
+      <c r="F12" s="112" t="s">
+        <v>334</v>
+      </c>
+      <c r="G12" s="112"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="112"/>
+      <c r="J12" s="112"/>
+      <c r="K12" s="98" t="s">
+        <v>339</v>
+      </c>
+      <c r="L12" s="99"/>
+      <c r="M12" s="100"/>
+    </row>
+    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B13" s="107"/>
+      <c r="C13" s="51" t="s">
+        <v>323</v>
+      </c>
+      <c r="D13" s="108" t="s">
+        <v>340</v>
+      </c>
+      <c r="E13" s="108"/>
+      <c r="F13" s="112" t="s">
+        <v>335</v>
+      </c>
+      <c r="G13" s="112"/>
+      <c r="H13" s="112"/>
+      <c r="I13" s="112"/>
+      <c r="J13" s="112"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="65"/>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:J11"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -3942,40 +4360,40 @@
     <row r="9" spans="2:11" ht="20.100000000000001" hidden="1" customHeight="1" outlineLevel="1"/>
     <row r="10" spans="2:11" ht="20.100000000000001" hidden="1" customHeight="1" outlineLevel="1"/>
     <row r="11" spans="2:11" ht="26.25" customHeight="1" collapsed="1">
-      <c r="B11" s="102" t="s">
+      <c r="B11" s="109" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="110"/>
+      <c r="D11" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="103"/>
-      <c r="D11" s="113" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" s="113"/>
-      <c r="F11" s="113"/>
-      <c r="G11" s="113"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="J11" s="104"/>
-      <c r="K11" s="103"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="109" t="s">
+        <v>103</v>
+      </c>
+      <c r="J11" s="111"/>
+      <c r="K11" s="110"/>
     </row>
     <row r="12" spans="2:11" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="98" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="98"/>
-      <c r="D12" s="105" t="s">
-        <v>227</v>
-      </c>
-      <c r="E12" s="105"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="98" t="s">
-        <v>399</v>
-      </c>
-      <c r="J12" s="98"/>
-      <c r="K12" s="98"/>
+      <c r="B12" s="108" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="108"/>
+      <c r="D12" s="112" t="s">
+        <v>220</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="112"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="108" t="s">
+        <v>391</v>
+      </c>
+      <c r="J12" s="108"/>
+      <c r="K12" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3991,7 +4409,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -4009,15 +4427,15 @@
         <v>16</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="2:11" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B3" s="81" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>17</v>
@@ -4034,58 +4452,58 @@
       <c r="F4" s="20"/>
     </row>
     <row r="5" spans="2:11" ht="26.25" customHeight="1">
-      <c r="B5" s="102" t="s">
+      <c r="B5" s="109" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="110"/>
+      <c r="D5" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="103"/>
-      <c r="D5" s="113" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="J5" s="104"/>
-      <c r="K5" s="103"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="109" t="s">
+        <v>103</v>
+      </c>
+      <c r="J5" s="111"/>
+      <c r="K5" s="110"/>
     </row>
     <row r="6" spans="2:11" ht="20.100000000000001" customHeight="1">
-      <c r="B6" s="98" t="s">
-        <v>214</v>
-      </c>
-      <c r="C6" s="98"/>
-      <c r="D6" s="105" t="s">
-        <v>216</v>
-      </c>
-      <c r="E6" s="105"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="105"/>
-      <c r="H6" s="105"/>
-      <c r="I6" s="98" t="s">
-        <v>218</v>
-      </c>
-      <c r="J6" s="98"/>
-      <c r="K6" s="98"/>
+      <c r="B6" s="108" t="s">
+        <v>207</v>
+      </c>
+      <c r="C6" s="108"/>
+      <c r="D6" s="112" t="s">
+        <v>209</v>
+      </c>
+      <c r="E6" s="112"/>
+      <c r="F6" s="112"/>
+      <c r="G6" s="112"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="108" t="s">
+        <v>211</v>
+      </c>
+      <c r="J6" s="108"/>
+      <c r="K6" s="108"/>
     </row>
     <row r="7" spans="2:11" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="98" t="s">
-        <v>215</v>
-      </c>
-      <c r="C7" s="98"/>
-      <c r="D7" s="105" t="s">
-        <v>217</v>
-      </c>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="98" t="s">
-        <v>219</v>
-      </c>
-      <c r="J7" s="98"/>
-      <c r="K7" s="98"/>
+      <c r="B7" s="108" t="s">
+        <v>208</v>
+      </c>
+      <c r="C7" s="108"/>
+      <c r="D7" s="112" t="s">
+        <v>210</v>
+      </c>
+      <c r="E7" s="112"/>
+      <c r="F7" s="112"/>
+      <c r="G7" s="112"/>
+      <c r="H7" s="112"/>
+      <c r="I7" s="108" t="s">
+        <v>212</v>
+      </c>
+      <c r="J7" s="108"/>
+      <c r="K7" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -4104,7 +4522,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -4125,18 +4543,18 @@
         <v>11</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B3" s="82" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>17</v>
@@ -4153,119 +4571,119 @@
     </row>
     <row r="5" spans="2:13" ht="26.25" customHeight="1">
       <c r="B5" s="71" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C5" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="109" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="110"/>
+      <c r="F5" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="102" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="103"/>
-      <c r="F5" s="113" t="s">
-        <v>91</v>
-      </c>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="L5" s="104"/>
-      <c r="M5" s="103"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="119"/>
+      <c r="K5" s="109" t="s">
+        <v>103</v>
+      </c>
+      <c r="L5" s="111"/>
+      <c r="M5" s="110"/>
     </row>
     <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B6" s="75" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="D6" s="95" t="s">
-        <v>226</v>
-      </c>
-      <c r="E6" s="97"/>
-      <c r="F6" s="105" t="s">
-        <v>222</v>
-      </c>
-      <c r="G6" s="105"/>
-      <c r="H6" s="105"/>
-      <c r="I6" s="105"/>
-      <c r="J6" s="105"/>
-      <c r="K6" s="98" t="s">
-        <v>392</v>
-      </c>
-      <c r="L6" s="98"/>
-      <c r="M6" s="98"/>
+        <v>255</v>
+      </c>
+      <c r="D6" s="98" t="s">
+        <v>219</v>
+      </c>
+      <c r="E6" s="100"/>
+      <c r="F6" s="112" t="s">
+        <v>215</v>
+      </c>
+      <c r="G6" s="112"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="112"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="108" t="s">
+        <v>384</v>
+      </c>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108"/>
     </row>
     <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="109" t="s">
-        <v>393</v>
+      <c r="B7" s="104" t="s">
+        <v>385</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>394</v>
-      </c>
-      <c r="D7" s="95" t="s">
-        <v>397</v>
-      </c>
-      <c r="E7" s="97"/>
-      <c r="F7" s="99" t="s">
-        <v>223</v>
-      </c>
-      <c r="G7" s="100"/>
-      <c r="H7" s="100"/>
-      <c r="I7" s="100"/>
-      <c r="J7" s="100"/>
-      <c r="K7" s="95" t="s">
-        <v>221</v>
-      </c>
-      <c r="L7" s="96"/>
-      <c r="M7" s="97"/>
+        <v>386</v>
+      </c>
+      <c r="D7" s="98" t="s">
+        <v>389</v>
+      </c>
+      <c r="E7" s="100"/>
+      <c r="F7" s="95" t="s">
+        <v>216</v>
+      </c>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="98" t="s">
+        <v>214</v>
+      </c>
+      <c r="L7" s="99"/>
+      <c r="M7" s="100"/>
     </row>
     <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="110"/>
+      <c r="B8" s="105"/>
       <c r="C8" s="51" t="s">
-        <v>395</v>
-      </c>
-      <c r="D8" s="95" t="s">
-        <v>397</v>
-      </c>
-      <c r="E8" s="97"/>
-      <c r="F8" s="99" t="s">
-        <v>224</v>
-      </c>
-      <c r="G8" s="100"/>
-      <c r="H8" s="100"/>
-      <c r="I8" s="100"/>
-      <c r="J8" s="100"/>
-      <c r="K8" s="95" t="s">
-        <v>220</v>
-      </c>
-      <c r="L8" s="96"/>
-      <c r="M8" s="97"/>
+        <v>387</v>
+      </c>
+      <c r="D8" s="98" t="s">
+        <v>389</v>
+      </c>
+      <c r="E8" s="100"/>
+      <c r="F8" s="95" t="s">
+        <v>217</v>
+      </c>
+      <c r="G8" s="96"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="96"/>
+      <c r="J8" s="96"/>
+      <c r="K8" s="98" t="s">
+        <v>213</v>
+      </c>
+      <c r="L8" s="99"/>
+      <c r="M8" s="100"/>
     </row>
     <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="111"/>
+      <c r="B9" s="106"/>
       <c r="C9" s="91" t="s">
-        <v>396</v>
-      </c>
-      <c r="D9" s="95" t="s">
-        <v>397</v>
-      </c>
-      <c r="E9" s="97"/>
-      <c r="F9" s="99" t="s">
-        <v>225</v>
-      </c>
-      <c r="G9" s="100"/>
-      <c r="H9" s="100"/>
-      <c r="I9" s="100"/>
-      <c r="J9" s="101"/>
-      <c r="K9" s="95" t="s">
-        <v>398</v>
-      </c>
-      <c r="L9" s="96"/>
-      <c r="M9" s="97"/>
+        <v>388</v>
+      </c>
+      <c r="D9" s="98" t="s">
+        <v>389</v>
+      </c>
+      <c r="E9" s="100"/>
+      <c r="F9" s="95" t="s">
+        <v>218</v>
+      </c>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="97"/>
+      <c r="K9" s="98" t="s">
+        <v>390</v>
+      </c>
+      <c r="L9" s="99"/>
+      <c r="M9" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -4291,7 +4709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor theme="6" tint="-0.249977111117893"/>
@@ -4309,19 +4727,19 @@
         <v>13</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1">
@@ -4329,7 +4747,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>17</v>
@@ -4431,380 +4849,423 @@
     </row>
     <row r="10" spans="2:13" ht="26.25" customHeight="1">
       <c r="B10" s="71" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C10" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="109" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" s="110"/>
+      <c r="F10" s="109" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="102" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" s="103"/>
-      <c r="F10" s="102" t="s">
-        <v>91</v>
-      </c>
-      <c r="G10" s="104"/>
-      <c r="H10" s="104"/>
-      <c r="I10" s="104"/>
-      <c r="J10" s="103"/>
-      <c r="K10" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="L10" s="104"/>
-      <c r="M10" s="103"/>
+      <c r="G10" s="111"/>
+      <c r="H10" s="111"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="110"/>
+      <c r="K10" s="109" t="s">
+        <v>103</v>
+      </c>
+      <c r="L10" s="111"/>
+      <c r="M10" s="110"/>
     </row>
     <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="109" t="s">
-        <v>429</v>
+      <c r="B11" s="104" t="s">
+        <v>421</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" s="95" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="98" t="s">
+        <v>392</v>
+      </c>
+      <c r="E11" s="100"/>
+      <c r="F11" s="95" t="s">
+        <v>394</v>
+      </c>
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="97"/>
+      <c r="K11" s="108"/>
+      <c r="L11" s="108"/>
+      <c r="M11" s="108"/>
+    </row>
+    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B12" s="106"/>
+      <c r="C12" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="98" t="s">
+        <v>393</v>
+      </c>
+      <c r="E12" s="100"/>
+      <c r="F12" s="95" t="s">
+        <v>395</v>
+      </c>
+      <c r="G12" s="96"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="96"/>
+      <c r="J12" s="97"/>
+      <c r="K12" s="108"/>
+      <c r="L12" s="108"/>
+      <c r="M12" s="108"/>
+    </row>
+    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B13" s="107" t="s">
+        <v>422</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="127" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="128"/>
+      <c r="F13" s="95" t="s">
+        <v>396</v>
+      </c>
+      <c r="G13" s="96"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="97"/>
+      <c r="K13" s="108"/>
+      <c r="L13" s="108"/>
+      <c r="M13" s="108"/>
+    </row>
+    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B14" s="107"/>
+      <c r="C14" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="127" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="128"/>
+      <c r="F14" s="95" t="s">
+        <v>397</v>
+      </c>
+      <c r="G14" s="96"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="97"/>
+      <c r="K14" s="108"/>
+      <c r="L14" s="108"/>
+      <c r="M14" s="108"/>
+    </row>
+    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B15" s="107"/>
+      <c r="C15" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="127" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="128"/>
+      <c r="F15" s="95" t="s">
+        <v>398</v>
+      </c>
+      <c r="G15" s="96"/>
+      <c r="H15" s="96"/>
+      <c r="I15" s="96"/>
+      <c r="J15" s="97"/>
+      <c r="K15" s="108"/>
+      <c r="L15" s="108"/>
+      <c r="M15" s="108"/>
+    </row>
+    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B16" s="107"/>
+      <c r="C16" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="127" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="128"/>
+      <c r="F16" s="95" t="s">
+        <v>399</v>
+      </c>
+      <c r="G16" s="96"/>
+      <c r="H16" s="96"/>
+      <c r="I16" s="96"/>
+      <c r="J16" s="97"/>
+      <c r="K16" s="98"/>
+      <c r="L16" s="99"/>
+      <c r="M16" s="100"/>
+    </row>
+    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B17" s="107" t="s">
+        <v>423</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="122" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="123"/>
+      <c r="F17" s="95" t="s">
         <v>400</v>
       </c>
-      <c r="E11" s="97"/>
-      <c r="F11" s="99" t="s">
+      <c r="G17" s="96"/>
+      <c r="H17" s="96"/>
+      <c r="I17" s="96"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="108"/>
+      <c r="L17" s="108"/>
+      <c r="M17" s="108"/>
+    </row>
+    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B18" s="107"/>
+      <c r="C18" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="129" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="130"/>
+      <c r="F18" s="95" t="s">
+        <v>401</v>
+      </c>
+      <c r="G18" s="96"/>
+      <c r="H18" s="96"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="108"/>
+      <c r="L18" s="108"/>
+      <c r="M18" s="108"/>
+    </row>
+    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B19" s="107"/>
+      <c r="C19" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="129" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="130"/>
+      <c r="F19" s="95" t="s">
         <v>402</v>
       </c>
-      <c r="G11" s="100"/>
-      <c r="H11" s="100"/>
-      <c r="I11" s="100"/>
-      <c r="J11" s="101"/>
-      <c r="K11" s="98"/>
-      <c r="L11" s="98"/>
-      <c r="M11" s="98"/>
-    </row>
-    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="111"/>
-      <c r="C12" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" s="95" t="s">
-        <v>401</v>
-      </c>
-      <c r="E12" s="97"/>
-      <c r="F12" s="99" t="s">
+      <c r="G19" s="96"/>
+      <c r="H19" s="96"/>
+      <c r="I19" s="96"/>
+      <c r="J19" s="96"/>
+      <c r="K19" s="108"/>
+      <c r="L19" s="108"/>
+      <c r="M19" s="108"/>
+    </row>
+    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B20" s="104" t="s">
         <v>403</v>
       </c>
-      <c r="G12" s="100"/>
-      <c r="H12" s="100"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="101"/>
-      <c r="K12" s="98"/>
-      <c r="L12" s="98"/>
-      <c r="M12" s="98"/>
-    </row>
-    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="112" t="s">
-        <v>430</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" s="122" t="s">
+      <c r="C20" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="129" t="s">
+        <v>404</v>
+      </c>
+      <c r="E20" s="130"/>
+      <c r="F20" s="112" t="s">
+        <v>413</v>
+      </c>
+      <c r="G20" s="112"/>
+      <c r="H20" s="112"/>
+      <c r="I20" s="112"/>
+      <c r="J20" s="112"/>
+      <c r="K20" s="108"/>
+      <c r="L20" s="108"/>
+      <c r="M20" s="108"/>
+    </row>
+    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B21" s="105"/>
+      <c r="C21" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="123"/>
-      <c r="F13" s="99" t="s">
-        <v>404</v>
-      </c>
-      <c r="G13" s="100"/>
-      <c r="H13" s="100"/>
-      <c r="I13" s="100"/>
-      <c r="J13" s="101"/>
-      <c r="K13" s="98"/>
-      <c r="L13" s="98"/>
-      <c r="M13" s="98"/>
-    </row>
-    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B14" s="112"/>
-      <c r="C14" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" s="122" t="s">
+      <c r="D21" s="127" t="s">
+        <v>405</v>
+      </c>
+      <c r="E21" s="128"/>
+      <c r="F21" s="112" t="s">
+        <v>414</v>
+      </c>
+      <c r="G21" s="112"/>
+      <c r="H21" s="112"/>
+      <c r="I21" s="112"/>
+      <c r="J21" s="112"/>
+      <c r="K21" s="108"/>
+      <c r="L21" s="108"/>
+      <c r="M21" s="108"/>
+    </row>
+    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B22" s="105"/>
+      <c r="C22" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" s="122" t="s">
+        <v>406</v>
+      </c>
+      <c r="E22" s="123"/>
+      <c r="F22" s="112" t="s">
+        <v>415</v>
+      </c>
+      <c r="G22" s="112"/>
+      <c r="H22" s="112"/>
+      <c r="I22" s="112"/>
+      <c r="J22" s="112"/>
+      <c r="K22" s="108"/>
+      <c r="L22" s="108"/>
+      <c r="M22" s="108"/>
+    </row>
+    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B23" s="106"/>
+      <c r="C23" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="123"/>
-      <c r="F14" s="99" t="s">
-        <v>405</v>
-      </c>
-      <c r="G14" s="100"/>
-      <c r="H14" s="100"/>
-      <c r="I14" s="100"/>
-      <c r="J14" s="101"/>
-      <c r="K14" s="98"/>
-      <c r="L14" s="98"/>
-      <c r="M14" s="98"/>
-    </row>
-    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B15" s="112"/>
-      <c r="C15" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="D15" s="122" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="123"/>
-      <c r="F15" s="99" t="s">
-        <v>406</v>
-      </c>
-      <c r="G15" s="100"/>
-      <c r="H15" s="100"/>
-      <c r="I15" s="100"/>
-      <c r="J15" s="101"/>
-      <c r="K15" s="98"/>
-      <c r="L15" s="98"/>
-      <c r="M15" s="98"/>
-    </row>
-    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B16" s="112"/>
-      <c r="C16" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" s="122" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" s="123"/>
-      <c r="F16" s="99" t="s">
+      <c r="D23" s="122" t="s">
         <v>407</v>
       </c>
-      <c r="G16" s="100"/>
-      <c r="H16" s="100"/>
-      <c r="I16" s="100"/>
-      <c r="J16" s="101"/>
-      <c r="K16" s="95"/>
-      <c r="L16" s="96"/>
-      <c r="M16" s="97"/>
-    </row>
-    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B17" s="112" t="s">
-        <v>431</v>
-      </c>
-      <c r="C17" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" s="124" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="125"/>
-      <c r="F17" s="99" t="s">
+      <c r="E23" s="123"/>
+      <c r="F23" s="112" t="s">
+        <v>416</v>
+      </c>
+      <c r="G23" s="112"/>
+      <c r="H23" s="112"/>
+      <c r="I23" s="112"/>
+      <c r="J23" s="112"/>
+      <c r="K23" s="108"/>
+      <c r="L23" s="108"/>
+      <c r="M23" s="108"/>
+    </row>
+    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B24" s="124" t="s">
         <v>408</v>
       </c>
-      <c r="G17" s="100"/>
-      <c r="H17" s="100"/>
-      <c r="I17" s="100"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="98"/>
-      <c r="L17" s="98"/>
-      <c r="M17" s="98"/>
-    </row>
-    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B18" s="112"/>
-      <c r="C18" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" s="126" t="s">
+      <c r="C24" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="127"/>
-      <c r="F18" s="99" t="s">
+      <c r="D24" s="98" t="s">
         <v>409</v>
       </c>
-      <c r="G18" s="100"/>
-      <c r="H18" s="100"/>
-      <c r="I18" s="100"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="98"/>
-      <c r="L18" s="98"/>
-      <c r="M18" s="98"/>
-    </row>
-    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B19" s="112"/>
-      <c r="C19" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" s="126" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" s="127"/>
-      <c r="F19" s="99" t="s">
+      <c r="E24" s="100"/>
+      <c r="F24" s="112" t="s">
+        <v>417</v>
+      </c>
+      <c r="G24" s="112"/>
+      <c r="H24" s="112"/>
+      <c r="I24" s="112"/>
+      <c r="J24" s="112"/>
+      <c r="K24" s="108"/>
+      <c r="L24" s="108"/>
+      <c r="M24" s="108"/>
+    </row>
+    <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B25" s="125"/>
+      <c r="C25" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="98" t="s">
         <v>410</v>
       </c>
-      <c r="G19" s="100"/>
-      <c r="H19" s="100"/>
-      <c r="I19" s="100"/>
-      <c r="J19" s="100"/>
-      <c r="K19" s="98"/>
-      <c r="L19" s="98"/>
-      <c r="M19" s="98"/>
-    </row>
-    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B20" s="109" t="s">
+      <c r="E25" s="100"/>
+      <c r="F25" s="112" t="s">
+        <v>418</v>
+      </c>
+      <c r="G25" s="112"/>
+      <c r="H25" s="112"/>
+      <c r="I25" s="112"/>
+      <c r="J25" s="112"/>
+      <c r="K25" s="108"/>
+      <c r="L25" s="108"/>
+      <c r="M25" s="108"/>
+    </row>
+    <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B26" s="125"/>
+      <c r="C26" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" s="98" t="s">
         <v>411</v>
       </c>
-      <c r="C20" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" s="126" t="s">
+      <c r="E26" s="100"/>
+      <c r="F26" s="112" t="s">
+        <v>419</v>
+      </c>
+      <c r="G26" s="112"/>
+      <c r="H26" s="112"/>
+      <c r="I26" s="112"/>
+      <c r="J26" s="112"/>
+      <c r="K26" s="108"/>
+      <c r="L26" s="108"/>
+      <c r="M26" s="108"/>
+    </row>
+    <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B27" s="126"/>
+      <c r="C27" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="98" t="s">
         <v>412</v>
       </c>
-      <c r="E20" s="127"/>
-      <c r="F20" s="105" t="s">
-        <v>421</v>
-      </c>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="105"/>
-      <c r="K20" s="98"/>
-      <c r="L20" s="98"/>
-      <c r="M20" s="98"/>
-    </row>
-    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="110"/>
-      <c r="C21" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" s="122" t="s">
-        <v>413</v>
-      </c>
-      <c r="E21" s="123"/>
-      <c r="F21" s="105" t="s">
-        <v>422</v>
-      </c>
-      <c r="G21" s="105"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="105"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="98"/>
-    </row>
-    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B22" s="110"/>
-      <c r="C22" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="D22" s="124" t="s">
-        <v>414</v>
-      </c>
-      <c r="E22" s="125"/>
-      <c r="F22" s="105" t="s">
-        <v>423</v>
-      </c>
-      <c r="G22" s="105"/>
-      <c r="H22" s="105"/>
-      <c r="I22" s="105"/>
-      <c r="J22" s="105"/>
-      <c r="K22" s="98"/>
-      <c r="L22" s="98"/>
-      <c r="M22" s="98"/>
-    </row>
-    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B23" s="111"/>
-      <c r="C23" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="D23" s="124" t="s">
-        <v>415</v>
-      </c>
-      <c r="E23" s="125"/>
-      <c r="F23" s="105" t="s">
-        <v>424</v>
-      </c>
-      <c r="G23" s="105"/>
-      <c r="H23" s="105"/>
-      <c r="I23" s="105"/>
-      <c r="J23" s="105"/>
-      <c r="K23" s="98"/>
-      <c r="L23" s="98"/>
-      <c r="M23" s="98"/>
-    </row>
-    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B24" s="128" t="s">
-        <v>416</v>
-      </c>
-      <c r="C24" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" s="95" t="s">
-        <v>417</v>
-      </c>
-      <c r="E24" s="97"/>
-      <c r="F24" s="105" t="s">
-        <v>425</v>
-      </c>
-      <c r="G24" s="105"/>
-      <c r="H24" s="105"/>
-      <c r="I24" s="105"/>
-      <c r="J24" s="105"/>
-      <c r="K24" s="98"/>
-      <c r="L24" s="98"/>
-      <c r="M24" s="98"/>
-    </row>
-    <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B25" s="129"/>
-      <c r="C25" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="95" t="s">
-        <v>418</v>
-      </c>
-      <c r="E25" s="97"/>
-      <c r="F25" s="105" t="s">
-        <v>426</v>
-      </c>
-      <c r="G25" s="105"/>
-      <c r="H25" s="105"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="105"/>
-      <c r="K25" s="98"/>
-      <c r="L25" s="98"/>
-      <c r="M25" s="98"/>
-    </row>
-    <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B26" s="129"/>
-      <c r="C26" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" s="95" t="s">
-        <v>419</v>
-      </c>
-      <c r="E26" s="97"/>
-      <c r="F26" s="105" t="s">
-        <v>427</v>
-      </c>
-      <c r="G26" s="105"/>
-      <c r="H26" s="105"/>
-      <c r="I26" s="105"/>
-      <c r="J26" s="105"/>
-      <c r="K26" s="98"/>
-      <c r="L26" s="98"/>
-      <c r="M26" s="98"/>
-    </row>
-    <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B27" s="130"/>
-      <c r="C27" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" s="95" t="s">
+      <c r="E27" s="100"/>
+      <c r="F27" s="112" t="s">
         <v>420</v>
       </c>
-      <c r="E27" s="97"/>
-      <c r="F27" s="105" t="s">
-        <v>428</v>
-      </c>
-      <c r="G27" s="105"/>
-      <c r="H27" s="105"/>
-      <c r="I27" s="105"/>
-      <c r="J27" s="105"/>
-      <c r="K27" s="98"/>
-      <c r="L27" s="98"/>
-      <c r="M27" s="98"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="112"/>
+      <c r="I27" s="112"/>
+      <c r="J27" s="112"/>
+      <c r="K27" s="108"/>
+      <c r="L27" s="108"/>
+      <c r="M27" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="59">
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:J24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="K25:M25"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="F27:J27"/>
     <mergeCell ref="K27:M27"/>
@@ -4821,49 +5282,6 @@
     <mergeCell ref="K14:M14"/>
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="F26:J26"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:J24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:J25"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:J23"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:J13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4871,7 +5289,567 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="7.875" customWidth="1"/>
+    <col min="2" max="2" width="79.75" style="152" customWidth="1"/>
+    <col min="3" max="4" width="9.375" customWidth="1"/>
+    <col min="5" max="5" width="47.125" style="152" customWidth="1"/>
+    <col min="6" max="6" width="19.875" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="151" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1" s="166"/>
+    </row>
+    <row r="2" spans="1:7" ht="14.25" thickBot="1">
+      <c r="A2" s="153" t="s">
+        <v>476</v>
+      </c>
+      <c r="B2" s="167"/>
+      <c r="C2" s="168"/>
+      <c r="D2" s="169"/>
+    </row>
+    <row r="3" spans="1:7" s="159" customFormat="1" ht="19.5" thickBot="1">
+      <c r="A3" s="154" t="s">
+        <v>477</v>
+      </c>
+      <c r="B3" s="155" t="s">
+        <v>478</v>
+      </c>
+      <c r="C3" s="156" t="s">
+        <v>479</v>
+      </c>
+      <c r="D3" s="157" t="s">
+        <v>480</v>
+      </c>
+      <c r="E3" s="158" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="13.5" customHeight="1">
+      <c r="F4" s="160" t="s">
+        <v>482</v>
+      </c>
+      <c r="G4" s="160"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="F5" s="160"/>
+      <c r="G5" s="160"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="F6" s="160"/>
+      <c r="G6" s="160"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="B7"/>
+      <c r="F7" s="161" t="s">
+        <v>483</v>
+      </c>
+      <c r="G7" s="162"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="F8" s="161"/>
+      <c r="G8" s="161"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="F9" s="161"/>
+      <c r="G9" s="161"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="F4:G6"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor theme="9" tint="-0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="13.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18" customHeight="1">
+      <c r="A1" s="163" t="s">
+        <v>484</v>
+      </c>
+      <c r="B1" s="164"/>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
+      <c r="G1" s="164"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="163" t="s">
+        <v>485</v>
+      </c>
+      <c r="B7" s="164"/>
+      <c r="C7" s="164"/>
+      <c r="D7" s="164"/>
+      <c r="E7" s="164"/>
+      <c r="F7" s="164"/>
+      <c r="G7" s="164"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="163" t="s">
+        <v>486</v>
+      </c>
+      <c r="B15" s="164"/>
+      <c r="C15" s="164"/>
+      <c r="D15" s="164"/>
+      <c r="E15" s="164"/>
+      <c r="F15" s="164"/>
+      <c r="G15" s="164"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="163" t="s">
+        <v>487</v>
+      </c>
+      <c r="B22" s="164"/>
+      <c r="C22" s="164"/>
+      <c r="D22" s="164"/>
+      <c r="E22" s="164"/>
+      <c r="F22" s="164"/>
+      <c r="G22" s="164"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="B1:M19"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="1.25" style="1" customWidth="1"/>
+    <col min="2" max="13" width="15.625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" ht="6" customHeight="1" thickBot="1"/>
+    <row r="2" spans="2:13" ht="39.75" customHeight="1" thickBot="1">
+      <c r="B2" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="I2" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" s="79" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="L2" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="165" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" ht="24.95" customHeight="1">
+      <c r="B3" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="F3" s="43">
+        <v>0</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" s="29" t="s">
+        <v>288</v>
+      </c>
+      <c r="L3" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" s="47"/>
+    </row>
+    <row r="4" spans="2:13" ht="24.95" customHeight="1">
+      <c r="B4" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>452</v>
+      </c>
+      <c r="G4" s="30"/>
+      <c r="H4" s="23" t="s">
+        <v>430</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4" s="24"/>
+      <c r="K4" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="L4" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" s="48"/>
+    </row>
+    <row r="5" spans="2:13" ht="24.95" customHeight="1">
+      <c r="B5" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>455</v>
+      </c>
+      <c r="G5" s="30"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+    </row>
+    <row r="6" spans="2:13" ht="24.95" customHeight="1">
+      <c r="B6" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>452</v>
+      </c>
+      <c r="G6" s="30"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+    </row>
+    <row r="7" spans="2:13" ht="24.95" customHeight="1">
+      <c r="B7" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>454</v>
+      </c>
+      <c r="G7" s="30"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+    </row>
+    <row r="8" spans="2:13" ht="24.95" customHeight="1">
+      <c r="B8" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="92" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>456</v>
+      </c>
+      <c r="G8" s="30"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
+    </row>
+    <row r="9" spans="2:13" ht="24.95" customHeight="1">
+      <c r="B9" s="44"/>
+      <c r="C9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="23"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="23" t="s">
+        <v>453</v>
+      </c>
+      <c r="G9" s="30"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+    </row>
+    <row r="10" spans="2:13" ht="24.95" customHeight="1">
+      <c r="B10" s="44"/>
+      <c r="C10" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="23"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
+    </row>
+    <row r="11" spans="2:13" ht="24.95" customHeight="1">
+      <c r="B11" s="45"/>
+      <c r="C11" s="78" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="49"/>
+      <c r="M11" s="49"/>
+    </row>
+    <row r="12" spans="2:13" ht="24.95" customHeight="1">
+      <c r="B12" s="45"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="49"/>
+      <c r="M12" s="49"/>
+    </row>
+    <row r="13" spans="2:13" ht="24.95" customHeight="1">
+      <c r="B13" s="45"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
+    </row>
+    <row r="14" spans="2:13" ht="24.95" customHeight="1">
+      <c r="B14" s="45"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="49"/>
+    </row>
+    <row r="15" spans="2:13" ht="24.95" customHeight="1">
+      <c r="B15" s="45"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
+    </row>
+    <row r="16" spans="2:13" ht="24.95" customHeight="1">
+      <c r="B16" s="45"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="49"/>
+      <c r="M16" s="49"/>
+    </row>
+    <row r="17" spans="2:13" ht="24.95" customHeight="1">
+      <c r="B17" s="45"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="49"/>
+      <c r="M17" s="49"/>
+    </row>
+    <row r="18" spans="2:13" ht="24.95" customHeight="1" thickBot="1">
+      <c r="B18" s="46"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="50"/>
+      <c r="M18" s="50"/>
+    </row>
+    <row r="19" spans="2:13" s="37" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B19" s="34" t="s">
+        <v>435</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>433</v>
+      </c>
+      <c r="D19" s="54" t="s">
+        <v>436</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>432</v>
+      </c>
+      <c r="F19" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>431</v>
+      </c>
+      <c r="H19" s="93" t="s">
+        <v>437</v>
+      </c>
+      <c r="I19" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="J19" s="94"/>
+      <c r="K19" s="67"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="E2" location="并发!A1" display="并发"/>
+    <hyperlink ref="B2" location="基本功能!A1" display="基本功能"/>
+    <hyperlink ref="F2" location="边界!A1" display="边界"/>
+    <hyperlink ref="L2" location="部署!A1" display="部署"/>
+    <hyperlink ref="K2" location="性能!A1" display="性能"/>
+    <hyperlink ref="D2" location="数据构造!A1" display="数据构造"/>
+    <hyperlink ref="C2" location="相关功能!A1" display="相关功能"/>
+    <hyperlink ref="G2" location="约束!A1" display="约束"/>
+    <hyperlink ref="H2" location="一致性!A1" display="一致性"/>
+    <hyperlink ref="I2" location="可靠性!A1" display="可靠性"/>
+    <hyperlink ref="J2" location="均匀性!A1" display="均匀性"/>
+    <hyperlink ref="M2" location="异常!A1" display="异常"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -4886,39 +5864,39 @@
     <row r="1" spans="2:13" ht="9.75" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:13" ht="26.25" thickBot="1">
       <c r="B2" s="6" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="K2" s="16" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B3" s="84" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="C3" s="70" t="s">
         <v>26</v>
@@ -4951,7 +5929,7 @@
     </row>
     <row r="4" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B4" s="86" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>26</v>
@@ -5072,682 +6050,684 @@
     </row>
     <row r="10" spans="2:13" ht="26.25" customHeight="1">
       <c r="B10" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="109" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" s="110"/>
+      <c r="F10" s="109" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="111"/>
+      <c r="H10" s="111"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="110"/>
+      <c r="K10" s="109" t="s">
+        <v>103</v>
+      </c>
+      <c r="L10" s="111"/>
+      <c r="M10" s="110"/>
+    </row>
+    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B11" s="107" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="72" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" s="102" t="s">
+      <c r="C11" s="101" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="98" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="100"/>
+      <c r="F11" s="95" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="103"/>
-      <c r="F10" s="102" t="s">
-        <v>91</v>
-      </c>
-      <c r="G10" s="104"/>
-      <c r="H10" s="104"/>
-      <c r="I10" s="104"/>
-      <c r="J10" s="103"/>
-      <c r="K10" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="L10" s="104"/>
-      <c r="M10" s="103"/>
-    </row>
-    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="112" t="s">
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="97"/>
+      <c r="K11" s="98" t="s">
+        <v>102</v>
+      </c>
+      <c r="L11" s="99"/>
+      <c r="M11" s="100"/>
+    </row>
+    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B12" s="107"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="98" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12" s="100"/>
+      <c r="F12" s="95" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="96"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="96"/>
+      <c r="J12" s="97"/>
+      <c r="K12" s="98"/>
+      <c r="L12" s="99"/>
+      <c r="M12" s="100"/>
+    </row>
+    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B13" s="107"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="98" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" s="100"/>
+      <c r="F13" s="95" t="s">
         <v>90</v>
       </c>
-      <c r="C11" s="106" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" s="95" t="s">
-        <v>85</v>
-      </c>
-      <c r="E11" s="97"/>
-      <c r="F11" s="99" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="100"/>
-      <c r="H11" s="100"/>
-      <c r="I11" s="100"/>
-      <c r="J11" s="101"/>
-      <c r="K11" s="95" t="s">
-        <v>109</v>
-      </c>
-      <c r="L11" s="96"/>
-      <c r="M11" s="97"/>
-    </row>
-    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="112"/>
-      <c r="C12" s="107"/>
-      <c r="D12" s="95" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" s="97"/>
-      <c r="F12" s="99" t="s">
-        <v>96</v>
-      </c>
-      <c r="G12" s="100"/>
-      <c r="H12" s="100"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="101"/>
-      <c r="K12" s="95"/>
-      <c r="L12" s="96"/>
-      <c r="M12" s="97"/>
-    </row>
-    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="112"/>
-      <c r="C13" s="107"/>
-      <c r="D13" s="95" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" s="97"/>
-      <c r="F13" s="99" t="s">
-        <v>97</v>
-      </c>
-      <c r="G13" s="100"/>
-      <c r="H13" s="100"/>
-      <c r="I13" s="100"/>
-      <c r="J13" s="101"/>
+      <c r="G13" s="96"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="97"/>
       <c r="K13" s="63"/>
       <c r="L13" s="64"/>
       <c r="M13" s="65"/>
     </row>
     <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B14" s="112"/>
-      <c r="C14" s="108"/>
-      <c r="D14" s="95" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" s="97"/>
-      <c r="F14" s="99" t="s">
-        <v>98</v>
-      </c>
-      <c r="G14" s="100"/>
-      <c r="H14" s="100"/>
-      <c r="I14" s="100"/>
-      <c r="J14" s="101"/>
+      <c r="B14" s="107"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="98" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="100"/>
+      <c r="F14" s="95" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="96"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="97"/>
       <c r="K14" s="63"/>
       <c r="L14" s="64"/>
       <c r="M14" s="65"/>
     </row>
     <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B15" s="112"/>
-      <c r="C15" s="106" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" s="95" t="s">
-        <v>86</v>
-      </c>
-      <c r="E15" s="97"/>
-      <c r="F15" s="99" t="s">
+      <c r="B15" s="107"/>
+      <c r="C15" s="101" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="98" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="100"/>
+      <c r="F15" s="95" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" s="96"/>
+      <c r="H15" s="96"/>
+      <c r="I15" s="96"/>
+      <c r="J15" s="97"/>
+      <c r="K15" s="98"/>
+      <c r="L15" s="99"/>
+      <c r="M15" s="100"/>
+    </row>
+    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B16" s="107"/>
+      <c r="C16" s="102"/>
+      <c r="D16" s="98" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="100"/>
+      <c r="F16" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" s="96"/>
+      <c r="H16" s="96"/>
+      <c r="I16" s="96"/>
+      <c r="J16" s="97"/>
+      <c r="K16" s="98"/>
+      <c r="L16" s="99"/>
+      <c r="M16" s="100"/>
+    </row>
+    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B17" s="107"/>
+      <c r="C17" s="102"/>
+      <c r="D17" s="98" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" s="100"/>
+      <c r="F17" s="95" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="96"/>
+      <c r="H17" s="96"/>
+      <c r="I17" s="96"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="108"/>
+      <c r="L17" s="108"/>
+      <c r="M17" s="108"/>
+    </row>
+    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B18" s="107"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="98" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" s="100"/>
+      <c r="F18" s="95" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" s="96"/>
+      <c r="H18" s="96"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="108"/>
+      <c r="L18" s="108"/>
+      <c r="M18" s="108"/>
+    </row>
+    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B19" s="107"/>
+      <c r="C19" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="100"/>
-      <c r="H15" s="100"/>
-      <c r="I15" s="100"/>
-      <c r="J15" s="101"/>
-      <c r="K15" s="95"/>
-      <c r="L15" s="96"/>
-      <c r="M15" s="97"/>
-    </row>
-    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B16" s="112"/>
-      <c r="C16" s="107"/>
-      <c r="D16" s="95" t="s">
+      <c r="D19" s="98" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" s="100"/>
+      <c r="F19" s="112" t="s">
         <v>101</v>
       </c>
-      <c r="E16" s="97"/>
-      <c r="F16" s="99" t="s">
+      <c r="G19" s="112"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="112"/>
+      <c r="J19" s="112"/>
+      <c r="K19" s="108"/>
+      <c r="L19" s="108"/>
+      <c r="M19" s="108"/>
+    </row>
+    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B20" s="107"/>
+      <c r="C20" s="66" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="100"/>
+      <c r="F20" s="112" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="112"/>
+      <c r="H20" s="112"/>
+      <c r="I20" s="112"/>
+      <c r="J20" s="112"/>
+      <c r="K20" s="108"/>
+      <c r="L20" s="108"/>
+      <c r="M20" s="108"/>
+    </row>
+    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B21" s="107"/>
+      <c r="C21" s="66" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="98" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="100"/>
+      <c r="F21" s="112" t="s">
+        <v>81</v>
+      </c>
+      <c r="G21" s="112"/>
+      <c r="H21" s="112"/>
+      <c r="I21" s="112"/>
+      <c r="J21" s="112"/>
+      <c r="K21" s="108"/>
+      <c r="L21" s="108"/>
+      <c r="M21" s="108"/>
+    </row>
+    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B22" s="107"/>
+      <c r="C22" s="66" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="98" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="100"/>
+      <c r="F22" s="112" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="112"/>
+      <c r="H22" s="112"/>
+      <c r="I22" s="112"/>
+      <c r="J22" s="112"/>
+      <c r="K22" s="108"/>
+      <c r="L22" s="108"/>
+      <c r="M22" s="108"/>
+    </row>
+    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B23" s="104" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="101" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="98" t="s">
+        <v>115</v>
+      </c>
+      <c r="E23" s="100"/>
+      <c r="F23" s="95" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="96"/>
+      <c r="H23" s="96"/>
+      <c r="I23" s="96"/>
+      <c r="J23" s="97"/>
+      <c r="K23" s="108" t="s">
+        <v>118</v>
+      </c>
+      <c r="L23" s="108"/>
+      <c r="M23" s="108"/>
+    </row>
+    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B24" s="105"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="98" t="s">
+        <v>116</v>
+      </c>
+      <c r="E24" s="100"/>
+      <c r="F24" s="95" t="s">
+        <v>117</v>
+      </c>
+      <c r="G24" s="96"/>
+      <c r="H24" s="96"/>
+      <c r="I24" s="96"/>
+      <c r="J24" s="97"/>
+      <c r="K24" s="98"/>
+      <c r="L24" s="99"/>
+      <c r="M24" s="100"/>
+    </row>
+    <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B25" s="105"/>
+      <c r="C25" s="101" t="s">
         <v>104</v>
       </c>
-      <c r="G16" s="100"/>
-      <c r="H16" s="100"/>
-      <c r="I16" s="100"/>
-      <c r="J16" s="101"/>
-      <c r="K16" s="95"/>
-      <c r="L16" s="96"/>
-      <c r="M16" s="97"/>
-    </row>
-    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B17" s="112"/>
-      <c r="C17" s="107"/>
-      <c r="D17" s="95" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17" s="97"/>
-      <c r="F17" s="99" t="s">
-        <v>105</v>
-      </c>
-      <c r="G17" s="100"/>
-      <c r="H17" s="100"/>
-      <c r="I17" s="100"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="98"/>
-      <c r="L17" s="98"/>
-      <c r="M17" s="98"/>
-    </row>
-    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B18" s="112"/>
-      <c r="C18" s="108"/>
-      <c r="D18" s="95" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" s="97"/>
-      <c r="F18" s="99" t="s">
+      <c r="D25" s="98" t="s">
+        <v>120</v>
+      </c>
+      <c r="E25" s="100"/>
+      <c r="F25" s="95" t="s">
+        <v>111</v>
+      </c>
+      <c r="G25" s="96"/>
+      <c r="H25" s="96"/>
+      <c r="I25" s="96"/>
+      <c r="J25" s="97"/>
+      <c r="K25" s="108"/>
+      <c r="L25" s="108"/>
+      <c r="M25" s="108"/>
+    </row>
+    <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B26" s="105"/>
+      <c r="C26" s="103"/>
+      <c r="D26" s="98" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" s="100"/>
+      <c r="F26" s="95" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26" s="96"/>
+      <c r="H26" s="96"/>
+      <c r="I26" s="96"/>
+      <c r="J26" s="97"/>
+      <c r="K26" s="98"/>
+      <c r="L26" s="99"/>
+      <c r="M26" s="100"/>
+    </row>
+    <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B27" s="105"/>
+      <c r="C27" s="66" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="98" t="s">
         <v>106</v>
       </c>
-      <c r="G18" s="100"/>
-      <c r="H18" s="100"/>
-      <c r="I18" s="100"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="98"/>
-      <c r="L18" s="98"/>
-      <c r="M18" s="98"/>
-    </row>
-    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B19" s="112"/>
-      <c r="C19" s="66" t="s">
+      <c r="E27" s="100"/>
+      <c r="F27" s="95" t="s">
+        <v>109</v>
+      </c>
+      <c r="G27" s="96"/>
+      <c r="H27" s="96"/>
+      <c r="I27" s="96"/>
+      <c r="J27" s="97"/>
+      <c r="K27" s="108"/>
+      <c r="L27" s="108"/>
+      <c r="M27" s="108"/>
+    </row>
+    <row r="28" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B28" s="105"/>
+      <c r="C28" s="101" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" s="98" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" s="100"/>
+      <c r="F28" s="95" t="s">
+        <v>112</v>
+      </c>
+      <c r="G28" s="96"/>
+      <c r="H28" s="96"/>
+      <c r="I28" s="96"/>
+      <c r="J28" s="97"/>
+      <c r="K28" s="108"/>
+      <c r="L28" s="108"/>
+      <c r="M28" s="108"/>
+    </row>
+    <row r="29" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B29" s="105"/>
+      <c r="C29" s="103"/>
+      <c r="D29" s="98" t="s">
+        <v>124</v>
+      </c>
+      <c r="E29" s="100"/>
+      <c r="F29" s="95" t="s">
+        <v>122</v>
+      </c>
+      <c r="G29" s="96"/>
+      <c r="H29" s="96"/>
+      <c r="I29" s="96"/>
+      <c r="J29" s="97"/>
+      <c r="K29" s="108"/>
+      <c r="L29" s="108"/>
+      <c r="M29" s="108"/>
+    </row>
+    <row r="30" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B30" s="105"/>
+      <c r="C30" s="66" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" s="98" t="s">
         <v>107</v>
       </c>
-      <c r="D19" s="95" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" s="97"/>
-      <c r="F19" s="105" t="s">
+      <c r="E30" s="100"/>
+      <c r="F30" s="95" t="s">
+        <v>113</v>
+      </c>
+      <c r="G30" s="96"/>
+      <c r="H30" s="96"/>
+      <c r="I30" s="96"/>
+      <c r="J30" s="97"/>
+      <c r="K30" s="108"/>
+      <c r="L30" s="108"/>
+      <c r="M30" s="108"/>
+    </row>
+    <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B31" s="106"/>
+      <c r="C31" s="66" t="s">
+        <v>82</v>
+      </c>
+      <c r="D31" s="98" t="s">
         <v>108</v>
       </c>
-      <c r="G19" s="105"/>
-      <c r="H19" s="105"/>
-      <c r="I19" s="105"/>
-      <c r="J19" s="105"/>
-      <c r="K19" s="98"/>
-      <c r="L19" s="98"/>
-      <c r="M19" s="98"/>
-    </row>
-    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B20" s="112"/>
-      <c r="C20" s="66" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" s="95" t="s">
-        <v>87</v>
-      </c>
-      <c r="E20" s="97"/>
-      <c r="F20" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="105"/>
-      <c r="K20" s="98"/>
-      <c r="L20" s="98"/>
-      <c r="M20" s="98"/>
-    </row>
-    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="112"/>
-      <c r="C21" s="66" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" s="95" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21" s="97"/>
-      <c r="F21" s="105" t="s">
-        <v>88</v>
-      </c>
-      <c r="G21" s="105"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="105"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="98"/>
-    </row>
-    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B22" s="112"/>
-      <c r="C22" s="66" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22" s="95" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="97"/>
-      <c r="F22" s="105" t="s">
-        <v>89</v>
-      </c>
-      <c r="G22" s="105"/>
-      <c r="H22" s="105"/>
-      <c r="I22" s="105"/>
-      <c r="J22" s="105"/>
-      <c r="K22" s="98"/>
-      <c r="L22" s="98"/>
-      <c r="M22" s="98"/>
-    </row>
-    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B23" s="109" t="s">
-        <v>112</v>
-      </c>
-      <c r="C23" s="106" t="s">
-        <v>85</v>
-      </c>
-      <c r="D23" s="95" t="s">
-        <v>122</v>
-      </c>
-      <c r="E23" s="97"/>
-      <c r="F23" s="99" t="s">
-        <v>117</v>
-      </c>
-      <c r="G23" s="100"/>
-      <c r="H23" s="100"/>
-      <c r="I23" s="100"/>
-      <c r="J23" s="101"/>
-      <c r="K23" s="98" t="s">
+      <c r="E31" s="100"/>
+      <c r="F31" s="95" t="s">
+        <v>114</v>
+      </c>
+      <c r="G31" s="96"/>
+      <c r="H31" s="96"/>
+      <c r="I31" s="96"/>
+      <c r="J31" s="97"/>
+      <c r="K31" s="108"/>
+      <c r="L31" s="108"/>
+      <c r="M31" s="108"/>
+    </row>
+    <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B32" s="104" t="s">
         <v>125</v>
       </c>
-      <c r="L23" s="98"/>
-      <c r="M23" s="98"/>
-    </row>
-    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B24" s="110"/>
-      <c r="C24" s="108"/>
-      <c r="D24" s="95" t="s">
-        <v>123</v>
-      </c>
-      <c r="E24" s="97"/>
-      <c r="F24" s="99" t="s">
-        <v>124</v>
-      </c>
-      <c r="G24" s="100"/>
-      <c r="H24" s="100"/>
-      <c r="I24" s="100"/>
-      <c r="J24" s="101"/>
-      <c r="K24" s="95"/>
-      <c r="L24" s="96"/>
-      <c r="M24" s="97"/>
-    </row>
-    <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B25" s="110"/>
-      <c r="C25" s="106" t="s">
-        <v>111</v>
-      </c>
-      <c r="D25" s="95" t="s">
+      <c r="C32" s="66" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" s="98" t="s">
+        <v>134</v>
+      </c>
+      <c r="E32" s="100"/>
+      <c r="F32" s="95" t="s">
+        <v>147</v>
+      </c>
+      <c r="G32" s="96"/>
+      <c r="H32" s="96"/>
+      <c r="I32" s="96"/>
+      <c r="J32" s="97"/>
+      <c r="K32" s="98" t="s">
+        <v>146</v>
+      </c>
+      <c r="L32" s="99"/>
+      <c r="M32" s="100"/>
+    </row>
+    <row r="33" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B33" s="105"/>
+      <c r="C33" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="E25" s="97"/>
-      <c r="F25" s="99" t="s">
-        <v>118</v>
-      </c>
-      <c r="G25" s="100"/>
-      <c r="H25" s="100"/>
-      <c r="I25" s="100"/>
-      <c r="J25" s="101"/>
-      <c r="K25" s="98"/>
-      <c r="L25" s="98"/>
-      <c r="M25" s="98"/>
-    </row>
-    <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B26" s="110"/>
-      <c r="C26" s="108"/>
-      <c r="D26" s="95" t="s">
-        <v>126</v>
-      </c>
-      <c r="E26" s="97"/>
-      <c r="F26" s="99" t="s">
+      <c r="D33" s="98" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" s="100"/>
+      <c r="F33" s="95" t="s">
+        <v>148</v>
+      </c>
+      <c r="G33" s="96"/>
+      <c r="H33" s="96"/>
+      <c r="I33" s="96"/>
+      <c r="J33" s="97"/>
+      <c r="K33" s="98"/>
+      <c r="L33" s="99"/>
+      <c r="M33" s="100"/>
+    </row>
+    <row r="34" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B34" s="105"/>
+      <c r="C34" s="66" t="s">
         <v>128</v>
       </c>
-      <c r="G26" s="100"/>
-      <c r="H26" s="100"/>
-      <c r="I26" s="100"/>
-      <c r="J26" s="101"/>
-      <c r="K26" s="95"/>
-      <c r="L26" s="96"/>
-      <c r="M26" s="97"/>
-    </row>
-    <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B27" s="110"/>
-      <c r="C27" s="66" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" s="95" t="s">
-        <v>113</v>
-      </c>
-      <c r="E27" s="97"/>
-      <c r="F27" s="99" t="s">
-        <v>116</v>
-      </c>
-      <c r="G27" s="100"/>
-      <c r="H27" s="100"/>
-      <c r="I27" s="100"/>
-      <c r="J27" s="101"/>
-      <c r="K27" s="98"/>
-      <c r="L27" s="98"/>
-      <c r="M27" s="98"/>
-    </row>
-    <row r="28" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B28" s="110"/>
-      <c r="C28" s="106" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" s="95" t="s">
+      <c r="D34" s="98" t="s">
+        <v>136</v>
+      </c>
+      <c r="E34" s="100"/>
+      <c r="F34" s="95" t="s">
+        <v>149</v>
+      </c>
+      <c r="G34" s="96"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="96"/>
+      <c r="J34" s="97"/>
+      <c r="K34" s="98"/>
+      <c r="L34" s="99"/>
+      <c r="M34" s="100"/>
+    </row>
+    <row r="35" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B35" s="105"/>
+      <c r="C35" s="66" t="s">
+        <v>129</v>
+      </c>
+      <c r="D35" s="98" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" s="100"/>
+      <c r="F35" s="95" t="s">
+        <v>150</v>
+      </c>
+      <c r="G35" s="96"/>
+      <c r="H35" s="96"/>
+      <c r="I35" s="96"/>
+      <c r="J35" s="97"/>
+      <c r="K35" s="98"/>
+      <c r="L35" s="99"/>
+      <c r="M35" s="100"/>
+    </row>
+    <row r="36" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B36" s="105"/>
+      <c r="C36" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="D36" s="98" t="s">
+        <v>138</v>
+      </c>
+      <c r="E36" s="100"/>
+      <c r="F36" s="95" t="s">
+        <v>151</v>
+      </c>
+      <c r="G36" s="96"/>
+      <c r="H36" s="96"/>
+      <c r="I36" s="96"/>
+      <c r="J36" s="97"/>
+      <c r="K36" s="98"/>
+      <c r="L36" s="99"/>
+      <c r="M36" s="100"/>
+    </row>
+    <row r="37" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B37" s="105"/>
+      <c r="C37" s="66" t="s">
+        <v>139</v>
+      </c>
+      <c r="D37" s="98" t="s">
+        <v>142</v>
+      </c>
+      <c r="E37" s="100"/>
+      <c r="F37" s="95" t="s">
+        <v>148</v>
+      </c>
+      <c r="G37" s="96"/>
+      <c r="H37" s="96"/>
+      <c r="I37" s="96"/>
+      <c r="J37" s="97"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="99"/>
+      <c r="M37" s="100"/>
+    </row>
+    <row r="38" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B38" s="105"/>
+      <c r="C38" s="66" t="s">
+        <v>140</v>
+      </c>
+      <c r="D38" s="98" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" s="100"/>
+      <c r="F38" s="95" t="s">
+        <v>149</v>
+      </c>
+      <c r="G38" s="96"/>
+      <c r="H38" s="96"/>
+      <c r="I38" s="96"/>
+      <c r="J38" s="97"/>
+      <c r="K38" s="98"/>
+      <c r="L38" s="99"/>
+      <c r="M38" s="100"/>
+    </row>
+    <row r="39" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B39" s="105"/>
+      <c r="C39" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="E28" s="97"/>
-      <c r="F28" s="99" t="s">
-        <v>119</v>
-      </c>
-      <c r="G28" s="100"/>
-      <c r="H28" s="100"/>
-      <c r="I28" s="100"/>
-      <c r="J28" s="101"/>
-      <c r="K28" s="98"/>
-      <c r="L28" s="98"/>
-      <c r="M28" s="98"/>
-    </row>
-    <row r="29" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B29" s="110"/>
-      <c r="C29" s="108"/>
-      <c r="D29" s="95" t="s">
-        <v>131</v>
-      </c>
-      <c r="E29" s="97"/>
-      <c r="F29" s="99" t="s">
-        <v>129</v>
-      </c>
-      <c r="G29" s="100"/>
-      <c r="H29" s="100"/>
-      <c r="I29" s="100"/>
-      <c r="J29" s="101"/>
-      <c r="K29" s="98"/>
-      <c r="L29" s="98"/>
-      <c r="M29" s="98"/>
-    </row>
-    <row r="30" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B30" s="110"/>
-      <c r="C30" s="66" t="s">
-        <v>88</v>
-      </c>
-      <c r="D30" s="95" t="s">
-        <v>114</v>
-      </c>
-      <c r="E30" s="97"/>
-      <c r="F30" s="99" t="s">
-        <v>120</v>
-      </c>
-      <c r="G30" s="100"/>
-      <c r="H30" s="100"/>
-      <c r="I30" s="100"/>
-      <c r="J30" s="101"/>
-      <c r="K30" s="98"/>
-      <c r="L30" s="98"/>
-      <c r="M30" s="98"/>
-    </row>
-    <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B31" s="111"/>
-      <c r="C31" s="66" t="s">
-        <v>89</v>
-      </c>
-      <c r="D31" s="95" t="s">
-        <v>115</v>
-      </c>
-      <c r="E31" s="97"/>
-      <c r="F31" s="99" t="s">
-        <v>121</v>
-      </c>
-      <c r="G31" s="100"/>
-      <c r="H31" s="100"/>
-      <c r="I31" s="100"/>
-      <c r="J31" s="101"/>
-      <c r="K31" s="98"/>
-      <c r="L31" s="98"/>
-      <c r="M31" s="98"/>
-    </row>
-    <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B32" s="109" t="s">
+      <c r="D39" s="98" t="s">
+        <v>144</v>
+      </c>
+      <c r="E39" s="100"/>
+      <c r="F39" s="95" t="s">
+        <v>150</v>
+      </c>
+      <c r="G39" s="96"/>
+      <c r="H39" s="96"/>
+      <c r="I39" s="96"/>
+      <c r="J39" s="97"/>
+      <c r="K39" s="98"/>
+      <c r="L39" s="99"/>
+      <c r="M39" s="100"/>
+    </row>
+    <row r="40" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B40" s="105"/>
+      <c r="C40" s="66" t="s">
+        <v>141</v>
+      </c>
+      <c r="D40" s="98" t="s">
+        <v>145</v>
+      </c>
+      <c r="E40" s="100"/>
+      <c r="F40" s="95" t="s">
+        <v>151</v>
+      </c>
+      <c r="G40" s="96"/>
+      <c r="H40" s="96"/>
+      <c r="I40" s="96"/>
+      <c r="J40" s="97"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="99"/>
+      <c r="M40" s="100"/>
+    </row>
+    <row r="41" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B41" s="106"/>
+      <c r="C41" s="69" t="s">
+        <v>450</v>
+      </c>
+      <c r="D41" s="98" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="E41" s="100"/>
+      <c r="F41" s="95" t="s">
         <v>133</v>
       </c>
-      <c r="D32" s="95" t="s">
-        <v>141</v>
-      </c>
-      <c r="E32" s="97"/>
-      <c r="F32" s="99" t="s">
-        <v>154</v>
-      </c>
-      <c r="G32" s="100"/>
-      <c r="H32" s="100"/>
-      <c r="I32" s="100"/>
-      <c r="J32" s="101"/>
-      <c r="K32" s="95" t="s">
-        <v>153</v>
-      </c>
-      <c r="L32" s="96"/>
-      <c r="M32" s="97"/>
-    </row>
-    <row r="33" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B33" s="110"/>
-      <c r="C33" s="66" t="s">
-        <v>134</v>
-      </c>
-      <c r="D33" s="95" t="s">
-        <v>142</v>
-      </c>
-      <c r="E33" s="97"/>
-      <c r="F33" s="99" t="s">
-        <v>155</v>
-      </c>
-      <c r="G33" s="100"/>
-      <c r="H33" s="100"/>
-      <c r="I33" s="100"/>
-      <c r="J33" s="101"/>
-      <c r="K33" s="95"/>
-      <c r="L33" s="96"/>
-      <c r="M33" s="97"/>
-    </row>
-    <row r="34" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B34" s="110"/>
-      <c r="C34" s="66" t="s">
-        <v>135</v>
-      </c>
-      <c r="D34" s="95" t="s">
-        <v>143</v>
-      </c>
-      <c r="E34" s="97"/>
-      <c r="F34" s="99" t="s">
-        <v>156</v>
-      </c>
-      <c r="G34" s="100"/>
-      <c r="H34" s="100"/>
-      <c r="I34" s="100"/>
-      <c r="J34" s="101"/>
-      <c r="K34" s="95"/>
-      <c r="L34" s="96"/>
-      <c r="M34" s="97"/>
-    </row>
-    <row r="35" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B35" s="110"/>
-      <c r="C35" s="66" t="s">
-        <v>136</v>
-      </c>
-      <c r="D35" s="95" t="s">
-        <v>144</v>
-      </c>
-      <c r="E35" s="97"/>
-      <c r="F35" s="99" t="s">
-        <v>157</v>
-      </c>
-      <c r="G35" s="100"/>
-      <c r="H35" s="100"/>
-      <c r="I35" s="100"/>
-      <c r="J35" s="101"/>
-      <c r="K35" s="95"/>
-      <c r="L35" s="96"/>
-      <c r="M35" s="97"/>
-    </row>
-    <row r="36" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B36" s="110"/>
-      <c r="C36" s="66" t="s">
-        <v>138</v>
-      </c>
-      <c r="D36" s="95" t="s">
-        <v>145</v>
-      </c>
-      <c r="E36" s="97"/>
-      <c r="F36" s="99" t="s">
-        <v>158</v>
-      </c>
-      <c r="G36" s="100"/>
-      <c r="H36" s="100"/>
-      <c r="I36" s="100"/>
-      <c r="J36" s="101"/>
-      <c r="K36" s="95"/>
-      <c r="L36" s="96"/>
-      <c r="M36" s="97"/>
-    </row>
-    <row r="37" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B37" s="110"/>
-      <c r="C37" s="66" t="s">
-        <v>146</v>
-      </c>
-      <c r="D37" s="95" t="s">
-        <v>149</v>
-      </c>
-      <c r="E37" s="97"/>
-      <c r="F37" s="99" t="s">
-        <v>155</v>
-      </c>
-      <c r="G37" s="100"/>
-      <c r="H37" s="100"/>
-      <c r="I37" s="100"/>
-      <c r="J37" s="101"/>
-      <c r="K37" s="95"/>
-      <c r="L37" s="96"/>
-      <c r="M37" s="97"/>
-    </row>
-    <row r="38" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B38" s="110"/>
-      <c r="C38" s="66" t="s">
-        <v>147</v>
-      </c>
-      <c r="D38" s="95" t="s">
-        <v>150</v>
-      </c>
-      <c r="E38" s="97"/>
-      <c r="F38" s="99" t="s">
-        <v>156</v>
-      </c>
-      <c r="G38" s="100"/>
-      <c r="H38" s="100"/>
-      <c r="I38" s="100"/>
-      <c r="J38" s="101"/>
-      <c r="K38" s="95"/>
-      <c r="L38" s="96"/>
-      <c r="M38" s="97"/>
-    </row>
-    <row r="39" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B39" s="110"/>
-      <c r="C39" s="66" t="s">
-        <v>137</v>
-      </c>
-      <c r="D39" s="95" t="s">
-        <v>151</v>
-      </c>
-      <c r="E39" s="97"/>
-      <c r="F39" s="99" t="s">
-        <v>157</v>
-      </c>
-      <c r="G39" s="100"/>
-      <c r="H39" s="100"/>
-      <c r="I39" s="100"/>
-      <c r="J39" s="101"/>
-      <c r="K39" s="95"/>
-      <c r="L39" s="96"/>
-      <c r="M39" s="97"/>
-    </row>
-    <row r="40" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B40" s="110"/>
-      <c r="C40" s="66" t="s">
-        <v>148</v>
-      </c>
-      <c r="D40" s="95" t="s">
-        <v>152</v>
-      </c>
-      <c r="E40" s="97"/>
-      <c r="F40" s="99" t="s">
-        <v>158</v>
-      </c>
-      <c r="G40" s="100"/>
-      <c r="H40" s="100"/>
-      <c r="I40" s="100"/>
-      <c r="J40" s="101"/>
-      <c r="K40" s="95"/>
-      <c r="L40" s="96"/>
-      <c r="M40" s="97"/>
-    </row>
-    <row r="41" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B41" s="111"/>
-      <c r="C41" s="69" t="s">
-        <v>458</v>
-      </c>
-      <c r="D41" s="95" t="s">
-        <v>139</v>
-      </c>
-      <c r="E41" s="97"/>
-      <c r="F41" s="99" t="s">
-        <v>140</v>
-      </c>
-      <c r="G41" s="100"/>
-      <c r="H41" s="100"/>
-      <c r="I41" s="100"/>
-      <c r="J41" s="101"/>
-      <c r="K41" s="95"/>
-      <c r="L41" s="96"/>
-      <c r="M41" s="97"/>
+      <c r="G41" s="96"/>
+      <c r="H41" s="96"/>
+      <c r="I41" s="96"/>
+      <c r="J41" s="97"/>
+      <c r="K41" s="98"/>
+      <c r="L41" s="99"/>
+      <c r="M41" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="102">
-    <mergeCell ref="F32:J32"/>
-    <mergeCell ref="F33:J33"/>
-    <mergeCell ref="F34:J34"/>
-    <mergeCell ref="F35:J35"/>
-    <mergeCell ref="F36:J36"/>
-    <mergeCell ref="F41:J41"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="K33:M33"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="F37:J37"/>
-    <mergeCell ref="F38:J38"/>
-    <mergeCell ref="F39:J39"/>
-    <mergeCell ref="F40:J40"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="B32:B41"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="B23:B31"/>
-    <mergeCell ref="B11:B22"/>
-    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="F28:J28"/>
+    <mergeCell ref="F30:J30"/>
+    <mergeCell ref="F31:J31"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="F22:J22"/>
     <mergeCell ref="K23:M23"/>
     <mergeCell ref="K25:M25"/>
     <mergeCell ref="K27:M27"/>
@@ -5772,46 +6752,44 @@
     <mergeCell ref="F23:J23"/>
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="F27:J27"/>
-    <mergeCell ref="F28:J28"/>
-    <mergeCell ref="F30:J30"/>
-    <mergeCell ref="F31:J31"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="F18:J18"/>
-    <mergeCell ref="F19:J19"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="F20:J20"/>
-    <mergeCell ref="F21:J21"/>
-    <mergeCell ref="F22:J22"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="B32:B41"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="B23:B31"/>
+    <mergeCell ref="B11:B22"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="F32:J32"/>
+    <mergeCell ref="F33:J33"/>
+    <mergeCell ref="F34:J34"/>
+    <mergeCell ref="F35:J35"/>
+    <mergeCell ref="F36:J36"/>
+    <mergeCell ref="F41:J41"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="K33:M33"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="F37:J37"/>
+    <mergeCell ref="F38:J38"/>
+    <mergeCell ref="F39:J39"/>
+    <mergeCell ref="F40:J40"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="K40:M40"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5819,7 +6797,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -5834,10 +6812,10 @@
     <row r="1" spans="2:13" ht="6" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:13" ht="26.25" thickBot="1">
       <c r="B2" s="6" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D2" s="17" t="s">
         <v>6</v>
@@ -5852,7 +6830,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="J2" s="16" t="s">
         <v>7</v>
@@ -5863,7 +6841,7 @@
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B3" s="61" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>26</v>
@@ -5981,354 +6959,364 @@
     </row>
     <row r="10" spans="2:13" ht="26.25" customHeight="1">
       <c r="B10" s="71" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C10" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="109" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" s="110"/>
+      <c r="F10" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="102" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" s="103"/>
-      <c r="F10" s="113" t="s">
-        <v>91</v>
-      </c>
-      <c r="G10" s="113"/>
-      <c r="H10" s="113"/>
-      <c r="I10" s="113"/>
-      <c r="J10" s="113"/>
-      <c r="K10" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="L10" s="104"/>
-      <c r="M10" s="103"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="109" t="s">
+        <v>103</v>
+      </c>
+      <c r="L10" s="111"/>
+      <c r="M10" s="110"/>
     </row>
     <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="109" t="s">
+      <c r="B11" s="104" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" s="98" t="s">
+        <v>158</v>
+      </c>
+      <c r="E11" s="100"/>
+      <c r="F11" s="112" t="s">
+        <v>438</v>
+      </c>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="112"/>
+      <c r="K11" s="108" t="s">
+        <v>160</v>
+      </c>
+      <c r="L11" s="108"/>
+      <c r="M11" s="108"/>
+    </row>
+    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B12" s="106"/>
+      <c r="C12" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" s="98" t="s">
+        <v>159</v>
+      </c>
+      <c r="E12" s="100"/>
+      <c r="F12" s="112" t="s">
+        <v>439</v>
+      </c>
+      <c r="G12" s="112"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="112"/>
+      <c r="J12" s="112"/>
+      <c r="K12" s="98"/>
+      <c r="L12" s="99"/>
+      <c r="M12" s="100"/>
+    </row>
+    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B13" s="107" t="s">
+        <v>161</v>
+      </c>
+      <c r="C13" s="51" t="s">
         <v>162</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="D13" s="98" t="s">
+        <v>164</v>
+      </c>
+      <c r="E13" s="100"/>
+      <c r="F13" s="95" t="s">
+        <v>166</v>
+      </c>
+      <c r="G13" s="96"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="98" t="s">
+        <v>168</v>
+      </c>
+      <c r="L13" s="99"/>
+      <c r="M13" s="100"/>
+    </row>
+    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B14" s="107"/>
+      <c r="C14" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="D11" s="95" t="s">
+      <c r="D14" s="98" t="s">
         <v>165</v>
       </c>
-      <c r="E11" s="97"/>
-      <c r="F11" s="105" t="s">
+      <c r="E14" s="100"/>
+      <c r="F14" s="95" t="s">
+        <v>167</v>
+      </c>
+      <c r="G14" s="96"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="98" t="s">
+        <v>169</v>
+      </c>
+      <c r="L14" s="99"/>
+      <c r="M14" s="100"/>
+    </row>
+    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B15" s="107" t="s">
+        <v>170</v>
+      </c>
+      <c r="C15" s="66" t="s">
+        <v>440</v>
+      </c>
+      <c r="D15" s="98" t="s">
+        <v>441</v>
+      </c>
+      <c r="E15" s="100"/>
+      <c r="F15" s="95" t="s">
+        <v>442</v>
+      </c>
+      <c r="G15" s="96"/>
+      <c r="H15" s="96"/>
+      <c r="I15" s="96"/>
+      <c r="J15" s="96"/>
+      <c r="K15" s="108" t="s">
+        <v>443</v>
+      </c>
+      <c r="L15" s="108"/>
+      <c r="M15" s="108"/>
+    </row>
+    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B16" s="107"/>
+      <c r="C16" s="66" t="s">
+        <v>444</v>
+      </c>
+      <c r="D16" s="98" t="s">
+        <v>445</v>
+      </c>
+      <c r="E16" s="100"/>
+      <c r="F16" s="95" t="s">
         <v>446</v>
       </c>
-      <c r="G11" s="105"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="105"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="98" t="s">
-        <v>167</v>
-      </c>
-      <c r="L11" s="98"/>
-      <c r="M11" s="98"/>
-    </row>
-    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="111"/>
-      <c r="C12" s="51" t="s">
-        <v>164</v>
-      </c>
-      <c r="D12" s="95" t="s">
-        <v>166</v>
-      </c>
-      <c r="E12" s="97"/>
-      <c r="F12" s="105" t="s">
+      <c r="G16" s="96"/>
+      <c r="H16" s="96"/>
+      <c r="I16" s="96"/>
+      <c r="J16" s="96"/>
+      <c r="K16" s="108" t="s">
         <v>447</v>
       </c>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="95"/>
-      <c r="L12" s="96"/>
-      <c r="M12" s="97"/>
-    </row>
-    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="112" t="s">
-        <v>168</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="D13" s="95" t="s">
+      <c r="L16" s="108"/>
+      <c r="M16" s="108"/>
+    </row>
+    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B17" s="107" t="s">
         <v>171</v>
       </c>
-      <c r="E13" s="97"/>
-      <c r="F13" s="99" t="s">
+      <c r="C17" s="66" t="s">
+        <v>172</v>
+      </c>
+      <c r="D17" s="98" t="s">
+        <v>192</v>
+      </c>
+      <c r="E17" s="100"/>
+      <c r="F17" s="95" t="s">
+        <v>196</v>
+      </c>
+      <c r="G17" s="96"/>
+      <c r="H17" s="96"/>
+      <c r="I17" s="96"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="113" t="s">
+        <v>448</v>
+      </c>
+      <c r="L17" s="114"/>
+      <c r="M17" s="115"/>
+    </row>
+    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B18" s="107"/>
+      <c r="C18" s="66" t="s">
         <v>173</v>
       </c>
-      <c r="G13" s="100"/>
-      <c r="H13" s="100"/>
-      <c r="I13" s="100"/>
-      <c r="J13" s="100"/>
-      <c r="K13" s="95" t="s">
+      <c r="D18" s="98" t="s">
+        <v>193</v>
+      </c>
+      <c r="E18" s="100"/>
+      <c r="F18" s="95" t="s">
+        <v>197</v>
+      </c>
+      <c r="G18" s="96"/>
+      <c r="H18" s="96"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="116"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="118"/>
+    </row>
+    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B19" s="104" t="s">
+        <v>174</v>
+      </c>
+      <c r="C19" s="66" t="s">
         <v>175</v>
       </c>
-      <c r="L13" s="96"/>
-      <c r="M13" s="97"/>
-    </row>
-    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B14" s="112"/>
-      <c r="C14" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="D14" s="95" t="s">
-        <v>172</v>
-      </c>
-      <c r="E14" s="97"/>
-      <c r="F14" s="99" t="s">
-        <v>174</v>
-      </c>
-      <c r="G14" s="100"/>
-      <c r="H14" s="100"/>
-      <c r="I14" s="100"/>
-      <c r="J14" s="100"/>
-      <c r="K14" s="95" t="s">
+      <c r="D19" s="98" t="s">
+        <v>194</v>
+      </c>
+      <c r="E19" s="100"/>
+      <c r="F19" s="95" t="s">
+        <v>198</v>
+      </c>
+      <c r="G19" s="96"/>
+      <c r="H19" s="96"/>
+      <c r="I19" s="96"/>
+      <c r="J19" s="96"/>
+      <c r="K19" s="108" t="s">
+        <v>449</v>
+      </c>
+      <c r="L19" s="108"/>
+      <c r="M19" s="108"/>
+    </row>
+    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B20" s="106"/>
+      <c r="C20" s="66" t="s">
         <v>176</v>
       </c>
-      <c r="L14" s="96"/>
-      <c r="M14" s="97"/>
-    </row>
-    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B15" s="112" t="s">
+      <c r="D20" s="98" t="s">
+        <v>195</v>
+      </c>
+      <c r="E20" s="100"/>
+      <c r="F20" s="95" t="s">
+        <v>199</v>
+      </c>
+      <c r="G20" s="96"/>
+      <c r="H20" s="96"/>
+      <c r="I20" s="96"/>
+      <c r="J20" s="96"/>
+      <c r="K20" s="108"/>
+      <c r="L20" s="108"/>
+      <c r="M20" s="108"/>
+    </row>
+    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B21" s="104" t="s">
         <v>177</v>
       </c>
-      <c r="C15" s="66" t="s">
-        <v>448</v>
-      </c>
-      <c r="D15" s="95" t="s">
-        <v>449</v>
-      </c>
-      <c r="E15" s="97"/>
-      <c r="F15" s="99" t="s">
-        <v>450</v>
-      </c>
-      <c r="G15" s="100"/>
-      <c r="H15" s="100"/>
-      <c r="I15" s="100"/>
-      <c r="J15" s="100"/>
-      <c r="K15" s="98" t="s">
-        <v>451</v>
-      </c>
-      <c r="L15" s="98"/>
-      <c r="M15" s="98"/>
-    </row>
-    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B16" s="112"/>
-      <c r="C16" s="66" t="s">
-        <v>452</v>
-      </c>
-      <c r="D16" s="95" t="s">
-        <v>453</v>
-      </c>
-      <c r="E16" s="97"/>
-      <c r="F16" s="99" t="s">
-        <v>454</v>
-      </c>
-      <c r="G16" s="100"/>
-      <c r="H16" s="100"/>
-      <c r="I16" s="100"/>
-      <c r="J16" s="100"/>
-      <c r="K16" s="98" t="s">
-        <v>455</v>
-      </c>
-      <c r="L16" s="98"/>
-      <c r="M16" s="98"/>
-    </row>
-    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B17" s="112" t="s">
-        <v>178</v>
-      </c>
-      <c r="C17" s="66" t="s">
+      <c r="C21" s="66" t="s">
         <v>179</v>
       </c>
-      <c r="D17" s="95" t="s">
-        <v>199</v>
-      </c>
-      <c r="E17" s="97"/>
-      <c r="F17" s="99" t="s">
-        <v>203</v>
-      </c>
-      <c r="G17" s="100"/>
-      <c r="H17" s="100"/>
-      <c r="I17" s="100"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="114" t="s">
-        <v>456</v>
-      </c>
-      <c r="L17" s="115"/>
-      <c r="M17" s="116"/>
-    </row>
-    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B18" s="112"/>
-      <c r="C18" s="66" t="s">
+      <c r="D21" s="98" t="s">
+        <v>181</v>
+      </c>
+      <c r="E21" s="100"/>
+      <c r="F21" s="112" t="s">
+        <v>186</v>
+      </c>
+      <c r="G21" s="112"/>
+      <c r="H21" s="112"/>
+      <c r="I21" s="112"/>
+      <c r="J21" s="112"/>
+      <c r="K21" s="108"/>
+      <c r="L21" s="108"/>
+      <c r="M21" s="108"/>
+    </row>
+    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B22" s="105"/>
+      <c r="C22" s="66" t="s">
         <v>180</v>
       </c>
-      <c r="D18" s="95" t="s">
-        <v>200</v>
-      </c>
-      <c r="E18" s="97"/>
-      <c r="F18" s="99" t="s">
-        <v>204</v>
-      </c>
-      <c r="G18" s="100"/>
-      <c r="H18" s="100"/>
-      <c r="I18" s="100"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="119"/>
-    </row>
-    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B19" s="109" t="s">
-        <v>181</v>
-      </c>
-      <c r="C19" s="66" t="s">
+      <c r="D22" s="98" t="s">
         <v>182</v>
       </c>
-      <c r="D19" s="95" t="s">
-        <v>201</v>
-      </c>
-      <c r="E19" s="97"/>
-      <c r="F19" s="99" t="s">
-        <v>205</v>
-      </c>
-      <c r="G19" s="100"/>
-      <c r="H19" s="100"/>
-      <c r="I19" s="100"/>
-      <c r="J19" s="100"/>
-      <c r="K19" s="98" t="s">
-        <v>457</v>
-      </c>
-      <c r="L19" s="98"/>
-      <c r="M19" s="98"/>
-    </row>
-    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B20" s="111"/>
-      <c r="C20" s="66" t="s">
+      <c r="E22" s="100"/>
+      <c r="F22" s="112" t="s">
+        <v>185</v>
+      </c>
+      <c r="G22" s="112"/>
+      <c r="H22" s="112"/>
+      <c r="I22" s="112"/>
+      <c r="J22" s="112"/>
+      <c r="K22" s="108"/>
+      <c r="L22" s="108"/>
+      <c r="M22" s="108"/>
+    </row>
+    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B23" s="106"/>
+      <c r="C23" s="66" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" s="98" t="s">
         <v>183</v>
       </c>
-      <c r="D20" s="95" t="s">
-        <v>202</v>
-      </c>
-      <c r="E20" s="97"/>
-      <c r="F20" s="99" t="s">
-        <v>206</v>
-      </c>
-      <c r="G20" s="100"/>
-      <c r="H20" s="100"/>
-      <c r="I20" s="100"/>
-      <c r="J20" s="100"/>
-      <c r="K20" s="98"/>
-      <c r="L20" s="98"/>
-      <c r="M20" s="98"/>
-    </row>
-    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="109" t="s">
-        <v>184</v>
-      </c>
-      <c r="C21" s="66" t="s">
-        <v>186</v>
-      </c>
-      <c r="D21" s="95" t="s">
+      <c r="E23" s="100"/>
+      <c r="F23" s="112" t="s">
+        <v>187</v>
+      </c>
+      <c r="G23" s="112"/>
+      <c r="H23" s="112"/>
+      <c r="I23" s="112"/>
+      <c r="J23" s="112"/>
+      <c r="K23" s="108" t="s">
         <v>188</v>
       </c>
-      <c r="E21" s="97"/>
-      <c r="F21" s="105" t="s">
-        <v>193</v>
-      </c>
-      <c r="G21" s="105"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="105"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="98"/>
-    </row>
-    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B22" s="110"/>
-      <c r="C22" s="66" t="s">
-        <v>187</v>
-      </c>
-      <c r="D22" s="95" t="s">
-        <v>189</v>
-      </c>
-      <c r="E22" s="97"/>
-      <c r="F22" s="105" t="s">
-        <v>192</v>
-      </c>
-      <c r="G22" s="105"/>
-      <c r="H22" s="105"/>
-      <c r="I22" s="105"/>
-      <c r="J22" s="105"/>
-      <c r="K22" s="98"/>
-      <c r="L22" s="98"/>
-      <c r="M22" s="98"/>
-    </row>
-    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B23" s="111"/>
-      <c r="C23" s="66" t="s">
-        <v>191</v>
-      </c>
-      <c r="D23" s="95" t="s">
-        <v>190</v>
-      </c>
-      <c r="E23" s="97"/>
-      <c r="F23" s="105" t="s">
-        <v>194</v>
-      </c>
-      <c r="G23" s="105"/>
-      <c r="H23" s="105"/>
-      <c r="I23" s="105"/>
-      <c r="J23" s="105"/>
-      <c r="K23" s="98" t="s">
-        <v>195</v>
-      </c>
-      <c r="L23" s="98"/>
-      <c r="M23" s="98"/>
+      <c r="L23" s="108"/>
+      <c r="M23" s="108"/>
     </row>
     <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B24" s="76" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C24" s="66" t="s">
-        <v>196</v>
-      </c>
-      <c r="D24" s="95" t="s">
-        <v>196</v>
-      </c>
-      <c r="E24" s="97"/>
-      <c r="F24" s="105" t="s">
-        <v>197</v>
-      </c>
-      <c r="G24" s="105"/>
-      <c r="H24" s="105"/>
-      <c r="I24" s="105"/>
-      <c r="J24" s="105"/>
-      <c r="K24" s="98" t="s">
-        <v>198</v>
-      </c>
-      <c r="L24" s="98"/>
-      <c r="M24" s="98"/>
+        <v>189</v>
+      </c>
+      <c r="D24" s="98" t="s">
+        <v>189</v>
+      </c>
+      <c r="E24" s="100"/>
+      <c r="F24" s="112" t="s">
+        <v>190</v>
+      </c>
+      <c r="G24" s="112"/>
+      <c r="H24" s="112"/>
+      <c r="I24" s="112"/>
+      <c r="J24" s="112"/>
+      <c r="K24" s="108" t="s">
+        <v>191</v>
+      </c>
+      <c r="L24" s="108"/>
+      <c r="M24" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="K17:M18"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:J21"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:J23"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:J19"/>
-    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:J17"/>
     <mergeCell ref="K24:M24"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="B13:B14"/>
@@ -6345,28 +7333,18 @@
     <mergeCell ref="F24:J24"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:J18"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="K17:M18"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="K19:M19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6374,7 +7352,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor theme="6" tint="-0.249977111117893"/>
@@ -6392,27 +7370,27 @@
         <v>13</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B3" s="19" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>17</v>
@@ -6435,186 +7413,174 @@
     </row>
     <row r="5" spans="2:13" ht="26.25" customHeight="1">
       <c r="B5" s="71" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C5" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="109" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="110"/>
+      <c r="F5" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="102" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="103"/>
-      <c r="F5" s="113" t="s">
-        <v>91</v>
-      </c>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="L5" s="104"/>
-      <c r="M5" s="103"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="119"/>
+      <c r="K5" s="109" t="s">
+        <v>103</v>
+      </c>
+      <c r="L5" s="111"/>
+      <c r="M5" s="110"/>
     </row>
     <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B6" s="75" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C6" s="51" t="s">
+        <v>255</v>
+      </c>
+      <c r="D6" s="98" t="s">
+        <v>256</v>
+      </c>
+      <c r="E6" s="100"/>
+      <c r="F6" s="112" t="s">
         <v>262</v>
       </c>
-      <c r="D6" s="95" t="s">
-        <v>263</v>
-      </c>
-      <c r="E6" s="97"/>
-      <c r="F6" s="105" t="s">
-        <v>269</v>
-      </c>
-      <c r="G6" s="105"/>
-      <c r="H6" s="105"/>
-      <c r="I6" s="105"/>
-      <c r="J6" s="105"/>
-      <c r="K6" s="98" t="s">
-        <v>275</v>
-      </c>
-      <c r="L6" s="98"/>
-      <c r="M6" s="98"/>
+      <c r="G6" s="112"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="112"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="108" t="s">
+        <v>268</v>
+      </c>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108"/>
     </row>
     <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B7" s="73" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="D7" s="95" t="s">
-        <v>264</v>
-      </c>
-      <c r="E7" s="97"/>
-      <c r="F7" s="105" t="s">
-        <v>270</v>
-      </c>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="105"/>
-      <c r="K7" s="98" t="s">
-        <v>276</v>
-      </c>
-      <c r="L7" s="98"/>
-      <c r="M7" s="98"/>
+        <v>255</v>
+      </c>
+      <c r="D7" s="98" t="s">
+        <v>257</v>
+      </c>
+      <c r="E7" s="100"/>
+      <c r="F7" s="112" t="s">
+        <v>263</v>
+      </c>
+      <c r="G7" s="112"/>
+      <c r="H7" s="112"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="108" t="s">
+        <v>269</v>
+      </c>
+      <c r="L7" s="108"/>
+      <c r="M7" s="108"/>
     </row>
     <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B8" s="73" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="D8" s="95" t="s">
-        <v>265</v>
-      </c>
-      <c r="E8" s="97"/>
-      <c r="F8" s="105" t="s">
-        <v>271</v>
-      </c>
-      <c r="G8" s="105"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="105"/>
-      <c r="K8" s="98" t="s">
-        <v>277</v>
-      </c>
-      <c r="L8" s="98"/>
-      <c r="M8" s="98"/>
+        <v>255</v>
+      </c>
+      <c r="D8" s="98" t="s">
+        <v>258</v>
+      </c>
+      <c r="E8" s="100"/>
+      <c r="F8" s="112" t="s">
+        <v>264</v>
+      </c>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="112"/>
+      <c r="K8" s="108" t="s">
+        <v>270</v>
+      </c>
+      <c r="L8" s="108"/>
+      <c r="M8" s="108"/>
     </row>
     <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B9" s="73" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="D9" s="95" t="s">
-        <v>266</v>
-      </c>
-      <c r="E9" s="97"/>
-      <c r="F9" s="105" t="s">
-        <v>272</v>
-      </c>
-      <c r="G9" s="105"/>
-      <c r="H9" s="105"/>
-      <c r="I9" s="105"/>
-      <c r="J9" s="105"/>
-      <c r="K9" s="98" t="s">
-        <v>278</v>
-      </c>
-      <c r="L9" s="98"/>
-      <c r="M9" s="98"/>
+        <v>255</v>
+      </c>
+      <c r="D9" s="98" t="s">
+        <v>259</v>
+      </c>
+      <c r="E9" s="100"/>
+      <c r="F9" s="112" t="s">
+        <v>265</v>
+      </c>
+      <c r="G9" s="112"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="112"/>
+      <c r="K9" s="108" t="s">
+        <v>271</v>
+      </c>
+      <c r="L9" s="108"/>
+      <c r="M9" s="108"/>
     </row>
     <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B10" s="73" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="D10" s="95" t="s">
-        <v>267</v>
-      </c>
-      <c r="E10" s="97"/>
-      <c r="F10" s="105" t="s">
-        <v>273</v>
-      </c>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="105"/>
-      <c r="K10" s="98" t="s">
-        <v>279</v>
-      </c>
-      <c r="L10" s="98"/>
-      <c r="M10" s="98"/>
+        <v>255</v>
+      </c>
+      <c r="D10" s="98" t="s">
+        <v>260</v>
+      </c>
+      <c r="E10" s="100"/>
+      <c r="F10" s="112" t="s">
+        <v>266</v>
+      </c>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="112"/>
+      <c r="K10" s="108" t="s">
+        <v>272</v>
+      </c>
+      <c r="L10" s="108"/>
+      <c r="M10" s="108"/>
     </row>
     <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B11" s="73" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="D11" s="95" t="s">
-        <v>268</v>
-      </c>
-      <c r="E11" s="97"/>
-      <c r="F11" s="105" t="s">
-        <v>274</v>
-      </c>
-      <c r="G11" s="105"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="105"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="98" t="s">
-        <v>280</v>
-      </c>
-      <c r="L11" s="98"/>
-      <c r="M11" s="98"/>
+        <v>255</v>
+      </c>
+      <c r="D11" s="98" t="s">
+        <v>261</v>
+      </c>
+      <c r="E11" s="100"/>
+      <c r="F11" s="112" t="s">
+        <v>267</v>
+      </c>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="112"/>
+      <c r="K11" s="108" t="s">
+        <v>273</v>
+      </c>
+      <c r="L11" s="108"/>
+      <c r="M11" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:J8"/>
-    <mergeCell ref="K8:M8"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="F7:J7"/>
     <mergeCell ref="K7:M7"/>
@@ -6624,13 +7590,25 @@
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:J6"/>
     <mergeCell ref="K6:M6"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="K10:M10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
@@ -6645,36 +7623,36 @@
     <row r="1" spans="2:13" ht="6" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:13" ht="25.5">
       <c r="B2" s="88" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C2" s="89" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D2" s="89" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E2" s="89" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F2" s="89" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G2" s="89" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="H2" s="89" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="I2" s="89" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="J2" s="90" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B3" s="13" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
@@ -6701,397 +7679,409 @@
     </row>
     <row r="5" spans="2:13" ht="26.25" customHeight="1">
       <c r="B5" s="71" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C5" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="109" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="110"/>
+      <c r="F5" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="102" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="103"/>
-      <c r="F5" s="113" t="s">
-        <v>91</v>
-      </c>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="L5" s="104"/>
-      <c r="M5" s="103"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="119"/>
+      <c r="K5" s="109" t="s">
+        <v>103</v>
+      </c>
+      <c r="L5" s="111"/>
+      <c r="M5" s="110"/>
     </row>
     <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B6" s="112" t="s">
+      <c r="B6" s="107" t="s">
+        <v>221</v>
+      </c>
+      <c r="C6" s="74" t="s">
+        <v>222</v>
+      </c>
+      <c r="D6" s="98" t="s">
+        <v>225</v>
+      </c>
+      <c r="E6" s="100"/>
+      <c r="F6" s="112" t="s">
+        <v>226</v>
+      </c>
+      <c r="G6" s="112"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="112"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="108" t="s">
         <v>228</v>
       </c>
-      <c r="C6" s="74" t="s">
+      <c r="L6" s="108"/>
+      <c r="M6" s="108"/>
+    </row>
+    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B7" s="107"/>
+      <c r="C7" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="D7" s="98" t="s">
+        <v>224</v>
+      </c>
+      <c r="E7" s="100"/>
+      <c r="F7" s="95" t="s">
+        <v>227</v>
+      </c>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="98"/>
+      <c r="L7" s="99"/>
+      <c r="M7" s="100"/>
+    </row>
+    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B8" s="107" t="s">
         <v>229</v>
       </c>
-      <c r="D6" s="95" t="s">
+      <c r="C8" s="51" t="s">
+        <v>222</v>
+      </c>
+      <c r="D8" s="98" t="s">
+        <v>230</v>
+      </c>
+      <c r="E8" s="100"/>
+      <c r="F8" s="112" t="s">
         <v>232</v>
       </c>
-      <c r="E6" s="97"/>
-      <c r="F6" s="105" t="s">
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="112"/>
+      <c r="K8" s="98" t="s">
+        <v>234</v>
+      </c>
+      <c r="L8" s="99"/>
+      <c r="M8" s="100"/>
+    </row>
+    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B9" s="107"/>
+      <c r="C9" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="D9" s="98" t="s">
+        <v>231</v>
+      </c>
+      <c r="E9" s="100"/>
+      <c r="F9" s="95" t="s">
         <v>233</v>
       </c>
-      <c r="G6" s="105"/>
-      <c r="H6" s="105"/>
-      <c r="I6" s="105"/>
-      <c r="J6" s="105"/>
-      <c r="K6" s="98" t="s">
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="96"/>
+      <c r="K9" s="98"/>
+      <c r="L9" s="99"/>
+      <c r="M9" s="100"/>
+    </row>
+    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B10" s="107" t="s">
         <v>235</v>
       </c>
-      <c r="L6" s="98"/>
-      <c r="M6" s="98"/>
-    </row>
-    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="112"/>
-      <c r="C7" s="51" t="s">
-        <v>230</v>
-      </c>
-      <c r="D7" s="95" t="s">
-        <v>231</v>
-      </c>
-      <c r="E7" s="97"/>
-      <c r="F7" s="99" t="s">
-        <v>234</v>
-      </c>
-      <c r="G7" s="100"/>
-      <c r="H7" s="100"/>
-      <c r="I7" s="100"/>
-      <c r="J7" s="100"/>
-      <c r="K7" s="95"/>
-      <c r="L7" s="96"/>
-      <c r="M7" s="97"/>
-    </row>
-    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="112" t="s">
+      <c r="C10" s="51" t="s">
+        <v>222</v>
+      </c>
+      <c r="D10" s="98" t="s">
         <v>236</v>
       </c>
-      <c r="C8" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="D8" s="95" t="s">
+      <c r="E10" s="100"/>
+      <c r="F10" s="112" t="s">
+        <v>238</v>
+      </c>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="112"/>
+      <c r="K10" s="98" t="s">
+        <v>240</v>
+      </c>
+      <c r="L10" s="99"/>
+      <c r="M10" s="100"/>
+    </row>
+    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B11" s="107"/>
+      <c r="C11" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="D11" s="98" t="s">
         <v>237</v>
       </c>
-      <c r="E8" s="97"/>
-      <c r="F8" s="105" t="s">
+      <c r="E11" s="100"/>
+      <c r="F11" s="95" t="s">
         <v>239</v>
       </c>
-      <c r="G8" s="105"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="105"/>
-      <c r="K8" s="95" t="s">
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="96"/>
+      <c r="K11" s="98"/>
+      <c r="L11" s="99"/>
+      <c r="M11" s="100"/>
+    </row>
+    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B12" s="107" t="s">
         <v>241</v>
       </c>
-      <c r="L8" s="96"/>
-      <c r="M8" s="97"/>
-    </row>
-    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="112"/>
-      <c r="C9" s="51" t="s">
-        <v>230</v>
-      </c>
-      <c r="D9" s="95" t="s">
-        <v>238</v>
-      </c>
-      <c r="E9" s="97"/>
-      <c r="F9" s="99" t="s">
-        <v>240</v>
-      </c>
-      <c r="G9" s="100"/>
-      <c r="H9" s="100"/>
-      <c r="I9" s="100"/>
-      <c r="J9" s="100"/>
-      <c r="K9" s="95"/>
-      <c r="L9" s="96"/>
-      <c r="M9" s="97"/>
-    </row>
-    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B10" s="112" t="s">
+      <c r="C12" s="51" t="s">
+        <v>222</v>
+      </c>
+      <c r="D12" s="98" t="s">
         <v>242</v>
       </c>
-      <c r="C10" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="D10" s="95" t="s">
+      <c r="E12" s="100"/>
+      <c r="F12" s="112" t="s">
+        <v>244</v>
+      </c>
+      <c r="G12" s="112"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="112"/>
+      <c r="J12" s="112"/>
+      <c r="K12" s="98" t="s">
+        <v>246</v>
+      </c>
+      <c r="L12" s="99"/>
+      <c r="M12" s="100"/>
+    </row>
+    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B13" s="107"/>
+      <c r="C13" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="D13" s="98" t="s">
         <v>243</v>
       </c>
-      <c r="E10" s="97"/>
-      <c r="F10" s="105" t="s">
+      <c r="E13" s="100"/>
+      <c r="F13" s="95" t="s">
         <v>245</v>
       </c>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="105"/>
-      <c r="K10" s="95" t="s">
+      <c r="G13" s="96"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="98"/>
+      <c r="L13" s="99"/>
+      <c r="M13" s="100"/>
+    </row>
+    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B14" s="107" t="s">
         <v>247</v>
       </c>
-      <c r="L10" s="96"/>
-      <c r="M10" s="97"/>
-    </row>
-    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="112"/>
-      <c r="C11" s="51" t="s">
-        <v>230</v>
-      </c>
-      <c r="D11" s="95" t="s">
-        <v>244</v>
-      </c>
-      <c r="E11" s="97"/>
-      <c r="F11" s="99" t="s">
-        <v>246</v>
-      </c>
-      <c r="G11" s="100"/>
-      <c r="H11" s="100"/>
-      <c r="I11" s="100"/>
-      <c r="J11" s="100"/>
-      <c r="K11" s="95"/>
-      <c r="L11" s="96"/>
-      <c r="M11" s="97"/>
-    </row>
-    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="112" t="s">
+      <c r="C14" s="51" t="s">
+        <v>222</v>
+      </c>
+      <c r="D14" s="98" t="s">
         <v>248</v>
       </c>
-      <c r="C12" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="D12" s="95" t="s">
+      <c r="E14" s="100"/>
+      <c r="F14" s="112" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="112"/>
+      <c r="H14" s="112"/>
+      <c r="I14" s="112"/>
+      <c r="J14" s="112"/>
+      <c r="K14" s="98" t="s">
+        <v>283</v>
+      </c>
+      <c r="L14" s="99"/>
+      <c r="M14" s="100"/>
+    </row>
+    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B15" s="107"/>
+      <c r="C15" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="D15" s="98" t="s">
         <v>249</v>
       </c>
-      <c r="E12" s="97"/>
-      <c r="F12" s="105" t="s">
-        <v>251</v>
-      </c>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="95" t="s">
-        <v>253</v>
-      </c>
-      <c r="L12" s="96"/>
-      <c r="M12" s="97"/>
-    </row>
-    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="112"/>
-      <c r="C13" s="51" t="s">
-        <v>230</v>
-      </c>
-      <c r="D13" s="95" t="s">
-        <v>250</v>
-      </c>
-      <c r="E13" s="97"/>
-      <c r="F13" s="99" t="s">
-        <v>252</v>
-      </c>
-      <c r="G13" s="100"/>
-      <c r="H13" s="100"/>
-      <c r="I13" s="100"/>
-      <c r="J13" s="100"/>
-      <c r="K13" s="95"/>
-      <c r="L13" s="96"/>
-      <c r="M13" s="97"/>
-    </row>
-    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B14" s="112" t="s">
-        <v>254</v>
-      </c>
-      <c r="C14" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="D14" s="95" t="s">
-        <v>255</v>
-      </c>
-      <c r="E14" s="97"/>
-      <c r="F14" s="105" t="s">
-        <v>108</v>
-      </c>
-      <c r="G14" s="105"/>
-      <c r="H14" s="105"/>
-      <c r="I14" s="105"/>
-      <c r="J14" s="105"/>
-      <c r="K14" s="95" t="s">
-        <v>290</v>
-      </c>
-      <c r="L14" s="96"/>
-      <c r="M14" s="97"/>
-    </row>
-    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B15" s="112"/>
-      <c r="C15" s="51" t="s">
-        <v>230</v>
-      </c>
-      <c r="D15" s="95" t="s">
-        <v>256</v>
-      </c>
-      <c r="E15" s="97"/>
-      <c r="F15" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="105"/>
-      <c r="H15" s="105"/>
-      <c r="I15" s="105"/>
-      <c r="J15" s="105"/>
-      <c r="K15" s="95"/>
-      <c r="L15" s="96"/>
-      <c r="M15" s="97"/>
+      <c r="E15" s="100"/>
+      <c r="F15" s="112" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="112"/>
+      <c r="H15" s="112"/>
+      <c r="I15" s="112"/>
+      <c r="J15" s="112"/>
+      <c r="K15" s="98"/>
+      <c r="L15" s="99"/>
+      <c r="M15" s="100"/>
     </row>
     <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B16" s="109" t="s">
-        <v>287</v>
+      <c r="B16" s="104" t="s">
+        <v>280</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="D16" s="95" t="s">
-        <v>288</v>
-      </c>
-      <c r="E16" s="97"/>
-      <c r="F16" s="105" t="s">
-        <v>288</v>
-      </c>
-      <c r="G16" s="105"/>
-      <c r="H16" s="105"/>
-      <c r="I16" s="105"/>
-      <c r="J16" s="105"/>
-      <c r="K16" s="95" t="s">
-        <v>291</v>
-      </c>
-      <c r="L16" s="96"/>
-      <c r="M16" s="97"/>
+        <v>222</v>
+      </c>
+      <c r="D16" s="98" t="s">
+        <v>281</v>
+      </c>
+      <c r="E16" s="100"/>
+      <c r="F16" s="112" t="s">
+        <v>281</v>
+      </c>
+      <c r="G16" s="112"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="112"/>
+      <c r="J16" s="112"/>
+      <c r="K16" s="98" t="s">
+        <v>284</v>
+      </c>
+      <c r="L16" s="99"/>
+      <c r="M16" s="100"/>
     </row>
     <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B17" s="111"/>
+      <c r="B17" s="106"/>
       <c r="C17" s="51" t="s">
-        <v>230</v>
-      </c>
-      <c r="D17" s="95" t="s">
-        <v>289</v>
-      </c>
-      <c r="E17" s="97"/>
-      <c r="F17" s="105" t="s">
-        <v>289</v>
-      </c>
-      <c r="G17" s="105"/>
-      <c r="H17" s="105"/>
-      <c r="I17" s="105"/>
-      <c r="J17" s="105"/>
-      <c r="K17" s="95"/>
-      <c r="L17" s="96"/>
-      <c r="M17" s="97"/>
+        <v>223</v>
+      </c>
+      <c r="D17" s="98" t="s">
+        <v>282</v>
+      </c>
+      <c r="E17" s="100"/>
+      <c r="F17" s="112" t="s">
+        <v>282</v>
+      </c>
+      <c r="G17" s="112"/>
+      <c r="H17" s="112"/>
+      <c r="I17" s="112"/>
+      <c r="J17" s="112"/>
+      <c r="K17" s="98"/>
+      <c r="L17" s="99"/>
+      <c r="M17" s="100"/>
     </row>
     <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B18" s="120" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>383</v>
-      </c>
-      <c r="D18" s="95" t="s">
-        <v>385</v>
-      </c>
-      <c r="E18" s="97"/>
-      <c r="F18" s="99" t="s">
-        <v>387</v>
-      </c>
-      <c r="G18" s="100"/>
-      <c r="H18" s="100"/>
-      <c r="I18" s="100"/>
-      <c r="J18" s="101"/>
-      <c r="K18" s="95" t="s">
-        <v>389</v>
-      </c>
-      <c r="L18" s="96"/>
-      <c r="M18" s="97"/>
+        <v>375</v>
+      </c>
+      <c r="D18" s="98" t="s">
+        <v>377</v>
+      </c>
+      <c r="E18" s="100"/>
+      <c r="F18" s="95" t="s">
+        <v>379</v>
+      </c>
+      <c r="G18" s="96"/>
+      <c r="H18" s="96"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="97"/>
+      <c r="K18" s="98" t="s">
+        <v>381</v>
+      </c>
+      <c r="L18" s="99"/>
+      <c r="M18" s="100"/>
     </row>
     <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B19" s="121"/>
       <c r="C19" s="51" t="s">
-        <v>384</v>
-      </c>
-      <c r="D19" s="95" t="s">
-        <v>386</v>
-      </c>
-      <c r="E19" s="97"/>
-      <c r="F19" s="99" t="s">
-        <v>388</v>
-      </c>
-      <c r="G19" s="100"/>
-      <c r="H19" s="100"/>
-      <c r="I19" s="100"/>
-      <c r="J19" s="101"/>
+        <v>376</v>
+      </c>
+      <c r="D19" s="98" t="s">
+        <v>378</v>
+      </c>
+      <c r="E19" s="100"/>
+      <c r="F19" s="95" t="s">
+        <v>380</v>
+      </c>
+      <c r="G19" s="96"/>
+      <c r="H19" s="96"/>
+      <c r="I19" s="96"/>
+      <c r="J19" s="97"/>
       <c r="K19" s="63"/>
       <c r="L19" s="64"/>
       <c r="M19" s="65"/>
     </row>
     <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B20" s="120" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="D20" s="95" t="s">
-        <v>255</v>
-      </c>
-      <c r="E20" s="97"/>
-      <c r="F20" s="105" t="s">
-        <v>108</v>
-      </c>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="105"/>
-      <c r="K20" s="95" t="s">
-        <v>292</v>
-      </c>
-      <c r="L20" s="96"/>
-      <c r="M20" s="97"/>
+        <v>222</v>
+      </c>
+      <c r="D20" s="98" t="s">
+        <v>248</v>
+      </c>
+      <c r="E20" s="100"/>
+      <c r="F20" s="112" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" s="112"/>
+      <c r="H20" s="112"/>
+      <c r="I20" s="112"/>
+      <c r="J20" s="112"/>
+      <c r="K20" s="98" t="s">
+        <v>285</v>
+      </c>
+      <c r="L20" s="99"/>
+      <c r="M20" s="100"/>
     </row>
     <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B21" s="121"/>
       <c r="C21" s="51" t="s">
-        <v>230</v>
-      </c>
-      <c r="D21" s="95" t="s">
-        <v>256</v>
-      </c>
-      <c r="E21" s="97"/>
-      <c r="F21" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="105"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="105"/>
-      <c r="K21" s="95"/>
-      <c r="L21" s="96"/>
-      <c r="M21" s="97"/>
+        <v>223</v>
+      </c>
+      <c r="D21" s="98" t="s">
+        <v>249</v>
+      </c>
+      <c r="E21" s="100"/>
+      <c r="F21" s="112" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" s="112"/>
+      <c r="H21" s="112"/>
+      <c r="I21" s="112"/>
+      <c r="J21" s="112"/>
+      <c r="K21" s="98"/>
+      <c r="L21" s="99"/>
+      <c r="M21" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:J18"/>
-    <mergeCell ref="F19:J19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="K18:M18"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="K8:M8"/>
@@ -7108,40 +8098,28 @@
     <mergeCell ref="K7:M7"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="F8:J8"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:J20"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF002060"/>
@@ -7162,30 +8140,30 @@
         <v>0</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E2" s="14" t="s">
         <v>41</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B3" s="82" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>17</v>
@@ -7225,178 +8203,193 @@
     </row>
     <row r="5" spans="2:13" ht="26.25" customHeight="1">
       <c r="B5" s="71" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C5" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="109" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="110"/>
+      <c r="F5" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="102" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="103"/>
-      <c r="F5" s="113" t="s">
-        <v>91</v>
-      </c>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="L5" s="104"/>
-      <c r="M5" s="103"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="119"/>
+      <c r="K5" s="109" t="s">
+        <v>103</v>
+      </c>
+      <c r="L5" s="111"/>
+      <c r="M5" s="110"/>
     </row>
     <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B6" s="73">
         <v>0</v>
       </c>
       <c r="C6" s="74" t="s">
+        <v>292</v>
+      </c>
+      <c r="D6" s="98" t="s">
+        <v>293</v>
+      </c>
+      <c r="E6" s="100"/>
+      <c r="F6" s="112"/>
+      <c r="G6" s="112"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="112"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="108" t="s">
+        <v>294</v>
+      </c>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108"/>
+    </row>
+    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B7" s="107" t="s">
+        <v>295</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>296</v>
+      </c>
+      <c r="D7" s="98" t="s">
         <v>299</v>
       </c>
-      <c r="D6" s="95" t="s">
+      <c r="E7" s="100"/>
+      <c r="F7" s="112" t="s">
         <v>300</v>
       </c>
-      <c r="E6" s="97"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="105"/>
-      <c r="H6" s="105"/>
-      <c r="I6" s="105"/>
-      <c r="J6" s="105"/>
-      <c r="K6" s="98" t="s">
+      <c r="G7" s="112"/>
+      <c r="H7" s="112"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="98" t="s">
+        <v>303</v>
+      </c>
+      <c r="L7" s="99"/>
+      <c r="M7" s="100"/>
+    </row>
+    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B8" s="107"/>
+      <c r="C8" s="51" t="s">
+        <v>297</v>
+      </c>
+      <c r="D8" s="98" t="s">
+        <v>308</v>
+      </c>
+      <c r="E8" s="100"/>
+      <c r="F8" s="112" t="s">
         <v>301</v>
       </c>
-      <c r="L6" s="98"/>
-      <c r="M6" s="98"/>
-    </row>
-    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="112" t="s">
-        <v>302</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>303</v>
-      </c>
-      <c r="D7" s="95" t="s">
-        <v>306</v>
-      </c>
-      <c r="E7" s="97"/>
-      <c r="F7" s="105" t="s">
-        <v>307</v>
-      </c>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="105"/>
-      <c r="K7" s="95" t="s">
-        <v>310</v>
-      </c>
-      <c r="L7" s="96"/>
-      <c r="M7" s="97"/>
-    </row>
-    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="112"/>
-      <c r="C8" s="51" t="s">
-        <v>304</v>
-      </c>
-      <c r="D8" s="95" t="s">
-        <v>315</v>
-      </c>
-      <c r="E8" s="97"/>
-      <c r="F8" s="105" t="s">
-        <v>308</v>
-      </c>
-      <c r="G8" s="105"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="105"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="112"/>
       <c r="K8" s="63"/>
       <c r="L8" s="64"/>
       <c r="M8" s="65"/>
     </row>
     <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="112"/>
+      <c r="B9" s="107"/>
       <c r="C9" s="51" t="s">
-        <v>305</v>
-      </c>
-      <c r="D9" s="95" t="s">
-        <v>316</v>
-      </c>
-      <c r="E9" s="97"/>
-      <c r="F9" s="105" t="s">
+        <v>298</v>
+      </c>
+      <c r="D9" s="98" t="s">
         <v>309</v>
       </c>
-      <c r="G9" s="105"/>
-      <c r="H9" s="105"/>
-      <c r="I9" s="105"/>
-      <c r="J9" s="105"/>
-      <c r="K9" s="95"/>
-      <c r="L9" s="96"/>
-      <c r="M9" s="97"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="112" t="s">
+        <v>302</v>
+      </c>
+      <c r="G9" s="112"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="112"/>
+      <c r="K9" s="98"/>
+      <c r="L9" s="99"/>
+      <c r="M9" s="100"/>
     </row>
     <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B10" s="112" t="s">
-        <v>320</v>
+      <c r="B10" s="120" t="s">
+        <v>451</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>311</v>
-      </c>
-      <c r="D10" s="95" t="s">
-        <v>314</v>
-      </c>
-      <c r="E10" s="97"/>
-      <c r="F10" s="105" t="s">
-        <v>319</v>
-      </c>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="105"/>
-      <c r="K10" s="95"/>
-      <c r="L10" s="96"/>
-      <c r="M10" s="97"/>
+        <v>304</v>
+      </c>
+      <c r="D10" s="98" t="s">
+        <v>307</v>
+      </c>
+      <c r="E10" s="100"/>
+      <c r="F10" s="112" t="s">
+        <v>312</v>
+      </c>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="112"/>
+      <c r="K10" s="98"/>
+      <c r="L10" s="99"/>
+      <c r="M10" s="100"/>
     </row>
     <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="112"/>
+      <c r="B11" s="131"/>
       <c r="C11" s="51" t="s">
-        <v>313</v>
-      </c>
-      <c r="D11" s="95" t="s">
-        <v>317</v>
-      </c>
-      <c r="E11" s="97"/>
-      <c r="F11" s="105" t="s">
-        <v>319</v>
-      </c>
-      <c r="G11" s="105"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="105"/>
-      <c r="J11" s="105"/>
+        <v>306</v>
+      </c>
+      <c r="D11" s="98" t="s">
+        <v>310</v>
+      </c>
+      <c r="E11" s="100"/>
+      <c r="F11" s="112" t="s">
+        <v>312</v>
+      </c>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="112"/>
       <c r="K11" s="63"/>
       <c r="L11" s="64"/>
       <c r="M11" s="65"/>
     </row>
     <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="112"/>
+      <c r="B12" s="121"/>
       <c r="C12" s="51" t="s">
+        <v>305</v>
+      </c>
+      <c r="D12" s="98" t="s">
+        <v>311</v>
+      </c>
+      <c r="E12" s="100"/>
+      <c r="F12" s="112" t="s">
         <v>312</v>
       </c>
-      <c r="D12" s="95" t="s">
-        <v>318</v>
-      </c>
-      <c r="E12" s="97"/>
-      <c r="F12" s="105" t="s">
-        <v>319</v>
-      </c>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="95"/>
-      <c r="L12" s="96"/>
-      <c r="M12" s="97"/>
+      <c r="G12" s="112"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="112"/>
+      <c r="J12" s="112"/>
+      <c r="K12" s="98"/>
+      <c r="L12" s="99"/>
+      <c r="M12" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:J8"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="F10:J10"/>
@@ -7406,28 +8399,13 @@
     <mergeCell ref="K12:M12"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="F11:J11"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:J8"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:J6"/>
-    <mergeCell ref="K6:M6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
@@ -7441,40 +8419,40 @@
   <sheetData>
     <row r="1" spans="2:11" ht="6" customHeight="1"/>
     <row r="2" spans="2:11" ht="26.25" customHeight="1">
-      <c r="B2" s="102" t="s">
+      <c r="B2" s="109" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="110"/>
+      <c r="D2" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="113" t="s">
-        <v>91</v>
-      </c>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="J2" s="104"/>
-      <c r="K2" s="103"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="109" t="s">
+        <v>103</v>
+      </c>
+      <c r="J2" s="111"/>
+      <c r="K2" s="110"/>
     </row>
     <row r="3" spans="2:11" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="95" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="97"/>
-      <c r="D3" s="105" t="s">
-        <v>360</v>
-      </c>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="105"/>
-      <c r="I3" s="98" t="s">
-        <v>361</v>
-      </c>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
+      <c r="B3" s="98" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="100"/>
+      <c r="D3" s="112" t="s">
+        <v>352</v>
+      </c>
+      <c r="E3" s="112"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="112"/>
+      <c r="I3" s="108" t="s">
+        <v>353</v>
+      </c>
+      <c r="J3" s="108"/>
+      <c r="K3" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -7490,7 +8468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF002060"/>
@@ -7508,10 +8486,10 @@
         <v>14</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1">
@@ -7538,172 +8516,162 @@
     </row>
     <row r="6" spans="2:13" ht="26.25" customHeight="1">
       <c r="B6" s="71" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C6" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="109" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="110"/>
+      <c r="F6" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="102" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" s="103"/>
-      <c r="F6" s="113" t="s">
-        <v>91</v>
-      </c>
-      <c r="G6" s="113"/>
-      <c r="H6" s="113"/>
-      <c r="I6" s="113"/>
-      <c r="J6" s="113"/>
-      <c r="K6" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="L6" s="104"/>
-      <c r="M6" s="103"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="119"/>
+      <c r="J6" s="119"/>
+      <c r="K6" s="109" t="s">
+        <v>103</v>
+      </c>
+      <c r="L6" s="111"/>
+      <c r="M6" s="110"/>
     </row>
     <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="109" t="s">
-        <v>364</v>
+      <c r="B7" s="104" t="s">
+        <v>356</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="D7" s="95" t="s">
-        <v>375</v>
-      </c>
-      <c r="E7" s="97"/>
-      <c r="F7" s="105" t="s">
-        <v>376</v>
-      </c>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="105"/>
-      <c r="K7" s="98" t="s">
-        <v>379</v>
-      </c>
-      <c r="L7" s="98"/>
-      <c r="M7" s="98"/>
+        <v>357</v>
+      </c>
+      <c r="D7" s="98" t="s">
+        <v>367</v>
+      </c>
+      <c r="E7" s="100"/>
+      <c r="F7" s="112" t="s">
+        <v>368</v>
+      </c>
+      <c r="G7" s="112"/>
+      <c r="H7" s="112"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="108" t="s">
+        <v>371</v>
+      </c>
+      <c r="L7" s="108"/>
+      <c r="M7" s="108"/>
     </row>
     <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="110"/>
+      <c r="B8" s="105"/>
       <c r="C8" s="51" t="s">
-        <v>366</v>
-      </c>
-      <c r="D8" s="95" t="s">
-        <v>375</v>
-      </c>
-      <c r="E8" s="97"/>
-      <c r="F8" s="105" t="s">
-        <v>377</v>
-      </c>
-      <c r="G8" s="105"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="105"/>
+        <v>358</v>
+      </c>
+      <c r="D8" s="98" t="s">
+        <v>367</v>
+      </c>
+      <c r="E8" s="100"/>
+      <c r="F8" s="112" t="s">
+        <v>369</v>
+      </c>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="112"/>
       <c r="K8" s="63"/>
       <c r="L8" s="64"/>
       <c r="M8" s="65"/>
     </row>
     <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="111"/>
+      <c r="B9" s="106"/>
       <c r="C9" s="51" t="s">
+        <v>359</v>
+      </c>
+      <c r="D9" s="98" t="s">
         <v>367</v>
       </c>
-      <c r="D9" s="95" t="s">
-        <v>375</v>
-      </c>
-      <c r="E9" s="97"/>
-      <c r="F9" s="105" t="s">
-        <v>378</v>
-      </c>
-      <c r="G9" s="105"/>
-      <c r="H9" s="105"/>
-      <c r="I9" s="105"/>
-      <c r="J9" s="105"/>
-      <c r="K9" s="95"/>
-      <c r="L9" s="96"/>
-      <c r="M9" s="97"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="112" t="s">
+        <v>370</v>
+      </c>
+      <c r="G9" s="112"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="112"/>
+      <c r="K9" s="98"/>
+      <c r="L9" s="99"/>
+      <c r="M9" s="100"/>
     </row>
     <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B10" s="112" t="s">
-        <v>368</v>
+      <c r="B10" s="107" t="s">
+        <v>360</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="D10" s="95" t="s">
-        <v>370</v>
-      </c>
-      <c r="E10" s="97"/>
-      <c r="F10" s="99" t="s">
-        <v>371</v>
-      </c>
-      <c r="G10" s="100"/>
-      <c r="H10" s="100"/>
-      <c r="I10" s="100"/>
-      <c r="J10" s="100"/>
-      <c r="K10" s="95" t="s">
-        <v>374</v>
-      </c>
-      <c r="L10" s="96"/>
-      <c r="M10" s="97"/>
+        <v>251</v>
+      </c>
+      <c r="D10" s="98" t="s">
+        <v>362</v>
+      </c>
+      <c r="E10" s="100"/>
+      <c r="F10" s="95" t="s">
+        <v>363</v>
+      </c>
+      <c r="G10" s="96"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="96"/>
+      <c r="K10" s="98" t="s">
+        <v>366</v>
+      </c>
+      <c r="L10" s="99"/>
+      <c r="M10" s="100"/>
     </row>
     <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="112"/>
+      <c r="B11" s="107"/>
       <c r="C11" s="51" t="s">
-        <v>369</v>
-      </c>
-      <c r="D11" s="95" t="s">
-        <v>372</v>
-      </c>
-      <c r="E11" s="97"/>
-      <c r="F11" s="99" t="s">
-        <v>373</v>
-      </c>
-      <c r="G11" s="100"/>
-      <c r="H11" s="100"/>
-      <c r="I11" s="100"/>
-      <c r="J11" s="100"/>
-      <c r="K11" s="95"/>
-      <c r="L11" s="96"/>
-      <c r="M11" s="97"/>
+        <v>361</v>
+      </c>
+      <c r="D11" s="98" t="s">
+        <v>364</v>
+      </c>
+      <c r="E11" s="100"/>
+      <c r="F11" s="95" t="s">
+        <v>365</v>
+      </c>
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="96"/>
+      <c r="K11" s="98"/>
+      <c r="L11" s="99"/>
+      <c r="M11" s="100"/>
     </row>
     <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B12" s="73" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C12" s="73" t="s">
-        <v>390</v>
-      </c>
-      <c r="D12" s="95" t="s">
-        <v>390</v>
-      </c>
-      <c r="E12" s="97"/>
-      <c r="F12" s="99" t="s">
-        <v>325</v>
-      </c>
-      <c r="G12" s="100"/>
-      <c r="H12" s="100"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="101"/>
-      <c r="K12" s="95" t="s">
-        <v>374</v>
-      </c>
-      <c r="L12" s="96"/>
-      <c r="M12" s="97"/>
+        <v>382</v>
+      </c>
+      <c r="D12" s="98" t="s">
+        <v>382</v>
+      </c>
+      <c r="E12" s="100"/>
+      <c r="F12" s="95" t="s">
+        <v>317</v>
+      </c>
+      <c r="G12" s="96"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="96"/>
+      <c r="J12" s="97"/>
+      <c r="K12" s="98" t="s">
+        <v>366</v>
+      </c>
+      <c r="L12" s="99"/>
+      <c r="M12" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K11:M11"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:J6"/>
     <mergeCell ref="K6:M6"/>
@@ -7716,255 +8684,16 @@
     <mergeCell ref="K9:M9"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="F8:J8"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <tabColor rgb="FF0070C0"/>
-  </sheetPr>
-  <dimension ref="B1:M13"/>
-  <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="1.25" customWidth="1"/>
-    <col min="2" max="20" width="15.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:13" ht="6" customHeight="1" thickBot="1"/>
-    <row r="2" spans="2:13" ht="26.25" thickBot="1">
-      <c r="B2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>327</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B3" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B4" s="82" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B5" s="20"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-    </row>
-    <row r="7" spans="2:13" ht="26.25" customHeight="1">
-      <c r="B7" s="71" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="72" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="102" t="s">
-        <v>349</v>
-      </c>
-      <c r="E7" s="103"/>
-      <c r="F7" s="113" t="s">
-        <v>350</v>
-      </c>
-      <c r="G7" s="113"/>
-      <c r="H7" s="113"/>
-      <c r="I7" s="113"/>
-      <c r="J7" s="113"/>
-      <c r="K7" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="L7" s="104"/>
-      <c r="M7" s="103"/>
-    </row>
-    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="109" t="s">
-        <v>329</v>
-      </c>
-      <c r="C8" s="74" t="s">
-        <v>330</v>
-      </c>
-      <c r="D8" s="95" t="s">
-        <v>333</v>
-      </c>
-      <c r="E8" s="97"/>
-      <c r="F8" s="105" t="s">
-        <v>332</v>
-      </c>
-      <c r="G8" s="105"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="105"/>
-      <c r="K8" s="98" t="s">
-        <v>346</v>
-      </c>
-      <c r="L8" s="98"/>
-      <c r="M8" s="98"/>
-    </row>
-    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="111"/>
-      <c r="C9" s="74" t="s">
-        <v>331</v>
-      </c>
-      <c r="D9" s="95" t="s">
-        <v>334</v>
-      </c>
-      <c r="E9" s="97"/>
-      <c r="F9" s="105" t="s">
-        <v>334</v>
-      </c>
-      <c r="G9" s="105"/>
-      <c r="H9" s="105"/>
-      <c r="I9" s="105"/>
-      <c r="J9" s="105"/>
-      <c r="K9" s="63"/>
-      <c r="L9" s="64"/>
-      <c r="M9" s="65"/>
-    </row>
-    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B10" s="112" t="s">
-        <v>335</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="D10" s="95" t="s">
-        <v>337</v>
-      </c>
-      <c r="E10" s="97"/>
-      <c r="F10" s="105" t="s">
-        <v>339</v>
-      </c>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="105"/>
-      <c r="K10" s="95" t="s">
-        <v>344</v>
-      </c>
-      <c r="L10" s="96"/>
-      <c r="M10" s="97"/>
-    </row>
-    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="112"/>
-      <c r="C11" s="51" t="s">
-        <v>331</v>
-      </c>
-      <c r="D11" s="95" t="s">
-        <v>338</v>
-      </c>
-      <c r="E11" s="97"/>
-      <c r="F11" s="105" t="s">
-        <v>340</v>
-      </c>
-      <c r="G11" s="105"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="105"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="95" t="s">
-        <v>345</v>
-      </c>
-      <c r="L11" s="96"/>
-      <c r="M11" s="97"/>
-    </row>
-    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="112" t="s">
-        <v>336</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="D12" s="98" t="s">
-        <v>341</v>
-      </c>
-      <c r="E12" s="98"/>
-      <c r="F12" s="105" t="s">
-        <v>342</v>
-      </c>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="95" t="s">
-        <v>347</v>
-      </c>
-      <c r="L12" s="96"/>
-      <c r="M12" s="97"/>
-    </row>
-    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="112"/>
-      <c r="C13" s="51" t="s">
-        <v>331</v>
-      </c>
-      <c r="D13" s="98" t="s">
-        <v>348</v>
-      </c>
-      <c r="E13" s="98"/>
-      <c r="F13" s="105" t="s">
-        <v>343</v>
-      </c>
-      <c r="G13" s="105"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="105"/>
-      <c r="J13" s="105"/>
-      <c r="K13" s="63"/>
-      <c r="L13" s="64"/>
-      <c r="M13" s="65"/>
-    </row>
-  </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="B12:B13"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="F12:J12"/>
     <mergeCell ref="K12:M12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:J13"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="F10:J10"/>
     <mergeCell ref="K10:M10"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="F11:J11"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:J8"/>
-    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="K11:M11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testprocess/1-process/大对象测试/Testing_LOB.xlsx
+++ b/testprocess/1-process/大对象测试/Testing_LOB.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="8"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="测试主题" sheetId="14" r:id="rId1"/>
@@ -3348,120 +3348,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3489,27 +3375,6 @@
     <xf numFmtId="49" fontId="0" fillId="13" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="13" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="13" borderId="50" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="13" borderId="41" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3532,9 +3397,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3548,14 +3410,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="50" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="41" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3860,185 +3860,185 @@
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
     <col min="2" max="2" width="13.125" customWidth="1"/>
-    <col min="3" max="3" width="99.375" style="134" customWidth="1"/>
-    <col min="4" max="4" width="66.375" style="133" customWidth="1"/>
+    <col min="3" max="3" width="99.375" style="96" customWidth="1"/>
+    <col min="4" max="4" width="66.375" style="95" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="6" customHeight="1">
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
     </row>
     <row r="2" spans="2:4" ht="14.25" thickBot="1">
-      <c r="B2" s="132" t="s">
+      <c r="B2" s="122" t="s">
         <v>457</v>
       </c>
-      <c r="C2" s="132"/>
+      <c r="C2" s="122"/>
     </row>
     <row r="3" spans="2:4" ht="25.5">
-      <c r="B3" s="135" t="s">
+      <c r="B3" s="97" t="s">
         <v>458</v>
       </c>
-      <c r="C3" s="136" t="s">
+      <c r="C3" s="98" t="s">
         <v>459</v>
       </c>
-      <c r="D3" s="137" t="s">
+      <c r="D3" s="99" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="4" spans="2:4">
-      <c r="B4" s="138" t="s">
+      <c r="B4" s="100" t="s">
         <v>461</v>
       </c>
-      <c r="C4" s="139">
+      <c r="C4" s="101">
         <v>41849</v>
       </c>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="99" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="5" spans="2:4">
-      <c r="B5" s="138" t="s">
+      <c r="B5" s="100" t="s">
         <v>463</v>
       </c>
-      <c r="C5" s="139"/>
-      <c r="D5" s="137" t="s">
+      <c r="C5" s="101"/>
+      <c r="D5" s="99" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="6" spans="2:4">
-      <c r="B6" s="138" t="s">
+      <c r="B6" s="100" t="s">
         <v>465</v>
       </c>
-      <c r="C6" s="140" t="s">
+      <c r="C6" s="102" t="s">
         <v>466</v>
       </c>
-      <c r="D6" s="137" t="s">
+      <c r="D6" s="99" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="13.5" customHeight="1">
-      <c r="B7" s="141" t="s">
+      <c r="B7" s="103" t="s">
         <v>468</v>
       </c>
-      <c r="C7" s="140"/>
-      <c r="D7" s="137" t="s">
+      <c r="C7" s="102"/>
+      <c r="D7" s="99" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="142" t="s">
+      <c r="B8" s="104" t="s">
         <v>470</v>
       </c>
-      <c r="C8" s="143"/>
-      <c r="D8" s="137" t="s">
+      <c r="C8" s="105"/>
+      <c r="D8" s="99" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="40.5" customHeight="1">
-      <c r="B9" s="144" t="s">
+      <c r="B9" s="123" t="s">
         <v>472</v>
       </c>
-      <c r="C9" s="145" t="s">
+      <c r="C9" s="126" t="s">
         <v>473</v>
       </c>
-      <c r="D9" s="146" t="s">
+      <c r="D9" s="129" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="147"/>
-      <c r="C10" s="148"/>
-      <c r="D10" s="146"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="129"/>
     </row>
     <row r="11" spans="2:4">
-      <c r="B11" s="147"/>
-      <c r="C11" s="148"/>
-      <c r="D11" s="146"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="129"/>
     </row>
     <row r="12" spans="2:4">
-      <c r="B12" s="147"/>
-      <c r="C12" s="148"/>
-      <c r="D12" s="146"/>
+      <c r="B12" s="124"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="129"/>
     </row>
     <row r="13" spans="2:4">
-      <c r="B13" s="147"/>
-      <c r="C13" s="148"/>
-      <c r="D13" s="146"/>
+      <c r="B13" s="124"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="129"/>
     </row>
     <row r="14" spans="2:4">
-      <c r="B14" s="147"/>
-      <c r="C14" s="148"/>
-      <c r="D14" s="146"/>
+      <c r="B14" s="124"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="129"/>
     </row>
     <row r="15" spans="2:4">
-      <c r="B15" s="147"/>
-      <c r="C15" s="148"/>
-      <c r="D15" s="146"/>
+      <c r="B15" s="124"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="129"/>
     </row>
     <row r="16" spans="2:4">
-      <c r="B16" s="147"/>
-      <c r="C16" s="148"/>
-      <c r="D16" s="146"/>
+      <c r="B16" s="124"/>
+      <c r="C16" s="127"/>
+      <c r="D16" s="129"/>
     </row>
     <row r="17" spans="2:4">
-      <c r="B17" s="147"/>
-      <c r="C17" s="148"/>
-      <c r="D17" s="146"/>
+      <c r="B17" s="124"/>
+      <c r="C17" s="127"/>
+      <c r="D17" s="129"/>
     </row>
     <row r="18" spans="2:4">
-      <c r="B18" s="147"/>
-      <c r="C18" s="148"/>
-      <c r="D18" s="146"/>
+      <c r="B18" s="124"/>
+      <c r="C18" s="127"/>
+      <c r="D18" s="129"/>
     </row>
     <row r="19" spans="2:4">
-      <c r="B19" s="147"/>
-      <c r="C19" s="148"/>
-      <c r="D19" s="146"/>
+      <c r="B19" s="124"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="129"/>
     </row>
     <row r="20" spans="2:4">
-      <c r="B20" s="147"/>
-      <c r="C20" s="148"/>
-      <c r="D20" s="146"/>
+      <c r="B20" s="124"/>
+      <c r="C20" s="127"/>
+      <c r="D20" s="129"/>
     </row>
     <row r="21" spans="2:4">
-      <c r="B21" s="147"/>
-      <c r="C21" s="148"/>
-      <c r="D21" s="146"/>
+      <c r="B21" s="124"/>
+      <c r="C21" s="127"/>
+      <c r="D21" s="129"/>
     </row>
     <row r="22" spans="2:4">
-      <c r="B22" s="147"/>
-      <c r="C22" s="148"/>
-      <c r="D22" s="146"/>
+      <c r="B22" s="124"/>
+      <c r="C22" s="127"/>
+      <c r="D22" s="129"/>
     </row>
     <row r="23" spans="2:4">
-      <c r="B23" s="147"/>
-      <c r="C23" s="148"/>
-      <c r="D23" s="146"/>
+      <c r="B23" s="124"/>
+      <c r="C23" s="127"/>
+      <c r="D23" s="129"/>
     </row>
     <row r="24" spans="2:4">
-      <c r="B24" s="147"/>
-      <c r="C24" s="148"/>
-      <c r="D24" s="146"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="127"/>
+      <c r="D24" s="129"/>
     </row>
     <row r="25" spans="2:4">
-      <c r="B25" s="147"/>
-      <c r="C25" s="148"/>
-      <c r="D25" s="146"/>
+      <c r="B25" s="124"/>
+      <c r="C25" s="127"/>
+      <c r="D25" s="129"/>
     </row>
     <row r="26" spans="2:4">
-      <c r="B26" s="147"/>
-      <c r="C26" s="148"/>
-      <c r="D26" s="146"/>
+      <c r="B26" s="124"/>
+      <c r="C26" s="127"/>
+      <c r="D26" s="129"/>
     </row>
     <row r="27" spans="2:4">
-      <c r="B27" s="147"/>
-      <c r="C27" s="148"/>
-      <c r="D27" s="146"/>
+      <c r="B27" s="124"/>
+      <c r="C27" s="127"/>
+      <c r="D27" s="129"/>
     </row>
     <row r="28" spans="2:4" ht="14.25" thickBot="1">
-      <c r="B28" s="149"/>
-      <c r="C28" s="150"/>
-      <c r="D28" s="146"/>
+      <c r="B28" s="125"/>
+      <c r="C28" s="128"/>
+      <c r="D28" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4121,165 +4121,159 @@
       <c r="C7" s="72" t="s">
         <v>77</v>
       </c>
-      <c r="D7" s="109" t="s">
+      <c r="D7" s="137" t="s">
         <v>341</v>
       </c>
-      <c r="E7" s="110"/>
-      <c r="F7" s="119" t="s">
+      <c r="E7" s="138"/>
+      <c r="F7" s="148" t="s">
         <v>342</v>
       </c>
-      <c r="G7" s="119"/>
-      <c r="H7" s="119"/>
-      <c r="I7" s="119"/>
-      <c r="J7" s="119"/>
-      <c r="K7" s="109" t="s">
+      <c r="G7" s="148"/>
+      <c r="H7" s="148"/>
+      <c r="I7" s="148"/>
+      <c r="J7" s="148"/>
+      <c r="K7" s="137" t="s">
         <v>103</v>
       </c>
-      <c r="L7" s="111"/>
-      <c r="M7" s="110"/>
+      <c r="L7" s="139"/>
+      <c r="M7" s="138"/>
     </row>
     <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="104" t="s">
+      <c r="B8" s="144" t="s">
         <v>321</v>
       </c>
       <c r="C8" s="74" t="s">
         <v>322</v>
       </c>
-      <c r="D8" s="98" t="s">
+      <c r="D8" s="130" t="s">
         <v>325</v>
       </c>
-      <c r="E8" s="100"/>
-      <c r="F8" s="112" t="s">
+      <c r="E8" s="132"/>
+      <c r="F8" s="140" t="s">
         <v>324</v>
       </c>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="108" t="s">
+      <c r="G8" s="140"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="140"/>
+      <c r="J8" s="140"/>
+      <c r="K8" s="133" t="s">
         <v>338</v>
       </c>
-      <c r="L8" s="108"/>
-      <c r="M8" s="108"/>
+      <c r="L8" s="133"/>
+      <c r="M8" s="133"/>
     </row>
     <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="106"/>
+      <c r="B9" s="146"/>
       <c r="C9" s="74" t="s">
         <v>323</v>
       </c>
-      <c r="D9" s="98" t="s">
+      <c r="D9" s="130" t="s">
         <v>326</v>
       </c>
-      <c r="E9" s="100"/>
-      <c r="F9" s="112" t="s">
+      <c r="E9" s="132"/>
+      <c r="F9" s="140" t="s">
         <v>326</v>
       </c>
-      <c r="G9" s="112"/>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="112"/>
+      <c r="G9" s="140"/>
+      <c r="H9" s="140"/>
+      <c r="I9" s="140"/>
+      <c r="J9" s="140"/>
       <c r="K9" s="63"/>
       <c r="L9" s="64"/>
       <c r="M9" s="65"/>
     </row>
     <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B10" s="107" t="s">
+      <c r="B10" s="147" t="s">
         <v>327</v>
       </c>
       <c r="C10" s="51" t="s">
         <v>322</v>
       </c>
-      <c r="D10" s="98" t="s">
+      <c r="D10" s="130" t="s">
         <v>329</v>
       </c>
-      <c r="E10" s="100"/>
-      <c r="F10" s="112" t="s">
+      <c r="E10" s="132"/>
+      <c r="F10" s="140" t="s">
         <v>331</v>
       </c>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="112"/>
-      <c r="K10" s="98" t="s">
+      <c r="G10" s="140"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="140"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="130" t="s">
         <v>336</v>
       </c>
-      <c r="L10" s="99"/>
-      <c r="M10" s="100"/>
+      <c r="L10" s="131"/>
+      <c r="M10" s="132"/>
     </row>
     <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="107"/>
+      <c r="B11" s="147"/>
       <c r="C11" s="51" t="s">
         <v>323</v>
       </c>
-      <c r="D11" s="98" t="s">
+      <c r="D11" s="130" t="s">
         <v>330</v>
       </c>
-      <c r="E11" s="100"/>
-      <c r="F11" s="112" t="s">
+      <c r="E11" s="132"/>
+      <c r="F11" s="140" t="s">
         <v>332</v>
       </c>
-      <c r="G11" s="112"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="112"/>
-      <c r="J11" s="112"/>
-      <c r="K11" s="98" t="s">
+      <c r="G11" s="140"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="140"/>
+      <c r="K11" s="130" t="s">
         <v>337</v>
       </c>
-      <c r="L11" s="99"/>
-      <c r="M11" s="100"/>
+      <c r="L11" s="131"/>
+      <c r="M11" s="132"/>
     </row>
     <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="107" t="s">
+      <c r="B12" s="147" t="s">
         <v>328</v>
       </c>
       <c r="C12" s="51" t="s">
         <v>322</v>
       </c>
-      <c r="D12" s="108" t="s">
+      <c r="D12" s="133" t="s">
         <v>333</v>
       </c>
-      <c r="E12" s="108"/>
-      <c r="F12" s="112" t="s">
+      <c r="E12" s="133"/>
+      <c r="F12" s="140" t="s">
         <v>334</v>
       </c>
-      <c r="G12" s="112"/>
-      <c r="H12" s="112"/>
-      <c r="I12" s="112"/>
-      <c r="J12" s="112"/>
-      <c r="K12" s="98" t="s">
+      <c r="G12" s="140"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="140"/>
+      <c r="K12" s="130" t="s">
         <v>339</v>
       </c>
-      <c r="L12" s="99"/>
-      <c r="M12" s="100"/>
+      <c r="L12" s="131"/>
+      <c r="M12" s="132"/>
     </row>
     <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="107"/>
+      <c r="B13" s="147"/>
       <c r="C13" s="51" t="s">
         <v>323</v>
       </c>
-      <c r="D13" s="108" t="s">
+      <c r="D13" s="133" t="s">
         <v>340</v>
       </c>
-      <c r="E13" s="108"/>
-      <c r="F13" s="112" t="s">
+      <c r="E13" s="133"/>
+      <c r="F13" s="140" t="s">
         <v>335</v>
       </c>
-      <c r="G13" s="112"/>
-      <c r="H13" s="112"/>
-      <c r="I13" s="112"/>
-      <c r="J13" s="112"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="140"/>
+      <c r="J13" s="140"/>
       <c r="K13" s="63"/>
       <c r="L13" s="64"/>
       <c r="M13" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:J8"/>
-    <mergeCell ref="K8:M8"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="F9:J9"/>
@@ -4296,6 +4290,12 @@
     <mergeCell ref="K10:M10"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="F11:J11"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:J8"/>
+    <mergeCell ref="K8:M8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4360,40 +4360,40 @@
     <row r="9" spans="2:11" ht="20.100000000000001" hidden="1" customHeight="1" outlineLevel="1"/>
     <row r="10" spans="2:11" ht="20.100000000000001" hidden="1" customHeight="1" outlineLevel="1"/>
     <row r="11" spans="2:11" ht="26.25" customHeight="1" collapsed="1">
-      <c r="B11" s="109" t="s">
+      <c r="B11" s="137" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="110"/>
-      <c r="D11" s="119" t="s">
+      <c r="C11" s="138"/>
+      <c r="D11" s="148" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="109" t="s">
+      <c r="E11" s="148"/>
+      <c r="F11" s="148"/>
+      <c r="G11" s="148"/>
+      <c r="H11" s="148"/>
+      <c r="I11" s="137" t="s">
         <v>103</v>
       </c>
-      <c r="J11" s="111"/>
-      <c r="K11" s="110"/>
+      <c r="J11" s="139"/>
+      <c r="K11" s="138"/>
     </row>
     <row r="12" spans="2:11" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="108" t="s">
+      <c r="B12" s="133" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="108"/>
-      <c r="D12" s="112" t="s">
+      <c r="C12" s="133"/>
+      <c r="D12" s="140" t="s">
         <v>220</v>
       </c>
-      <c r="E12" s="112"/>
-      <c r="F12" s="112"/>
-      <c r="G12" s="112"/>
-      <c r="H12" s="112"/>
-      <c r="I12" s="108" t="s">
+      <c r="E12" s="140"/>
+      <c r="F12" s="140"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="133" t="s">
         <v>391</v>
       </c>
-      <c r="J12" s="108"/>
-      <c r="K12" s="108"/>
+      <c r="J12" s="133"/>
+      <c r="K12" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4452,58 +4452,58 @@
       <c r="F4" s="20"/>
     </row>
     <row r="5" spans="2:11" ht="26.25" customHeight="1">
-      <c r="B5" s="109" t="s">
+      <c r="B5" s="137" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="110"/>
-      <c r="D5" s="119" t="s">
+      <c r="C5" s="138"/>
+      <c r="D5" s="148" t="s">
         <v>84</v>
       </c>
-      <c r="E5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="119"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="109" t="s">
+      <c r="E5" s="148"/>
+      <c r="F5" s="148"/>
+      <c r="G5" s="148"/>
+      <c r="H5" s="148"/>
+      <c r="I5" s="137" t="s">
         <v>103</v>
       </c>
-      <c r="J5" s="111"/>
-      <c r="K5" s="110"/>
+      <c r="J5" s="139"/>
+      <c r="K5" s="138"/>
     </row>
     <row r="6" spans="2:11" ht="20.100000000000001" customHeight="1">
-      <c r="B6" s="108" t="s">
+      <c r="B6" s="133" t="s">
         <v>207</v>
       </c>
-      <c r="C6" s="108"/>
-      <c r="D6" s="112" t="s">
+      <c r="C6" s="133"/>
+      <c r="D6" s="140" t="s">
         <v>209</v>
       </c>
-      <c r="E6" s="112"/>
-      <c r="F6" s="112"/>
-      <c r="G6" s="112"/>
-      <c r="H6" s="112"/>
-      <c r="I6" s="108" t="s">
+      <c r="E6" s="140"/>
+      <c r="F6" s="140"/>
+      <c r="G6" s="140"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="133" t="s">
         <v>211</v>
       </c>
-      <c r="J6" s="108"/>
-      <c r="K6" s="108"/>
+      <c r="J6" s="133"/>
+      <c r="K6" s="133"/>
     </row>
     <row r="7" spans="2:11" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="133" t="s">
         <v>208</v>
       </c>
-      <c r="C7" s="108"/>
-      <c r="D7" s="112" t="s">
+      <c r="C7" s="133"/>
+      <c r="D7" s="140" t="s">
         <v>210</v>
       </c>
-      <c r="E7" s="112"/>
-      <c r="F7" s="112"/>
-      <c r="G7" s="112"/>
-      <c r="H7" s="112"/>
-      <c r="I7" s="108" t="s">
+      <c r="E7" s="140"/>
+      <c r="F7" s="140"/>
+      <c r="G7" s="140"/>
+      <c r="H7" s="140"/>
+      <c r="I7" s="133" t="s">
         <v>212</v>
       </c>
-      <c r="J7" s="108"/>
-      <c r="K7" s="108"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -4576,22 +4576,22 @@
       <c r="C5" s="72" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="109" t="s">
+      <c r="D5" s="137" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="110"/>
-      <c r="F5" s="119" t="s">
+      <c r="E5" s="138"/>
+      <c r="F5" s="148" t="s">
         <v>84</v>
       </c>
-      <c r="G5" s="119"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
-      <c r="J5" s="119"/>
-      <c r="K5" s="109" t="s">
+      <c r="G5" s="148"/>
+      <c r="H5" s="148"/>
+      <c r="I5" s="148"/>
+      <c r="J5" s="148"/>
+      <c r="K5" s="137" t="s">
         <v>103</v>
       </c>
-      <c r="L5" s="111"/>
-      <c r="M5" s="110"/>
+      <c r="L5" s="139"/>
+      <c r="M5" s="138"/>
     </row>
     <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B6" s="75" t="s">
@@ -4600,90 +4600,90 @@
       <c r="C6" s="51" t="s">
         <v>255</v>
       </c>
-      <c r="D6" s="98" t="s">
+      <c r="D6" s="130" t="s">
         <v>219</v>
       </c>
-      <c r="E6" s="100"/>
-      <c r="F6" s="112" t="s">
+      <c r="E6" s="132"/>
+      <c r="F6" s="140" t="s">
         <v>215</v>
       </c>
-      <c r="G6" s="112"/>
-      <c r="H6" s="112"/>
-      <c r="I6" s="112"/>
-      <c r="J6" s="112"/>
-      <c r="K6" s="108" t="s">
+      <c r="G6" s="140"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="140"/>
+      <c r="K6" s="133" t="s">
         <v>384</v>
       </c>
-      <c r="L6" s="108"/>
-      <c r="M6" s="108"/>
+      <c r="L6" s="133"/>
+      <c r="M6" s="133"/>
     </row>
     <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="144" t="s">
         <v>385</v>
       </c>
       <c r="C7" s="51" t="s">
         <v>386</v>
       </c>
-      <c r="D7" s="98" t="s">
+      <c r="D7" s="130" t="s">
         <v>389</v>
       </c>
-      <c r="E7" s="100"/>
-      <c r="F7" s="95" t="s">
+      <c r="E7" s="132"/>
+      <c r="F7" s="134" t="s">
         <v>216</v>
       </c>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="96"/>
-      <c r="K7" s="98" t="s">
+      <c r="G7" s="135"/>
+      <c r="H7" s="135"/>
+      <c r="I7" s="135"/>
+      <c r="J7" s="135"/>
+      <c r="K7" s="130" t="s">
         <v>214</v>
       </c>
-      <c r="L7" s="99"/>
-      <c r="M7" s="100"/>
+      <c r="L7" s="131"/>
+      <c r="M7" s="132"/>
     </row>
     <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="105"/>
+      <c r="B8" s="145"/>
       <c r="C8" s="51" t="s">
         <v>387</v>
       </c>
-      <c r="D8" s="98" t="s">
+      <c r="D8" s="130" t="s">
         <v>389</v>
       </c>
-      <c r="E8" s="100"/>
-      <c r="F8" s="95" t="s">
+      <c r="E8" s="132"/>
+      <c r="F8" s="134" t="s">
         <v>217</v>
       </c>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="98" t="s">
+      <c r="G8" s="135"/>
+      <c r="H8" s="135"/>
+      <c r="I8" s="135"/>
+      <c r="J8" s="135"/>
+      <c r="K8" s="130" t="s">
         <v>213</v>
       </c>
-      <c r="L8" s="99"/>
-      <c r="M8" s="100"/>
+      <c r="L8" s="131"/>
+      <c r="M8" s="132"/>
     </row>
     <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="106"/>
+      <c r="B9" s="146"/>
       <c r="C9" s="91" t="s">
         <v>388</v>
       </c>
-      <c r="D9" s="98" t="s">
+      <c r="D9" s="130" t="s">
         <v>389</v>
       </c>
-      <c r="E9" s="100"/>
-      <c r="F9" s="95" t="s">
+      <c r="E9" s="132"/>
+      <c r="F9" s="134" t="s">
         <v>218</v>
       </c>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="97"/>
-      <c r="K9" s="98" t="s">
+      <c r="G9" s="135"/>
+      <c r="H9" s="135"/>
+      <c r="I9" s="135"/>
+      <c r="J9" s="136"/>
+      <c r="K9" s="130" t="s">
         <v>390</v>
       </c>
-      <c r="L9" s="99"/>
-      <c r="M9" s="100"/>
+      <c r="L9" s="131"/>
+      <c r="M9" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -4854,418 +4854,375 @@
       <c r="C10" s="72" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="109" t="s">
+      <c r="D10" s="137" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="110"/>
-      <c r="F10" s="109" t="s">
+      <c r="E10" s="138"/>
+      <c r="F10" s="137" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="111"/>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="110"/>
-      <c r="K10" s="109" t="s">
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="138"/>
+      <c r="K10" s="137" t="s">
         <v>103</v>
       </c>
-      <c r="L10" s="111"/>
-      <c r="M10" s="110"/>
+      <c r="L10" s="139"/>
+      <c r="M10" s="138"/>
     </row>
     <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="104" t="s">
+      <c r="B11" s="144" t="s">
         <v>421</v>
       </c>
       <c r="C11" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="98" t="s">
+      <c r="D11" s="130" t="s">
         <v>392</v>
       </c>
-      <c r="E11" s="100"/>
-      <c r="F11" s="95" t="s">
+      <c r="E11" s="132"/>
+      <c r="F11" s="134" t="s">
         <v>394</v>
       </c>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="97"/>
-      <c r="K11" s="108"/>
-      <c r="L11" s="108"/>
-      <c r="M11" s="108"/>
+      <c r="G11" s="135"/>
+      <c r="H11" s="135"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="136"/>
+      <c r="K11" s="133"/>
+      <c r="L11" s="133"/>
+      <c r="M11" s="133"/>
     </row>
     <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="106"/>
+      <c r="B12" s="146"/>
       <c r="C12" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="98" t="s">
+      <c r="D12" s="130" t="s">
         <v>393</v>
       </c>
-      <c r="E12" s="100"/>
-      <c r="F12" s="95" t="s">
+      <c r="E12" s="132"/>
+      <c r="F12" s="134" t="s">
         <v>395</v>
       </c>
-      <c r="G12" s="96"/>
-      <c r="H12" s="96"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="97"/>
-      <c r="K12" s="108"/>
-      <c r="L12" s="108"/>
-      <c r="M12" s="108"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="135"/>
+      <c r="I12" s="135"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="133"/>
+      <c r="L12" s="133"/>
+      <c r="M12" s="133"/>
     </row>
     <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="107" t="s">
+      <c r="B13" s="147" t="s">
         <v>422</v>
       </c>
       <c r="C13" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="127" t="s">
+      <c r="D13" s="158" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="128"/>
-      <c r="F13" s="95" t="s">
+      <c r="E13" s="159"/>
+      <c r="F13" s="134" t="s">
         <v>396</v>
       </c>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="97"/>
-      <c r="K13" s="108"/>
-      <c r="L13" s="108"/>
-      <c r="M13" s="108"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="135"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="136"/>
+      <c r="K13" s="133"/>
+      <c r="L13" s="133"/>
+      <c r="M13" s="133"/>
     </row>
     <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B14" s="107"/>
+      <c r="B14" s="147"/>
       <c r="C14" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="127" t="s">
+      <c r="D14" s="158" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="128"/>
-      <c r="F14" s="95" t="s">
+      <c r="E14" s="159"/>
+      <c r="F14" s="134" t="s">
         <v>397</v>
       </c>
-      <c r="G14" s="96"/>
-      <c r="H14" s="96"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="97"/>
-      <c r="K14" s="108"/>
-      <c r="L14" s="108"/>
-      <c r="M14" s="108"/>
+      <c r="G14" s="135"/>
+      <c r="H14" s="135"/>
+      <c r="I14" s="135"/>
+      <c r="J14" s="136"/>
+      <c r="K14" s="133"/>
+      <c r="L14" s="133"/>
+      <c r="M14" s="133"/>
     </row>
     <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B15" s="107"/>
+      <c r="B15" s="147"/>
       <c r="C15" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="127" t="s">
+      <c r="D15" s="158" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="128"/>
-      <c r="F15" s="95" t="s">
+      <c r="E15" s="159"/>
+      <c r="F15" s="134" t="s">
         <v>398</v>
       </c>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="97"/>
-      <c r="K15" s="108"/>
-      <c r="L15" s="108"/>
-      <c r="M15" s="108"/>
+      <c r="G15" s="135"/>
+      <c r="H15" s="135"/>
+      <c r="I15" s="135"/>
+      <c r="J15" s="136"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="133"/>
+      <c r="M15" s="133"/>
     </row>
     <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B16" s="107"/>
+      <c r="B16" s="147"/>
       <c r="C16" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="127" t="s">
+      <c r="D16" s="158" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="128"/>
-      <c r="F16" s="95" t="s">
+      <c r="E16" s="159"/>
+      <c r="F16" s="134" t="s">
         <v>399</v>
       </c>
-      <c r="G16" s="96"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="97"/>
-      <c r="K16" s="98"/>
-      <c r="L16" s="99"/>
-      <c r="M16" s="100"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135"/>
+      <c r="I16" s="135"/>
+      <c r="J16" s="136"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="131"/>
+      <c r="M16" s="132"/>
     </row>
     <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B17" s="107" t="s">
+      <c r="B17" s="147" t="s">
         <v>423</v>
       </c>
       <c r="C17" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="122" t="s">
+      <c r="D17" s="160" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="123"/>
-      <c r="F17" s="95" t="s">
+      <c r="E17" s="161"/>
+      <c r="F17" s="134" t="s">
         <v>400</v>
       </c>
-      <c r="G17" s="96"/>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96"/>
-      <c r="K17" s="108"/>
-      <c r="L17" s="108"/>
-      <c r="M17" s="108"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="135"/>
+      <c r="I17" s="135"/>
+      <c r="J17" s="135"/>
+      <c r="K17" s="133"/>
+      <c r="L17" s="133"/>
+      <c r="M17" s="133"/>
     </row>
     <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B18" s="107"/>
+      <c r="B18" s="147"/>
       <c r="C18" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="D18" s="129" t="s">
+      <c r="D18" s="162" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="130"/>
-      <c r="F18" s="95" t="s">
+      <c r="E18" s="163"/>
+      <c r="F18" s="134" t="s">
         <v>401</v>
       </c>
-      <c r="G18" s="96"/>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="96"/>
-      <c r="K18" s="108"/>
-      <c r="L18" s="108"/>
-      <c r="M18" s="108"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="135"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="135"/>
+      <c r="K18" s="133"/>
+      <c r="L18" s="133"/>
+      <c r="M18" s="133"/>
     </row>
     <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B19" s="107"/>
+      <c r="B19" s="147"/>
       <c r="C19" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="129" t="s">
+      <c r="D19" s="162" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="130"/>
-      <c r="F19" s="95" t="s">
+      <c r="E19" s="163"/>
+      <c r="F19" s="134" t="s">
         <v>402</v>
       </c>
-      <c r="G19" s="96"/>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="96"/>
-      <c r="K19" s="108"/>
-      <c r="L19" s="108"/>
-      <c r="M19" s="108"/>
+      <c r="G19" s="135"/>
+      <c r="H19" s="135"/>
+      <c r="I19" s="135"/>
+      <c r="J19" s="135"/>
+      <c r="K19" s="133"/>
+      <c r="L19" s="133"/>
+      <c r="M19" s="133"/>
     </row>
     <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B20" s="104" t="s">
+      <c r="B20" s="144" t="s">
         <v>403</v>
       </c>
       <c r="C20" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="129" t="s">
+      <c r="D20" s="162" t="s">
         <v>404</v>
       </c>
-      <c r="E20" s="130"/>
-      <c r="F20" s="112" t="s">
+      <c r="E20" s="163"/>
+      <c r="F20" s="140" t="s">
         <v>413</v>
       </c>
-      <c r="G20" s="112"/>
-      <c r="H20" s="112"/>
-      <c r="I20" s="112"/>
-      <c r="J20" s="112"/>
-      <c r="K20" s="108"/>
-      <c r="L20" s="108"/>
-      <c r="M20" s="108"/>
+      <c r="G20" s="140"/>
+      <c r="H20" s="140"/>
+      <c r="I20" s="140"/>
+      <c r="J20" s="140"/>
+      <c r="K20" s="133"/>
+      <c r="L20" s="133"/>
+      <c r="M20" s="133"/>
     </row>
     <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="105"/>
+      <c r="B21" s="145"/>
       <c r="C21" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="D21" s="127" t="s">
+      <c r="D21" s="158" t="s">
         <v>405</v>
       </c>
-      <c r="E21" s="128"/>
-      <c r="F21" s="112" t="s">
+      <c r="E21" s="159"/>
+      <c r="F21" s="140" t="s">
         <v>414</v>
       </c>
-      <c r="G21" s="112"/>
-      <c r="H21" s="112"/>
-      <c r="I21" s="112"/>
-      <c r="J21" s="112"/>
-      <c r="K21" s="108"/>
-      <c r="L21" s="108"/>
-      <c r="M21" s="108"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="140"/>
+      <c r="I21" s="140"/>
+      <c r="J21" s="140"/>
+      <c r="K21" s="133"/>
+      <c r="L21" s="133"/>
+      <c r="M21" s="133"/>
     </row>
     <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B22" s="105"/>
+      <c r="B22" s="145"/>
       <c r="C22" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="122" t="s">
+      <c r="D22" s="160" t="s">
         <v>406</v>
       </c>
-      <c r="E22" s="123"/>
-      <c r="F22" s="112" t="s">
+      <c r="E22" s="161"/>
+      <c r="F22" s="140" t="s">
         <v>415</v>
       </c>
-      <c r="G22" s="112"/>
-      <c r="H22" s="112"/>
-      <c r="I22" s="112"/>
-      <c r="J22" s="112"/>
-      <c r="K22" s="108"/>
-      <c r="L22" s="108"/>
-      <c r="M22" s="108"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="140"/>
+      <c r="I22" s="140"/>
+      <c r="J22" s="140"/>
+      <c r="K22" s="133"/>
+      <c r="L22" s="133"/>
+      <c r="M22" s="133"/>
     </row>
     <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B23" s="106"/>
+      <c r="B23" s="146"/>
       <c r="C23" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="122" t="s">
+      <c r="D23" s="160" t="s">
         <v>407</v>
       </c>
-      <c r="E23" s="123"/>
-      <c r="F23" s="112" t="s">
+      <c r="E23" s="161"/>
+      <c r="F23" s="140" t="s">
         <v>416</v>
       </c>
-      <c r="G23" s="112"/>
-      <c r="H23" s="112"/>
-      <c r="I23" s="112"/>
-      <c r="J23" s="112"/>
-      <c r="K23" s="108"/>
-      <c r="L23" s="108"/>
-      <c r="M23" s="108"/>
+      <c r="G23" s="140"/>
+      <c r="H23" s="140"/>
+      <c r="I23" s="140"/>
+      <c r="J23" s="140"/>
+      <c r="K23" s="133"/>
+      <c r="L23" s="133"/>
+      <c r="M23" s="133"/>
     </row>
     <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B24" s="124" t="s">
+      <c r="B24" s="164" t="s">
         <v>408</v>
       </c>
       <c r="C24" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="98" t="s">
+      <c r="D24" s="130" t="s">
         <v>409</v>
       </c>
-      <c r="E24" s="100"/>
-      <c r="F24" s="112" t="s">
+      <c r="E24" s="132"/>
+      <c r="F24" s="140" t="s">
         <v>417</v>
       </c>
-      <c r="G24" s="112"/>
-      <c r="H24" s="112"/>
-      <c r="I24" s="112"/>
-      <c r="J24" s="112"/>
-      <c r="K24" s="108"/>
-      <c r="L24" s="108"/>
-      <c r="M24" s="108"/>
+      <c r="G24" s="140"/>
+      <c r="H24" s="140"/>
+      <c r="I24" s="140"/>
+      <c r="J24" s="140"/>
+      <c r="K24" s="133"/>
+      <c r="L24" s="133"/>
+      <c r="M24" s="133"/>
     </row>
     <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B25" s="125"/>
+      <c r="B25" s="165"/>
       <c r="C25" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="98" t="s">
+      <c r="D25" s="130" t="s">
         <v>410</v>
       </c>
-      <c r="E25" s="100"/>
-      <c r="F25" s="112" t="s">
+      <c r="E25" s="132"/>
+      <c r="F25" s="140" t="s">
         <v>418</v>
       </c>
-      <c r="G25" s="112"/>
-      <c r="H25" s="112"/>
-      <c r="I25" s="112"/>
-      <c r="J25" s="112"/>
-      <c r="K25" s="108"/>
-      <c r="L25" s="108"/>
-      <c r="M25" s="108"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="140"/>
+      <c r="I25" s="140"/>
+      <c r="J25" s="140"/>
+      <c r="K25" s="133"/>
+      <c r="L25" s="133"/>
+      <c r="M25" s="133"/>
     </row>
     <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B26" s="125"/>
+      <c r="B26" s="165"/>
       <c r="C26" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="D26" s="98" t="s">
+      <c r="D26" s="130" t="s">
         <v>411</v>
       </c>
-      <c r="E26" s="100"/>
-      <c r="F26" s="112" t="s">
+      <c r="E26" s="132"/>
+      <c r="F26" s="140" t="s">
         <v>419</v>
       </c>
-      <c r="G26" s="112"/>
-      <c r="H26" s="112"/>
-      <c r="I26" s="112"/>
-      <c r="J26" s="112"/>
-      <c r="K26" s="108"/>
-      <c r="L26" s="108"/>
-      <c r="M26" s="108"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="140"/>
+      <c r="I26" s="140"/>
+      <c r="J26" s="140"/>
+      <c r="K26" s="133"/>
+      <c r="L26" s="133"/>
+      <c r="M26" s="133"/>
     </row>
     <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B27" s="126"/>
+      <c r="B27" s="166"/>
       <c r="C27" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="98" t="s">
+      <c r="D27" s="130" t="s">
         <v>412</v>
       </c>
-      <c r="E27" s="100"/>
-      <c r="F27" s="112" t="s">
+      <c r="E27" s="132"/>
+      <c r="F27" s="140" t="s">
         <v>420</v>
       </c>
-      <c r="G27" s="112"/>
-      <c r="H27" s="112"/>
-      <c r="I27" s="112"/>
-      <c r="J27" s="112"/>
-      <c r="K27" s="108"/>
-      <c r="L27" s="108"/>
-      <c r="M27" s="108"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="140"/>
+      <c r="I27" s="140"/>
+      <c r="J27" s="140"/>
+      <c r="K27" s="133"/>
+      <c r="L27" s="133"/>
+      <c r="M27" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:J23"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:J24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:J25"/>
-    <mergeCell ref="K25:M25"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="F27:J27"/>
     <mergeCell ref="K27:M27"/>
@@ -5282,6 +5239,49 @@
     <mergeCell ref="K14:M14"/>
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="F26:J26"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:J24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:J13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5298,72 +5298,72 @@
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.875" customWidth="1"/>
-    <col min="2" max="2" width="79.75" style="152" customWidth="1"/>
+    <col min="2" max="2" width="79.75" style="107" customWidth="1"/>
     <col min="3" max="4" width="9.375" customWidth="1"/>
-    <col min="5" max="5" width="47.125" style="152" customWidth="1"/>
+    <col min="5" max="5" width="47.125" style="107" customWidth="1"/>
     <col min="6" max="6" width="19.875" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="106" t="s">
         <v>475</v>
       </c>
-      <c r="B1" s="166"/>
+      <c r="B1" s="120"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" thickBot="1">
-      <c r="A2" s="153" t="s">
+      <c r="A2" s="108" t="s">
         <v>476</v>
       </c>
       <c r="B2" s="167"/>
       <c r="C2" s="168"/>
-      <c r="D2" s="169"/>
-    </row>
-    <row r="3" spans="1:7" s="159" customFormat="1" ht="19.5" thickBot="1">
-      <c r="A3" s="154" t="s">
+      <c r="D2" s="121"/>
+    </row>
+    <row r="3" spans="1:7" s="114" customFormat="1" ht="19.5" thickBot="1">
+      <c r="A3" s="109" t="s">
         <v>477</v>
       </c>
-      <c r="B3" s="155" t="s">
+      <c r="B3" s="110" t="s">
         <v>478</v>
       </c>
-      <c r="C3" s="156" t="s">
+      <c r="C3" s="111" t="s">
         <v>479</v>
       </c>
-      <c r="D3" s="157" t="s">
+      <c r="D3" s="112" t="s">
         <v>480</v>
       </c>
-      <c r="E3" s="158" t="s">
+      <c r="E3" s="113" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1">
-      <c r="F4" s="160" t="s">
+      <c r="F4" s="169" t="s">
         <v>482</v>
       </c>
-      <c r="G4" s="160"/>
+      <c r="G4" s="169"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="F5" s="160"/>
-      <c r="G5" s="160"/>
+      <c r="F5" s="169"/>
+      <c r="G5" s="169"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="F6" s="160"/>
-      <c r="G6" s="160"/>
+      <c r="F6" s="169"/>
+      <c r="G6" s="169"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7"/>
-      <c r="F7" s="161" t="s">
+      <c r="F7" s="115" t="s">
         <v>483</v>
       </c>
-      <c r="G7" s="162"/>
+      <c r="G7" s="116"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="F8" s="161"/>
-      <c r="G8" s="161"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="115"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="F9" s="161"/>
-      <c r="G9" s="161"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5387,48 +5387,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="117" t="s">
         <v>484</v>
       </c>
-      <c r="B1" s="164"/>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
-      <c r="G1" s="164"/>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="163" t="s">
+      <c r="A7" s="117" t="s">
         <v>485</v>
       </c>
-      <c r="B7" s="164"/>
-      <c r="C7" s="164"/>
-      <c r="D7" s="164"/>
-      <c r="E7" s="164"/>
-      <c r="F7" s="164"/>
-      <c r="G7" s="164"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="163" t="s">
+      <c r="A15" s="117" t="s">
         <v>486</v>
       </c>
-      <c r="B15" s="164"/>
-      <c r="C15" s="164"/>
-      <c r="D15" s="164"/>
-      <c r="E15" s="164"/>
-      <c r="F15" s="164"/>
-      <c r="G15" s="164"/>
+      <c r="B15" s="118"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="118"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="163" t="s">
+      <c r="A22" s="117" t="s">
         <v>487</v>
       </c>
-      <c r="B22" s="164"/>
-      <c r="C22" s="164"/>
-      <c r="D22" s="164"/>
-      <c r="E22" s="164"/>
-      <c r="F22" s="164"/>
-      <c r="G22" s="164"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="118"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5484,7 +5484,7 @@
       <c r="L2" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="165" t="s">
+      <c r="M2" s="119" t="s">
         <v>488</v>
       </c>
     </row>
@@ -6055,655 +6055,701 @@
       <c r="C10" s="72" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="109" t="s">
+      <c r="D10" s="137" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="110"/>
-      <c r="F10" s="109" t="s">
+      <c r="E10" s="138"/>
+      <c r="F10" s="137" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="111"/>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="110"/>
-      <c r="K10" s="109" t="s">
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="138"/>
+      <c r="K10" s="137" t="s">
         <v>103</v>
       </c>
-      <c r="L10" s="111"/>
-      <c r="M10" s="110"/>
+      <c r="L10" s="139"/>
+      <c r="M10" s="138"/>
     </row>
     <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="107" t="s">
+      <c r="B11" s="147" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="101" t="s">
+      <c r="C11" s="141" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="98" t="s">
+      <c r="D11" s="130" t="s">
         <v>78</v>
       </c>
-      <c r="E11" s="100"/>
-      <c r="F11" s="95" t="s">
+      <c r="E11" s="132"/>
+      <c r="F11" s="134" t="s">
         <v>92</v>
       </c>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="97"/>
-      <c r="K11" s="98" t="s">
+      <c r="G11" s="135"/>
+      <c r="H11" s="135"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="136"/>
+      <c r="K11" s="130" t="s">
         <v>102</v>
       </c>
-      <c r="L11" s="99"/>
-      <c r="M11" s="100"/>
+      <c r="L11" s="131"/>
+      <c r="M11" s="132"/>
     </row>
     <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="107"/>
-      <c r="C12" s="102"/>
-      <c r="D12" s="98" t="s">
+      <c r="B12" s="147"/>
+      <c r="C12" s="142"/>
+      <c r="D12" s="130" t="s">
         <v>86</v>
       </c>
-      <c r="E12" s="100"/>
-      <c r="F12" s="95" t="s">
+      <c r="E12" s="132"/>
+      <c r="F12" s="134" t="s">
         <v>89</v>
       </c>
-      <c r="G12" s="96"/>
-      <c r="H12" s="96"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="97"/>
-      <c r="K12" s="98"/>
-      <c r="L12" s="99"/>
-      <c r="M12" s="100"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="135"/>
+      <c r="I12" s="135"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="131"/>
+      <c r="M12" s="132"/>
     </row>
     <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="107"/>
-      <c r="C13" s="102"/>
-      <c r="D13" s="98" t="s">
+      <c r="B13" s="147"/>
+      <c r="C13" s="142"/>
+      <c r="D13" s="130" t="s">
         <v>87</v>
       </c>
-      <c r="E13" s="100"/>
-      <c r="F13" s="95" t="s">
+      <c r="E13" s="132"/>
+      <c r="F13" s="134" t="s">
         <v>90</v>
       </c>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="97"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="135"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="136"/>
       <c r="K13" s="63"/>
       <c r="L13" s="64"/>
       <c r="M13" s="65"/>
     </row>
     <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B14" s="107"/>
-      <c r="C14" s="103"/>
-      <c r="D14" s="98" t="s">
+      <c r="B14" s="147"/>
+      <c r="C14" s="143"/>
+      <c r="D14" s="130" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="100"/>
-      <c r="F14" s="95" t="s">
+      <c r="E14" s="132"/>
+      <c r="F14" s="134" t="s">
         <v>91</v>
       </c>
-      <c r="G14" s="96"/>
-      <c r="H14" s="96"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="97"/>
+      <c r="G14" s="135"/>
+      <c r="H14" s="135"/>
+      <c r="I14" s="135"/>
+      <c r="J14" s="136"/>
       <c r="K14" s="63"/>
       <c r="L14" s="64"/>
       <c r="M14" s="65"/>
     </row>
     <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B15" s="107"/>
-      <c r="C15" s="101" t="s">
+      <c r="B15" s="147"/>
+      <c r="C15" s="141" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="98" t="s">
+      <c r="D15" s="130" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="100"/>
-      <c r="F15" s="95" t="s">
+      <c r="E15" s="132"/>
+      <c r="F15" s="134" t="s">
         <v>93</v>
       </c>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="97"/>
-      <c r="K15" s="98"/>
-      <c r="L15" s="99"/>
-      <c r="M15" s="100"/>
+      <c r="G15" s="135"/>
+      <c r="H15" s="135"/>
+      <c r="I15" s="135"/>
+      <c r="J15" s="136"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="131"/>
+      <c r="M15" s="132"/>
     </row>
     <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B16" s="107"/>
-      <c r="C16" s="102"/>
-      <c r="D16" s="98" t="s">
+      <c r="B16" s="147"/>
+      <c r="C16" s="142"/>
+      <c r="D16" s="130" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="100"/>
-      <c r="F16" s="95" t="s">
+      <c r="E16" s="132"/>
+      <c r="F16" s="134" t="s">
         <v>97</v>
       </c>
-      <c r="G16" s="96"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="97"/>
-      <c r="K16" s="98"/>
-      <c r="L16" s="99"/>
-      <c r="M16" s="100"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135"/>
+      <c r="I16" s="135"/>
+      <c r="J16" s="136"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="131"/>
+      <c r="M16" s="132"/>
     </row>
     <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B17" s="107"/>
-      <c r="C17" s="102"/>
-      <c r="D17" s="98" t="s">
+      <c r="B17" s="147"/>
+      <c r="C17" s="142"/>
+      <c r="D17" s="130" t="s">
         <v>95</v>
       </c>
-      <c r="E17" s="100"/>
-      <c r="F17" s="95" t="s">
+      <c r="E17" s="132"/>
+      <c r="F17" s="134" t="s">
         <v>98</v>
       </c>
-      <c r="G17" s="96"/>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96"/>
-      <c r="K17" s="108"/>
-      <c r="L17" s="108"/>
-      <c r="M17" s="108"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="135"/>
+      <c r="I17" s="135"/>
+      <c r="J17" s="135"/>
+      <c r="K17" s="133"/>
+      <c r="L17" s="133"/>
+      <c r="M17" s="133"/>
     </row>
     <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B18" s="107"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="98" t="s">
+      <c r="B18" s="147"/>
+      <c r="C18" s="143"/>
+      <c r="D18" s="130" t="s">
         <v>96</v>
       </c>
-      <c r="E18" s="100"/>
-      <c r="F18" s="95" t="s">
+      <c r="E18" s="132"/>
+      <c r="F18" s="134" t="s">
         <v>99</v>
       </c>
-      <c r="G18" s="96"/>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="96"/>
-      <c r="K18" s="108"/>
-      <c r="L18" s="108"/>
-      <c r="M18" s="108"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="135"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="135"/>
+      <c r="K18" s="133"/>
+      <c r="L18" s="133"/>
+      <c r="M18" s="133"/>
     </row>
     <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B19" s="107"/>
+      <c r="B19" s="147"/>
       <c r="C19" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="98" t="s">
+      <c r="D19" s="130" t="s">
         <v>100</v>
       </c>
-      <c r="E19" s="100"/>
-      <c r="F19" s="112" t="s">
+      <c r="E19" s="132"/>
+      <c r="F19" s="140" t="s">
         <v>101</v>
       </c>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="108"/>
-      <c r="L19" s="108"/>
-      <c r="M19" s="108"/>
+      <c r="G19" s="140"/>
+      <c r="H19" s="140"/>
+      <c r="I19" s="140"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="133"/>
+      <c r="L19" s="133"/>
+      <c r="M19" s="133"/>
     </row>
     <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B20" s="107"/>
+      <c r="B20" s="147"/>
       <c r="C20" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="98" t="s">
+      <c r="D20" s="130" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="100"/>
-      <c r="F20" s="112" t="s">
+      <c r="E20" s="132"/>
+      <c r="F20" s="140" t="s">
         <v>80</v>
       </c>
-      <c r="G20" s="112"/>
-      <c r="H20" s="112"/>
-      <c r="I20" s="112"/>
-      <c r="J20" s="112"/>
-      <c r="K20" s="108"/>
-      <c r="L20" s="108"/>
-      <c r="M20" s="108"/>
+      <c r="G20" s="140"/>
+      <c r="H20" s="140"/>
+      <c r="I20" s="140"/>
+      <c r="J20" s="140"/>
+      <c r="K20" s="133"/>
+      <c r="L20" s="133"/>
+      <c r="M20" s="133"/>
     </row>
     <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="107"/>
+      <c r="B21" s="147"/>
       <c r="C21" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="D21" s="98" t="s">
+      <c r="D21" s="130" t="s">
         <v>81</v>
       </c>
-      <c r="E21" s="100"/>
-      <c r="F21" s="112" t="s">
+      <c r="E21" s="132"/>
+      <c r="F21" s="140" t="s">
         <v>81</v>
       </c>
-      <c r="G21" s="112"/>
-      <c r="H21" s="112"/>
-      <c r="I21" s="112"/>
-      <c r="J21" s="112"/>
-      <c r="K21" s="108"/>
-      <c r="L21" s="108"/>
-      <c r="M21" s="108"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="140"/>
+      <c r="I21" s="140"/>
+      <c r="J21" s="140"/>
+      <c r="K21" s="133"/>
+      <c r="L21" s="133"/>
+      <c r="M21" s="133"/>
     </row>
     <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B22" s="107"/>
+      <c r="B22" s="147"/>
       <c r="C22" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="98" t="s">
+      <c r="D22" s="130" t="s">
         <v>82</v>
       </c>
-      <c r="E22" s="100"/>
-      <c r="F22" s="112" t="s">
+      <c r="E22" s="132"/>
+      <c r="F22" s="140" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="112"/>
-      <c r="H22" s="112"/>
-      <c r="I22" s="112"/>
-      <c r="J22" s="112"/>
-      <c r="K22" s="108"/>
-      <c r="L22" s="108"/>
-      <c r="M22" s="108"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="140"/>
+      <c r="I22" s="140"/>
+      <c r="J22" s="140"/>
+      <c r="K22" s="133"/>
+      <c r="L22" s="133"/>
+      <c r="M22" s="133"/>
     </row>
     <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B23" s="104" t="s">
+      <c r="B23" s="144" t="s">
         <v>105</v>
       </c>
-      <c r="C23" s="101" t="s">
+      <c r="C23" s="141" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="98" t="s">
+      <c r="D23" s="130" t="s">
         <v>115</v>
       </c>
-      <c r="E23" s="100"/>
-      <c r="F23" s="95" t="s">
+      <c r="E23" s="132"/>
+      <c r="F23" s="134" t="s">
         <v>110</v>
       </c>
-      <c r="G23" s="96"/>
-      <c r="H23" s="96"/>
-      <c r="I23" s="96"/>
-      <c r="J23" s="97"/>
-      <c r="K23" s="108" t="s">
+      <c r="G23" s="135"/>
+      <c r="H23" s="135"/>
+      <c r="I23" s="135"/>
+      <c r="J23" s="136"/>
+      <c r="K23" s="133" t="s">
         <v>118</v>
       </c>
-      <c r="L23" s="108"/>
-      <c r="M23" s="108"/>
+      <c r="L23" s="133"/>
+      <c r="M23" s="133"/>
     </row>
     <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B24" s="105"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="98" t="s">
+      <c r="B24" s="145"/>
+      <c r="C24" s="143"/>
+      <c r="D24" s="130" t="s">
         <v>116</v>
       </c>
-      <c r="E24" s="100"/>
-      <c r="F24" s="95" t="s">
+      <c r="E24" s="132"/>
+      <c r="F24" s="134" t="s">
         <v>117</v>
       </c>
-      <c r="G24" s="96"/>
-      <c r="H24" s="96"/>
-      <c r="I24" s="96"/>
-      <c r="J24" s="97"/>
-      <c r="K24" s="98"/>
-      <c r="L24" s="99"/>
-      <c r="M24" s="100"/>
+      <c r="G24" s="135"/>
+      <c r="H24" s="135"/>
+      <c r="I24" s="135"/>
+      <c r="J24" s="136"/>
+      <c r="K24" s="130"/>
+      <c r="L24" s="131"/>
+      <c r="M24" s="132"/>
     </row>
     <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B25" s="105"/>
-      <c r="C25" s="101" t="s">
+      <c r="B25" s="145"/>
+      <c r="C25" s="141" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="98" t="s">
+      <c r="D25" s="130" t="s">
         <v>120</v>
       </c>
-      <c r="E25" s="100"/>
-      <c r="F25" s="95" t="s">
+      <c r="E25" s="132"/>
+      <c r="F25" s="134" t="s">
         <v>111</v>
       </c>
-      <c r="G25" s="96"/>
-      <c r="H25" s="96"/>
-      <c r="I25" s="96"/>
-      <c r="J25" s="97"/>
-      <c r="K25" s="108"/>
-      <c r="L25" s="108"/>
-      <c r="M25" s="108"/>
+      <c r="G25" s="135"/>
+      <c r="H25" s="135"/>
+      <c r="I25" s="135"/>
+      <c r="J25" s="136"/>
+      <c r="K25" s="133"/>
+      <c r="L25" s="133"/>
+      <c r="M25" s="133"/>
     </row>
     <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B26" s="105"/>
-      <c r="C26" s="103"/>
-      <c r="D26" s="98" t="s">
+      <c r="B26" s="145"/>
+      <c r="C26" s="143"/>
+      <c r="D26" s="130" t="s">
         <v>119</v>
       </c>
-      <c r="E26" s="100"/>
-      <c r="F26" s="95" t="s">
+      <c r="E26" s="132"/>
+      <c r="F26" s="134" t="s">
         <v>121</v>
       </c>
-      <c r="G26" s="96"/>
-      <c r="H26" s="96"/>
-      <c r="I26" s="96"/>
-      <c r="J26" s="97"/>
-      <c r="K26" s="98"/>
-      <c r="L26" s="99"/>
-      <c r="M26" s="100"/>
+      <c r="G26" s="135"/>
+      <c r="H26" s="135"/>
+      <c r="I26" s="135"/>
+      <c r="J26" s="136"/>
+      <c r="K26" s="130"/>
+      <c r="L26" s="131"/>
+      <c r="M26" s="132"/>
     </row>
     <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B27" s="105"/>
+      <c r="B27" s="145"/>
       <c r="C27" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="98" t="s">
+      <c r="D27" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="E27" s="100"/>
-      <c r="F27" s="95" t="s">
+      <c r="E27" s="132"/>
+      <c r="F27" s="134" t="s">
         <v>109</v>
       </c>
-      <c r="G27" s="96"/>
-      <c r="H27" s="96"/>
-      <c r="I27" s="96"/>
-      <c r="J27" s="97"/>
-      <c r="K27" s="108"/>
-      <c r="L27" s="108"/>
-      <c r="M27" s="108"/>
+      <c r="G27" s="135"/>
+      <c r="H27" s="135"/>
+      <c r="I27" s="135"/>
+      <c r="J27" s="136"/>
+      <c r="K27" s="133"/>
+      <c r="L27" s="133"/>
+      <c r="M27" s="133"/>
     </row>
     <row r="28" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B28" s="105"/>
-      <c r="C28" s="101" t="s">
+      <c r="B28" s="145"/>
+      <c r="C28" s="141" t="s">
         <v>100</v>
       </c>
-      <c r="D28" s="98" t="s">
+      <c r="D28" s="130" t="s">
         <v>123</v>
       </c>
-      <c r="E28" s="100"/>
-      <c r="F28" s="95" t="s">
+      <c r="E28" s="132"/>
+      <c r="F28" s="134" t="s">
         <v>112</v>
       </c>
-      <c r="G28" s="96"/>
-      <c r="H28" s="96"/>
-      <c r="I28" s="96"/>
-      <c r="J28" s="97"/>
-      <c r="K28" s="108"/>
-      <c r="L28" s="108"/>
-      <c r="M28" s="108"/>
+      <c r="G28" s="135"/>
+      <c r="H28" s="135"/>
+      <c r="I28" s="135"/>
+      <c r="J28" s="136"/>
+      <c r="K28" s="133"/>
+      <c r="L28" s="133"/>
+      <c r="M28" s="133"/>
     </row>
     <row r="29" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B29" s="105"/>
-      <c r="C29" s="103"/>
-      <c r="D29" s="98" t="s">
+      <c r="B29" s="145"/>
+      <c r="C29" s="143"/>
+      <c r="D29" s="130" t="s">
         <v>124</v>
       </c>
-      <c r="E29" s="100"/>
-      <c r="F29" s="95" t="s">
+      <c r="E29" s="132"/>
+      <c r="F29" s="134" t="s">
         <v>122</v>
       </c>
-      <c r="G29" s="96"/>
-      <c r="H29" s="96"/>
-      <c r="I29" s="96"/>
-      <c r="J29" s="97"/>
-      <c r="K29" s="108"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="108"/>
+      <c r="G29" s="135"/>
+      <c r="H29" s="135"/>
+      <c r="I29" s="135"/>
+      <c r="J29" s="136"/>
+      <c r="K29" s="133"/>
+      <c r="L29" s="133"/>
+      <c r="M29" s="133"/>
     </row>
     <row r="30" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B30" s="105"/>
+      <c r="B30" s="145"/>
       <c r="C30" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="D30" s="98" t="s">
+      <c r="D30" s="130" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="100"/>
-      <c r="F30" s="95" t="s">
+      <c r="E30" s="132"/>
+      <c r="F30" s="134" t="s">
         <v>113</v>
       </c>
-      <c r="G30" s="96"/>
-      <c r="H30" s="96"/>
-      <c r="I30" s="96"/>
-      <c r="J30" s="97"/>
-      <c r="K30" s="108"/>
-      <c r="L30" s="108"/>
-      <c r="M30" s="108"/>
+      <c r="G30" s="135"/>
+      <c r="H30" s="135"/>
+      <c r="I30" s="135"/>
+      <c r="J30" s="136"/>
+      <c r="K30" s="133"/>
+      <c r="L30" s="133"/>
+      <c r="M30" s="133"/>
     </row>
     <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B31" s="106"/>
+      <c r="B31" s="146"/>
       <c r="C31" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="98" t="s">
+      <c r="D31" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="E31" s="100"/>
-      <c r="F31" s="95" t="s">
+      <c r="E31" s="132"/>
+      <c r="F31" s="134" t="s">
         <v>114</v>
       </c>
-      <c r="G31" s="96"/>
-      <c r="H31" s="96"/>
-      <c r="I31" s="96"/>
-      <c r="J31" s="97"/>
-      <c r="K31" s="108"/>
-      <c r="L31" s="108"/>
-      <c r="M31" s="108"/>
+      <c r="G31" s="135"/>
+      <c r="H31" s="135"/>
+      <c r="I31" s="135"/>
+      <c r="J31" s="136"/>
+      <c r="K31" s="133"/>
+      <c r="L31" s="133"/>
+      <c r="M31" s="133"/>
     </row>
     <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B32" s="104" t="s">
+      <c r="B32" s="144" t="s">
         <v>125</v>
       </c>
       <c r="C32" s="66" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="98" t="s">
+      <c r="D32" s="130" t="s">
         <v>134</v>
       </c>
-      <c r="E32" s="100"/>
-      <c r="F32" s="95" t="s">
+      <c r="E32" s="132"/>
+      <c r="F32" s="134" t="s">
         <v>147</v>
       </c>
-      <c r="G32" s="96"/>
-      <c r="H32" s="96"/>
-      <c r="I32" s="96"/>
-      <c r="J32" s="97"/>
-      <c r="K32" s="98" t="s">
+      <c r="G32" s="135"/>
+      <c r="H32" s="135"/>
+      <c r="I32" s="135"/>
+      <c r="J32" s="136"/>
+      <c r="K32" s="130" t="s">
         <v>146</v>
       </c>
-      <c r="L32" s="99"/>
-      <c r="M32" s="100"/>
+      <c r="L32" s="131"/>
+      <c r="M32" s="132"/>
     </row>
     <row r="33" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B33" s="105"/>
+      <c r="B33" s="145"/>
       <c r="C33" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="D33" s="98" t="s">
+      <c r="D33" s="130" t="s">
         <v>135</v>
       </c>
-      <c r="E33" s="100"/>
-      <c r="F33" s="95" t="s">
+      <c r="E33" s="132"/>
+      <c r="F33" s="134" t="s">
         <v>148</v>
       </c>
-      <c r="G33" s="96"/>
-      <c r="H33" s="96"/>
-      <c r="I33" s="96"/>
-      <c r="J33" s="97"/>
-      <c r="K33" s="98"/>
-      <c r="L33" s="99"/>
-      <c r="M33" s="100"/>
+      <c r="G33" s="135"/>
+      <c r="H33" s="135"/>
+      <c r="I33" s="135"/>
+      <c r="J33" s="136"/>
+      <c r="K33" s="130"/>
+      <c r="L33" s="131"/>
+      <c r="M33" s="132"/>
     </row>
     <row r="34" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B34" s="105"/>
+      <c r="B34" s="145"/>
       <c r="C34" s="66" t="s">
         <v>128</v>
       </c>
-      <c r="D34" s="98" t="s">
+      <c r="D34" s="130" t="s">
         <v>136</v>
       </c>
-      <c r="E34" s="100"/>
-      <c r="F34" s="95" t="s">
+      <c r="E34" s="132"/>
+      <c r="F34" s="134" t="s">
         <v>149</v>
       </c>
-      <c r="G34" s="96"/>
-      <c r="H34" s="96"/>
-      <c r="I34" s="96"/>
-      <c r="J34" s="97"/>
-      <c r="K34" s="98"/>
-      <c r="L34" s="99"/>
-      <c r="M34" s="100"/>
+      <c r="G34" s="135"/>
+      <c r="H34" s="135"/>
+      <c r="I34" s="135"/>
+      <c r="J34" s="136"/>
+      <c r="K34" s="130"/>
+      <c r="L34" s="131"/>
+      <c r="M34" s="132"/>
     </row>
     <row r="35" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B35" s="105"/>
+      <c r="B35" s="145"/>
       <c r="C35" s="66" t="s">
         <v>129</v>
       </c>
-      <c r="D35" s="98" t="s">
+      <c r="D35" s="130" t="s">
         <v>137</v>
       </c>
-      <c r="E35" s="100"/>
-      <c r="F35" s="95" t="s">
+      <c r="E35" s="132"/>
+      <c r="F35" s="134" t="s">
         <v>150</v>
       </c>
-      <c r="G35" s="96"/>
-      <c r="H35" s="96"/>
-      <c r="I35" s="96"/>
-      <c r="J35" s="97"/>
-      <c r="K35" s="98"/>
-      <c r="L35" s="99"/>
-      <c r="M35" s="100"/>
+      <c r="G35" s="135"/>
+      <c r="H35" s="135"/>
+      <c r="I35" s="135"/>
+      <c r="J35" s="136"/>
+      <c r="K35" s="130"/>
+      <c r="L35" s="131"/>
+      <c r="M35" s="132"/>
     </row>
     <row r="36" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B36" s="105"/>
+      <c r="B36" s="145"/>
       <c r="C36" s="66" t="s">
         <v>131</v>
       </c>
-      <c r="D36" s="98" t="s">
+      <c r="D36" s="130" t="s">
         <v>138</v>
       </c>
-      <c r="E36" s="100"/>
-      <c r="F36" s="95" t="s">
+      <c r="E36" s="132"/>
+      <c r="F36" s="134" t="s">
         <v>151</v>
       </c>
-      <c r="G36" s="96"/>
-      <c r="H36" s="96"/>
-      <c r="I36" s="96"/>
-      <c r="J36" s="97"/>
-      <c r="K36" s="98"/>
-      <c r="L36" s="99"/>
-      <c r="M36" s="100"/>
+      <c r="G36" s="135"/>
+      <c r="H36" s="135"/>
+      <c r="I36" s="135"/>
+      <c r="J36" s="136"/>
+      <c r="K36" s="130"/>
+      <c r="L36" s="131"/>
+      <c r="M36" s="132"/>
     </row>
     <row r="37" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B37" s="105"/>
+      <c r="B37" s="145"/>
       <c r="C37" s="66" t="s">
         <v>139</v>
       </c>
-      <c r="D37" s="98" t="s">
+      <c r="D37" s="130" t="s">
         <v>142</v>
       </c>
-      <c r="E37" s="100"/>
-      <c r="F37" s="95" t="s">
+      <c r="E37" s="132"/>
+      <c r="F37" s="134" t="s">
         <v>148</v>
       </c>
-      <c r="G37" s="96"/>
-      <c r="H37" s="96"/>
-      <c r="I37" s="96"/>
-      <c r="J37" s="97"/>
-      <c r="K37" s="98"/>
-      <c r="L37" s="99"/>
-      <c r="M37" s="100"/>
+      <c r="G37" s="135"/>
+      <c r="H37" s="135"/>
+      <c r="I37" s="135"/>
+      <c r="J37" s="136"/>
+      <c r="K37" s="130"/>
+      <c r="L37" s="131"/>
+      <c r="M37" s="132"/>
     </row>
     <row r="38" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B38" s="105"/>
+      <c r="B38" s="145"/>
       <c r="C38" s="66" t="s">
         <v>140</v>
       </c>
-      <c r="D38" s="98" t="s">
+      <c r="D38" s="130" t="s">
         <v>143</v>
       </c>
-      <c r="E38" s="100"/>
-      <c r="F38" s="95" t="s">
+      <c r="E38" s="132"/>
+      <c r="F38" s="134" t="s">
         <v>149</v>
       </c>
-      <c r="G38" s="96"/>
-      <c r="H38" s="96"/>
-      <c r="I38" s="96"/>
-      <c r="J38" s="97"/>
-      <c r="K38" s="98"/>
-      <c r="L38" s="99"/>
-      <c r="M38" s="100"/>
+      <c r="G38" s="135"/>
+      <c r="H38" s="135"/>
+      <c r="I38" s="135"/>
+      <c r="J38" s="136"/>
+      <c r="K38" s="130"/>
+      <c r="L38" s="131"/>
+      <c r="M38" s="132"/>
     </row>
     <row r="39" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B39" s="105"/>
+      <c r="B39" s="145"/>
       <c r="C39" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="D39" s="98" t="s">
+      <c r="D39" s="130" t="s">
         <v>144</v>
       </c>
-      <c r="E39" s="100"/>
-      <c r="F39" s="95" t="s">
+      <c r="E39" s="132"/>
+      <c r="F39" s="134" t="s">
         <v>150</v>
       </c>
-      <c r="G39" s="96"/>
-      <c r="H39" s="96"/>
-      <c r="I39" s="96"/>
-      <c r="J39" s="97"/>
-      <c r="K39" s="98"/>
-      <c r="L39" s="99"/>
-      <c r="M39" s="100"/>
+      <c r="G39" s="135"/>
+      <c r="H39" s="135"/>
+      <c r="I39" s="135"/>
+      <c r="J39" s="136"/>
+      <c r="K39" s="130"/>
+      <c r="L39" s="131"/>
+      <c r="M39" s="132"/>
     </row>
     <row r="40" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B40" s="105"/>
+      <c r="B40" s="145"/>
       <c r="C40" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="D40" s="98" t="s">
+      <c r="D40" s="130" t="s">
         <v>145</v>
       </c>
-      <c r="E40" s="100"/>
-      <c r="F40" s="95" t="s">
+      <c r="E40" s="132"/>
+      <c r="F40" s="134" t="s">
         <v>151</v>
       </c>
-      <c r="G40" s="96"/>
-      <c r="H40" s="96"/>
-      <c r="I40" s="96"/>
-      <c r="J40" s="97"/>
-      <c r="K40" s="98"/>
-      <c r="L40" s="99"/>
-      <c r="M40" s="100"/>
+      <c r="G40" s="135"/>
+      <c r="H40" s="135"/>
+      <c r="I40" s="135"/>
+      <c r="J40" s="136"/>
+      <c r="K40" s="130"/>
+      <c r="L40" s="131"/>
+      <c r="M40" s="132"/>
     </row>
     <row r="41" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B41" s="106"/>
+      <c r="B41" s="146"/>
       <c r="C41" s="69" t="s">
         <v>450</v>
       </c>
-      <c r="D41" s="98" t="s">
+      <c r="D41" s="130" t="s">
         <v>132</v>
       </c>
-      <c r="E41" s="100"/>
-      <c r="F41" s="95" t="s">
+      <c r="E41" s="132"/>
+      <c r="F41" s="134" t="s">
         <v>133</v>
       </c>
-      <c r="G41" s="96"/>
-      <c r="H41" s="96"/>
-      <c r="I41" s="96"/>
-      <c r="J41" s="97"/>
-      <c r="K41" s="98"/>
-      <c r="L41" s="99"/>
-      <c r="M41" s="100"/>
+      <c r="G41" s="135"/>
+      <c r="H41" s="135"/>
+      <c r="I41" s="135"/>
+      <c r="J41" s="136"/>
+      <c r="K41" s="130"/>
+      <c r="L41" s="131"/>
+      <c r="M41" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="102">
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="F32:J32"/>
+    <mergeCell ref="F33:J33"/>
+    <mergeCell ref="F34:J34"/>
+    <mergeCell ref="F35:J35"/>
+    <mergeCell ref="F36:J36"/>
+    <mergeCell ref="F41:J41"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="K33:M33"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="F37:J37"/>
+    <mergeCell ref="F38:J38"/>
+    <mergeCell ref="F39:J39"/>
+    <mergeCell ref="F40:J40"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="B32:B41"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="B23:B31"/>
+    <mergeCell ref="B11:B22"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="K28:M28"/>
+    <mergeCell ref="K30:M30"/>
+    <mergeCell ref="K31:M31"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:J24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:J26"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:J29"/>
+    <mergeCell ref="K29:M29"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="F27:J27"/>
     <mergeCell ref="F28:J28"/>
     <mergeCell ref="F30:J30"/>
     <mergeCell ref="F31:J31"/>
@@ -6728,68 +6774,22 @@
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="F21:J21"/>
     <mergeCell ref="F22:J22"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="K28:M28"/>
-    <mergeCell ref="K30:M30"/>
-    <mergeCell ref="K31:M31"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:J24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:J26"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:J29"/>
-    <mergeCell ref="K29:M29"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F23:J23"/>
-    <mergeCell ref="F25:J25"/>
-    <mergeCell ref="F27:J27"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="B32:B41"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="B23:B31"/>
-    <mergeCell ref="B11:B22"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="F32:J32"/>
-    <mergeCell ref="F33:J33"/>
-    <mergeCell ref="F34:J34"/>
-    <mergeCell ref="F35:J35"/>
-    <mergeCell ref="F36:J36"/>
-    <mergeCell ref="F41:J41"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="K33:M33"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="F37:J37"/>
-    <mergeCell ref="F38:J38"/>
-    <mergeCell ref="F39:J39"/>
-    <mergeCell ref="F40:J40"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="K22:M22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6964,310 +6964,310 @@
       <c r="C10" s="72" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="109" t="s">
+      <c r="D10" s="137" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="110"/>
-      <c r="F10" s="119" t="s">
+      <c r="E10" s="138"/>
+      <c r="F10" s="148" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="119"/>
-      <c r="K10" s="109" t="s">
+      <c r="G10" s="148"/>
+      <c r="H10" s="148"/>
+      <c r="I10" s="148"/>
+      <c r="J10" s="148"/>
+      <c r="K10" s="137" t="s">
         <v>103</v>
       </c>
-      <c r="L10" s="111"/>
-      <c r="M10" s="110"/>
+      <c r="L10" s="139"/>
+      <c r="M10" s="138"/>
     </row>
     <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="104" t="s">
+      <c r="B11" s="144" t="s">
         <v>155</v>
       </c>
       <c r="C11" s="51" t="s">
         <v>156</v>
       </c>
-      <c r="D11" s="98" t="s">
+      <c r="D11" s="130" t="s">
         <v>158</v>
       </c>
-      <c r="E11" s="100"/>
-      <c r="F11" s="112" t="s">
+      <c r="E11" s="132"/>
+      <c r="F11" s="140" t="s">
         <v>438</v>
       </c>
-      <c r="G11" s="112"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="112"/>
-      <c r="J11" s="112"/>
-      <c r="K11" s="108" t="s">
+      <c r="G11" s="140"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="140"/>
+      <c r="K11" s="133" t="s">
         <v>160</v>
       </c>
-      <c r="L11" s="108"/>
-      <c r="M11" s="108"/>
+      <c r="L11" s="133"/>
+      <c r="M11" s="133"/>
     </row>
     <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="106"/>
+      <c r="B12" s="146"/>
       <c r="C12" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="D12" s="98" t="s">
+      <c r="D12" s="130" t="s">
         <v>159</v>
       </c>
-      <c r="E12" s="100"/>
-      <c r="F12" s="112" t="s">
+      <c r="E12" s="132"/>
+      <c r="F12" s="140" t="s">
         <v>439</v>
       </c>
-      <c r="G12" s="112"/>
-      <c r="H12" s="112"/>
-      <c r="I12" s="112"/>
-      <c r="J12" s="112"/>
-      <c r="K12" s="98"/>
-      <c r="L12" s="99"/>
-      <c r="M12" s="100"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="140"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="131"/>
+      <c r="M12" s="132"/>
     </row>
     <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="107" t="s">
+      <c r="B13" s="147" t="s">
         <v>161</v>
       </c>
       <c r="C13" s="51" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="98" t="s">
+      <c r="D13" s="130" t="s">
         <v>164</v>
       </c>
-      <c r="E13" s="100"/>
-      <c r="F13" s="95" t="s">
+      <c r="E13" s="132"/>
+      <c r="F13" s="134" t="s">
         <v>166</v>
       </c>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="98" t="s">
+      <c r="G13" s="135"/>
+      <c r="H13" s="135"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="135"/>
+      <c r="K13" s="130" t="s">
         <v>168</v>
       </c>
-      <c r="L13" s="99"/>
-      <c r="M13" s="100"/>
+      <c r="L13" s="131"/>
+      <c r="M13" s="132"/>
     </row>
     <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B14" s="107"/>
+      <c r="B14" s="147"/>
       <c r="C14" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="D14" s="98" t="s">
+      <c r="D14" s="130" t="s">
         <v>165</v>
       </c>
-      <c r="E14" s="100"/>
-      <c r="F14" s="95" t="s">
+      <c r="E14" s="132"/>
+      <c r="F14" s="134" t="s">
         <v>167</v>
       </c>
-      <c r="G14" s="96"/>
-      <c r="H14" s="96"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="96"/>
-      <c r="K14" s="98" t="s">
+      <c r="G14" s="135"/>
+      <c r="H14" s="135"/>
+      <c r="I14" s="135"/>
+      <c r="J14" s="135"/>
+      <c r="K14" s="130" t="s">
         <v>169</v>
       </c>
-      <c r="L14" s="99"/>
-      <c r="M14" s="100"/>
+      <c r="L14" s="131"/>
+      <c r="M14" s="132"/>
     </row>
     <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B15" s="107" t="s">
+      <c r="B15" s="147" t="s">
         <v>170</v>
       </c>
       <c r="C15" s="66" t="s">
         <v>440</v>
       </c>
-      <c r="D15" s="98" t="s">
+      <c r="D15" s="130" t="s">
         <v>441</v>
       </c>
-      <c r="E15" s="100"/>
-      <c r="F15" s="95" t="s">
+      <c r="E15" s="132"/>
+      <c r="F15" s="134" t="s">
         <v>442</v>
       </c>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="108" t="s">
+      <c r="G15" s="135"/>
+      <c r="H15" s="135"/>
+      <c r="I15" s="135"/>
+      <c r="J15" s="135"/>
+      <c r="K15" s="133" t="s">
         <v>443</v>
       </c>
-      <c r="L15" s="108"/>
-      <c r="M15" s="108"/>
+      <c r="L15" s="133"/>
+      <c r="M15" s="133"/>
     </row>
     <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B16" s="107"/>
+      <c r="B16" s="147"/>
       <c r="C16" s="66" t="s">
         <v>444</v>
       </c>
-      <c r="D16" s="98" t="s">
+      <c r="D16" s="130" t="s">
         <v>445</v>
       </c>
-      <c r="E16" s="100"/>
-      <c r="F16" s="95" t="s">
+      <c r="E16" s="132"/>
+      <c r="F16" s="134" t="s">
         <v>446</v>
       </c>
-      <c r="G16" s="96"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="96"/>
-      <c r="K16" s="108" t="s">
+      <c r="G16" s="135"/>
+      <c r="H16" s="135"/>
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="133" t="s">
         <v>447</v>
       </c>
-      <c r="L16" s="108"/>
-      <c r="M16" s="108"/>
+      <c r="L16" s="133"/>
+      <c r="M16" s="133"/>
     </row>
     <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B17" s="107" t="s">
+      <c r="B17" s="147" t="s">
         <v>171</v>
       </c>
       <c r="C17" s="66" t="s">
         <v>172</v>
       </c>
-      <c r="D17" s="98" t="s">
+      <c r="D17" s="130" t="s">
         <v>192</v>
       </c>
-      <c r="E17" s="100"/>
-      <c r="F17" s="95" t="s">
+      <c r="E17" s="132"/>
+      <c r="F17" s="134" t="s">
         <v>196</v>
       </c>
-      <c r="G17" s="96"/>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96"/>
-      <c r="K17" s="113" t="s">
+      <c r="G17" s="135"/>
+      <c r="H17" s="135"/>
+      <c r="I17" s="135"/>
+      <c r="J17" s="135"/>
+      <c r="K17" s="149" t="s">
         <v>448</v>
       </c>
-      <c r="L17" s="114"/>
-      <c r="M17" s="115"/>
+      <c r="L17" s="150"/>
+      <c r="M17" s="151"/>
     </row>
     <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B18" s="107"/>
+      <c r="B18" s="147"/>
       <c r="C18" s="66" t="s">
         <v>173</v>
       </c>
-      <c r="D18" s="98" t="s">
+      <c r="D18" s="130" t="s">
         <v>193</v>
       </c>
-      <c r="E18" s="100"/>
-      <c r="F18" s="95" t="s">
+      <c r="E18" s="132"/>
+      <c r="F18" s="134" t="s">
         <v>197</v>
       </c>
-      <c r="G18" s="96"/>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="96"/>
-      <c r="K18" s="116"/>
-      <c r="L18" s="117"/>
-      <c r="M18" s="118"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="135"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="135"/>
+      <c r="K18" s="152"/>
+      <c r="L18" s="153"/>
+      <c r="M18" s="154"/>
     </row>
     <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B19" s="104" t="s">
+      <c r="B19" s="144" t="s">
         <v>174</v>
       </c>
       <c r="C19" s="66" t="s">
         <v>175</v>
       </c>
-      <c r="D19" s="98" t="s">
+      <c r="D19" s="130" t="s">
         <v>194</v>
       </c>
-      <c r="E19" s="100"/>
-      <c r="F19" s="95" t="s">
+      <c r="E19" s="132"/>
+      <c r="F19" s="134" t="s">
         <v>198</v>
       </c>
-      <c r="G19" s="96"/>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="96"/>
-      <c r="K19" s="108" t="s">
+      <c r="G19" s="135"/>
+      <c r="H19" s="135"/>
+      <c r="I19" s="135"/>
+      <c r="J19" s="135"/>
+      <c r="K19" s="133" t="s">
         <v>449</v>
       </c>
-      <c r="L19" s="108"/>
-      <c r="M19" s="108"/>
+      <c r="L19" s="133"/>
+      <c r="M19" s="133"/>
     </row>
     <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B20" s="106"/>
+      <c r="B20" s="146"/>
       <c r="C20" s="66" t="s">
         <v>176</v>
       </c>
-      <c r="D20" s="98" t="s">
+      <c r="D20" s="130" t="s">
         <v>195</v>
       </c>
-      <c r="E20" s="100"/>
-      <c r="F20" s="95" t="s">
+      <c r="E20" s="132"/>
+      <c r="F20" s="134" t="s">
         <v>199</v>
       </c>
-      <c r="G20" s="96"/>
-      <c r="H20" s="96"/>
-      <c r="I20" s="96"/>
-      <c r="J20" s="96"/>
-      <c r="K20" s="108"/>
-      <c r="L20" s="108"/>
-      <c r="M20" s="108"/>
+      <c r="G20" s="135"/>
+      <c r="H20" s="135"/>
+      <c r="I20" s="135"/>
+      <c r="J20" s="135"/>
+      <c r="K20" s="133"/>
+      <c r="L20" s="133"/>
+      <c r="M20" s="133"/>
     </row>
     <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="104" t="s">
+      <c r="B21" s="144" t="s">
         <v>177</v>
       </c>
       <c r="C21" s="66" t="s">
         <v>179</v>
       </c>
-      <c r="D21" s="98" t="s">
+      <c r="D21" s="130" t="s">
         <v>181</v>
       </c>
-      <c r="E21" s="100"/>
-      <c r="F21" s="112" t="s">
+      <c r="E21" s="132"/>
+      <c r="F21" s="140" t="s">
         <v>186</v>
       </c>
-      <c r="G21" s="112"/>
-      <c r="H21" s="112"/>
-      <c r="I21" s="112"/>
-      <c r="J21" s="112"/>
-      <c r="K21" s="108"/>
-      <c r="L21" s="108"/>
-      <c r="M21" s="108"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="140"/>
+      <c r="I21" s="140"/>
+      <c r="J21" s="140"/>
+      <c r="K21" s="133"/>
+      <c r="L21" s="133"/>
+      <c r="M21" s="133"/>
     </row>
     <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B22" s="105"/>
+      <c r="B22" s="145"/>
       <c r="C22" s="66" t="s">
         <v>180</v>
       </c>
-      <c r="D22" s="98" t="s">
+      <c r="D22" s="130" t="s">
         <v>182</v>
       </c>
-      <c r="E22" s="100"/>
-      <c r="F22" s="112" t="s">
+      <c r="E22" s="132"/>
+      <c r="F22" s="140" t="s">
         <v>185</v>
       </c>
-      <c r="G22" s="112"/>
-      <c r="H22" s="112"/>
-      <c r="I22" s="112"/>
-      <c r="J22" s="112"/>
-      <c r="K22" s="108"/>
-      <c r="L22" s="108"/>
-      <c r="M22" s="108"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="140"/>
+      <c r="I22" s="140"/>
+      <c r="J22" s="140"/>
+      <c r="K22" s="133"/>
+      <c r="L22" s="133"/>
+      <c r="M22" s="133"/>
     </row>
     <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B23" s="106"/>
+      <c r="B23" s="146"/>
       <c r="C23" s="66" t="s">
         <v>184</v>
       </c>
-      <c r="D23" s="98" t="s">
+      <c r="D23" s="130" t="s">
         <v>183</v>
       </c>
-      <c r="E23" s="100"/>
-      <c r="F23" s="112" t="s">
+      <c r="E23" s="132"/>
+      <c r="F23" s="140" t="s">
         <v>187</v>
       </c>
-      <c r="G23" s="112"/>
-      <c r="H23" s="112"/>
-      <c r="I23" s="112"/>
-      <c r="J23" s="112"/>
-      <c r="K23" s="108" t="s">
+      <c r="G23" s="140"/>
+      <c r="H23" s="140"/>
+      <c r="I23" s="140"/>
+      <c r="J23" s="140"/>
+      <c r="K23" s="133" t="s">
         <v>188</v>
       </c>
-      <c r="L23" s="108"/>
-      <c r="M23" s="108"/>
+      <c r="L23" s="133"/>
+      <c r="M23" s="133"/>
     </row>
     <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B24" s="76" t="s">
@@ -7276,47 +7276,37 @@
       <c r="C24" s="66" t="s">
         <v>189</v>
       </c>
-      <c r="D24" s="98" t="s">
+      <c r="D24" s="130" t="s">
         <v>189</v>
       </c>
-      <c r="E24" s="100"/>
-      <c r="F24" s="112" t="s">
+      <c r="E24" s="132"/>
+      <c r="F24" s="140" t="s">
         <v>190</v>
       </c>
-      <c r="G24" s="112"/>
-      <c r="H24" s="112"/>
-      <c r="I24" s="112"/>
-      <c r="J24" s="112"/>
-      <c r="K24" s="108" t="s">
+      <c r="G24" s="140"/>
+      <c r="H24" s="140"/>
+      <c r="I24" s="140"/>
+      <c r="J24" s="140"/>
+      <c r="K24" s="133" t="s">
         <v>191</v>
       </c>
-      <c r="L24" s="108"/>
-      <c r="M24" s="108"/>
+      <c r="L24" s="133"/>
+      <c r="M24" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="K17:M18"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="K19:M19"/>
     <mergeCell ref="K24:M24"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="B13:B14"/>
@@ -7333,18 +7323,28 @@
     <mergeCell ref="F24:J24"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:J18"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="K17:M18"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:J21"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:J23"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:J19"/>
-    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:J13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7418,22 +7418,22 @@
       <c r="C5" s="72" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="109" t="s">
+      <c r="D5" s="137" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="110"/>
-      <c r="F5" s="119" t="s">
+      <c r="E5" s="138"/>
+      <c r="F5" s="148" t="s">
         <v>84</v>
       </c>
-      <c r="G5" s="119"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
-      <c r="J5" s="119"/>
-      <c r="K5" s="109" t="s">
+      <c r="G5" s="148"/>
+      <c r="H5" s="148"/>
+      <c r="I5" s="148"/>
+      <c r="J5" s="148"/>
+      <c r="K5" s="137" t="s">
         <v>103</v>
       </c>
-      <c r="L5" s="111"/>
-      <c r="M5" s="110"/>
+      <c r="L5" s="139"/>
+      <c r="M5" s="138"/>
     </row>
     <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B6" s="75" t="s">
@@ -7442,22 +7442,22 @@
       <c r="C6" s="51" t="s">
         <v>255</v>
       </c>
-      <c r="D6" s="98" t="s">
+      <c r="D6" s="130" t="s">
         <v>256</v>
       </c>
-      <c r="E6" s="100"/>
-      <c r="F6" s="112" t="s">
+      <c r="E6" s="132"/>
+      <c r="F6" s="140" t="s">
         <v>262</v>
       </c>
-      <c r="G6" s="112"/>
-      <c r="H6" s="112"/>
-      <c r="I6" s="112"/>
-      <c r="J6" s="112"/>
-      <c r="K6" s="108" t="s">
+      <c r="G6" s="140"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="140"/>
+      <c r="K6" s="133" t="s">
         <v>268</v>
       </c>
-      <c r="L6" s="108"/>
-      <c r="M6" s="108"/>
+      <c r="L6" s="133"/>
+      <c r="M6" s="133"/>
     </row>
     <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B7" s="73" t="s">
@@ -7466,22 +7466,22 @@
       <c r="C7" s="51" t="s">
         <v>255</v>
       </c>
-      <c r="D7" s="98" t="s">
+      <c r="D7" s="130" t="s">
         <v>257</v>
       </c>
-      <c r="E7" s="100"/>
-      <c r="F7" s="112" t="s">
+      <c r="E7" s="132"/>
+      <c r="F7" s="140" t="s">
         <v>263</v>
       </c>
-      <c r="G7" s="112"/>
-      <c r="H7" s="112"/>
-      <c r="I7" s="112"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="108" t="s">
+      <c r="G7" s="140"/>
+      <c r="H7" s="140"/>
+      <c r="I7" s="140"/>
+      <c r="J7" s="140"/>
+      <c r="K7" s="133" t="s">
         <v>269</v>
       </c>
-      <c r="L7" s="108"/>
-      <c r="M7" s="108"/>
+      <c r="L7" s="133"/>
+      <c r="M7" s="133"/>
     </row>
     <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B8" s="73" t="s">
@@ -7490,22 +7490,22 @@
       <c r="C8" s="51" t="s">
         <v>255</v>
       </c>
-      <c r="D8" s="98" t="s">
+      <c r="D8" s="130" t="s">
         <v>258</v>
       </c>
-      <c r="E8" s="100"/>
-      <c r="F8" s="112" t="s">
+      <c r="E8" s="132"/>
+      <c r="F8" s="140" t="s">
         <v>264</v>
       </c>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="108" t="s">
+      <c r="G8" s="140"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="140"/>
+      <c r="J8" s="140"/>
+      <c r="K8" s="133" t="s">
         <v>270</v>
       </c>
-      <c r="L8" s="108"/>
-      <c r="M8" s="108"/>
+      <c r="L8" s="133"/>
+      <c r="M8" s="133"/>
     </row>
     <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B9" s="73" t="s">
@@ -7514,22 +7514,22 @@
       <c r="C9" s="51" t="s">
         <v>255</v>
       </c>
-      <c r="D9" s="98" t="s">
+      <c r="D9" s="130" t="s">
         <v>259</v>
       </c>
-      <c r="E9" s="100"/>
-      <c r="F9" s="112" t="s">
+      <c r="E9" s="132"/>
+      <c r="F9" s="140" t="s">
         <v>265</v>
       </c>
-      <c r="G9" s="112"/>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="112"/>
-      <c r="K9" s="108" t="s">
+      <c r="G9" s="140"/>
+      <c r="H9" s="140"/>
+      <c r="I9" s="140"/>
+      <c r="J9" s="140"/>
+      <c r="K9" s="133" t="s">
         <v>271</v>
       </c>
-      <c r="L9" s="108"/>
-      <c r="M9" s="108"/>
+      <c r="L9" s="133"/>
+      <c r="M9" s="133"/>
     </row>
     <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B10" s="73" t="s">
@@ -7538,22 +7538,22 @@
       <c r="C10" s="51" t="s">
         <v>255</v>
       </c>
-      <c r="D10" s="98" t="s">
+      <c r="D10" s="130" t="s">
         <v>260</v>
       </c>
-      <c r="E10" s="100"/>
-      <c r="F10" s="112" t="s">
+      <c r="E10" s="132"/>
+      <c r="F10" s="140" t="s">
         <v>266</v>
       </c>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="112"/>
-      <c r="K10" s="108" t="s">
+      <c r="G10" s="140"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="140"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="133" t="s">
         <v>272</v>
       </c>
-      <c r="L10" s="108"/>
-      <c r="M10" s="108"/>
+      <c r="L10" s="133"/>
+      <c r="M10" s="133"/>
     </row>
     <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B11" s="73" t="s">
@@ -7562,25 +7562,37 @@
       <c r="C11" s="51" t="s">
         <v>255</v>
       </c>
-      <c r="D11" s="98" t="s">
+      <c r="D11" s="130" t="s">
         <v>261</v>
       </c>
-      <c r="E11" s="100"/>
-      <c r="F11" s="112" t="s">
+      <c r="E11" s="132"/>
+      <c r="F11" s="140" t="s">
         <v>267</v>
       </c>
-      <c r="G11" s="112"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="112"/>
-      <c r="J11" s="112"/>
-      <c r="K11" s="108" t="s">
+      <c r="G11" s="140"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="140"/>
+      <c r="K11" s="133" t="s">
         <v>273</v>
       </c>
-      <c r="L11" s="108"/>
-      <c r="M11" s="108"/>
+      <c r="L11" s="133"/>
+      <c r="M11" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:J8"/>
+    <mergeCell ref="K8:M8"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="F7:J7"/>
     <mergeCell ref="K7:M7"/>
@@ -7590,18 +7602,6 @@
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:J6"/>
     <mergeCell ref="K6:M6"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="K10:M10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7684,377 +7684,419 @@
       <c r="C5" s="72" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="109" t="s">
+      <c r="D5" s="137" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="110"/>
-      <c r="F5" s="119" t="s">
+      <c r="E5" s="138"/>
+      <c r="F5" s="148" t="s">
         <v>84</v>
       </c>
-      <c r="G5" s="119"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
-      <c r="J5" s="119"/>
-      <c r="K5" s="109" t="s">
+      <c r="G5" s="148"/>
+      <c r="H5" s="148"/>
+      <c r="I5" s="148"/>
+      <c r="J5" s="148"/>
+      <c r="K5" s="137" t="s">
         <v>103</v>
       </c>
-      <c r="L5" s="111"/>
-      <c r="M5" s="110"/>
+      <c r="L5" s="139"/>
+      <c r="M5" s="138"/>
     </row>
     <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B6" s="107" t="s">
+      <c r="B6" s="147" t="s">
         <v>221</v>
       </c>
       <c r="C6" s="74" t="s">
         <v>222</v>
       </c>
-      <c r="D6" s="98" t="s">
+      <c r="D6" s="130" t="s">
         <v>225</v>
       </c>
-      <c r="E6" s="100"/>
-      <c r="F6" s="112" t="s">
+      <c r="E6" s="132"/>
+      <c r="F6" s="140" t="s">
         <v>226</v>
       </c>
-      <c r="G6" s="112"/>
-      <c r="H6" s="112"/>
-      <c r="I6" s="112"/>
-      <c r="J6" s="112"/>
-      <c r="K6" s="108" t="s">
+      <c r="G6" s="140"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="140"/>
+      <c r="K6" s="133" t="s">
         <v>228</v>
       </c>
-      <c r="L6" s="108"/>
-      <c r="M6" s="108"/>
+      <c r="L6" s="133"/>
+      <c r="M6" s="133"/>
     </row>
     <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="107"/>
+      <c r="B7" s="147"/>
       <c r="C7" s="51" t="s">
         <v>223</v>
       </c>
-      <c r="D7" s="98" t="s">
+      <c r="D7" s="130" t="s">
         <v>224</v>
       </c>
-      <c r="E7" s="100"/>
-      <c r="F7" s="95" t="s">
+      <c r="E7" s="132"/>
+      <c r="F7" s="134" t="s">
         <v>227</v>
       </c>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="96"/>
-      <c r="K7" s="98"/>
-      <c r="L7" s="99"/>
-      <c r="M7" s="100"/>
+      <c r="G7" s="135"/>
+      <c r="H7" s="135"/>
+      <c r="I7" s="135"/>
+      <c r="J7" s="135"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="131"/>
+      <c r="M7" s="132"/>
     </row>
     <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="107" t="s">
+      <c r="B8" s="147" t="s">
         <v>229</v>
       </c>
       <c r="C8" s="51" t="s">
         <v>222</v>
       </c>
-      <c r="D8" s="98" t="s">
+      <c r="D8" s="130" t="s">
         <v>230</v>
       </c>
-      <c r="E8" s="100"/>
-      <c r="F8" s="112" t="s">
+      <c r="E8" s="132"/>
+      <c r="F8" s="140" t="s">
         <v>232</v>
       </c>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="98" t="s">
+      <c r="G8" s="140"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="140"/>
+      <c r="J8" s="140"/>
+      <c r="K8" s="130" t="s">
         <v>234</v>
       </c>
-      <c r="L8" s="99"/>
-      <c r="M8" s="100"/>
+      <c r="L8" s="131"/>
+      <c r="M8" s="132"/>
     </row>
     <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="107"/>
+      <c r="B9" s="147"/>
       <c r="C9" s="51" t="s">
         <v>223</v>
       </c>
-      <c r="D9" s="98" t="s">
+      <c r="D9" s="130" t="s">
         <v>231</v>
       </c>
-      <c r="E9" s="100"/>
-      <c r="F9" s="95" t="s">
+      <c r="E9" s="132"/>
+      <c r="F9" s="134" t="s">
         <v>233</v>
       </c>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
-      <c r="K9" s="98"/>
-      <c r="L9" s="99"/>
-      <c r="M9" s="100"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="135"/>
+      <c r="I9" s="135"/>
+      <c r="J9" s="135"/>
+      <c r="K9" s="130"/>
+      <c r="L9" s="131"/>
+      <c r="M9" s="132"/>
     </row>
     <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B10" s="107" t="s">
+      <c r="B10" s="147" t="s">
         <v>235</v>
       </c>
       <c r="C10" s="51" t="s">
         <v>222</v>
       </c>
-      <c r="D10" s="98" t="s">
+      <c r="D10" s="130" t="s">
         <v>236</v>
       </c>
-      <c r="E10" s="100"/>
-      <c r="F10" s="112" t="s">
+      <c r="E10" s="132"/>
+      <c r="F10" s="140" t="s">
         <v>238</v>
       </c>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="112"/>
-      <c r="K10" s="98" t="s">
+      <c r="G10" s="140"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="140"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="130" t="s">
         <v>240</v>
       </c>
-      <c r="L10" s="99"/>
-      <c r="M10" s="100"/>
+      <c r="L10" s="131"/>
+      <c r="M10" s="132"/>
     </row>
     <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="107"/>
+      <c r="B11" s="147"/>
       <c r="C11" s="51" t="s">
         <v>223</v>
       </c>
-      <c r="D11" s="98" t="s">
+      <c r="D11" s="130" t="s">
         <v>237</v>
       </c>
-      <c r="E11" s="100"/>
-      <c r="F11" s="95" t="s">
+      <c r="E11" s="132"/>
+      <c r="F11" s="134" t="s">
         <v>239</v>
       </c>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="96"/>
-      <c r="K11" s="98"/>
-      <c r="L11" s="99"/>
-      <c r="M11" s="100"/>
+      <c r="G11" s="135"/>
+      <c r="H11" s="135"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="135"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="131"/>
+      <c r="M11" s="132"/>
     </row>
     <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="107" t="s">
+      <c r="B12" s="147" t="s">
         <v>241</v>
       </c>
       <c r="C12" s="51" t="s">
         <v>222</v>
       </c>
-      <c r="D12" s="98" t="s">
+      <c r="D12" s="130" t="s">
         <v>242</v>
       </c>
-      <c r="E12" s="100"/>
-      <c r="F12" s="112" t="s">
+      <c r="E12" s="132"/>
+      <c r="F12" s="140" t="s">
         <v>244</v>
       </c>
-      <c r="G12" s="112"/>
-      <c r="H12" s="112"/>
-      <c r="I12" s="112"/>
-      <c r="J12" s="112"/>
-      <c r="K12" s="98" t="s">
+      <c r="G12" s="140"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="140"/>
+      <c r="K12" s="130" t="s">
         <v>246</v>
       </c>
-      <c r="L12" s="99"/>
-      <c r="M12" s="100"/>
+      <c r="L12" s="131"/>
+      <c r="M12" s="132"/>
     </row>
     <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="107"/>
+      <c r="B13" s="147"/>
       <c r="C13" s="51" t="s">
         <v>223</v>
       </c>
-      <c r="D13" s="98" t="s">
+      <c r="D13" s="130" t="s">
         <v>243</v>
       </c>
-      <c r="E13" s="100"/>
-      <c r="F13" s="95" t="s">
+      <c r="E13" s="132"/>
+      <c r="F13" s="134" t="s">
         <v>245</v>
       </c>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="98"/>
-      <c r="L13" s="99"/>
-      <c r="M13" s="100"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="135"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="135"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="131"/>
+      <c r="M13" s="132"/>
     </row>
     <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B14" s="107" t="s">
+      <c r="B14" s="147" t="s">
         <v>247</v>
       </c>
       <c r="C14" s="51" t="s">
         <v>222</v>
       </c>
-      <c r="D14" s="98" t="s">
+      <c r="D14" s="130" t="s">
         <v>248</v>
       </c>
-      <c r="E14" s="100"/>
-      <c r="F14" s="112" t="s">
+      <c r="E14" s="132"/>
+      <c r="F14" s="140" t="s">
         <v>101</v>
       </c>
-      <c r="G14" s="112"/>
-      <c r="H14" s="112"/>
-      <c r="I14" s="112"/>
-      <c r="J14" s="112"/>
-      <c r="K14" s="98" t="s">
+      <c r="G14" s="140"/>
+      <c r="H14" s="140"/>
+      <c r="I14" s="140"/>
+      <c r="J14" s="140"/>
+      <c r="K14" s="130" t="s">
         <v>283</v>
       </c>
-      <c r="L14" s="99"/>
-      <c r="M14" s="100"/>
+      <c r="L14" s="131"/>
+      <c r="M14" s="132"/>
     </row>
     <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B15" s="107"/>
+      <c r="B15" s="147"/>
       <c r="C15" s="51" t="s">
         <v>223</v>
       </c>
-      <c r="D15" s="98" t="s">
+      <c r="D15" s="130" t="s">
         <v>249</v>
       </c>
-      <c r="E15" s="100"/>
-      <c r="F15" s="112" t="s">
+      <c r="E15" s="132"/>
+      <c r="F15" s="140" t="s">
         <v>80</v>
       </c>
-      <c r="G15" s="112"/>
-      <c r="H15" s="112"/>
-      <c r="I15" s="112"/>
-      <c r="J15" s="112"/>
-      <c r="K15" s="98"/>
-      <c r="L15" s="99"/>
-      <c r="M15" s="100"/>
+      <c r="G15" s="140"/>
+      <c r="H15" s="140"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="140"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="131"/>
+      <c r="M15" s="132"/>
     </row>
     <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B16" s="104" t="s">
+      <c r="B16" s="144" t="s">
         <v>280</v>
       </c>
       <c r="C16" s="51" t="s">
         <v>222</v>
       </c>
-      <c r="D16" s="98" t="s">
+      <c r="D16" s="130" t="s">
         <v>281</v>
       </c>
-      <c r="E16" s="100"/>
-      <c r="F16" s="112" t="s">
+      <c r="E16" s="132"/>
+      <c r="F16" s="140" t="s">
         <v>281</v>
       </c>
-      <c r="G16" s="112"/>
-      <c r="H16" s="112"/>
-      <c r="I16" s="112"/>
-      <c r="J16" s="112"/>
-      <c r="K16" s="98" t="s">
+      <c r="G16" s="140"/>
+      <c r="H16" s="140"/>
+      <c r="I16" s="140"/>
+      <c r="J16" s="140"/>
+      <c r="K16" s="130" t="s">
         <v>284</v>
       </c>
-      <c r="L16" s="99"/>
-      <c r="M16" s="100"/>
+      <c r="L16" s="131"/>
+      <c r="M16" s="132"/>
     </row>
     <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B17" s="106"/>
+      <c r="B17" s="146"/>
       <c r="C17" s="51" t="s">
         <v>223</v>
       </c>
-      <c r="D17" s="98" t="s">
+      <c r="D17" s="130" t="s">
         <v>282</v>
       </c>
-      <c r="E17" s="100"/>
-      <c r="F17" s="112" t="s">
+      <c r="E17" s="132"/>
+      <c r="F17" s="140" t="s">
         <v>282</v>
       </c>
-      <c r="G17" s="112"/>
-      <c r="H17" s="112"/>
-      <c r="I17" s="112"/>
-      <c r="J17" s="112"/>
-      <c r="K17" s="98"/>
-      <c r="L17" s="99"/>
-      <c r="M17" s="100"/>
+      <c r="G17" s="140"/>
+      <c r="H17" s="140"/>
+      <c r="I17" s="140"/>
+      <c r="J17" s="140"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="131"/>
+      <c r="M17" s="132"/>
     </row>
     <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B18" s="120" t="s">
+      <c r="B18" s="155" t="s">
         <v>374</v>
       </c>
       <c r="C18" s="51" t="s">
         <v>375</v>
       </c>
-      <c r="D18" s="98" t="s">
+      <c r="D18" s="130" t="s">
         <v>377</v>
       </c>
-      <c r="E18" s="100"/>
-      <c r="F18" s="95" t="s">
+      <c r="E18" s="132"/>
+      <c r="F18" s="134" t="s">
         <v>379</v>
       </c>
-      <c r="G18" s="96"/>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="97"/>
-      <c r="K18" s="98" t="s">
+      <c r="G18" s="135"/>
+      <c r="H18" s="135"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="136"/>
+      <c r="K18" s="130" t="s">
         <v>381</v>
       </c>
-      <c r="L18" s="99"/>
-      <c r="M18" s="100"/>
+      <c r="L18" s="131"/>
+      <c r="M18" s="132"/>
     </row>
     <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B19" s="121"/>
+      <c r="B19" s="156"/>
       <c r="C19" s="51" t="s">
         <v>376</v>
       </c>
-      <c r="D19" s="98" t="s">
+      <c r="D19" s="130" t="s">
         <v>378</v>
       </c>
-      <c r="E19" s="100"/>
-      <c r="F19" s="95" t="s">
+      <c r="E19" s="132"/>
+      <c r="F19" s="134" t="s">
         <v>380</v>
       </c>
-      <c r="G19" s="96"/>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="97"/>
+      <c r="G19" s="135"/>
+      <c r="H19" s="135"/>
+      <c r="I19" s="135"/>
+      <c r="J19" s="136"/>
       <c r="K19" s="63"/>
       <c r="L19" s="64"/>
       <c r="M19" s="65"/>
     </row>
     <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B20" s="120" t="s">
+      <c r="B20" s="155" t="s">
         <v>372</v>
       </c>
       <c r="C20" s="51" t="s">
         <v>222</v>
       </c>
-      <c r="D20" s="98" t="s">
+      <c r="D20" s="130" t="s">
         <v>248</v>
       </c>
-      <c r="E20" s="100"/>
-      <c r="F20" s="112" t="s">
+      <c r="E20" s="132"/>
+      <c r="F20" s="140" t="s">
         <v>101</v>
       </c>
-      <c r="G20" s="112"/>
-      <c r="H20" s="112"/>
-      <c r="I20" s="112"/>
-      <c r="J20" s="112"/>
-      <c r="K20" s="98" t="s">
+      <c r="G20" s="140"/>
+      <c r="H20" s="140"/>
+      <c r="I20" s="140"/>
+      <c r="J20" s="140"/>
+      <c r="K20" s="130" t="s">
         <v>285</v>
       </c>
-      <c r="L20" s="99"/>
-      <c r="M20" s="100"/>
+      <c r="L20" s="131"/>
+      <c r="M20" s="132"/>
     </row>
     <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="121"/>
+      <c r="B21" s="156"/>
       <c r="C21" s="51" t="s">
         <v>223</v>
       </c>
-      <c r="D21" s="98" t="s">
+      <c r="D21" s="130" t="s">
         <v>249</v>
       </c>
-      <c r="E21" s="100"/>
-      <c r="F21" s="112" t="s">
+      <c r="E21" s="132"/>
+      <c r="F21" s="140" t="s">
         <v>80</v>
       </c>
-      <c r="G21" s="112"/>
-      <c r="H21" s="112"/>
-      <c r="I21" s="112"/>
-      <c r="J21" s="112"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="99"/>
-      <c r="M21" s="100"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="140"/>
+      <c r="I21" s="140"/>
+      <c r="J21" s="140"/>
+      <c r="K21" s="130"/>
+      <c r="L21" s="131"/>
+      <c r="M21" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:J8"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="K18:M18"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="F9:J9"/>
     <mergeCell ref="K16:M16"/>
@@ -8071,48 +8113,6 @@
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="F13:J13"/>
     <mergeCell ref="K13:M13"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:J8"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:J18"/>
-    <mergeCell ref="F19:J19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:J20"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8208,22 +8208,22 @@
       <c r="C5" s="72" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="109" t="s">
+      <c r="D5" s="137" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="110"/>
-      <c r="F5" s="119" t="s">
+      <c r="E5" s="138"/>
+      <c r="F5" s="148" t="s">
         <v>84</v>
       </c>
-      <c r="G5" s="119"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
-      <c r="J5" s="119"/>
-      <c r="K5" s="109" t="s">
+      <c r="G5" s="148"/>
+      <c r="H5" s="148"/>
+      <c r="I5" s="148"/>
+      <c r="J5" s="148"/>
+      <c r="K5" s="137" t="s">
         <v>103</v>
       </c>
-      <c r="L5" s="111"/>
-      <c r="M5" s="110"/>
+      <c r="L5" s="139"/>
+      <c r="M5" s="138"/>
     </row>
     <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B6" s="73">
@@ -8232,155 +8232,158 @@
       <c r="C6" s="74" t="s">
         <v>292</v>
       </c>
-      <c r="D6" s="98" t="s">
+      <c r="D6" s="130" t="s">
         <v>293</v>
       </c>
-      <c r="E6" s="100"/>
-      <c r="F6" s="112"/>
-      <c r="G6" s="112"/>
-      <c r="H6" s="112"/>
-      <c r="I6" s="112"/>
-      <c r="J6" s="112"/>
-      <c r="K6" s="108" t="s">
+      <c r="E6" s="132"/>
+      <c r="F6" s="140"/>
+      <c r="G6" s="140"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="140"/>
+      <c r="K6" s="133" t="s">
         <v>294</v>
       </c>
-      <c r="L6" s="108"/>
-      <c r="M6" s="108"/>
+      <c r="L6" s="133"/>
+      <c r="M6" s="133"/>
     </row>
     <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="107" t="s">
+      <c r="B7" s="147" t="s">
         <v>295</v>
       </c>
       <c r="C7" s="51" t="s">
         <v>296</v>
       </c>
-      <c r="D7" s="98" t="s">
+      <c r="D7" s="130" t="s">
         <v>299</v>
       </c>
-      <c r="E7" s="100"/>
-      <c r="F7" s="112" t="s">
+      <c r="E7" s="132"/>
+      <c r="F7" s="140" t="s">
         <v>300</v>
       </c>
-      <c r="G7" s="112"/>
-      <c r="H7" s="112"/>
-      <c r="I7" s="112"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="98" t="s">
+      <c r="G7" s="140"/>
+      <c r="H7" s="140"/>
+      <c r="I7" s="140"/>
+      <c r="J7" s="140"/>
+      <c r="K7" s="130" t="s">
         <v>303</v>
       </c>
-      <c r="L7" s="99"/>
-      <c r="M7" s="100"/>
+      <c r="L7" s="131"/>
+      <c r="M7" s="132"/>
     </row>
     <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="107"/>
+      <c r="B8" s="147"/>
       <c r="C8" s="51" t="s">
         <v>297</v>
       </c>
-      <c r="D8" s="98" t="s">
+      <c r="D8" s="130" t="s">
         <v>308</v>
       </c>
-      <c r="E8" s="100"/>
-      <c r="F8" s="112" t="s">
+      <c r="E8" s="132"/>
+      <c r="F8" s="140" t="s">
         <v>301</v>
       </c>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="112"/>
+      <c r="G8" s="140"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="140"/>
+      <c r="J8" s="140"/>
       <c r="K8" s="63"/>
       <c r="L8" s="64"/>
       <c r="M8" s="65"/>
     </row>
     <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="107"/>
+      <c r="B9" s="147"/>
       <c r="C9" s="51" t="s">
         <v>298</v>
       </c>
-      <c r="D9" s="98" t="s">
+      <c r="D9" s="130" t="s">
         <v>309</v>
       </c>
-      <c r="E9" s="100"/>
-      <c r="F9" s="112" t="s">
+      <c r="E9" s="132"/>
+      <c r="F9" s="140" t="s">
         <v>302</v>
       </c>
-      <c r="G9" s="112"/>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="112"/>
-      <c r="K9" s="98"/>
-      <c r="L9" s="99"/>
-      <c r="M9" s="100"/>
+      <c r="G9" s="140"/>
+      <c r="H9" s="140"/>
+      <c r="I9" s="140"/>
+      <c r="J9" s="140"/>
+      <c r="K9" s="130"/>
+      <c r="L9" s="131"/>
+      <c r="M9" s="132"/>
     </row>
     <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B10" s="120" t="s">
+      <c r="B10" s="155" t="s">
         <v>451</v>
       </c>
       <c r="C10" s="51" t="s">
         <v>304</v>
       </c>
-      <c r="D10" s="98" t="s">
+      <c r="D10" s="130" t="s">
         <v>307</v>
       </c>
-      <c r="E10" s="100"/>
-      <c r="F10" s="112" t="s">
+      <c r="E10" s="132"/>
+      <c r="F10" s="140" t="s">
         <v>312</v>
       </c>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="112"/>
-      <c r="K10" s="98"/>
-      <c r="L10" s="99"/>
-      <c r="M10" s="100"/>
+      <c r="G10" s="140"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="140"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="130"/>
+      <c r="L10" s="131"/>
+      <c r="M10" s="132"/>
     </row>
     <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="131"/>
+      <c r="B11" s="157"/>
       <c r="C11" s="51" t="s">
         <v>306</v>
       </c>
-      <c r="D11" s="98" t="s">
+      <c r="D11" s="130" t="s">
         <v>310</v>
       </c>
-      <c r="E11" s="100"/>
-      <c r="F11" s="112" t="s">
+      <c r="E11" s="132"/>
+      <c r="F11" s="140" t="s">
         <v>312</v>
       </c>
-      <c r="G11" s="112"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="112"/>
-      <c r="J11" s="112"/>
+      <c r="G11" s="140"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="140"/>
       <c r="K11" s="63"/>
       <c r="L11" s="64"/>
       <c r="M11" s="65"/>
     </row>
     <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="121"/>
+      <c r="B12" s="156"/>
       <c r="C12" s="51" t="s">
         <v>305</v>
       </c>
-      <c r="D12" s="98" t="s">
+      <c r="D12" s="130" t="s">
         <v>311</v>
       </c>
-      <c r="E12" s="100"/>
-      <c r="F12" s="112" t="s">
+      <c r="E12" s="132"/>
+      <c r="F12" s="140" t="s">
         <v>312</v>
       </c>
-      <c r="G12" s="112"/>
-      <c r="H12" s="112"/>
-      <c r="I12" s="112"/>
-      <c r="J12" s="112"/>
-      <c r="K12" s="98"/>
-      <c r="L12" s="99"/>
-      <c r="M12" s="100"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="140"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="131"/>
+      <c r="M12" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:J6"/>
-    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:J11"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="F7:J7"/>
@@ -8390,15 +8393,12 @@
     <mergeCell ref="K9:M9"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="F8:J8"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="K6:M6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8419,40 +8419,40 @@
   <sheetData>
     <row r="1" spans="2:11" ht="6" customHeight="1"/>
     <row r="2" spans="2:11" ht="26.25" customHeight="1">
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="137" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="119" t="s">
+      <c r="C2" s="138"/>
+      <c r="D2" s="148" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="109" t="s">
+      <c r="E2" s="148"/>
+      <c r="F2" s="148"/>
+      <c r="G2" s="148"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="137" t="s">
         <v>103</v>
       </c>
-      <c r="J2" s="111"/>
-      <c r="K2" s="110"/>
+      <c r="J2" s="139"/>
+      <c r="K2" s="138"/>
     </row>
     <row r="3" spans="2:11" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="98" t="s">
+      <c r="B3" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="100"/>
-      <c r="D3" s="112" t="s">
+      <c r="C3" s="132"/>
+      <c r="D3" s="140" t="s">
         <v>352</v>
       </c>
-      <c r="E3" s="112"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="112"/>
-      <c r="I3" s="108" t="s">
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="140"/>
+      <c r="H3" s="140"/>
+      <c r="I3" s="133" t="s">
         <v>353</v>
       </c>
-      <c r="J3" s="108"/>
-      <c r="K3" s="108"/>
+      <c r="J3" s="133"/>
+      <c r="K3" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -8521,130 +8521,130 @@
       <c r="C6" s="72" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="109" t="s">
+      <c r="D6" s="137" t="s">
         <v>85</v>
       </c>
-      <c r="E6" s="110"/>
-      <c r="F6" s="119" t="s">
+      <c r="E6" s="138"/>
+      <c r="F6" s="148" t="s">
         <v>84</v>
       </c>
-      <c r="G6" s="119"/>
-      <c r="H6" s="119"/>
-      <c r="I6" s="119"/>
-      <c r="J6" s="119"/>
-      <c r="K6" s="109" t="s">
+      <c r="G6" s="148"/>
+      <c r="H6" s="148"/>
+      <c r="I6" s="148"/>
+      <c r="J6" s="148"/>
+      <c r="K6" s="137" t="s">
         <v>103</v>
       </c>
-      <c r="L6" s="111"/>
-      <c r="M6" s="110"/>
+      <c r="L6" s="139"/>
+      <c r="M6" s="138"/>
     </row>
     <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="144" t="s">
         <v>356</v>
       </c>
       <c r="C7" s="51" t="s">
         <v>357</v>
       </c>
-      <c r="D7" s="98" t="s">
+      <c r="D7" s="130" t="s">
         <v>367</v>
       </c>
-      <c r="E7" s="100"/>
-      <c r="F7" s="112" t="s">
+      <c r="E7" s="132"/>
+      <c r="F7" s="140" t="s">
         <v>368</v>
       </c>
-      <c r="G7" s="112"/>
-      <c r="H7" s="112"/>
-      <c r="I7" s="112"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="108" t="s">
+      <c r="G7" s="140"/>
+      <c r="H7" s="140"/>
+      <c r="I7" s="140"/>
+      <c r="J7" s="140"/>
+      <c r="K7" s="133" t="s">
         <v>371</v>
       </c>
-      <c r="L7" s="108"/>
-      <c r="M7" s="108"/>
+      <c r="L7" s="133"/>
+      <c r="M7" s="133"/>
     </row>
     <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="105"/>
+      <c r="B8" s="145"/>
       <c r="C8" s="51" t="s">
         <v>358</v>
       </c>
-      <c r="D8" s="98" t="s">
+      <c r="D8" s="130" t="s">
         <v>367</v>
       </c>
-      <c r="E8" s="100"/>
-      <c r="F8" s="112" t="s">
+      <c r="E8" s="132"/>
+      <c r="F8" s="140" t="s">
         <v>369</v>
       </c>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="112"/>
+      <c r="G8" s="140"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="140"/>
+      <c r="J8" s="140"/>
       <c r="K8" s="63"/>
       <c r="L8" s="64"/>
       <c r="M8" s="65"/>
     </row>
     <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="106"/>
+      <c r="B9" s="146"/>
       <c r="C9" s="51" t="s">
         <v>359</v>
       </c>
-      <c r="D9" s="98" t="s">
+      <c r="D9" s="130" t="s">
         <v>367</v>
       </c>
-      <c r="E9" s="100"/>
-      <c r="F9" s="112" t="s">
+      <c r="E9" s="132"/>
+      <c r="F9" s="140" t="s">
         <v>370</v>
       </c>
-      <c r="G9" s="112"/>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="112"/>
-      <c r="K9" s="98"/>
-      <c r="L9" s="99"/>
-      <c r="M9" s="100"/>
+      <c r="G9" s="140"/>
+      <c r="H9" s="140"/>
+      <c r="I9" s="140"/>
+      <c r="J9" s="140"/>
+      <c r="K9" s="130"/>
+      <c r="L9" s="131"/>
+      <c r="M9" s="132"/>
     </row>
     <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B10" s="107" t="s">
+      <c r="B10" s="147" t="s">
         <v>360</v>
       </c>
       <c r="C10" s="51" t="s">
         <v>251</v>
       </c>
-      <c r="D10" s="98" t="s">
+      <c r="D10" s="130" t="s">
         <v>362</v>
       </c>
-      <c r="E10" s="100"/>
-      <c r="F10" s="95" t="s">
+      <c r="E10" s="132"/>
+      <c r="F10" s="134" t="s">
         <v>363</v>
       </c>
-      <c r="G10" s="96"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="96"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="98" t="s">
+      <c r="G10" s="135"/>
+      <c r="H10" s="135"/>
+      <c r="I10" s="135"/>
+      <c r="J10" s="135"/>
+      <c r="K10" s="130" t="s">
         <v>366</v>
       </c>
-      <c r="L10" s="99"/>
-      <c r="M10" s="100"/>
+      <c r="L10" s="131"/>
+      <c r="M10" s="132"/>
     </row>
     <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="107"/>
+      <c r="B11" s="147"/>
       <c r="C11" s="51" t="s">
         <v>361</v>
       </c>
-      <c r="D11" s="98" t="s">
+      <c r="D11" s="130" t="s">
         <v>364</v>
       </c>
-      <c r="E11" s="100"/>
-      <c r="F11" s="95" t="s">
+      <c r="E11" s="132"/>
+      <c r="F11" s="134" t="s">
         <v>365</v>
       </c>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="96"/>
-      <c r="K11" s="98"/>
-      <c r="L11" s="99"/>
-      <c r="M11" s="100"/>
+      <c r="G11" s="135"/>
+      <c r="H11" s="135"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="135"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="131"/>
+      <c r="M11" s="132"/>
     </row>
     <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B12" s="73" t="s">
@@ -8653,25 +8653,35 @@
       <c r="C12" s="73" t="s">
         <v>382</v>
       </c>
-      <c r="D12" s="98" t="s">
+      <c r="D12" s="130" t="s">
         <v>382</v>
       </c>
-      <c r="E12" s="100"/>
-      <c r="F12" s="95" t="s">
+      <c r="E12" s="132"/>
+      <c r="F12" s="134" t="s">
         <v>317</v>
       </c>
-      <c r="G12" s="96"/>
-      <c r="H12" s="96"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="97"/>
-      <c r="K12" s="98" t="s">
+      <c r="G12" s="135"/>
+      <c r="H12" s="135"/>
+      <c r="I12" s="135"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="130" t="s">
         <v>366</v>
       </c>
-      <c r="L12" s="99"/>
-      <c r="M12" s="100"/>
+      <c r="L12" s="131"/>
+      <c r="M12" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="K11:M11"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:J6"/>
     <mergeCell ref="K6:M6"/>
@@ -8684,16 +8694,6 @@
     <mergeCell ref="K9:M9"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="F8:J8"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K11:M11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testprocess/1-process/大对象测试/Testing_LOB.xlsx
+++ b/testprocess/1-process/大对象测试/Testing_LOB.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="15"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7785" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="测试主题" sheetId="14" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="526">
   <si>
     <t>可靠性</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -299,10 +299,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>大对象查找操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>大对象删除操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -348,14 +344,6 @@
   </si>
   <si>
     <t>128M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>链接文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文件夹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1095,10 +1083,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对同一个大对象操作执行并发写操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>对不同的大对象操作执行并发写操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1482,9 +1466,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>在写的过程中，进行数据读操作，读出已经写好的数据，数据正确，</t>
-  </si>
-  <si>
     <t>停(n-1)/2个节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1516,10 +1497,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>停掉(n-1)/3个节点后，执行读操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>kill掉主节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1533,18 +1510,6 @@
   </si>
   <si>
     <t>执行读操作过程中干掉主节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在写操作过程中杀掉主节点，写操作的状态，是停止，还是继续写</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在读操作过程中杀掉主节点，读操作的状态，是停止，还是继续读</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>写操作-宕机重启-读数据-写数据</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1661,18 +1626,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>W=0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>W=3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>W=7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>重启集群</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1693,10 +1650,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>重启集群之前先向数据库写入大对象，然后再重启集群，最后写大对象，最后判断大对象</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>读出的大对象与写入的大对象相等</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1776,18 +1729,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1机1组1节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3机3组3节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>7机7组7节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>此集群下大对象基本操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2066,10 +2011,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>大对象数据存储测试【如视频/音频/图片等文件】</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>*填写项目名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2119,6 +2060,69 @@
   </si>
   <si>
     <t>项目说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*填写项目与测试相关情况。例如项目背景、项目需求、实现技术等等。同时说明测试目标（例如验证xxx功能、获取性能数据等等）、测试方式（黑箱/白箱）、实现方式（脚本/程序/工具）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与会者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>评审意见</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>评审人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>说明：该表格用于记录评审意见，在测试设计与测试点评审时记录。解决完成后将条目背景色改为绿色填充。见下图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已解决</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.测试结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.测试结论</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.产物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.总结与建议</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常</t>
+  </si>
+  <si>
+    <t>大对象查找操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2132,70 +2136,243 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>*填写项目与测试相关情况。例如项目背景、项目需求、实现技术等等。同时说明测试目标（例如验证xxx功能、获取性能数据等等）、测试方式（黑箱/白箱）、实现方式（脚本/程序/工具）。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与会者</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>评审意见</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>评审人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>责任人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>说明：该表格用于记录评审意见，在测试设计与测试点评审时记录。解决完成后将条目背景色改为绿色填充。见下图</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已解决</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.测试结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.测试结论</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.产物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.总结与建议</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>异常</t>
+    <t>大对象数据存储测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大对象偏移读</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大对象偏移写</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取大对象元数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List大对象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清理未完成大对象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进行range切分【split和主子表】对大对象切分的影响。如何玩。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文件夹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>对同一个大对象操作执行并发写操作</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【结果：不支持并发打开同一个LOB，模式:写不支持】</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接句柄，相同句柄与不同句柄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大于256K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【pagesize:4-512k】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不支持range split和percent split</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不支持主子表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>范围切分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主子表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>W=0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>W=6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>W=1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重启集群之前先向数据库写入大对象，然后再重启集群，最后写大对象，最后判断大对象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在写的过程中，进行数据读操作，读出已经写好的数据，数据正确，</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全量同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>在写操作过程中杀掉主节点，写操作的状态，是停止</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【预期结果：停止】</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在读操作过程中杀掉主节点，读操作的状态，是停止，还是继续读</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停掉(n-1)/2个节点后，执行读操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停掉1~（n-1)个节点后，执行读操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>写操作-宕机重启-读数据-写数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>写过程中宕机时，会留下脏数据。【对之前遗留的大对象无法读与无法写】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hash切分存储之hash数据是否均匀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hash切分存储之hash数据是否均匀【需要提供工具dump】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大对象写操作性能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与mongodb对比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多线程的读写</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1机1组1节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7机7组7节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁盘空间满时，对大对象进行操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文件系统异常如何玩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络中断异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结果：节点间连接的重试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大对象写/读的过程中做split操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例编号</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试用例名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试过程描述</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>预期结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试脚本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试准备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lob.001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大对象写操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必须包含数据节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大对象写操作成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2312,8 +2489,49 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFFFF00"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFF00"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2396,8 +2614,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="mediumGray"/>
+    </fill>
   </fills>
-  <borders count="52">
+  <borders count="59">
     <border>
       <left/>
       <right/>
@@ -3060,6 +3281,87 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3068,7 +3370,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="224">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3268,9 +3570,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3413,6 +3712,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3556,6 +3867,157 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3860,185 +4322,185 @@
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
     <col min="2" max="2" width="13.125" customWidth="1"/>
-    <col min="3" max="3" width="99.375" style="96" customWidth="1"/>
-    <col min="4" max="4" width="66.375" style="95" customWidth="1"/>
+    <col min="3" max="3" width="99.375" style="95" customWidth="1"/>
+    <col min="4" max="4" width="66.375" style="94" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="6" customHeight="1">
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
     </row>
     <row r="2" spans="2:4" ht="14.25" thickBot="1">
-      <c r="B2" s="122" t="s">
+      <c r="B2" s="125" t="s">
+        <v>443</v>
+      </c>
+      <c r="C2" s="125"/>
+    </row>
+    <row r="3" spans="2:4" ht="25.5">
+      <c r="B3" s="96" t="s">
+        <v>444</v>
+      </c>
+      <c r="C3" s="97" t="s">
+        <v>475</v>
+      </c>
+      <c r="D3" s="98" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" s="99" t="s">
+        <v>446</v>
+      </c>
+      <c r="C4" s="100">
+        <v>41849</v>
+      </c>
+      <c r="D4" s="98" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" s="99" t="s">
+        <v>448</v>
+      </c>
+      <c r="C5" s="100"/>
+      <c r="D5" s="98" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" s="99" t="s">
+        <v>450</v>
+      </c>
+      <c r="C6" s="101" t="s">
+        <v>451</v>
+      </c>
+      <c r="D6" s="98" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="13.5" customHeight="1">
+      <c r="B7" s="102" t="s">
+        <v>453</v>
+      </c>
+      <c r="C7" s="101"/>
+      <c r="D7" s="98" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" s="103" t="s">
+        <v>455</v>
+      </c>
+      <c r="C8" s="104"/>
+      <c r="D8" s="98" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="40.5" customHeight="1">
+      <c r="B9" s="126" t="s">
         <v>457</v>
       </c>
-      <c r="C2" s="122"/>
-    </row>
-    <row r="3" spans="2:4" ht="25.5">
-      <c r="B3" s="97" t="s">
+      <c r="C9" s="129" t="s">
+        <v>474</v>
+      </c>
+      <c r="D9" s="132" t="s">
         <v>458</v>
       </c>
-      <c r="C3" s="98" t="s">
-        <v>459</v>
-      </c>
-      <c r="D3" s="99" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4">
-      <c r="B4" s="100" t="s">
-        <v>461</v>
-      </c>
-      <c r="C4" s="101">
-        <v>41849</v>
-      </c>
-      <c r="D4" s="99" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4">
-      <c r="B5" s="100" t="s">
-        <v>463</v>
-      </c>
-      <c r="C5" s="101"/>
-      <c r="D5" s="99" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4">
-      <c r="B6" s="100" t="s">
-        <v>465</v>
-      </c>
-      <c r="C6" s="102" t="s">
-        <v>466</v>
-      </c>
-      <c r="D6" s="99" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="13.5" customHeight="1">
-      <c r="B7" s="103" t="s">
-        <v>468</v>
-      </c>
-      <c r="C7" s="102"/>
-      <c r="D7" s="99" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4">
-      <c r="B8" s="104" t="s">
-        <v>470</v>
-      </c>
-      <c r="C8" s="105"/>
-      <c r="D8" s="99" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="40.5" customHeight="1">
-      <c r="B9" s="123" t="s">
-        <v>472</v>
-      </c>
-      <c r="C9" s="126" t="s">
-        <v>473</v>
-      </c>
-      <c r="D9" s="129" t="s">
-        <v>474</v>
-      </c>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="124"/>
-      <c r="C10" s="127"/>
-      <c r="D10" s="129"/>
+      <c r="B10" s="127"/>
+      <c r="C10" s="130"/>
+      <c r="D10" s="132"/>
     </row>
     <row r="11" spans="2:4">
-      <c r="B11" s="124"/>
-      <c r="C11" s="127"/>
-      <c r="D11" s="129"/>
+      <c r="B11" s="127"/>
+      <c r="C11" s="130"/>
+      <c r="D11" s="132"/>
     </row>
     <row r="12" spans="2:4">
-      <c r="B12" s="124"/>
-      <c r="C12" s="127"/>
-      <c r="D12" s="129"/>
+      <c r="B12" s="127"/>
+      <c r="C12" s="130"/>
+      <c r="D12" s="132"/>
     </row>
     <row r="13" spans="2:4">
-      <c r="B13" s="124"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="129"/>
+      <c r="B13" s="127"/>
+      <c r="C13" s="130"/>
+      <c r="D13" s="132"/>
     </row>
     <row r="14" spans="2:4">
-      <c r="B14" s="124"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="129"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="130"/>
+      <c r="D14" s="132"/>
     </row>
     <row r="15" spans="2:4">
-      <c r="B15" s="124"/>
-      <c r="C15" s="127"/>
-      <c r="D15" s="129"/>
+      <c r="B15" s="127"/>
+      <c r="C15" s="130"/>
+      <c r="D15" s="132"/>
     </row>
     <row r="16" spans="2:4">
-      <c r="B16" s="124"/>
-      <c r="C16" s="127"/>
-      <c r="D16" s="129"/>
+      <c r="B16" s="127"/>
+      <c r="C16" s="130"/>
+      <c r="D16" s="132"/>
     </row>
     <row r="17" spans="2:4">
-      <c r="B17" s="124"/>
-      <c r="C17" s="127"/>
-      <c r="D17" s="129"/>
+      <c r="B17" s="127"/>
+      <c r="C17" s="130"/>
+      <c r="D17" s="132"/>
     </row>
     <row r="18" spans="2:4">
-      <c r="B18" s="124"/>
-      <c r="C18" s="127"/>
-      <c r="D18" s="129"/>
+      <c r="B18" s="127"/>
+      <c r="C18" s="130"/>
+      <c r="D18" s="132"/>
     </row>
     <row r="19" spans="2:4">
-      <c r="B19" s="124"/>
-      <c r="C19" s="127"/>
-      <c r="D19" s="129"/>
+      <c r="B19" s="127"/>
+      <c r="C19" s="130"/>
+      <c r="D19" s="132"/>
     </row>
     <row r="20" spans="2:4">
-      <c r="B20" s="124"/>
-      <c r="C20" s="127"/>
-      <c r="D20" s="129"/>
+      <c r="B20" s="127"/>
+      <c r="C20" s="130"/>
+      <c r="D20" s="132"/>
     </row>
     <row r="21" spans="2:4">
-      <c r="B21" s="124"/>
-      <c r="C21" s="127"/>
-      <c r="D21" s="129"/>
+      <c r="B21" s="127"/>
+      <c r="C21" s="130"/>
+      <c r="D21" s="132"/>
     </row>
     <row r="22" spans="2:4">
-      <c r="B22" s="124"/>
-      <c r="C22" s="127"/>
-      <c r="D22" s="129"/>
+      <c r="B22" s="127"/>
+      <c r="C22" s="130"/>
+      <c r="D22" s="132"/>
     </row>
     <row r="23" spans="2:4">
-      <c r="B23" s="124"/>
-      <c r="C23" s="127"/>
-      <c r="D23" s="129"/>
+      <c r="B23" s="127"/>
+      <c r="C23" s="130"/>
+      <c r="D23" s="132"/>
     </row>
     <row r="24" spans="2:4">
-      <c r="B24" s="124"/>
-      <c r="C24" s="127"/>
-      <c r="D24" s="129"/>
+      <c r="B24" s="127"/>
+      <c r="C24" s="130"/>
+      <c r="D24" s="132"/>
     </row>
     <row r="25" spans="2:4">
-      <c r="B25" s="124"/>
-      <c r="C25" s="127"/>
-      <c r="D25" s="129"/>
+      <c r="B25" s="127"/>
+      <c r="C25" s="130"/>
+      <c r="D25" s="132"/>
     </row>
     <row r="26" spans="2:4">
-      <c r="B26" s="124"/>
-      <c r="C26" s="127"/>
-      <c r="D26" s="129"/>
+      <c r="B26" s="127"/>
+      <c r="C26" s="130"/>
+      <c r="D26" s="132"/>
     </row>
     <row r="27" spans="2:4">
-      <c r="B27" s="124"/>
-      <c r="C27" s="127"/>
-      <c r="D27" s="129"/>
+      <c r="B27" s="127"/>
+      <c r="C27" s="130"/>
+      <c r="D27" s="132"/>
     </row>
     <row r="28" spans="2:4" ht="14.25" thickBot="1">
-      <c r="B28" s="125"/>
-      <c r="C28" s="128"/>
-      <c r="D28" s="129"/>
+      <c r="B28" s="128"/>
+      <c r="C28" s="131"/>
+      <c r="D28" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4071,18 +4533,18 @@
         <v>21</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B3" s="10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>17</v>
@@ -4095,8 +4557,8 @@
       </c>
     </row>
     <row r="4" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B4" s="82" t="s">
-        <v>75</v>
+      <c r="B4" s="81" t="s">
+        <v>72</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>17</v>
@@ -4115,159 +4577,159 @@
       <c r="E5" s="36"/>
     </row>
     <row r="7" spans="2:13" ht="26.25" customHeight="1">
-      <c r="B7" s="71" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="72" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="137" t="s">
-        <v>341</v>
-      </c>
-      <c r="E7" s="138"/>
-      <c r="F7" s="148" t="s">
-        <v>342</v>
-      </c>
-      <c r="G7" s="148"/>
-      <c r="H7" s="148"/>
-      <c r="I7" s="148"/>
-      <c r="J7" s="148"/>
-      <c r="K7" s="137" t="s">
-        <v>103</v>
-      </c>
-      <c r="L7" s="139"/>
-      <c r="M7" s="138"/>
+      <c r="B7" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="140" t="s">
+        <v>332</v>
+      </c>
+      <c r="E7" s="141"/>
+      <c r="F7" s="151" t="s">
+        <v>333</v>
+      </c>
+      <c r="G7" s="151"/>
+      <c r="H7" s="151"/>
+      <c r="I7" s="151"/>
+      <c r="J7" s="151"/>
+      <c r="K7" s="140" t="s">
+        <v>100</v>
+      </c>
+      <c r="L7" s="142"/>
+      <c r="M7" s="141"/>
     </row>
     <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="144" t="s">
-        <v>321</v>
-      </c>
-      <c r="C8" s="74" t="s">
-        <v>322</v>
-      </c>
-      <c r="D8" s="130" t="s">
-        <v>325</v>
-      </c>
-      <c r="E8" s="132"/>
-      <c r="F8" s="140" t="s">
-        <v>324</v>
-      </c>
-      <c r="G8" s="140"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="140"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="133" t="s">
-        <v>338</v>
-      </c>
-      <c r="L8" s="133"/>
-      <c r="M8" s="133"/>
+      <c r="B8" s="147" t="s">
+        <v>316</v>
+      </c>
+      <c r="C8" s="73" t="s">
+        <v>317</v>
+      </c>
+      <c r="D8" s="133" t="s">
+        <v>320</v>
+      </c>
+      <c r="E8" s="135"/>
+      <c r="F8" s="143" t="s">
+        <v>319</v>
+      </c>
+      <c r="G8" s="143"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="143"/>
+      <c r="J8" s="143"/>
+      <c r="K8" s="136" t="s">
+        <v>329</v>
+      </c>
+      <c r="L8" s="136"/>
+      <c r="M8" s="136"/>
     </row>
     <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="146"/>
-      <c r="C9" s="74" t="s">
-        <v>323</v>
-      </c>
-      <c r="D9" s="130" t="s">
-        <v>326</v>
-      </c>
-      <c r="E9" s="132"/>
-      <c r="F9" s="140" t="s">
-        <v>326</v>
-      </c>
-      <c r="G9" s="140"/>
-      <c r="H9" s="140"/>
-      <c r="I9" s="140"/>
-      <c r="J9" s="140"/>
+      <c r="B9" s="149"/>
+      <c r="C9" s="73" t="s">
+        <v>318</v>
+      </c>
+      <c r="D9" s="189" t="s">
+        <v>500</v>
+      </c>
+      <c r="E9" s="190"/>
+      <c r="F9" s="143" t="s">
+        <v>499</v>
+      </c>
+      <c r="G9" s="143"/>
+      <c r="H9" s="143"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
       <c r="K9" s="63"/>
       <c r="L9" s="64"/>
       <c r="M9" s="65"/>
     </row>
     <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B10" s="147" t="s">
+      <c r="B10" s="150" t="s">
+        <v>321</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>317</v>
+      </c>
+      <c r="D10" s="133" t="s">
+        <v>323</v>
+      </c>
+      <c r="E10" s="135"/>
+      <c r="F10" s="143" t="s">
+        <v>497</v>
+      </c>
+      <c r="G10" s="143"/>
+      <c r="H10" s="143"/>
+      <c r="I10" s="143"/>
+      <c r="J10" s="143"/>
+      <c r="K10" s="133" t="s">
         <v>327</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="L10" s="134"/>
+      <c r="M10" s="135"/>
+    </row>
+    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B11" s="150"/>
+      <c r="C11" s="51" t="s">
+        <v>318</v>
+      </c>
+      <c r="D11" s="133" t="s">
+        <v>324</v>
+      </c>
+      <c r="E11" s="135"/>
+      <c r="F11" s="143" t="s">
+        <v>498</v>
+      </c>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="133" t="s">
+        <v>328</v>
+      </c>
+      <c r="L11" s="134"/>
+      <c r="M11" s="135"/>
+    </row>
+    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B12" s="150" t="s">
         <v>322</v>
       </c>
-      <c r="D10" s="130" t="s">
-        <v>329</v>
-      </c>
-      <c r="E10" s="132"/>
-      <c r="F10" s="140" t="s">
+      <c r="C12" s="51" t="s">
+        <v>317</v>
+      </c>
+      <c r="D12" s="136" t="s">
+        <v>501</v>
+      </c>
+      <c r="E12" s="136"/>
+      <c r="F12" s="143" t="s">
+        <v>325</v>
+      </c>
+      <c r="G12" s="143"/>
+      <c r="H12" s="143"/>
+      <c r="I12" s="143"/>
+      <c r="J12" s="143"/>
+      <c r="K12" s="133" t="s">
+        <v>330</v>
+      </c>
+      <c r="L12" s="134"/>
+      <c r="M12" s="135"/>
+    </row>
+    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B13" s="150"/>
+      <c r="C13" s="51" t="s">
+        <v>318</v>
+      </c>
+      <c r="D13" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="G10" s="140"/>
-      <c r="H10" s="140"/>
-      <c r="I10" s="140"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="130" t="s">
-        <v>336</v>
-      </c>
-      <c r="L10" s="131"/>
-      <c r="M10" s="132"/>
-    </row>
-    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="147"/>
-      <c r="C11" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="D11" s="130" t="s">
-        <v>330</v>
-      </c>
-      <c r="E11" s="132"/>
-      <c r="F11" s="140" t="s">
-        <v>332</v>
-      </c>
-      <c r="G11" s="140"/>
-      <c r="H11" s="140"/>
-      <c r="I11" s="140"/>
-      <c r="J11" s="140"/>
-      <c r="K11" s="130" t="s">
-        <v>337</v>
-      </c>
-      <c r="L11" s="131"/>
-      <c r="M11" s="132"/>
-    </row>
-    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="147" t="s">
-        <v>328</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="D12" s="133" t="s">
-        <v>333</v>
-      </c>
-      <c r="E12" s="133"/>
-      <c r="F12" s="140" t="s">
-        <v>334</v>
-      </c>
-      <c r="G12" s="140"/>
-      <c r="H12" s="140"/>
-      <c r="I12" s="140"/>
-      <c r="J12" s="140"/>
-      <c r="K12" s="130" t="s">
-        <v>339</v>
-      </c>
-      <c r="L12" s="131"/>
-      <c r="M12" s="132"/>
-    </row>
-    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="147"/>
-      <c r="C13" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="D13" s="133" t="s">
-        <v>340</v>
-      </c>
-      <c r="E13" s="133"/>
-      <c r="F13" s="140" t="s">
-        <v>335</v>
-      </c>
-      <c r="G13" s="140"/>
-      <c r="H13" s="140"/>
-      <c r="I13" s="140"/>
-      <c r="J13" s="140"/>
+      <c r="E13" s="136"/>
+      <c r="F13" s="143" t="s">
+        <v>326</v>
+      </c>
+      <c r="G13" s="143"/>
+      <c r="H13" s="143"/>
+      <c r="I13" s="143"/>
+      <c r="J13" s="143"/>
       <c r="K13" s="63"/>
       <c r="L13" s="64"/>
       <c r="M13" s="65"/>
@@ -4307,7 +4769,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="B1:K12"/>
+  <dimension ref="B1:K13"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
@@ -4360,43 +4822,58 @@
     <row r="9" spans="2:11" ht="20.100000000000001" hidden="1" customHeight="1" outlineLevel="1"/>
     <row r="10" spans="2:11" ht="20.100000000000001" hidden="1" customHeight="1" outlineLevel="1"/>
     <row r="11" spans="2:11" ht="26.25" customHeight="1" collapsed="1">
-      <c r="B11" s="137" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="138"/>
-      <c r="D11" s="148" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" s="148"/>
-      <c r="F11" s="148"/>
-      <c r="G11" s="148"/>
-      <c r="H11" s="148"/>
-      <c r="I11" s="137" t="s">
-        <v>103</v>
-      </c>
-      <c r="J11" s="139"/>
-      <c r="K11" s="138"/>
+      <c r="B11" s="140" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="141"/>
+      <c r="D11" s="151" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="151"/>
+      <c r="F11" s="151"/>
+      <c r="G11" s="151"/>
+      <c r="H11" s="151"/>
+      <c r="I11" s="140" t="s">
+        <v>100</v>
+      </c>
+      <c r="J11" s="142"/>
+      <c r="K11" s="141"/>
     </row>
     <row r="12" spans="2:11" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="133" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="133"/>
-      <c r="D12" s="140" t="s">
-        <v>220</v>
-      </c>
-      <c r="E12" s="140"/>
-      <c r="F12" s="140"/>
-      <c r="G12" s="140"/>
-      <c r="H12" s="140"/>
-      <c r="I12" s="133" t="s">
-        <v>391</v>
-      </c>
-      <c r="J12" s="133"/>
-      <c r="K12" s="133"/>
+      <c r="B12" s="136" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="136"/>
+      <c r="D12" s="143" t="s">
+        <v>217</v>
+      </c>
+      <c r="E12" s="143"/>
+      <c r="F12" s="143"/>
+      <c r="G12" s="143"/>
+      <c r="H12" s="143"/>
+      <c r="I12" s="136" t="s">
+        <v>377</v>
+      </c>
+      <c r="J12" s="136"/>
+      <c r="K12" s="136"/>
+    </row>
+    <row r="13" spans="2:11" ht="20.100000000000001" customHeight="1">
+      <c r="B13" s="191" t="s">
+        <v>503</v>
+      </c>
+      <c r="C13" s="191"/>
+      <c r="D13" s="192" t="s">
+        <v>504</v>
+      </c>
+      <c r="E13" s="192"/>
+      <c r="F13" s="192"/>
+      <c r="G13" s="192"/>
+      <c r="H13" s="192"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:H13"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:H11"/>
     <mergeCell ref="I11:K11"/>
@@ -4414,7 +4891,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="B1:K7"/>
+  <dimension ref="B1:K8"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
@@ -4427,15 +4904,15 @@
         <v>16</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" spans="2:11" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B3" s="81" t="s">
-        <v>290</v>
+      <c r="B3" s="80" t="s">
+        <v>286</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>17</v>
@@ -4452,61 +4929,68 @@
       <c r="F4" s="20"/>
     </row>
     <row r="5" spans="2:11" ht="26.25" customHeight="1">
-      <c r="B5" s="137" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="138"/>
-      <c r="D5" s="148" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" s="148"/>
-      <c r="F5" s="148"/>
-      <c r="G5" s="148"/>
-      <c r="H5" s="148"/>
-      <c r="I5" s="137" t="s">
-        <v>103</v>
-      </c>
-      <c r="J5" s="139"/>
-      <c r="K5" s="138"/>
+      <c r="B5" s="140" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="141"/>
+      <c r="D5" s="151" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="151"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="151"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="140" t="s">
+        <v>100</v>
+      </c>
+      <c r="J5" s="142"/>
+      <c r="K5" s="141"/>
     </row>
     <row r="6" spans="2:11" ht="20.100000000000001" customHeight="1">
-      <c r="B6" s="133" t="s">
+      <c r="B6" s="136" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="136"/>
+      <c r="D6" s="143" t="s">
+        <v>206</v>
+      </c>
+      <c r="E6" s="143"/>
+      <c r="F6" s="143"/>
+      <c r="G6" s="143"/>
+      <c r="H6" s="143"/>
+      <c r="I6" s="136" t="s">
+        <v>208</v>
+      </c>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+    </row>
+    <row r="7" spans="2:11" ht="20.100000000000001" customHeight="1">
+      <c r="B7" s="136" t="s">
+        <v>505</v>
+      </c>
+      <c r="C7" s="136"/>
+      <c r="D7" s="143" t="s">
         <v>207</v>
       </c>
-      <c r="C6" s="133"/>
-      <c r="D6" s="140" t="s">
+      <c r="E7" s="143"/>
+      <c r="F7" s="143"/>
+      <c r="G7" s="143"/>
+      <c r="H7" s="143"/>
+      <c r="I7" s="136" t="s">
         <v>209</v>
       </c>
-      <c r="E6" s="140"/>
-      <c r="F6" s="140"/>
-      <c r="G6" s="140"/>
-      <c r="H6" s="140"/>
-      <c r="I6" s="133" t="s">
-        <v>211</v>
-      </c>
-      <c r="J6" s="133"/>
-      <c r="K6" s="133"/>
-    </row>
-    <row r="7" spans="2:11" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="133" t="s">
-        <v>208</v>
-      </c>
-      <c r="C7" s="133"/>
-      <c r="D7" s="140" t="s">
-        <v>210</v>
-      </c>
-      <c r="E7" s="140"/>
-      <c r="F7" s="140"/>
-      <c r="G7" s="140"/>
-      <c r="H7" s="140"/>
-      <c r="I7" s="133" t="s">
-        <v>212</v>
-      </c>
-      <c r="J7" s="133"/>
-      <c r="K7" s="133"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="136"/>
+    </row>
+    <row r="8" spans="2:11" ht="20.100000000000001" customHeight="1">
+      <c r="B8" s="136" t="s">
+        <v>205</v>
+      </c>
+      <c r="C8" s="136"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="I7:K7"/>
@@ -4543,18 +5027,18 @@
         <v>11</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B3" s="82" t="s">
-        <v>274</v>
+      <c r="B3" s="81" t="s">
+        <v>270</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>17</v>
@@ -4570,120 +5054,120 @@
       </c>
     </row>
     <row r="5" spans="2:13" ht="26.25" customHeight="1">
-      <c r="B5" s="71" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="72" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" s="137" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="138"/>
-      <c r="F5" s="148" t="s">
-        <v>84</v>
-      </c>
-      <c r="G5" s="148"/>
-      <c r="H5" s="148"/>
-      <c r="I5" s="148"/>
-      <c r="J5" s="148"/>
-      <c r="K5" s="137" t="s">
-        <v>103</v>
-      </c>
-      <c r="L5" s="139"/>
-      <c r="M5" s="138"/>
+      <c r="B5" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="140" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="141"/>
+      <c r="F5" s="151" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="151"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="151"/>
+      <c r="K5" s="140" t="s">
+        <v>100</v>
+      </c>
+      <c r="L5" s="142"/>
+      <c r="M5" s="141"/>
     </row>
     <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B6" s="75" t="s">
-        <v>383</v>
+      <c r="B6" s="74" t="s">
+        <v>371</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>255</v>
-      </c>
-      <c r="D6" s="130" t="s">
-        <v>219</v>
-      </c>
-      <c r="E6" s="132"/>
-      <c r="F6" s="140" t="s">
+        <v>251</v>
+      </c>
+      <c r="D6" s="133" t="s">
+        <v>216</v>
+      </c>
+      <c r="E6" s="135"/>
+      <c r="F6" s="143" t="s">
+        <v>212</v>
+      </c>
+      <c r="G6" s="143"/>
+      <c r="H6" s="143"/>
+      <c r="I6" s="143"/>
+      <c r="J6" s="143"/>
+      <c r="K6" s="136" t="s">
+        <v>372</v>
+      </c>
+      <c r="L6" s="136"/>
+      <c r="M6" s="136"/>
+    </row>
+    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B7" s="147" t="s">
+        <v>373</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>508</v>
+      </c>
+      <c r="D7" s="133" t="s">
+        <v>375</v>
+      </c>
+      <c r="E7" s="135"/>
+      <c r="F7" s="137" t="s">
+        <v>213</v>
+      </c>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="138"/>
+      <c r="K7" s="133" t="s">
+        <v>211</v>
+      </c>
+      <c r="L7" s="134"/>
+      <c r="M7" s="135"/>
+    </row>
+    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B8" s="148"/>
+      <c r="C8" s="51" t="s">
+        <v>374</v>
+      </c>
+      <c r="D8" s="133" t="s">
+        <v>375</v>
+      </c>
+      <c r="E8" s="135"/>
+      <c r="F8" s="137" t="s">
+        <v>214</v>
+      </c>
+      <c r="G8" s="138"/>
+      <c r="H8" s="138"/>
+      <c r="I8" s="138"/>
+      <c r="J8" s="138"/>
+      <c r="K8" s="133" t="s">
+        <v>210</v>
+      </c>
+      <c r="L8" s="134"/>
+      <c r="M8" s="135"/>
+    </row>
+    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B9" s="149"/>
+      <c r="C9" s="90" t="s">
+        <v>509</v>
+      </c>
+      <c r="D9" s="133" t="s">
+        <v>375</v>
+      </c>
+      <c r="E9" s="135"/>
+      <c r="F9" s="137" t="s">
         <v>215</v>
       </c>
-      <c r="G6" s="140"/>
-      <c r="H6" s="140"/>
-      <c r="I6" s="140"/>
-      <c r="J6" s="140"/>
-      <c r="K6" s="133" t="s">
-        <v>384</v>
-      </c>
-      <c r="L6" s="133"/>
-      <c r="M6" s="133"/>
-    </row>
-    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="144" t="s">
-        <v>385</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>386</v>
-      </c>
-      <c r="D7" s="130" t="s">
-        <v>389</v>
-      </c>
-      <c r="E7" s="132"/>
-      <c r="F7" s="134" t="s">
-        <v>216</v>
-      </c>
-      <c r="G7" s="135"/>
-      <c r="H7" s="135"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="135"/>
-      <c r="K7" s="130" t="s">
-        <v>214</v>
-      </c>
-      <c r="L7" s="131"/>
-      <c r="M7" s="132"/>
-    </row>
-    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="145"/>
-      <c r="C8" s="51" t="s">
-        <v>387</v>
-      </c>
-      <c r="D8" s="130" t="s">
-        <v>389</v>
-      </c>
-      <c r="E8" s="132"/>
-      <c r="F8" s="134" t="s">
-        <v>217</v>
-      </c>
-      <c r="G8" s="135"/>
-      <c r="H8" s="135"/>
-      <c r="I8" s="135"/>
-      <c r="J8" s="135"/>
-      <c r="K8" s="130" t="s">
-        <v>213</v>
-      </c>
-      <c r="L8" s="131"/>
-      <c r="M8" s="132"/>
-    </row>
-    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="146"/>
-      <c r="C9" s="91" t="s">
-        <v>388</v>
-      </c>
-      <c r="D9" s="130" t="s">
-        <v>389</v>
-      </c>
-      <c r="E9" s="132"/>
-      <c r="F9" s="134" t="s">
-        <v>218</v>
-      </c>
-      <c r="G9" s="135"/>
-      <c r="H9" s="135"/>
-      <c r="I9" s="135"/>
-      <c r="J9" s="136"/>
-      <c r="K9" s="130" t="s">
-        <v>390</v>
-      </c>
-      <c r="L9" s="131"/>
-      <c r="M9" s="132"/>
+      <c r="G9" s="138"/>
+      <c r="H9" s="138"/>
+      <c r="I9" s="138"/>
+      <c r="J9" s="139"/>
+      <c r="K9" s="133" t="s">
+        <v>376</v>
+      </c>
+      <c r="L9" s="134"/>
+      <c r="M9" s="135"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -4714,7 +5198,7 @@
   <sheetPr>
     <tabColor theme="6" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="B1:M27"/>
+  <dimension ref="B1:M32"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
@@ -4727,19 +5211,19 @@
         <v>13</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1">
@@ -4747,7 +5231,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>17</v>
@@ -4839,390 +5323,413 @@
       <c r="G8" s="18"/>
     </row>
     <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="80"/>
-      <c r="C9" s="80"/>
-      <c r="D9" s="80"/>
-      <c r="E9" s="80"/>
-      <c r="F9" s="80"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="80"/>
+      <c r="B9" s="79"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="79"/>
+      <c r="G9" s="79"/>
+      <c r="H9" s="79"/>
     </row>
     <row r="10" spans="2:13" ht="26.25" customHeight="1">
-      <c r="B10" s="71" t="s">
+      <c r="B10" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="140" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="141"/>
+      <c r="F10" s="140" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="142"/>
+      <c r="H10" s="142"/>
+      <c r="I10" s="142"/>
+      <c r="J10" s="141"/>
+      <c r="K10" s="140" t="s">
+        <v>100</v>
+      </c>
+      <c r="L10" s="142"/>
+      <c r="M10" s="141"/>
+    </row>
+    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B11" s="147" t="s">
+        <v>407</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="133" t="s">
+        <v>378</v>
+      </c>
+      <c r="E11" s="135"/>
+      <c r="F11" s="137" t="s">
+        <v>380</v>
+      </c>
+      <c r="G11" s="138"/>
+      <c r="H11" s="138"/>
+      <c r="I11" s="138"/>
+      <c r="J11" s="139"/>
+      <c r="K11" s="136"/>
+      <c r="L11" s="136"/>
+      <c r="M11" s="136"/>
+    </row>
+    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B12" s="149"/>
+      <c r="C12" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="133" t="s">
+        <v>379</v>
+      </c>
+      <c r="E12" s="135"/>
+      <c r="F12" s="137" t="s">
+        <v>381</v>
+      </c>
+      <c r="G12" s="138"/>
+      <c r="H12" s="138"/>
+      <c r="I12" s="138"/>
+      <c r="J12" s="139"/>
+      <c r="K12" s="136"/>
+      <c r="L12" s="136"/>
+      <c r="M12" s="136"/>
+    </row>
+    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B13" s="150" t="s">
+        <v>408</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="161" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="162"/>
+      <c r="F13" s="137" t="s">
+        <v>382</v>
+      </c>
+      <c r="G13" s="138"/>
+      <c r="H13" s="138"/>
+      <c r="I13" s="138"/>
+      <c r="J13" s="139"/>
+      <c r="K13" s="136"/>
+      <c r="L13" s="136"/>
+      <c r="M13" s="136"/>
+    </row>
+    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B14" s="150"/>
+      <c r="C14" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="C10" s="72" t="s">
+      <c r="D14" s="161" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="162"/>
+      <c r="F14" s="137" t="s">
+        <v>383</v>
+      </c>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+    </row>
+    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B15" s="150"/>
+      <c r="C15" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="161" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="162"/>
+      <c r="F15" s="137" t="s">
+        <v>384</v>
+      </c>
+      <c r="G15" s="138"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="136"/>
+      <c r="L15" s="136"/>
+      <c r="M15" s="136"/>
+    </row>
+    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B16" s="150"/>
+      <c r="C16" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="137" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" s="138"/>
-      <c r="F10" s="137" t="s">
-        <v>84</v>
-      </c>
-      <c r="G10" s="139"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="139"/>
-      <c r="J10" s="138"/>
-      <c r="K10" s="137" t="s">
-        <v>103</v>
-      </c>
-      <c r="L10" s="139"/>
-      <c r="M10" s="138"/>
-    </row>
-    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="144" t="s">
-        <v>421</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="130" t="s">
+      <c r="D16" s="161" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="162"/>
+      <c r="F16" s="137" t="s">
+        <v>385</v>
+      </c>
+      <c r="G16" s="138"/>
+      <c r="H16" s="138"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="139"/>
+      <c r="K16" s="133"/>
+      <c r="L16" s="134"/>
+      <c r="M16" s="135"/>
+    </row>
+    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B17" s="150" t="s">
+        <v>409</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="163" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="164"/>
+      <c r="F17" s="137" t="s">
+        <v>386</v>
+      </c>
+      <c r="G17" s="138"/>
+      <c r="H17" s="138"/>
+      <c r="I17" s="138"/>
+      <c r="J17" s="138"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+    </row>
+    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B18" s="150"/>
+      <c r="C18" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="165" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="166"/>
+      <c r="F18" s="137" t="s">
+        <v>387</v>
+      </c>
+      <c r="G18" s="138"/>
+      <c r="H18" s="138"/>
+      <c r="I18" s="138"/>
+      <c r="J18" s="138"/>
+      <c r="K18" s="136"/>
+      <c r="L18" s="136"/>
+      <c r="M18" s="136"/>
+    </row>
+    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B19" s="150"/>
+      <c r="C19" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="165" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="166"/>
+      <c r="F19" s="137" t="s">
+        <v>388</v>
+      </c>
+      <c r="G19" s="138"/>
+      <c r="H19" s="138"/>
+      <c r="I19" s="138"/>
+      <c r="J19" s="138"/>
+      <c r="K19" s="136"/>
+      <c r="L19" s="136"/>
+      <c r="M19" s="136"/>
+    </row>
+    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B20" s="147" t="s">
+        <v>389</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="165" t="s">
+        <v>390</v>
+      </c>
+      <c r="E20" s="166"/>
+      <c r="F20" s="143" t="s">
+        <v>399</v>
+      </c>
+      <c r="G20" s="143"/>
+      <c r="H20" s="143"/>
+      <c r="I20" s="143"/>
+      <c r="J20" s="143"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="136"/>
+    </row>
+    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B21" s="148"/>
+      <c r="C21" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="161" t="s">
+        <v>391</v>
+      </c>
+      <c r="E21" s="162"/>
+      <c r="F21" s="143" t="s">
+        <v>400</v>
+      </c>
+      <c r="G21" s="143"/>
+      <c r="H21" s="143"/>
+      <c r="I21" s="143"/>
+      <c r="J21" s="143"/>
+      <c r="K21" s="136"/>
+      <c r="L21" s="136"/>
+      <c r="M21" s="136"/>
+    </row>
+    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B22" s="148"/>
+      <c r="C22" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="163" t="s">
         <v>392</v>
       </c>
-      <c r="E11" s="132"/>
-      <c r="F11" s="134" t="s">
+      <c r="E22" s="164"/>
+      <c r="F22" s="143" t="s">
+        <v>401</v>
+      </c>
+      <c r="G22" s="143"/>
+      <c r="H22" s="143"/>
+      <c r="I22" s="143"/>
+      <c r="J22" s="143"/>
+      <c r="K22" s="136"/>
+      <c r="L22" s="136"/>
+      <c r="M22" s="136"/>
+    </row>
+    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B23" s="149"/>
+      <c r="C23" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="163" t="s">
+        <v>393</v>
+      </c>
+      <c r="E23" s="164"/>
+      <c r="F23" s="143" t="s">
+        <v>402</v>
+      </c>
+      <c r="G23" s="143"/>
+      <c r="H23" s="143"/>
+      <c r="I23" s="143"/>
+      <c r="J23" s="143"/>
+      <c r="K23" s="136"/>
+      <c r="L23" s="136"/>
+      <c r="M23" s="136"/>
+    </row>
+    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B24" s="167" t="s">
         <v>394</v>
       </c>
-      <c r="G11" s="135"/>
-      <c r="H11" s="135"/>
-      <c r="I11" s="135"/>
-      <c r="J11" s="136"/>
-      <c r="K11" s="133"/>
-      <c r="L11" s="133"/>
-      <c r="M11" s="133"/>
-    </row>
-    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="146"/>
-      <c r="C12" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" s="130" t="s">
-        <v>393</v>
-      </c>
-      <c r="E12" s="132"/>
-      <c r="F12" s="134" t="s">
+      <c r="C24" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="133" t="s">
         <v>395</v>
       </c>
-      <c r="G12" s="135"/>
-      <c r="H12" s="135"/>
-      <c r="I12" s="135"/>
-      <c r="J12" s="136"/>
-      <c r="K12" s="133"/>
-      <c r="L12" s="133"/>
-      <c r="M12" s="133"/>
-    </row>
-    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="147" t="s">
-        <v>422</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="158" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="159"/>
-      <c r="F13" s="134" t="s">
+      <c r="E24" s="135"/>
+      <c r="F24" s="143" t="s">
+        <v>403</v>
+      </c>
+      <c r="G24" s="143"/>
+      <c r="H24" s="143"/>
+      <c r="I24" s="143"/>
+      <c r="J24" s="143"/>
+      <c r="K24" s="136"/>
+      <c r="L24" s="136"/>
+      <c r="M24" s="136"/>
+    </row>
+    <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B25" s="168"/>
+      <c r="C25" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="133" t="s">
         <v>396</v>
       </c>
-      <c r="G13" s="135"/>
-      <c r="H13" s="135"/>
-      <c r="I13" s="135"/>
-      <c r="J13" s="136"/>
-      <c r="K13" s="133"/>
-      <c r="L13" s="133"/>
-      <c r="M13" s="133"/>
-    </row>
-    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B14" s="147"/>
-      <c r="C14" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" s="158" t="s">
-        <v>73</v>
-      </c>
-      <c r="E14" s="159"/>
-      <c r="F14" s="134" t="s">
+      <c r="E25" s="135"/>
+      <c r="F25" s="143" t="s">
+        <v>404</v>
+      </c>
+      <c r="G25" s="143"/>
+      <c r="H25" s="143"/>
+      <c r="I25" s="143"/>
+      <c r="J25" s="143"/>
+      <c r="K25" s="136"/>
+      <c r="L25" s="136"/>
+      <c r="M25" s="136"/>
+    </row>
+    <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B26" s="168"/>
+      <c r="C26" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="133" t="s">
         <v>397</v>
       </c>
-      <c r="G14" s="135"/>
-      <c r="H14" s="135"/>
-      <c r="I14" s="135"/>
-      <c r="J14" s="136"/>
-      <c r="K14" s="133"/>
-      <c r="L14" s="133"/>
-      <c r="M14" s="133"/>
-    </row>
-    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B15" s="147"/>
-      <c r="C15" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="D15" s="158" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="159"/>
-      <c r="F15" s="134" t="s">
+      <c r="E26" s="135"/>
+      <c r="F26" s="143" t="s">
+        <v>405</v>
+      </c>
+      <c r="G26" s="143"/>
+      <c r="H26" s="143"/>
+      <c r="I26" s="143"/>
+      <c r="J26" s="143"/>
+      <c r="K26" s="136"/>
+      <c r="L26" s="136"/>
+      <c r="M26" s="136"/>
+    </row>
+    <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B27" s="169"/>
+      <c r="C27" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="133" t="s">
         <v>398</v>
       </c>
-      <c r="G15" s="135"/>
-      <c r="H15" s="135"/>
-      <c r="I15" s="135"/>
-      <c r="J15" s="136"/>
-      <c r="K15" s="133"/>
-      <c r="L15" s="133"/>
-      <c r="M15" s="133"/>
-    </row>
-    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B16" s="147"/>
-      <c r="C16" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="158" t="s">
-        <v>74</v>
-      </c>
-      <c r="E16" s="159"/>
-      <c r="F16" s="134" t="s">
-        <v>399</v>
-      </c>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135"/>
-      <c r="I16" s="135"/>
-      <c r="J16" s="136"/>
-      <c r="K16" s="130"/>
-      <c r="L16" s="131"/>
-      <c r="M16" s="132"/>
-    </row>
-    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B17" s="147" t="s">
-        <v>423</v>
-      </c>
-      <c r="C17" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" s="160" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="161"/>
-      <c r="F17" s="134" t="s">
-        <v>400</v>
-      </c>
-      <c r="G17" s="135"/>
-      <c r="H17" s="135"/>
-      <c r="I17" s="135"/>
-      <c r="J17" s="135"/>
-      <c r="K17" s="133"/>
-      <c r="L17" s="133"/>
-      <c r="M17" s="133"/>
-    </row>
-    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B18" s="147"/>
-      <c r="C18" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" s="162" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="163"/>
-      <c r="F18" s="134" t="s">
-        <v>401</v>
-      </c>
-      <c r="G18" s="135"/>
-      <c r="H18" s="135"/>
-      <c r="I18" s="135"/>
-      <c r="J18" s="135"/>
-      <c r="K18" s="133"/>
-      <c r="L18" s="133"/>
-      <c r="M18" s="133"/>
-    </row>
-    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B19" s="147"/>
-      <c r="C19" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" s="162" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="163"/>
-      <c r="F19" s="134" t="s">
-        <v>402</v>
-      </c>
-      <c r="G19" s="135"/>
-      <c r="H19" s="135"/>
-      <c r="I19" s="135"/>
-      <c r="J19" s="135"/>
-      <c r="K19" s="133"/>
-      <c r="L19" s="133"/>
-      <c r="M19" s="133"/>
-    </row>
-    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B20" s="144" t="s">
-        <v>403</v>
-      </c>
-      <c r="C20" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="162" t="s">
-        <v>404</v>
-      </c>
-      <c r="E20" s="163"/>
-      <c r="F20" s="140" t="s">
-        <v>413</v>
-      </c>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="140"/>
-      <c r="J20" s="140"/>
-      <c r="K20" s="133"/>
-      <c r="L20" s="133"/>
-      <c r="M20" s="133"/>
-    </row>
-    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="145"/>
-      <c r="C21" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" s="158" t="s">
-        <v>405</v>
-      </c>
-      <c r="E21" s="159"/>
-      <c r="F21" s="140" t="s">
-        <v>414</v>
-      </c>
-      <c r="G21" s="140"/>
-      <c r="H21" s="140"/>
-      <c r="I21" s="140"/>
-      <c r="J21" s="140"/>
-      <c r="K21" s="133"/>
-      <c r="L21" s="133"/>
-      <c r="M21" s="133"/>
-    </row>
-    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B22" s="145"/>
-      <c r="C22" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="D22" s="160" t="s">
+      <c r="E27" s="135"/>
+      <c r="F27" s="143" t="s">
         <v>406</v>
       </c>
-      <c r="E22" s="161"/>
-      <c r="F22" s="140" t="s">
-        <v>415</v>
-      </c>
-      <c r="G22" s="140"/>
-      <c r="H22" s="140"/>
-      <c r="I22" s="140"/>
-      <c r="J22" s="140"/>
-      <c r="K22" s="133"/>
-      <c r="L22" s="133"/>
-      <c r="M22" s="133"/>
-    </row>
-    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B23" s="146"/>
-      <c r="C23" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" s="160" t="s">
-        <v>407</v>
-      </c>
-      <c r="E23" s="161"/>
-      <c r="F23" s="140" t="s">
-        <v>416</v>
-      </c>
-      <c r="G23" s="140"/>
-      <c r="H23" s="140"/>
-      <c r="I23" s="140"/>
-      <c r="J23" s="140"/>
-      <c r="K23" s="133"/>
-      <c r="L23" s="133"/>
-      <c r="M23" s="133"/>
-    </row>
-    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B24" s="164" t="s">
-        <v>408</v>
-      </c>
-      <c r="C24" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="D24" s="130" t="s">
-        <v>409</v>
-      </c>
-      <c r="E24" s="132"/>
-      <c r="F24" s="140" t="s">
-        <v>417</v>
-      </c>
-      <c r="G24" s="140"/>
-      <c r="H24" s="140"/>
-      <c r="I24" s="140"/>
-      <c r="J24" s="140"/>
-      <c r="K24" s="133"/>
-      <c r="L24" s="133"/>
-      <c r="M24" s="133"/>
-    </row>
-    <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B25" s="165"/>
-      <c r="C25" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" s="130" t="s">
-        <v>410</v>
-      </c>
-      <c r="E25" s="132"/>
-      <c r="F25" s="140" t="s">
-        <v>418</v>
-      </c>
-      <c r="G25" s="140"/>
-      <c r="H25" s="140"/>
-      <c r="I25" s="140"/>
-      <c r="J25" s="140"/>
-      <c r="K25" s="133"/>
-      <c r="L25" s="133"/>
-      <c r="M25" s="133"/>
-    </row>
-    <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B26" s="165"/>
-      <c r="C26" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" s="130" t="s">
-        <v>411</v>
-      </c>
-      <c r="E26" s="132"/>
-      <c r="F26" s="140" t="s">
-        <v>419</v>
-      </c>
-      <c r="G26" s="140"/>
-      <c r="H26" s="140"/>
-      <c r="I26" s="140"/>
-      <c r="J26" s="140"/>
-      <c r="K26" s="133"/>
-      <c r="L26" s="133"/>
-      <c r="M26" s="133"/>
-    </row>
-    <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B27" s="166"/>
-      <c r="C27" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" s="130" t="s">
-        <v>412</v>
-      </c>
-      <c r="E27" s="132"/>
-      <c r="F27" s="140" t="s">
-        <v>420</v>
-      </c>
-      <c r="G27" s="140"/>
-      <c r="H27" s="140"/>
-      <c r="I27" s="140"/>
-      <c r="J27" s="140"/>
-      <c r="K27" s="133"/>
-      <c r="L27" s="133"/>
-      <c r="M27" s="133"/>
+      <c r="G27" s="143"/>
+      <c r="H27" s="143"/>
+      <c r="I27" s="143"/>
+      <c r="J27" s="143"/>
+      <c r="K27" s="136"/>
+      <c r="L27" s="136"/>
+      <c r="M27" s="136"/>
+    </row>
+    <row r="28" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B28" s="193" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B29" s="194"/>
+    </row>
+    <row r="30" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B30" s="194"/>
+    </row>
+    <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B31" s="195"/>
+    </row>
+    <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B32" s="197" t="s">
+        <v>512</v>
+      </c>
+      <c r="D32" s="197" t="s">
+        <v>513</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells count="60">
+    <mergeCell ref="B28:B31"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="F27:J27"/>
     <mergeCell ref="K27:M27"/>
@@ -5298,72 +5805,83 @@
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.875" customWidth="1"/>
-    <col min="2" max="2" width="79.75" style="107" customWidth="1"/>
+    <col min="2" max="2" width="79.75" style="106" customWidth="1"/>
     <col min="3" max="4" width="9.375" customWidth="1"/>
-    <col min="5" max="5" width="47.125" style="107" customWidth="1"/>
+    <col min="5" max="5" width="47.125" style="106" customWidth="1"/>
     <col min="6" max="6" width="19.875" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="106" t="s">
-        <v>475</v>
-      </c>
-      <c r="B1" s="120"/>
+      <c r="A1" s="105" t="s">
+        <v>459</v>
+      </c>
+      <c r="B1" s="119"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" thickBot="1">
-      <c r="A2" s="108" t="s">
-        <v>476</v>
-      </c>
-      <c r="B2" s="167"/>
-      <c r="C2" s="168"/>
-      <c r="D2" s="121"/>
-    </row>
-    <row r="3" spans="1:7" s="114" customFormat="1" ht="19.5" thickBot="1">
-      <c r="A3" s="109" t="s">
-        <v>477</v>
-      </c>
-      <c r="B3" s="110" t="s">
-        <v>478</v>
-      </c>
-      <c r="C3" s="111" t="s">
-        <v>479</v>
-      </c>
-      <c r="D3" s="112" t="s">
-        <v>480</v>
-      </c>
-      <c r="E3" s="113" t="s">
+      <c r="A2" s="107" t="s">
+        <v>460</v>
+      </c>
+      <c r="B2" s="170"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="120"/>
+    </row>
+    <row r="3" spans="1:7" s="113" customFormat="1" ht="19.5" thickBot="1">
+      <c r="A3" s="108" t="s">
+        <v>461</v>
+      </c>
+      <c r="B3" s="109" t="s">
+        <v>462</v>
+      </c>
+      <c r="C3" s="110" t="s">
+        <v>463</v>
+      </c>
+      <c r="D3" s="111" t="s">
+        <v>464</v>
+      </c>
+      <c r="E3" s="112" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="13.5" customHeight="1">
+      <c r="B4" s="174" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="13.5" customHeight="1">
-      <c r="F4" s="169" t="s">
-        <v>482</v>
-      </c>
-      <c r="G4" s="169"/>
+      <c r="F4" s="172" t="s">
+        <v>466</v>
+      </c>
+      <c r="G4" s="172"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="F5" s="169"/>
-      <c r="G5" s="169"/>
+      <c r="B5" s="174" t="s">
+        <v>484</v>
+      </c>
+      <c r="F5" s="172"/>
+      <c r="G5" s="172"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="F6" s="169"/>
-      <c r="G6" s="169"/>
+      <c r="B6" s="174" t="s">
+        <v>502</v>
+      </c>
+      <c r="F6" s="172"/>
+      <c r="G6" s="172"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="B7"/>
-      <c r="F7" s="115" t="s">
-        <v>483</v>
-      </c>
-      <c r="G7" s="116"/>
+      <c r="B7" s="196" t="s">
+        <v>511</v>
+      </c>
+      <c r="F7" s="114" t="s">
+        <v>467</v>
+      </c>
+      <c r="G7" s="115"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="F8" s="115"/>
-      <c r="G8" s="115"/>
+      <c r="F8" s="114"/>
+      <c r="G8" s="114"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="F9" s="115"/>
-      <c r="G9" s="115"/>
+      <c r="F9" s="114"/>
+      <c r="G9" s="114"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5387,48 +5905,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1">
-      <c r="A1" s="117" t="s">
-        <v>484</v>
-      </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
+      <c r="A1" s="116" t="s">
+        <v>468</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="117" t="s">
-        <v>485</v>
-      </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
+      <c r="A7" s="116" t="s">
+        <v>469</v>
+      </c>
+      <c r="B7" s="117"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="117"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="117" t="s">
-        <v>486</v>
-      </c>
-      <c r="B15" s="118"/>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="118"/>
+      <c r="A15" s="116" t="s">
+        <v>470</v>
+      </c>
+      <c r="B15" s="117"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="117"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="117" t="s">
-        <v>487</v>
-      </c>
-      <c r="B22" s="118"/>
-      <c r="C22" s="118"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="118"/>
-      <c r="G22" s="118"/>
+      <c r="A22" s="116" t="s">
+        <v>471</v>
+      </c>
+      <c r="B22" s="117"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="117"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="117"/>
+      <c r="G22" s="117"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5452,40 +5970,40 @@
     <row r="1" spans="2:13" ht="6" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:13" ht="39.75" customHeight="1" thickBot="1">
       <c r="B2" s="53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D2" s="42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2" s="42" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="42" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G2" s="42" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H2" s="42" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="79" t="s">
+      <c r="J2" s="78" t="s">
         <v>2</v>
       </c>
       <c r="K2" s="42" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L2" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="M2" s="119" t="s">
-        <v>488</v>
+        <v>45</v>
+      </c>
+      <c r="M2" s="118" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="24.95" customHeight="1">
@@ -5496,35 +6014,35 @@
         <v>3</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F3" s="43">
         <v>0</v>
       </c>
       <c r="G3" s="29" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H3" s="21" t="s">
         <v>27</v>
       </c>
       <c r="I3" s="29" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="K3" s="29" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="L3" s="47" t="s">
         <v>11</v>
       </c>
       <c r="M3" s="47"/>
     </row>
-    <row r="4" spans="2:13" ht="24.95" customHeight="1">
+    <row r="4" spans="2:13" ht="24.95" customHeight="1" thickBot="1">
       <c r="B4" s="55" t="s">
         <v>29</v>
       </c>
@@ -5532,24 +6050,26 @@
         <v>4</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>452</v>
-      </c>
-      <c r="G4" s="30"/>
+        <v>438</v>
+      </c>
+      <c r="G4" s="175" t="s">
+        <v>489</v>
+      </c>
       <c r="H4" s="23" t="s">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="J4" s="24"/>
       <c r="K4" s="30" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="L4" s="48" t="s">
         <v>12</v>
@@ -5557,68 +6077,76 @@
       <c r="M4" s="48"/>
     </row>
     <row r="5" spans="2:13" ht="24.95" customHeight="1">
-      <c r="B5" s="55" t="s">
-        <v>30</v>
+      <c r="B5" s="34" t="s">
+        <v>473</v>
       </c>
       <c r="C5" s="30" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>455</v>
-      </c>
-      <c r="G5" s="30"/>
+        <v>441</v>
+      </c>
+      <c r="G5" s="175" t="s">
+        <v>490</v>
+      </c>
       <c r="H5" s="23"/>
-      <c r="I5" s="68"/>
+      <c r="I5" s="188" t="s">
+        <v>496</v>
+      </c>
       <c r="J5" s="24"/>
-      <c r="K5" s="30"/>
+      <c r="K5" s="175" t="s">
+        <v>506</v>
+      </c>
       <c r="L5" s="48"/>
       <c r="M5" s="48"/>
     </row>
     <row r="6" spans="2:13" ht="24.95" customHeight="1">
       <c r="B6" s="44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" s="30" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>452</v>
+        <v>485</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="23"/>
       <c r="I6" s="30"/>
       <c r="J6" s="24"/>
-      <c r="K6" s="30"/>
+      <c r="K6" s="175" t="s">
+        <v>507</v>
+      </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
     </row>
-    <row r="7" spans="2:13" ht="24.95" customHeight="1">
+    <row r="7" spans="2:13" ht="24.95" customHeight="1" thickBot="1">
       <c r="B7" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="76" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="92" t="s">
-        <v>32</v>
+        <v>201</v>
+      </c>
+      <c r="E7" s="91" t="s">
+        <v>31</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="G7" s="30"/>
       <c r="H7" s="23"/>
@@ -5630,19 +6158,19 @@
     </row>
     <row r="8" spans="2:13" ht="24.95" customHeight="1">
       <c r="B8" s="44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="92" t="s">
-        <v>33</v>
+      <c r="D8" s="34" t="s">
+        <v>482</v>
+      </c>
+      <c r="E8" s="91" t="s">
+        <v>32</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="G8" s="30"/>
       <c r="H8" s="23"/>
@@ -5653,14 +6181,16 @@
       <c r="M8" s="48"/>
     </row>
     <row r="9" spans="2:13" ht="24.95" customHeight="1">
-      <c r="B9" s="44"/>
+      <c r="B9" s="173" t="s">
+        <v>476</v>
+      </c>
       <c r="C9" s="30" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="30"/>
       <c r="F9" s="23" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="G9" s="30"/>
       <c r="H9" s="23"/>
@@ -5671,13 +6201,17 @@
       <c r="M9" s="48"/>
     </row>
     <row r="10" spans="2:13" ht="24.95" customHeight="1">
-      <c r="B10" s="44"/>
-      <c r="C10" s="77" t="s">
+      <c r="B10" s="173" t="s">
+        <v>477</v>
+      </c>
+      <c r="C10" s="76" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="23"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="23"/>
+      <c r="F10" s="175" t="s">
+        <v>486</v>
+      </c>
       <c r="G10" s="30"/>
       <c r="H10" s="23"/>
       <c r="I10" s="30"/>
@@ -5687,8 +6221,10 @@
       <c r="M10" s="48"/>
     </row>
     <row r="11" spans="2:13" ht="24.95" customHeight="1">
-      <c r="B11" s="45"/>
-      <c r="C11" s="78" t="s">
+      <c r="B11" s="173" t="s">
+        <v>478</v>
+      </c>
+      <c r="C11" s="77" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="25"/>
@@ -5703,7 +6239,9 @@
       <c r="M11" s="49"/>
     </row>
     <row r="12" spans="2:13" ht="24.95" customHeight="1">
-      <c r="B12" s="45"/>
+      <c r="B12" s="173" t="s">
+        <v>479</v>
+      </c>
       <c r="C12" s="30"/>
       <c r="D12" s="25"/>
       <c r="E12" s="33"/>
@@ -5717,7 +6255,9 @@
       <c r="M12" s="49"/>
     </row>
     <row r="13" spans="2:13" ht="24.95" customHeight="1">
-      <c r="B13" s="45"/>
+      <c r="B13" s="173" t="s">
+        <v>480</v>
+      </c>
       <c r="C13" s="30"/>
       <c r="D13" s="25"/>
       <c r="E13" s="33"/>
@@ -5802,30 +6342,30 @@
     </row>
     <row r="19" spans="2:13" s="37" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B19" s="34" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="D19" s="54" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="E19" s="37" t="s">
-        <v>432</v>
-      </c>
-      <c r="F19" s="77" t="s">
+        <v>418</v>
+      </c>
+      <c r="F19" s="76" t="s">
         <v>10</v>
       </c>
       <c r="G19" s="37" t="s">
-        <v>431</v>
-      </c>
-      <c r="H19" s="93" t="s">
-        <v>437</v>
+        <v>417</v>
+      </c>
+      <c r="H19" s="92" t="s">
+        <v>423</v>
       </c>
       <c r="I19" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="J19" s="94"/>
+        <v>420</v>
+      </c>
+      <c r="J19" s="93"/>
       <c r="K19" s="67"/>
     </row>
   </sheetData>
@@ -5854,7 +6394,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="B1:M41"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
@@ -5864,59 +6404,59 @@
     <row r="1" spans="2:13" ht="9.75" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:13" ht="26.25" thickBot="1">
       <c r="B2" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="K2" s="16" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="84" t="s">
-        <v>350</v>
-      </c>
-      <c r="C3" s="70" t="s">
+      <c r="B3" s="83" t="s">
+        <v>341</v>
+      </c>
+      <c r="C3" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="70" t="s">
+      <c r="D3" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="70" t="s">
+      <c r="E3" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="70" t="s">
+      <c r="F3" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="70" t="s">
+      <c r="G3" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="85" t="s">
+      <c r="H3" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="83"/>
+      <c r="I3" s="82"/>
       <c r="J3" s="57" t="s">
         <v>18</v>
       </c>
@@ -5928,8 +6468,8 @@
       </c>
     </row>
     <row r="4" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B4" s="86" t="s">
-        <v>351</v>
+      <c r="B4" s="85" t="s">
+        <v>342</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>26</v>
@@ -5949,7 +6489,7 @@
       <c r="H4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="83"/>
+      <c r="I4" s="82"/>
       <c r="J4" s="58" t="s">
         <v>22</v>
       </c>
@@ -5968,7 +6508,7 @@
       <c r="F5" s="36"/>
       <c r="G5" s="36"/>
       <c r="H5" s="36"/>
-      <c r="I5" s="83"/>
+      <c r="I5" s="82"/>
       <c r="J5" s="58" t="s">
         <v>19</v>
       </c>
@@ -5987,7 +6527,7 @@
       <c r="F6" s="36"/>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
-      <c r="I6" s="83"/>
+      <c r="I6" s="82"/>
       <c r="J6" s="58" t="s">
         <v>20</v>
       </c>
@@ -6006,7 +6546,7 @@
       <c r="F7" s="36"/>
       <c r="G7" s="36"/>
       <c r="H7" s="36"/>
-      <c r="I7" s="83"/>
+      <c r="I7" s="82"/>
       <c r="J7" s="59" t="s">
         <v>24</v>
       </c>
@@ -6025,7 +6565,7 @@
       <c r="F8" s="36"/>
       <c r="G8" s="36"/>
       <c r="H8" s="36"/>
-      <c r="I8" s="83"/>
+      <c r="I8" s="82"/>
       <c r="J8" s="60" t="s">
         <v>23</v>
       </c>
@@ -6045,649 +6585,780 @@
       <c r="G9" s="36"/>
       <c r="H9" s="36"/>
       <c r="I9" s="20"/>
-      <c r="J9" s="87"/>
-      <c r="K9" s="87"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="86"/>
     </row>
     <row r="10" spans="2:13" ht="26.25" customHeight="1">
-      <c r="B10" s="71" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" s="72" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" s="137" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" s="138"/>
-      <c r="F10" s="137" t="s">
+      <c r="B10" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="140" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="141"/>
+      <c r="F10" s="140" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="142"/>
+      <c r="H10" s="142"/>
+      <c r="I10" s="142"/>
+      <c r="J10" s="141"/>
+      <c r="K10" s="140" t="s">
+        <v>100</v>
+      </c>
+      <c r="L10" s="142"/>
+      <c r="M10" s="141"/>
+    </row>
+    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B11" s="150" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="144" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="133" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="135"/>
+      <c r="F11" s="137" t="s">
+        <v>89</v>
+      </c>
+      <c r="G11" s="138"/>
+      <c r="H11" s="138"/>
+      <c r="I11" s="138"/>
+      <c r="J11" s="139"/>
+      <c r="K11" s="133" t="s">
+        <v>99</v>
+      </c>
+      <c r="L11" s="134"/>
+      <c r="M11" s="135"/>
+    </row>
+    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B12" s="150"/>
+      <c r="C12" s="145"/>
+      <c r="D12" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="135"/>
+      <c r="F12" s="137" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="138"/>
+      <c r="H12" s="138"/>
+      <c r="I12" s="138"/>
+      <c r="J12" s="139"/>
+      <c r="K12" s="133"/>
+      <c r="L12" s="134"/>
+      <c r="M12" s="135"/>
+    </row>
+    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B13" s="150"/>
+      <c r="C13" s="145"/>
+      <c r="D13" s="133" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="139"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="139"/>
-      <c r="J10" s="138"/>
-      <c r="K10" s="137" t="s">
-        <v>103</v>
-      </c>
-      <c r="L10" s="139"/>
-      <c r="M10" s="138"/>
-    </row>
-    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="147" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="141" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" s="130" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="132"/>
-      <c r="F11" s="134" t="s">
-        <v>92</v>
-      </c>
-      <c r="G11" s="135"/>
-      <c r="H11" s="135"/>
-      <c r="I11" s="135"/>
-      <c r="J11" s="136"/>
-      <c r="K11" s="130" t="s">
-        <v>102</v>
-      </c>
-      <c r="L11" s="131"/>
-      <c r="M11" s="132"/>
-    </row>
-    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="147"/>
-      <c r="C12" s="142"/>
-      <c r="D12" s="130" t="s">
-        <v>86</v>
-      </c>
-      <c r="E12" s="132"/>
-      <c r="F12" s="134" t="s">
-        <v>89</v>
-      </c>
-      <c r="G12" s="135"/>
-      <c r="H12" s="135"/>
-      <c r="I12" s="135"/>
-      <c r="J12" s="136"/>
-      <c r="K12" s="130"/>
-      <c r="L12" s="131"/>
-      <c r="M12" s="132"/>
-    </row>
-    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="147"/>
-      <c r="C13" s="142"/>
-      <c r="D13" s="130" t="s">
+      <c r="E13" s="135"/>
+      <c r="F13" s="137" t="s">
         <v>87</v>
       </c>
-      <c r="E13" s="132"/>
-      <c r="F13" s="134" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="135"/>
-      <c r="H13" s="135"/>
-      <c r="I13" s="135"/>
-      <c r="J13" s="136"/>
+      <c r="G13" s="138"/>
+      <c r="H13" s="138"/>
+      <c r="I13" s="138"/>
+      <c r="J13" s="139"/>
       <c r="K13" s="63"/>
       <c r="L13" s="64"/>
       <c r="M13" s="65"/>
     </row>
     <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B14" s="147"/>
-      <c r="C14" s="143"/>
-      <c r="D14" s="130" t="s">
+      <c r="B14" s="150"/>
+      <c r="C14" s="146"/>
+      <c r="D14" s="133" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="135"/>
+      <c r="F14" s="137" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="132"/>
-      <c r="F14" s="134" t="s">
-        <v>91</v>
-      </c>
-      <c r="G14" s="135"/>
-      <c r="H14" s="135"/>
-      <c r="I14" s="135"/>
-      <c r="J14" s="136"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="139"/>
       <c r="K14" s="63"/>
       <c r="L14" s="64"/>
       <c r="M14" s="65"/>
     </row>
     <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B15" s="147"/>
-      <c r="C15" s="141" t="s">
+      <c r="B15" s="150"/>
+      <c r="C15" s="144" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="133" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="135"/>
+      <c r="F15" s="137" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="138"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="134"/>
+      <c r="M15" s="135"/>
+    </row>
+    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B16" s="150"/>
+      <c r="C16" s="145"/>
+      <c r="D16" s="133" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16" s="135"/>
+      <c r="F16" s="137" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="138"/>
+      <c r="H16" s="138"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="139"/>
+      <c r="K16" s="133"/>
+      <c r="L16" s="134"/>
+      <c r="M16" s="135"/>
+    </row>
+    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B17" s="150"/>
+      <c r="C17" s="145"/>
+      <c r="D17" s="133" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="135"/>
+      <c r="F17" s="137" t="s">
+        <v>95</v>
+      </c>
+      <c r="G17" s="138"/>
+      <c r="H17" s="138"/>
+      <c r="I17" s="138"/>
+      <c r="J17" s="138"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+    </row>
+    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B18" s="150"/>
+      <c r="C18" s="146"/>
+      <c r="D18" s="133" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="135"/>
+      <c r="F18" s="137" t="s">
+        <v>96</v>
+      </c>
+      <c r="G18" s="138"/>
+      <c r="H18" s="138"/>
+      <c r="I18" s="138"/>
+      <c r="J18" s="138"/>
+      <c r="K18" s="136"/>
+      <c r="L18" s="136"/>
+      <c r="M18" s="136"/>
+    </row>
+    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B19" s="150"/>
+      <c r="C19" s="66" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="133" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="135"/>
+      <c r="F19" s="143" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="143"/>
+      <c r="H19" s="143"/>
+      <c r="I19" s="143"/>
+      <c r="J19" s="143"/>
+      <c r="K19" s="136"/>
+      <c r="L19" s="136"/>
+      <c r="M19" s="136"/>
+    </row>
+    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B20" s="150"/>
+      <c r="C20" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="133" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="135"/>
+      <c r="F20" s="143" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="143"/>
+      <c r="H20" s="143"/>
+      <c r="I20" s="143"/>
+      <c r="J20" s="143"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="136"/>
+    </row>
+    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B21" s="150"/>
+      <c r="C21" s="66" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="133" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="135"/>
+      <c r="F21" s="143" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="143"/>
+      <c r="H21" s="143"/>
+      <c r="I21" s="143"/>
+      <c r="J21" s="143"/>
+      <c r="K21" s="136"/>
+      <c r="L21" s="136"/>
+      <c r="M21" s="136"/>
+    </row>
+    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B22" s="150"/>
+      <c r="C22" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="130" t="s">
+      <c r="D22" s="133" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="132"/>
-      <c r="F15" s="134" t="s">
-        <v>93</v>
-      </c>
-      <c r="G15" s="135"/>
-      <c r="H15" s="135"/>
-      <c r="I15" s="135"/>
-      <c r="J15" s="136"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="131"/>
-      <c r="M15" s="132"/>
-    </row>
-    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B16" s="147"/>
-      <c r="C16" s="142"/>
-      <c r="D16" s="130" t="s">
-        <v>94</v>
-      </c>
-      <c r="E16" s="132"/>
-      <c r="F16" s="134" t="s">
+      <c r="E22" s="135"/>
+      <c r="F22" s="143" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="143"/>
+      <c r="H22" s="143"/>
+      <c r="I22" s="143"/>
+      <c r="J22" s="143"/>
+      <c r="K22" s="136"/>
+      <c r="L22" s="136"/>
+      <c r="M22" s="136"/>
+    </row>
+    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B23" s="147" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" s="144" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="133" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" s="135"/>
+      <c r="F23" s="137" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" s="138"/>
+      <c r="H23" s="138"/>
+      <c r="I23" s="138"/>
+      <c r="J23" s="139"/>
+      <c r="K23" s="136" t="s">
+        <v>115</v>
+      </c>
+      <c r="L23" s="136"/>
+      <c r="M23" s="136"/>
+    </row>
+    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B24" s="148"/>
+      <c r="C24" s="146"/>
+      <c r="D24" s="133" t="s">
+        <v>113</v>
+      </c>
+      <c r="E24" s="135"/>
+      <c r="F24" s="137" t="s">
+        <v>114</v>
+      </c>
+      <c r="G24" s="138"/>
+      <c r="H24" s="138"/>
+      <c r="I24" s="138"/>
+      <c r="J24" s="139"/>
+      <c r="K24" s="133"/>
+      <c r="L24" s="134"/>
+      <c r="M24" s="135"/>
+    </row>
+    <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B25" s="148"/>
+      <c r="C25" s="144" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" s="133" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" s="135"/>
+      <c r="F25" s="137" t="s">
+        <v>108</v>
+      </c>
+      <c r="G25" s="138"/>
+      <c r="H25" s="138"/>
+      <c r="I25" s="138"/>
+      <c r="J25" s="139"/>
+      <c r="K25" s="136"/>
+      <c r="L25" s="136"/>
+      <c r="M25" s="136"/>
+    </row>
+    <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B26" s="148"/>
+      <c r="C26" s="146"/>
+      <c r="D26" s="133" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" s="135"/>
+      <c r="F26" s="137" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" s="138"/>
+      <c r="H26" s="138"/>
+      <c r="I26" s="138"/>
+      <c r="J26" s="139"/>
+      <c r="K26" s="133"/>
+      <c r="L26" s="134"/>
+      <c r="M26" s="135"/>
+    </row>
+    <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B27" s="148"/>
+      <c r="C27" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="133" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27" s="135"/>
+      <c r="F27" s="137" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" s="138"/>
+      <c r="H27" s="138"/>
+      <c r="I27" s="138"/>
+      <c r="J27" s="139"/>
+      <c r="K27" s="136"/>
+      <c r="L27" s="136"/>
+      <c r="M27" s="136"/>
+    </row>
+    <row r="28" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B28" s="148"/>
+      <c r="C28" s="144" t="s">
         <v>97</v>
       </c>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135"/>
-      <c r="I16" s="135"/>
-      <c r="J16" s="136"/>
-      <c r="K16" s="130"/>
-      <c r="L16" s="131"/>
-      <c r="M16" s="132"/>
-    </row>
-    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B17" s="147"/>
-      <c r="C17" s="142"/>
-      <c r="D17" s="130" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="132"/>
-      <c r="F17" s="134" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" s="135"/>
-      <c r="H17" s="135"/>
-      <c r="I17" s="135"/>
-      <c r="J17" s="135"/>
-      <c r="K17" s="133"/>
-      <c r="L17" s="133"/>
-      <c r="M17" s="133"/>
-    </row>
-    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B18" s="147"/>
-      <c r="C18" s="143"/>
-      <c r="D18" s="130" t="s">
-        <v>96</v>
-      </c>
-      <c r="E18" s="132"/>
-      <c r="F18" s="134" t="s">
-        <v>99</v>
-      </c>
-      <c r="G18" s="135"/>
-      <c r="H18" s="135"/>
-      <c r="I18" s="135"/>
-      <c r="J18" s="135"/>
-      <c r="K18" s="133"/>
-      <c r="L18" s="133"/>
-      <c r="M18" s="133"/>
-    </row>
-    <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B19" s="147"/>
-      <c r="C19" s="66" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" s="130" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" s="132"/>
-      <c r="F19" s="140" t="s">
-        <v>101</v>
-      </c>
-      <c r="G19" s="140"/>
-      <c r="H19" s="140"/>
-      <c r="I19" s="140"/>
-      <c r="J19" s="140"/>
-      <c r="K19" s="133"/>
-      <c r="L19" s="133"/>
-      <c r="M19" s="133"/>
-    </row>
-    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B20" s="147"/>
-      <c r="C20" s="66" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="130" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="132"/>
-      <c r="F20" s="140" t="s">
-        <v>80</v>
-      </c>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="140"/>
-      <c r="J20" s="140"/>
-      <c r="K20" s="133"/>
-      <c r="L20" s="133"/>
-      <c r="M20" s="133"/>
-    </row>
-    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="147"/>
-      <c r="C21" s="66" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="130" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" s="132"/>
-      <c r="F21" s="140" t="s">
-        <v>81</v>
-      </c>
-      <c r="G21" s="140"/>
-      <c r="H21" s="140"/>
-      <c r="I21" s="140"/>
-      <c r="J21" s="140"/>
-      <c r="K21" s="133"/>
-      <c r="L21" s="133"/>
-      <c r="M21" s="133"/>
-    </row>
-    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B22" s="147"/>
-      <c r="C22" s="66" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" s="130" t="s">
-        <v>82</v>
-      </c>
-      <c r="E22" s="132"/>
-      <c r="F22" s="140" t="s">
-        <v>82</v>
-      </c>
-      <c r="G22" s="140"/>
-      <c r="H22" s="140"/>
-      <c r="I22" s="140"/>
-      <c r="J22" s="140"/>
-      <c r="K22" s="133"/>
-      <c r="L22" s="133"/>
-      <c r="M22" s="133"/>
-    </row>
-    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B23" s="144" t="s">
+      <c r="D28" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="E28" s="135"/>
+      <c r="F28" s="137" t="s">
+        <v>109</v>
+      </c>
+      <c r="G28" s="138"/>
+      <c r="H28" s="138"/>
+      <c r="I28" s="138"/>
+      <c r="J28" s="139"/>
+      <c r="K28" s="136"/>
+      <c r="L28" s="136"/>
+      <c r="M28" s="136"/>
+    </row>
+    <row r="29" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B29" s="148"/>
+      <c r="C29" s="146"/>
+      <c r="D29" s="133" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" s="135"/>
+      <c r="F29" s="137" t="s">
+        <v>119</v>
+      </c>
+      <c r="G29" s="138"/>
+      <c r="H29" s="138"/>
+      <c r="I29" s="138"/>
+      <c r="J29" s="139"/>
+      <c r="K29" s="136"/>
+      <c r="L29" s="136"/>
+      <c r="M29" s="136"/>
+    </row>
+    <row r="30" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B30" s="148"/>
+      <c r="C30" s="66" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="E30" s="135"/>
+      <c r="F30" s="137" t="s">
+        <v>110</v>
+      </c>
+      <c r="G30" s="138"/>
+      <c r="H30" s="138"/>
+      <c r="I30" s="138"/>
+      <c r="J30" s="139"/>
+      <c r="K30" s="136"/>
+      <c r="L30" s="136"/>
+      <c r="M30" s="136"/>
+    </row>
+    <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B31" s="149"/>
+      <c r="C31" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="133" t="s">
         <v>105</v>
       </c>
-      <c r="C23" s="141" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" s="130" t="s">
-        <v>115</v>
-      </c>
-      <c r="E23" s="132"/>
-      <c r="F23" s="134" t="s">
-        <v>110</v>
-      </c>
-      <c r="G23" s="135"/>
-      <c r="H23" s="135"/>
-      <c r="I23" s="135"/>
-      <c r="J23" s="136"/>
-      <c r="K23" s="133" t="s">
-        <v>118</v>
-      </c>
-      <c r="L23" s="133"/>
-      <c r="M23" s="133"/>
-    </row>
-    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B24" s="145"/>
-      <c r="C24" s="143"/>
-      <c r="D24" s="130" t="s">
-        <v>116</v>
-      </c>
-      <c r="E24" s="132"/>
-      <c r="F24" s="134" t="s">
-        <v>117</v>
-      </c>
-      <c r="G24" s="135"/>
-      <c r="H24" s="135"/>
-      <c r="I24" s="135"/>
-      <c r="J24" s="136"/>
-      <c r="K24" s="130"/>
-      <c r="L24" s="131"/>
-      <c r="M24" s="132"/>
-    </row>
-    <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B25" s="145"/>
-      <c r="C25" s="141" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" s="130" t="s">
-        <v>120</v>
-      </c>
-      <c r="E25" s="132"/>
-      <c r="F25" s="134" t="s">
+      <c r="E31" s="135"/>
+      <c r="F31" s="137" t="s">
         <v>111</v>
       </c>
-      <c r="G25" s="135"/>
-      <c r="H25" s="135"/>
-      <c r="I25" s="135"/>
-      <c r="J25" s="136"/>
-      <c r="K25" s="133"/>
-      <c r="L25" s="133"/>
-      <c r="M25" s="133"/>
-    </row>
-    <row r="26" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B26" s="145"/>
-      <c r="C26" s="143"/>
-      <c r="D26" s="130" t="s">
-        <v>119</v>
-      </c>
-      <c r="E26" s="132"/>
-      <c r="F26" s="134" t="s">
-        <v>121</v>
-      </c>
-      <c r="G26" s="135"/>
-      <c r="H26" s="135"/>
-      <c r="I26" s="135"/>
-      <c r="J26" s="136"/>
-      <c r="K26" s="130"/>
-      <c r="L26" s="131"/>
-      <c r="M26" s="132"/>
-    </row>
-    <row r="27" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B27" s="145"/>
-      <c r="C27" s="66" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" s="130" t="s">
-        <v>106</v>
-      </c>
-      <c r="E27" s="132"/>
-      <c r="F27" s="134" t="s">
-        <v>109</v>
-      </c>
-      <c r="G27" s="135"/>
-      <c r="H27" s="135"/>
-      <c r="I27" s="135"/>
-      <c r="J27" s="136"/>
-      <c r="K27" s="133"/>
-      <c r="L27" s="133"/>
-      <c r="M27" s="133"/>
-    </row>
-    <row r="28" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B28" s="145"/>
-      <c r="C28" s="141" t="s">
-        <v>100</v>
-      </c>
-      <c r="D28" s="130" t="s">
+      <c r="G31" s="138"/>
+      <c r="H31" s="138"/>
+      <c r="I31" s="138"/>
+      <c r="J31" s="139"/>
+      <c r="K31" s="136"/>
+      <c r="L31" s="136"/>
+      <c r="M31" s="136"/>
+    </row>
+    <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B32" s="147" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="E28" s="132"/>
-      <c r="F28" s="134" t="s">
-        <v>112</v>
-      </c>
-      <c r="G28" s="135"/>
-      <c r="H28" s="135"/>
-      <c r="I28" s="135"/>
-      <c r="J28" s="136"/>
-      <c r="K28" s="133"/>
-      <c r="L28" s="133"/>
-      <c r="M28" s="133"/>
-    </row>
-    <row r="29" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B29" s="145"/>
-      <c r="C29" s="143"/>
-      <c r="D29" s="130" t="s">
+      <c r="D32" s="133" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" s="135"/>
+      <c r="F32" s="137" t="s">
+        <v>144</v>
+      </c>
+      <c r="G32" s="138"/>
+      <c r="H32" s="138"/>
+      <c r="I32" s="138"/>
+      <c r="J32" s="139"/>
+      <c r="K32" s="133" t="s">
+        <v>143</v>
+      </c>
+      <c r="L32" s="134"/>
+      <c r="M32" s="135"/>
+    </row>
+    <row r="33" spans="1:13" ht="20.100000000000001" customHeight="1">
+      <c r="B33" s="148"/>
+      <c r="C33" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="E29" s="132"/>
-      <c r="F29" s="134" t="s">
-        <v>122</v>
-      </c>
-      <c r="G29" s="135"/>
-      <c r="H29" s="135"/>
-      <c r="I29" s="135"/>
-      <c r="J29" s="136"/>
-      <c r="K29" s="133"/>
-      <c r="L29" s="133"/>
-      <c r="M29" s="133"/>
-    </row>
-    <row r="30" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B30" s="145"/>
-      <c r="C30" s="66" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" s="130" t="s">
-        <v>107</v>
-      </c>
-      <c r="E30" s="132"/>
-      <c r="F30" s="134" t="s">
-        <v>113</v>
-      </c>
-      <c r="G30" s="135"/>
-      <c r="H30" s="135"/>
-      <c r="I30" s="135"/>
-      <c r="J30" s="136"/>
-      <c r="K30" s="133"/>
-      <c r="L30" s="133"/>
-      <c r="M30" s="133"/>
-    </row>
-    <row r="31" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B31" s="146"/>
-      <c r="C31" s="66" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31" s="130" t="s">
-        <v>108</v>
-      </c>
-      <c r="E31" s="132"/>
-      <c r="F31" s="134" t="s">
-        <v>114</v>
-      </c>
-      <c r="G31" s="135"/>
-      <c r="H31" s="135"/>
-      <c r="I31" s="135"/>
-      <c r="J31" s="136"/>
-      <c r="K31" s="133"/>
-      <c r="L31" s="133"/>
-      <c r="M31" s="133"/>
-    </row>
-    <row r="32" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B32" s="144" t="s">
+      <c r="D33" s="133" t="s">
+        <v>132</v>
+      </c>
+      <c r="E33" s="135"/>
+      <c r="F33" s="137" t="s">
+        <v>145</v>
+      </c>
+      <c r="G33" s="138"/>
+      <c r="H33" s="138"/>
+      <c r="I33" s="138"/>
+      <c r="J33" s="139"/>
+      <c r="K33" s="133"/>
+      <c r="L33" s="134"/>
+      <c r="M33" s="135"/>
+    </row>
+    <row r="34" spans="1:13" ht="20.100000000000001" customHeight="1">
+      <c r="B34" s="148"/>
+      <c r="C34" s="66" t="s">
         <v>125</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="D34" s="133" t="s">
+        <v>133</v>
+      </c>
+      <c r="E34" s="135"/>
+      <c r="F34" s="137" t="s">
+        <v>146</v>
+      </c>
+      <c r="G34" s="138"/>
+      <c r="H34" s="138"/>
+      <c r="I34" s="138"/>
+      <c r="J34" s="139"/>
+      <c r="K34" s="133"/>
+      <c r="L34" s="134"/>
+      <c r="M34" s="135"/>
+    </row>
+    <row r="35" spans="1:13" ht="20.100000000000001" customHeight="1">
+      <c r="B35" s="148"/>
+      <c r="C35" s="66" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="130" t="s">
+      <c r="D35" s="133" t="s">
         <v>134</v>
       </c>
-      <c r="E32" s="132"/>
-      <c r="F32" s="134" t="s">
+      <c r="E35" s="135"/>
+      <c r="F35" s="137" t="s">
         <v>147</v>
       </c>
-      <c r="G32" s="135"/>
-      <c r="H32" s="135"/>
-      <c r="I32" s="135"/>
-      <c r="J32" s="136"/>
-      <c r="K32" s="130" t="s">
+      <c r="G35" s="138"/>
+      <c r="H35" s="138"/>
+      <c r="I35" s="138"/>
+      <c r="J35" s="139"/>
+      <c r="K35" s="133"/>
+      <c r="L35" s="134"/>
+      <c r="M35" s="135"/>
+    </row>
+    <row r="36" spans="1:13" ht="20.100000000000001" customHeight="1">
+      <c r="B36" s="148"/>
+      <c r="C36" s="66" t="s">
+        <v>128</v>
+      </c>
+      <c r="D36" s="133" t="s">
+        <v>135</v>
+      </c>
+      <c r="E36" s="135"/>
+      <c r="F36" s="137" t="s">
+        <v>148</v>
+      </c>
+      <c r="G36" s="138"/>
+      <c r="H36" s="138"/>
+      <c r="I36" s="138"/>
+      <c r="J36" s="139"/>
+      <c r="K36" s="133"/>
+      <c r="L36" s="134"/>
+      <c r="M36" s="135"/>
+    </row>
+    <row r="37" spans="1:13" ht="20.100000000000001" customHeight="1">
+      <c r="B37" s="148"/>
+      <c r="C37" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="D37" s="133" t="s">
+        <v>139</v>
+      </c>
+      <c r="E37" s="135"/>
+      <c r="F37" s="137" t="s">
+        <v>145</v>
+      </c>
+      <c r="G37" s="138"/>
+      <c r="H37" s="138"/>
+      <c r="I37" s="138"/>
+      <c r="J37" s="139"/>
+      <c r="K37" s="133"/>
+      <c r="L37" s="134"/>
+      <c r="M37" s="135"/>
+    </row>
+    <row r="38" spans="1:13" ht="20.100000000000001" customHeight="1">
+      <c r="B38" s="148"/>
+      <c r="C38" s="66" t="s">
+        <v>137</v>
+      </c>
+      <c r="D38" s="133" t="s">
+        <v>140</v>
+      </c>
+      <c r="E38" s="135"/>
+      <c r="F38" s="137" t="s">
         <v>146</v>
       </c>
-      <c r="L32" s="131"/>
-      <c r="M32" s="132"/>
-    </row>
-    <row r="33" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B33" s="145"/>
-      <c r="C33" s="66" t="s">
+      <c r="G38" s="138"/>
+      <c r="H38" s="138"/>
+      <c r="I38" s="138"/>
+      <c r="J38" s="139"/>
+      <c r="K38" s="133"/>
+      <c r="L38" s="134"/>
+      <c r="M38" s="135"/>
+    </row>
+    <row r="39" spans="1:13" ht="20.100000000000001" customHeight="1">
+      <c r="B39" s="148"/>
+      <c r="C39" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="D33" s="130" t="s">
-        <v>135</v>
-      </c>
-      <c r="E33" s="132"/>
-      <c r="F33" s="134" t="s">
+      <c r="D39" s="133" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" s="135"/>
+      <c r="F39" s="137" t="s">
+        <v>147</v>
+      </c>
+      <c r="G39" s="138"/>
+      <c r="H39" s="138"/>
+      <c r="I39" s="138"/>
+      <c r="J39" s="139"/>
+      <c r="K39" s="133"/>
+      <c r="L39" s="134"/>
+      <c r="M39" s="135"/>
+    </row>
+    <row r="40" spans="1:13" ht="20.100000000000001" customHeight="1">
+      <c r="B40" s="148"/>
+      <c r="C40" s="66" t="s">
+        <v>138</v>
+      </c>
+      <c r="D40" s="133" t="s">
+        <v>142</v>
+      </c>
+      <c r="E40" s="135"/>
+      <c r="F40" s="137" t="s">
         <v>148</v>
       </c>
-      <c r="G33" s="135"/>
-      <c r="H33" s="135"/>
-      <c r="I33" s="135"/>
-      <c r="J33" s="136"/>
-      <c r="K33" s="130"/>
-      <c r="L33" s="131"/>
-      <c r="M33" s="132"/>
-    </row>
-    <row r="34" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B34" s="145"/>
-      <c r="C34" s="66" t="s">
-        <v>128</v>
-      </c>
-      <c r="D34" s="130" t="s">
-        <v>136</v>
-      </c>
-      <c r="E34" s="132"/>
-      <c r="F34" s="134" t="s">
-        <v>149</v>
-      </c>
-      <c r="G34" s="135"/>
-      <c r="H34" s="135"/>
-      <c r="I34" s="135"/>
-      <c r="J34" s="136"/>
-      <c r="K34" s="130"/>
-      <c r="L34" s="131"/>
-      <c r="M34" s="132"/>
-    </row>
-    <row r="35" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B35" s="145"/>
-      <c r="C35" s="66" t="s">
+      <c r="G40" s="138"/>
+      <c r="H40" s="138"/>
+      <c r="I40" s="138"/>
+      <c r="J40" s="139"/>
+      <c r="K40" s="133"/>
+      <c r="L40" s="134"/>
+      <c r="M40" s="135"/>
+    </row>
+    <row r="41" spans="1:13" ht="20.100000000000001" customHeight="1">
+      <c r="B41" s="149"/>
+      <c r="C41" s="68" t="s">
+        <v>436</v>
+      </c>
+      <c r="D41" s="133" t="s">
         <v>129</v>
       </c>
-      <c r="D35" s="130" t="s">
-        <v>137</v>
-      </c>
-      <c r="E35" s="132"/>
-      <c r="F35" s="134" t="s">
-        <v>150</v>
-      </c>
-      <c r="G35" s="135"/>
-      <c r="H35" s="135"/>
-      <c r="I35" s="135"/>
-      <c r="J35" s="136"/>
-      <c r="K35" s="130"/>
-      <c r="L35" s="131"/>
-      <c r="M35" s="132"/>
-    </row>
-    <row r="36" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B36" s="145"/>
-      <c r="C36" s="66" t="s">
-        <v>131</v>
-      </c>
-      <c r="D36" s="130" t="s">
-        <v>138</v>
-      </c>
-      <c r="E36" s="132"/>
-      <c r="F36" s="134" t="s">
-        <v>151</v>
-      </c>
-      <c r="G36" s="135"/>
-      <c r="H36" s="135"/>
-      <c r="I36" s="135"/>
-      <c r="J36" s="136"/>
-      <c r="K36" s="130"/>
-      <c r="L36" s="131"/>
-      <c r="M36" s="132"/>
-    </row>
-    <row r="37" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B37" s="145"/>
-      <c r="C37" s="66" t="s">
-        <v>139</v>
-      </c>
-      <c r="D37" s="130" t="s">
-        <v>142</v>
-      </c>
-      <c r="E37" s="132"/>
-      <c r="F37" s="134" t="s">
-        <v>148</v>
-      </c>
-      <c r="G37" s="135"/>
-      <c r="H37" s="135"/>
-      <c r="I37" s="135"/>
-      <c r="J37" s="136"/>
-      <c r="K37" s="130"/>
-      <c r="L37" s="131"/>
-      <c r="M37" s="132"/>
-    </row>
-    <row r="38" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B38" s="145"/>
-      <c r="C38" s="66" t="s">
-        <v>140</v>
-      </c>
-      <c r="D38" s="130" t="s">
-        <v>143</v>
-      </c>
-      <c r="E38" s="132"/>
-      <c r="F38" s="134" t="s">
-        <v>149</v>
-      </c>
-      <c r="G38" s="135"/>
-      <c r="H38" s="135"/>
-      <c r="I38" s="135"/>
-      <c r="J38" s="136"/>
-      <c r="K38" s="130"/>
-      <c r="L38" s="131"/>
-      <c r="M38" s="132"/>
-    </row>
-    <row r="39" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B39" s="145"/>
-      <c r="C39" s="66" t="s">
+      <c r="E41" s="135"/>
+      <c r="F41" s="137" t="s">
         <v>130</v>
       </c>
-      <c r="D39" s="130" t="s">
-        <v>144</v>
-      </c>
-      <c r="E39" s="132"/>
-      <c r="F39" s="134" t="s">
-        <v>150</v>
-      </c>
-      <c r="G39" s="135"/>
-      <c r="H39" s="135"/>
-      <c r="I39" s="135"/>
-      <c r="J39" s="136"/>
-      <c r="K39" s="130"/>
-      <c r="L39" s="131"/>
-      <c r="M39" s="132"/>
-    </row>
-    <row r="40" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B40" s="145"/>
-      <c r="C40" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="D40" s="130" t="s">
-        <v>145</v>
-      </c>
-      <c r="E40" s="132"/>
-      <c r="F40" s="134" t="s">
-        <v>151</v>
-      </c>
-      <c r="G40" s="135"/>
-      <c r="H40" s="135"/>
-      <c r="I40" s="135"/>
-      <c r="J40" s="136"/>
-      <c r="K40" s="130"/>
-      <c r="L40" s="131"/>
-      <c r="M40" s="132"/>
-    </row>
-    <row r="41" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B41" s="146"/>
-      <c r="C41" s="69" t="s">
-        <v>450</v>
-      </c>
-      <c r="D41" s="130" t="s">
-        <v>132</v>
-      </c>
-      <c r="E41" s="132"/>
-      <c r="F41" s="134" t="s">
-        <v>133</v>
-      </c>
-      <c r="G41" s="135"/>
-      <c r="H41" s="135"/>
-      <c r="I41" s="135"/>
-      <c r="J41" s="136"/>
-      <c r="K41" s="130"/>
-      <c r="L41" s="131"/>
-      <c r="M41" s="132"/>
+      <c r="G41" s="138"/>
+      <c r="H41" s="138"/>
+      <c r="I41" s="138"/>
+      <c r="J41" s="139"/>
+      <c r="K41" s="133"/>
+      <c r="L41" s="134"/>
+      <c r="M41" s="135"/>
+    </row>
+    <row r="43" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1"/>
+    <row r="44" spans="1:13" s="199" customFormat="1" ht="24.95" customHeight="1" thickBot="1">
+      <c r="A44" s="198"/>
+      <c r="B44" s="205" t="s">
+        <v>515</v>
+      </c>
+      <c r="C44" s="207" t="s">
+        <v>516</v>
+      </c>
+      <c r="D44" s="206" t="s">
+        <v>520</v>
+      </c>
+      <c r="E44" s="202" t="s">
+        <v>517</v>
+      </c>
+      <c r="F44" s="204"/>
+      <c r="G44" s="204"/>
+      <c r="H44" s="204"/>
+      <c r="I44" s="203"/>
+      <c r="J44" s="206" t="s">
+        <v>518</v>
+      </c>
+      <c r="K44" s="206" t="s">
+        <v>523</v>
+      </c>
+      <c r="L44" s="202" t="s">
+        <v>519</v>
+      </c>
+      <c r="M44" s="203"/>
+    </row>
+    <row r="45" spans="1:13" ht="20.100000000000001" customHeight="1">
+      <c r="B45" s="208" t="s">
+        <v>521</v>
+      </c>
+      <c r="C45" s="208" t="s">
+        <v>522</v>
+      </c>
+      <c r="D45" s="208" t="s">
+        <v>524</v>
+      </c>
+      <c r="E45" s="211"/>
+      <c r="F45" s="200"/>
+      <c r="G45" s="200"/>
+      <c r="H45" s="200"/>
+      <c r="I45" s="212"/>
+      <c r="J45" s="208" t="s">
+        <v>525</v>
+      </c>
+      <c r="K45" s="208"/>
+      <c r="L45" s="218"/>
+      <c r="M45" s="219"/>
+    </row>
+    <row r="46" spans="1:13" ht="20.100000000000001" customHeight="1">
+      <c r="B46" s="209"/>
+      <c r="C46" s="209"/>
+      <c r="D46" s="209"/>
+      <c r="E46" s="213"/>
+      <c r="F46" s="201"/>
+      <c r="G46" s="201"/>
+      <c r="H46" s="201"/>
+      <c r="I46" s="214"/>
+      <c r="J46" s="209"/>
+      <c r="K46" s="209"/>
+      <c r="L46" s="220"/>
+      <c r="M46" s="221"/>
+    </row>
+    <row r="47" spans="1:13" ht="20.100000000000001" customHeight="1">
+      <c r="B47" s="209"/>
+      <c r="C47" s="209"/>
+      <c r="D47" s="209"/>
+      <c r="E47" s="213"/>
+      <c r="F47" s="201"/>
+      <c r="G47" s="201"/>
+      <c r="H47" s="201"/>
+      <c r="I47" s="214"/>
+      <c r="J47" s="209"/>
+      <c r="K47" s="209"/>
+      <c r="L47" s="220"/>
+      <c r="M47" s="221"/>
+    </row>
+    <row r="48" spans="1:13" ht="20.100000000000001" customHeight="1">
+      <c r="B48" s="209"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="213"/>
+      <c r="F48" s="201"/>
+      <c r="G48" s="201"/>
+      <c r="H48" s="201"/>
+      <c r="I48" s="214"/>
+      <c r="J48" s="209"/>
+      <c r="K48" s="209"/>
+      <c r="L48" s="220"/>
+      <c r="M48" s="221"/>
+    </row>
+    <row r="49" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B49" s="209"/>
+      <c r="C49" s="209"/>
+      <c r="D49" s="209"/>
+      <c r="E49" s="213"/>
+      <c r="F49" s="201"/>
+      <c r="G49" s="201"/>
+      <c r="H49" s="201"/>
+      <c r="I49" s="214"/>
+      <c r="J49" s="209"/>
+      <c r="K49" s="209"/>
+      <c r="L49" s="220"/>
+      <c r="M49" s="221"/>
+    </row>
+    <row r="50" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B50" s="210"/>
+      <c r="C50" s="210"/>
+      <c r="D50" s="210"/>
+      <c r="E50" s="215"/>
+      <c r="F50" s="216"/>
+      <c r="G50" s="216"/>
+      <c r="H50" s="216"/>
+      <c r="I50" s="217"/>
+      <c r="J50" s="210"/>
+      <c r="K50" s="210"/>
+      <c r="L50" s="222"/>
+      <c r="M50" s="223"/>
     </row>
   </sheetData>
-  <mergeCells count="102">
+  <mergeCells count="111">
+    <mergeCell ref="E45:I50"/>
+    <mergeCell ref="J45:J50"/>
+    <mergeCell ref="K45:K50"/>
+    <mergeCell ref="L45:M50"/>
+    <mergeCell ref="D45:D50"/>
+    <mergeCell ref="C45:C50"/>
+    <mergeCell ref="B45:B50"/>
+    <mergeCell ref="E44:I44"/>
+    <mergeCell ref="L44:M44"/>
     <mergeCell ref="F32:J32"/>
     <mergeCell ref="F33:J33"/>
     <mergeCell ref="F34:J34"/>
@@ -6802,7 +7473,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="B1:M24"/>
+  <dimension ref="B1:M25"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
@@ -6812,10 +7483,10 @@
     <row r="1" spans="2:13" ht="6" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:13" ht="26.25" thickBot="1">
       <c r="B2" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D2" s="17" t="s">
         <v>6</v>
@@ -6824,13 +7495,13 @@
         <v>8</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2" s="15" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J2" s="16" t="s">
         <v>7</v>
@@ -6841,7 +7512,7 @@
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B3" s="61" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>26</v>
@@ -6958,393 +7629,410 @@
       <c r="I9" s="36"/>
     </row>
     <row r="10" spans="2:13" ht="26.25" customHeight="1">
-      <c r="B10" s="71" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" s="72" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" s="137" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" s="138"/>
-      <c r="F10" s="148" t="s">
-        <v>84</v>
-      </c>
-      <c r="G10" s="148"/>
-      <c r="H10" s="148"/>
-      <c r="I10" s="148"/>
-      <c r="J10" s="148"/>
-      <c r="K10" s="137" t="s">
-        <v>103</v>
-      </c>
-      <c r="L10" s="139"/>
-      <c r="M10" s="138"/>
+      <c r="B10" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="140" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="141"/>
+      <c r="F10" s="151" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="151"/>
+      <c r="H10" s="151"/>
+      <c r="I10" s="151"/>
+      <c r="J10" s="151"/>
+      <c r="K10" s="140" t="s">
+        <v>100</v>
+      </c>
+      <c r="L10" s="142"/>
+      <c r="M10" s="141"/>
     </row>
     <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="144" t="s">
+      <c r="B11" s="147" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" s="133" t="s">
         <v>155</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="E11" s="135"/>
+      <c r="F11" s="143" t="s">
+        <v>424</v>
+      </c>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="136" t="s">
+        <v>157</v>
+      </c>
+      <c r="L11" s="136"/>
+      <c r="M11" s="136"/>
+    </row>
+    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B12" s="148"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="189" t="s">
+        <v>514</v>
+      </c>
+      <c r="E12" s="190"/>
+      <c r="F12" s="124"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="124"/>
+      <c r="I12" s="124"/>
+      <c r="J12" s="124"/>
+      <c r="K12" s="121"/>
+      <c r="L12" s="122"/>
+      <c r="M12" s="123"/>
+    </row>
+    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B13" s="149"/>
+      <c r="C13" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="D13" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="D11" s="130" t="s">
+      <c r="E13" s="135"/>
+      <c r="F13" s="143" t="s">
+        <v>425</v>
+      </c>
+      <c r="G13" s="143"/>
+      <c r="H13" s="143"/>
+      <c r="I13" s="143"/>
+      <c r="J13" s="143"/>
+      <c r="K13" s="133"/>
+      <c r="L13" s="134"/>
+      <c r="M13" s="135"/>
+    </row>
+    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B14" s="150" t="s">
         <v>158</v>
       </c>
-      <c r="E11" s="132"/>
-      <c r="F11" s="140" t="s">
-        <v>438</v>
-      </c>
-      <c r="G11" s="140"/>
-      <c r="H11" s="140"/>
-      <c r="I11" s="140"/>
-      <c r="J11" s="140"/>
-      <c r="K11" s="133" t="s">
+      <c r="C14" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" s="133" t="s">
+        <v>161</v>
+      </c>
+      <c r="E14" s="135"/>
+      <c r="F14" s="137" t="s">
+        <v>163</v>
+      </c>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="133" t="s">
+        <v>165</v>
+      </c>
+      <c r="L14" s="134"/>
+      <c r="M14" s="135"/>
+    </row>
+    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B15" s="150"/>
+      <c r="C15" s="51" t="s">
         <v>160</v>
       </c>
-      <c r="L11" s="133"/>
-      <c r="M11" s="133"/>
-    </row>
-    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="146"/>
-      <c r="C12" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="D12" s="130" t="s">
-        <v>159</v>
-      </c>
-      <c r="E12" s="132"/>
-      <c r="F12" s="140" t="s">
-        <v>439</v>
-      </c>
-      <c r="G12" s="140"/>
-      <c r="H12" s="140"/>
-      <c r="I12" s="140"/>
-      <c r="J12" s="140"/>
-      <c r="K12" s="130"/>
-      <c r="L12" s="131"/>
-      <c r="M12" s="132"/>
-    </row>
-    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="147" t="s">
-        <v>161</v>
-      </c>
-      <c r="C13" s="51" t="s">
+      <c r="D15" s="133" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="130" t="s">
+      <c r="E15" s="135"/>
+      <c r="F15" s="137" t="s">
         <v>164</v>
       </c>
-      <c r="E13" s="132"/>
-      <c r="F13" s="134" t="s">
+      <c r="G15" s="138"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="138"/>
+      <c r="K15" s="133" t="s">
         <v>166</v>
       </c>
-      <c r="G13" s="135"/>
-      <c r="H13" s="135"/>
-      <c r="I13" s="135"/>
-      <c r="J13" s="135"/>
-      <c r="K13" s="130" t="s">
+      <c r="L15" s="134"/>
+      <c r="M15" s="135"/>
+    </row>
+    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B16" s="150" t="s">
+        <v>167</v>
+      </c>
+      <c r="C16" s="66" t="s">
+        <v>426</v>
+      </c>
+      <c r="D16" s="133" t="s">
+        <v>427</v>
+      </c>
+      <c r="E16" s="135"/>
+      <c r="F16" s="137" t="s">
+        <v>428</v>
+      </c>
+      <c r="G16" s="138"/>
+      <c r="H16" s="138"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="138"/>
+      <c r="K16" s="136" t="s">
+        <v>429</v>
+      </c>
+      <c r="L16" s="136"/>
+      <c r="M16" s="136"/>
+    </row>
+    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B17" s="150"/>
+      <c r="C17" s="66" t="s">
+        <v>430</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>431</v>
+      </c>
+      <c r="E17" s="135"/>
+      <c r="F17" s="137" t="s">
+        <v>432</v>
+      </c>
+      <c r="G17" s="138"/>
+      <c r="H17" s="138"/>
+      <c r="I17" s="138"/>
+      <c r="J17" s="138"/>
+      <c r="K17" s="136" t="s">
+        <v>433</v>
+      </c>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+    </row>
+    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B18" s="150" t="s">
         <v>168</v>
       </c>
-      <c r="L13" s="131"/>
-      <c r="M13" s="132"/>
-    </row>
-    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B14" s="147"/>
-      <c r="C14" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="D14" s="130" t="s">
-        <v>165</v>
-      </c>
-      <c r="E14" s="132"/>
-      <c r="F14" s="134" t="s">
-        <v>167</v>
-      </c>
-      <c r="G14" s="135"/>
-      <c r="H14" s="135"/>
-      <c r="I14" s="135"/>
-      <c r="J14" s="135"/>
-      <c r="K14" s="130" t="s">
+      <c r="C18" s="66" t="s">
         <v>169</v>
       </c>
-      <c r="L14" s="131"/>
-      <c r="M14" s="132"/>
-    </row>
-    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B15" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="C15" s="66" t="s">
-        <v>440</v>
-      </c>
-      <c r="D15" s="130" t="s">
-        <v>441</v>
-      </c>
-      <c r="E15" s="132"/>
-      <c r="F15" s="134" t="s">
-        <v>442</v>
-      </c>
-      <c r="G15" s="135"/>
-      <c r="H15" s="135"/>
-      <c r="I15" s="135"/>
-      <c r="J15" s="135"/>
-      <c r="K15" s="133" t="s">
-        <v>443</v>
-      </c>
-      <c r="L15" s="133"/>
-      <c r="M15" s="133"/>
-    </row>
-    <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B16" s="147"/>
-      <c r="C16" s="66" t="s">
-        <v>444</v>
-      </c>
-      <c r="D16" s="130" t="s">
-        <v>445</v>
-      </c>
-      <c r="E16" s="132"/>
-      <c r="F16" s="134" t="s">
-        <v>446</v>
-      </c>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135"/>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="133" t="s">
-        <v>447</v>
-      </c>
-      <c r="L16" s="133"/>
-      <c r="M16" s="133"/>
-    </row>
-    <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B17" s="147" t="s">
-        <v>171</v>
-      </c>
-      <c r="C17" s="66" t="s">
-        <v>172</v>
-      </c>
-      <c r="D17" s="130" t="s">
-        <v>192</v>
-      </c>
-      <c r="E17" s="132"/>
-      <c r="F17" s="134" t="s">
-        <v>196</v>
-      </c>
-      <c r="G17" s="135"/>
-      <c r="H17" s="135"/>
-      <c r="I17" s="135"/>
-      <c r="J17" s="135"/>
-      <c r="K17" s="149" t="s">
-        <v>448</v>
-      </c>
-      <c r="L17" s="150"/>
-      <c r="M17" s="151"/>
-    </row>
-    <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B18" s="147"/>
-      <c r="C18" s="66" t="s">
-        <v>173</v>
-      </c>
-      <c r="D18" s="130" t="s">
+      <c r="D18" s="133" t="s">
+        <v>189</v>
+      </c>
+      <c r="E18" s="135"/>
+      <c r="F18" s="137" t="s">
         <v>193</v>
       </c>
-      <c r="E18" s="132"/>
-      <c r="F18" s="134" t="s">
-        <v>197</v>
-      </c>
-      <c r="G18" s="135"/>
-      <c r="H18" s="135"/>
-      <c r="I18" s="135"/>
-      <c r="J18" s="135"/>
-      <c r="K18" s="152"/>
+      <c r="G18" s="138"/>
+      <c r="H18" s="138"/>
+      <c r="I18" s="138"/>
+      <c r="J18" s="138"/>
+      <c r="K18" s="152" t="s">
+        <v>434</v>
+      </c>
       <c r="L18" s="153"/>
       <c r="M18" s="154"/>
     </row>
     <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B19" s="144" t="s">
+      <c r="B19" s="150"/>
+      <c r="C19" s="66" t="s">
+        <v>170</v>
+      </c>
+      <c r="D19" s="133" t="s">
+        <v>190</v>
+      </c>
+      <c r="E19" s="135"/>
+      <c r="F19" s="137" t="s">
+        <v>194</v>
+      </c>
+      <c r="G19" s="138"/>
+      <c r="H19" s="138"/>
+      <c r="I19" s="138"/>
+      <c r="J19" s="138"/>
+      <c r="K19" s="155"/>
+      <c r="L19" s="156"/>
+      <c r="M19" s="157"/>
+    </row>
+    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B20" s="147" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" s="66" t="s">
+        <v>172</v>
+      </c>
+      <c r="D20" s="133" t="s">
+        <v>191</v>
+      </c>
+      <c r="E20" s="135"/>
+      <c r="F20" s="137" t="s">
+        <v>195</v>
+      </c>
+      <c r="G20" s="138"/>
+      <c r="H20" s="138"/>
+      <c r="I20" s="138"/>
+      <c r="J20" s="138"/>
+      <c r="K20" s="136" t="s">
+        <v>435</v>
+      </c>
+      <c r="L20" s="136"/>
+      <c r="M20" s="136"/>
+    </row>
+    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B21" s="149"/>
+      <c r="C21" s="66" t="s">
+        <v>173</v>
+      </c>
+      <c r="D21" s="133" t="s">
+        <v>192</v>
+      </c>
+      <c r="E21" s="135"/>
+      <c r="F21" s="137" t="s">
+        <v>196</v>
+      </c>
+      <c r="G21" s="138"/>
+      <c r="H21" s="138"/>
+      <c r="I21" s="138"/>
+      <c r="J21" s="138"/>
+      <c r="K21" s="136"/>
+      <c r="L21" s="136"/>
+      <c r="M21" s="136"/>
+    </row>
+    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B22" s="147" t="s">
         <v>174</v>
       </c>
-      <c r="C19" s="66" t="s">
+      <c r="C22" s="66" t="s">
+        <v>176</v>
+      </c>
+      <c r="D22" s="133" t="s">
+        <v>178</v>
+      </c>
+      <c r="E22" s="135"/>
+      <c r="F22" s="143" t="s">
+        <v>183</v>
+      </c>
+      <c r="G22" s="143"/>
+      <c r="H22" s="143"/>
+      <c r="I22" s="143"/>
+      <c r="J22" s="143"/>
+      <c r="K22" s="136"/>
+      <c r="L22" s="136"/>
+      <c r="M22" s="136"/>
+    </row>
+    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B23" s="148"/>
+      <c r="C23" s="66" t="s">
+        <v>177</v>
+      </c>
+      <c r="D23" s="133" t="s">
+        <v>179</v>
+      </c>
+      <c r="E23" s="135"/>
+      <c r="F23" s="143" t="s">
+        <v>182</v>
+      </c>
+      <c r="G23" s="143"/>
+      <c r="H23" s="143"/>
+      <c r="I23" s="143"/>
+      <c r="J23" s="143"/>
+      <c r="K23" s="136"/>
+      <c r="L23" s="136"/>
+      <c r="M23" s="136"/>
+    </row>
+    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B24" s="149"/>
+      <c r="C24" s="66" t="s">
+        <v>181</v>
+      </c>
+      <c r="D24" s="133" t="s">
+        <v>180</v>
+      </c>
+      <c r="E24" s="135"/>
+      <c r="F24" s="143" t="s">
+        <v>184</v>
+      </c>
+      <c r="G24" s="143"/>
+      <c r="H24" s="143"/>
+      <c r="I24" s="143"/>
+      <c r="J24" s="143"/>
+      <c r="K24" s="136" t="s">
+        <v>185</v>
+      </c>
+      <c r="L24" s="136"/>
+      <c r="M24" s="136"/>
+    </row>
+    <row r="25" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B25" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="D19" s="130" t="s">
-        <v>194</v>
-      </c>
-      <c r="E19" s="132"/>
-      <c r="F19" s="134" t="s">
-        <v>198</v>
-      </c>
-      <c r="G19" s="135"/>
-      <c r="H19" s="135"/>
-      <c r="I19" s="135"/>
-      <c r="J19" s="135"/>
-      <c r="K19" s="133" t="s">
-        <v>449</v>
-      </c>
-      <c r="L19" s="133"/>
-      <c r="M19" s="133"/>
-    </row>
-    <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B20" s="146"/>
-      <c r="C20" s="66" t="s">
-        <v>176</v>
-      </c>
-      <c r="D20" s="130" t="s">
-        <v>195</v>
-      </c>
-      <c r="E20" s="132"/>
-      <c r="F20" s="134" t="s">
-        <v>199</v>
-      </c>
-      <c r="G20" s="135"/>
-      <c r="H20" s="135"/>
-      <c r="I20" s="135"/>
-      <c r="J20" s="135"/>
-      <c r="K20" s="133"/>
-      <c r="L20" s="133"/>
-      <c r="M20" s="133"/>
-    </row>
-    <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="144" t="s">
-        <v>177</v>
-      </c>
-      <c r="C21" s="66" t="s">
-        <v>179</v>
-      </c>
-      <c r="D21" s="130" t="s">
-        <v>181</v>
-      </c>
-      <c r="E21" s="132"/>
-      <c r="F21" s="140" t="s">
+      <c r="C25" s="66" t="s">
         <v>186</v>
       </c>
-      <c r="G21" s="140"/>
-      <c r="H21" s="140"/>
-      <c r="I21" s="140"/>
-      <c r="J21" s="140"/>
-      <c r="K21" s="133"/>
-      <c r="L21" s="133"/>
-      <c r="M21" s="133"/>
-    </row>
-    <row r="22" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B22" s="145"/>
-      <c r="C22" s="66" t="s">
-        <v>180</v>
-      </c>
-      <c r="D22" s="130" t="s">
-        <v>182</v>
-      </c>
-      <c r="E22" s="132"/>
-      <c r="F22" s="140" t="s">
-        <v>185</v>
-      </c>
-      <c r="G22" s="140"/>
-      <c r="H22" s="140"/>
-      <c r="I22" s="140"/>
-      <c r="J22" s="140"/>
-      <c r="K22" s="133"/>
-      <c r="L22" s="133"/>
-      <c r="M22" s="133"/>
-    </row>
-    <row r="23" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B23" s="146"/>
-      <c r="C23" s="66" t="s">
-        <v>184</v>
-      </c>
-      <c r="D23" s="130" t="s">
-        <v>183</v>
-      </c>
-      <c r="E23" s="132"/>
-      <c r="F23" s="140" t="s">
+      <c r="D25" s="133" t="s">
+        <v>186</v>
+      </c>
+      <c r="E25" s="135"/>
+      <c r="F25" s="143" t="s">
         <v>187</v>
       </c>
-      <c r="G23" s="140"/>
-      <c r="H23" s="140"/>
-      <c r="I23" s="140"/>
-      <c r="J23" s="140"/>
-      <c r="K23" s="133" t="s">
+      <c r="G25" s="143"/>
+      <c r="H25" s="143"/>
+      <c r="I25" s="143"/>
+      <c r="J25" s="143"/>
+      <c r="K25" s="136" t="s">
         <v>188</v>
       </c>
-      <c r="L23" s="133"/>
-      <c r="M23" s="133"/>
-    </row>
-    <row r="24" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B24" s="76" t="s">
-        <v>178</v>
-      </c>
-      <c r="C24" s="66" t="s">
-        <v>189</v>
-      </c>
-      <c r="D24" s="130" t="s">
-        <v>189</v>
-      </c>
-      <c r="E24" s="132"/>
-      <c r="F24" s="140" t="s">
-        <v>190</v>
-      </c>
-      <c r="G24" s="140"/>
-      <c r="H24" s="140"/>
-      <c r="I24" s="140"/>
-      <c r="J24" s="140"/>
-      <c r="K24" s="133" t="s">
-        <v>191</v>
-      </c>
-      <c r="L24" s="133"/>
-      <c r="M24" s="133"/>
+      <c r="L25" s="136"/>
+      <c r="M25" s="136"/>
     </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="K21:M21"/>
+  <mergeCells count="51">
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="K18:M19"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:J22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:J24"/>
     <mergeCell ref="K23:M23"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="K17:M18"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:J21"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:J23"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B19:B20"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="K20:M20"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F22:J22"/>
-    <mergeCell ref="F24:J24"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="K17:M17"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:J18"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="K15:M15"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="F16:J16"/>
     <mergeCell ref="K16:M16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="K15:M15"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="F10:J10"/>
     <mergeCell ref="K10:M10"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="F11:J11"/>
     <mergeCell ref="K11:M11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:M12"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="F13:J13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:J14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7370,27 +8058,27 @@
         <v>13</v>
       </c>
       <c r="C2" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="G2" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="H2" s="15" t="s">
         <v>55</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B3" s="19" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>17</v>
@@ -7412,172 +8100,172 @@
       </c>
     </row>
     <row r="5" spans="2:13" ht="26.25" customHeight="1">
-      <c r="B5" s="71" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="72" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" s="137" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="138"/>
-      <c r="F5" s="148" t="s">
-        <v>84</v>
-      </c>
-      <c r="G5" s="148"/>
-      <c r="H5" s="148"/>
-      <c r="I5" s="148"/>
-      <c r="J5" s="148"/>
-      <c r="K5" s="137" t="s">
-        <v>103</v>
-      </c>
-      <c r="L5" s="139"/>
-      <c r="M5" s="138"/>
+      <c r="B5" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="140" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="141"/>
+      <c r="F5" s="151" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="151"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="151"/>
+      <c r="K5" s="140" t="s">
+        <v>100</v>
+      </c>
+      <c r="L5" s="142"/>
+      <c r="M5" s="141"/>
     </row>
     <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="74" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>251</v>
+      </c>
+      <c r="D6" s="133" t="s">
+        <v>252</v>
+      </c>
+      <c r="E6" s="135"/>
+      <c r="F6" s="143" t="s">
+        <v>258</v>
+      </c>
+      <c r="G6" s="143"/>
+      <c r="H6" s="143"/>
+      <c r="I6" s="143"/>
+      <c r="J6" s="143"/>
+      <c r="K6" s="136" t="s">
+        <v>264</v>
+      </c>
+      <c r="L6" s="136"/>
+      <c r="M6" s="136"/>
+    </row>
+    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B7" s="72" t="s">
+        <v>198</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>251</v>
+      </c>
+      <c r="D7" s="133" t="s">
+        <v>253</v>
+      </c>
+      <c r="E7" s="135"/>
+      <c r="F7" s="143" t="s">
+        <v>259</v>
+      </c>
+      <c r="G7" s="143"/>
+      <c r="H7" s="143"/>
+      <c r="I7" s="143"/>
+      <c r="J7" s="143"/>
+      <c r="K7" s="136" t="s">
+        <v>265</v>
+      </c>
+      <c r="L7" s="136"/>
+      <c r="M7" s="136"/>
+    </row>
+    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B8" s="72" t="s">
+        <v>199</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>251</v>
+      </c>
+      <c r="D8" s="133" t="s">
+        <v>254</v>
+      </c>
+      <c r="E8" s="135"/>
+      <c r="F8" s="143" t="s">
+        <v>260</v>
+      </c>
+      <c r="G8" s="143"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="143"/>
+      <c r="J8" s="143"/>
+      <c r="K8" s="136" t="s">
+        <v>266</v>
+      </c>
+      <c r="L8" s="136"/>
+      <c r="M8" s="136"/>
+    </row>
+    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B9" s="72" t="s">
         <v>200</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C9" s="51" t="s">
+        <v>251</v>
+      </c>
+      <c r="D9" s="133" t="s">
         <v>255</v>
       </c>
-      <c r="D6" s="130" t="s">
+      <c r="E9" s="135"/>
+      <c r="F9" s="143" t="s">
+        <v>261</v>
+      </c>
+      <c r="G9" s="143"/>
+      <c r="H9" s="143"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="136" t="s">
+        <v>267</v>
+      </c>
+      <c r="L9" s="136"/>
+      <c r="M9" s="136"/>
+    </row>
+    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B10" s="72" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>251</v>
+      </c>
+      <c r="D10" s="133" t="s">
         <v>256</v>
       </c>
-      <c r="E6" s="132"/>
-      <c r="F6" s="140" t="s">
+      <c r="E10" s="135"/>
+      <c r="F10" s="143" t="s">
         <v>262</v>
       </c>
-      <c r="G6" s="140"/>
-      <c r="H6" s="140"/>
-      <c r="I6" s="140"/>
-      <c r="J6" s="140"/>
-      <c r="K6" s="133" t="s">
+      <c r="G10" s="143"/>
+      <c r="H10" s="143"/>
+      <c r="I10" s="143"/>
+      <c r="J10" s="143"/>
+      <c r="K10" s="136" t="s">
         <v>268</v>
       </c>
-      <c r="L6" s="133"/>
-      <c r="M6" s="133"/>
-    </row>
-    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="73" t="s">
-        <v>201</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>255</v>
-      </c>
-      <c r="D7" s="130" t="s">
+      <c r="L10" s="136"/>
+      <c r="M10" s="136"/>
+    </row>
+    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B11" s="72" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>251</v>
+      </c>
+      <c r="D11" s="133" t="s">
         <v>257</v>
       </c>
-      <c r="E7" s="132"/>
-      <c r="F7" s="140" t="s">
+      <c r="E11" s="135"/>
+      <c r="F11" s="143" t="s">
         <v>263</v>
       </c>
-      <c r="G7" s="140"/>
-      <c r="H7" s="140"/>
-      <c r="I7" s="140"/>
-      <c r="J7" s="140"/>
-      <c r="K7" s="133" t="s">
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="136" t="s">
         <v>269</v>
       </c>
-      <c r="L7" s="133"/>
-      <c r="M7" s="133"/>
-    </row>
-    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="73" t="s">
-        <v>202</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>255</v>
-      </c>
-      <c r="D8" s="130" t="s">
-        <v>258</v>
-      </c>
-      <c r="E8" s="132"/>
-      <c r="F8" s="140" t="s">
-        <v>264</v>
-      </c>
-      <c r="G8" s="140"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="140"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="133" t="s">
-        <v>270</v>
-      </c>
-      <c r="L8" s="133"/>
-      <c r="M8" s="133"/>
-    </row>
-    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="73" t="s">
-        <v>203</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>255</v>
-      </c>
-      <c r="D9" s="130" t="s">
-        <v>259</v>
-      </c>
-      <c r="E9" s="132"/>
-      <c r="F9" s="140" t="s">
-        <v>265</v>
-      </c>
-      <c r="G9" s="140"/>
-      <c r="H9" s="140"/>
-      <c r="I9" s="140"/>
-      <c r="J9" s="140"/>
-      <c r="K9" s="133" t="s">
-        <v>271</v>
-      </c>
-      <c r="L9" s="133"/>
-      <c r="M9" s="133"/>
-    </row>
-    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B10" s="73" t="s">
-        <v>205</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>255</v>
-      </c>
-      <c r="D10" s="130" t="s">
-        <v>260</v>
-      </c>
-      <c r="E10" s="132"/>
-      <c r="F10" s="140" t="s">
-        <v>266</v>
-      </c>
-      <c r="G10" s="140"/>
-      <c r="H10" s="140"/>
-      <c r="I10" s="140"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="133" t="s">
-        <v>272</v>
-      </c>
-      <c r="L10" s="133"/>
-      <c r="M10" s="133"/>
-    </row>
-    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="73" t="s">
-        <v>206</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>255</v>
-      </c>
-      <c r="D11" s="130" t="s">
-        <v>261</v>
-      </c>
-      <c r="E11" s="132"/>
-      <c r="F11" s="140" t="s">
-        <v>267</v>
-      </c>
-      <c r="G11" s="140"/>
-      <c r="H11" s="140"/>
-      <c r="I11" s="140"/>
-      <c r="J11" s="140"/>
-      <c r="K11" s="133" t="s">
-        <v>273</v>
-      </c>
-      <c r="L11" s="133"/>
-      <c r="M11" s="133"/>
+      <c r="L11" s="136"/>
+      <c r="M11" s="136"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -7622,37 +8310,37 @@
   <sheetData>
     <row r="1" spans="2:13" ht="6" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:13" ht="25.5">
-      <c r="B2" s="88" t="s">
-        <v>277</v>
-      </c>
-      <c r="C2" s="89" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" s="89" t="s">
+      <c r="B2" s="87" t="s">
+        <v>273</v>
+      </c>
+      <c r="C2" s="88" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="88" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="88" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="88" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="89" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2" s="89" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="89" t="s">
-        <v>65</v>
-      </c>
-      <c r="H2" s="89" t="s">
-        <v>278</v>
-      </c>
-      <c r="I2" s="89" t="s">
-        <v>373</v>
-      </c>
-      <c r="J2" s="90" t="s">
-        <v>279</v>
+      <c r="H2" s="88" t="s">
+        <v>274</v>
+      </c>
+      <c r="I2" s="88" t="s">
+        <v>361</v>
+      </c>
+      <c r="J2" s="89" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B3" s="13" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
@@ -7678,380 +8366,380 @@
       </c>
     </row>
     <row r="5" spans="2:13" ht="26.25" customHeight="1">
-      <c r="B5" s="71" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="72" t="s">
+      <c r="B5" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="140" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="141"/>
+      <c r="F5" s="151" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="151"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="151"/>
+      <c r="K5" s="140" t="s">
+        <v>100</v>
+      </c>
+      <c r="L5" s="142"/>
+      <c r="M5" s="141"/>
+    </row>
+    <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B6" s="150" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="73" t="s">
+        <v>219</v>
+      </c>
+      <c r="D6" s="133" t="s">
+        <v>222</v>
+      </c>
+      <c r="E6" s="135"/>
+      <c r="F6" s="143" t="s">
+        <v>483</v>
+      </c>
+      <c r="G6" s="143"/>
+      <c r="H6" s="143"/>
+      <c r="I6" s="143"/>
+      <c r="J6" s="143"/>
+      <c r="K6" s="136" t="s">
+        <v>224</v>
+      </c>
+      <c r="L6" s="136"/>
+      <c r="M6" s="136"/>
+    </row>
+    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B7" s="150"/>
+      <c r="C7" s="51" t="s">
+        <v>220</v>
+      </c>
+      <c r="D7" s="133" t="s">
+        <v>221</v>
+      </c>
+      <c r="E7" s="135"/>
+      <c r="F7" s="137" t="s">
+        <v>223</v>
+      </c>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="138"/>
+      <c r="K7" s="133"/>
+      <c r="L7" s="134"/>
+      <c r="M7" s="135"/>
+    </row>
+    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B8" s="150" t="s">
+        <v>225</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="D8" s="133" t="s">
+        <v>226</v>
+      </c>
+      <c r="E8" s="135"/>
+      <c r="F8" s="143" t="s">
+        <v>228</v>
+      </c>
+      <c r="G8" s="143"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="143"/>
+      <c r="J8" s="143"/>
+      <c r="K8" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="L8" s="134"/>
+      <c r="M8" s="135"/>
+    </row>
+    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B9" s="150"/>
+      <c r="C9" s="51" t="s">
+        <v>220</v>
+      </c>
+      <c r="D9" s="133" t="s">
+        <v>227</v>
+      </c>
+      <c r="E9" s="135"/>
+      <c r="F9" s="137" t="s">
+        <v>229</v>
+      </c>
+      <c r="G9" s="138"/>
+      <c r="H9" s="138"/>
+      <c r="I9" s="138"/>
+      <c r="J9" s="138"/>
+      <c r="K9" s="133"/>
+      <c r="L9" s="134"/>
+      <c r="M9" s="135"/>
+    </row>
+    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B10" s="150" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="D10" s="133" t="s">
+        <v>232</v>
+      </c>
+      <c r="E10" s="135"/>
+      <c r="F10" s="143" t="s">
+        <v>234</v>
+      </c>
+      <c r="G10" s="143"/>
+      <c r="H10" s="143"/>
+      <c r="I10" s="143"/>
+      <c r="J10" s="143"/>
+      <c r="K10" s="133" t="s">
+        <v>236</v>
+      </c>
+      <c r="L10" s="134"/>
+      <c r="M10" s="135"/>
+    </row>
+    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B11" s="150"/>
+      <c r="C11" s="51" t="s">
+        <v>220</v>
+      </c>
+      <c r="D11" s="133" t="s">
+        <v>233</v>
+      </c>
+      <c r="E11" s="135"/>
+      <c r="F11" s="137" t="s">
+        <v>235</v>
+      </c>
+      <c r="G11" s="138"/>
+      <c r="H11" s="138"/>
+      <c r="I11" s="138"/>
+      <c r="J11" s="138"/>
+      <c r="K11" s="133"/>
+      <c r="L11" s="134"/>
+      <c r="M11" s="135"/>
+    </row>
+    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B12" s="150" t="s">
+        <v>237</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="D12" s="133" t="s">
+        <v>238</v>
+      </c>
+      <c r="E12" s="135"/>
+      <c r="F12" s="143" t="s">
+        <v>240</v>
+      </c>
+      <c r="G12" s="143"/>
+      <c r="H12" s="143"/>
+      <c r="I12" s="143"/>
+      <c r="J12" s="143"/>
+      <c r="K12" s="133" t="s">
+        <v>242</v>
+      </c>
+      <c r="L12" s="134"/>
+      <c r="M12" s="135"/>
+    </row>
+    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B13" s="150"/>
+      <c r="C13" s="51" t="s">
+        <v>220</v>
+      </c>
+      <c r="D13" s="133" t="s">
+        <v>239</v>
+      </c>
+      <c r="E13" s="135"/>
+      <c r="F13" s="137" t="s">
+        <v>241</v>
+      </c>
+      <c r="G13" s="138"/>
+      <c r="H13" s="138"/>
+      <c r="I13" s="138"/>
+      <c r="J13" s="138"/>
+      <c r="K13" s="133"/>
+      <c r="L13" s="134"/>
+      <c r="M13" s="135"/>
+    </row>
+    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B14" s="150" t="s">
+        <v>243</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="D14" s="133" t="s">
+        <v>244</v>
+      </c>
+      <c r="E14" s="135"/>
+      <c r="F14" s="143" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="143"/>
+      <c r="H14" s="143"/>
+      <c r="I14" s="143"/>
+      <c r="J14" s="143"/>
+      <c r="K14" s="133" t="s">
+        <v>279</v>
+      </c>
+      <c r="L14" s="134"/>
+      <c r="M14" s="135"/>
+    </row>
+    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B15" s="150"/>
+      <c r="C15" s="51" t="s">
+        <v>220</v>
+      </c>
+      <c r="D15" s="133" t="s">
+        <v>245</v>
+      </c>
+      <c r="E15" s="135"/>
+      <c r="F15" s="143" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="137" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="138"/>
-      <c r="F5" s="148" t="s">
-        <v>84</v>
-      </c>
-      <c r="G5" s="148"/>
-      <c r="H5" s="148"/>
-      <c r="I5" s="148"/>
-      <c r="J5" s="148"/>
-      <c r="K5" s="137" t="s">
-        <v>103</v>
-      </c>
-      <c r="L5" s="139"/>
-      <c r="M5" s="138"/>
-    </row>
-    <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B6" s="147" t="s">
-        <v>221</v>
-      </c>
-      <c r="C6" s="74" t="s">
-        <v>222</v>
-      </c>
-      <c r="D6" s="130" t="s">
-        <v>225</v>
-      </c>
-      <c r="E6" s="132"/>
-      <c r="F6" s="140" t="s">
-        <v>226</v>
-      </c>
-      <c r="G6" s="140"/>
-      <c r="H6" s="140"/>
-      <c r="I6" s="140"/>
-      <c r="J6" s="140"/>
-      <c r="K6" s="133" t="s">
-        <v>228</v>
-      </c>
-      <c r="L6" s="133"/>
-      <c r="M6" s="133"/>
-    </row>
-    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="147"/>
-      <c r="C7" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="D7" s="130" t="s">
-        <v>224</v>
-      </c>
-      <c r="E7" s="132"/>
-      <c r="F7" s="134" t="s">
-        <v>227</v>
-      </c>
-      <c r="G7" s="135"/>
-      <c r="H7" s="135"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="135"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="131"/>
-      <c r="M7" s="132"/>
-    </row>
-    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="147" t="s">
-        <v>229</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>222</v>
-      </c>
-      <c r="D8" s="130" t="s">
-        <v>230</v>
-      </c>
-      <c r="E8" s="132"/>
-      <c r="F8" s="140" t="s">
-        <v>232</v>
-      </c>
-      <c r="G8" s="140"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="140"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="130" t="s">
-        <v>234</v>
-      </c>
-      <c r="L8" s="131"/>
-      <c r="M8" s="132"/>
-    </row>
-    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="147"/>
-      <c r="C9" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="D9" s="130" t="s">
-        <v>231</v>
-      </c>
-      <c r="E9" s="132"/>
-      <c r="F9" s="134" t="s">
-        <v>233</v>
-      </c>
-      <c r="G9" s="135"/>
-      <c r="H9" s="135"/>
-      <c r="I9" s="135"/>
-      <c r="J9" s="135"/>
-      <c r="K9" s="130"/>
-      <c r="L9" s="131"/>
-      <c r="M9" s="132"/>
-    </row>
-    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B10" s="147" t="s">
-        <v>235</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>222</v>
-      </c>
-      <c r="D10" s="130" t="s">
-        <v>236</v>
-      </c>
-      <c r="E10" s="132"/>
-      <c r="F10" s="140" t="s">
-        <v>238</v>
-      </c>
-      <c r="G10" s="140"/>
-      <c r="H10" s="140"/>
-      <c r="I10" s="140"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="130" t="s">
-        <v>240</v>
-      </c>
-      <c r="L10" s="131"/>
-      <c r="M10" s="132"/>
-    </row>
-    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="147"/>
-      <c r="C11" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="D11" s="130" t="s">
-        <v>237</v>
-      </c>
-      <c r="E11" s="132"/>
-      <c r="F11" s="134" t="s">
-        <v>239</v>
-      </c>
-      <c r="G11" s="135"/>
-      <c r="H11" s="135"/>
-      <c r="I11" s="135"/>
-      <c r="J11" s="135"/>
-      <c r="K11" s="130"/>
-      <c r="L11" s="131"/>
-      <c r="M11" s="132"/>
-    </row>
-    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="147" t="s">
-        <v>241</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>222</v>
-      </c>
-      <c r="D12" s="130" t="s">
-        <v>242</v>
-      </c>
-      <c r="E12" s="132"/>
-      <c r="F12" s="140" t="s">
-        <v>244</v>
-      </c>
-      <c r="G12" s="140"/>
-      <c r="H12" s="140"/>
-      <c r="I12" s="140"/>
-      <c r="J12" s="140"/>
-      <c r="K12" s="130" t="s">
-        <v>246</v>
-      </c>
-      <c r="L12" s="131"/>
-      <c r="M12" s="132"/>
-    </row>
-    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B13" s="147"/>
-      <c r="C13" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="D13" s="130" t="s">
-        <v>243</v>
-      </c>
-      <c r="E13" s="132"/>
-      <c r="F13" s="134" t="s">
-        <v>245</v>
-      </c>
-      <c r="G13" s="135"/>
-      <c r="H13" s="135"/>
-      <c r="I13" s="135"/>
-      <c r="J13" s="135"/>
-      <c r="K13" s="130"/>
-      <c r="L13" s="131"/>
-      <c r="M13" s="132"/>
-    </row>
-    <row r="14" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B14" s="147" t="s">
-        <v>247</v>
-      </c>
-      <c r="C14" s="51" t="s">
-        <v>222</v>
-      </c>
-      <c r="D14" s="130" t="s">
-        <v>248</v>
-      </c>
-      <c r="E14" s="132"/>
-      <c r="F14" s="140" t="s">
-        <v>101</v>
-      </c>
-      <c r="G14" s="140"/>
-      <c r="H14" s="140"/>
-      <c r="I14" s="140"/>
-      <c r="J14" s="140"/>
-      <c r="K14" s="130" t="s">
-        <v>283</v>
-      </c>
-      <c r="L14" s="131"/>
-      <c r="M14" s="132"/>
-    </row>
-    <row r="15" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B15" s="147"/>
-      <c r="C15" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="D15" s="130" t="s">
-        <v>249</v>
-      </c>
-      <c r="E15" s="132"/>
-      <c r="F15" s="140" t="s">
-        <v>80</v>
-      </c>
-      <c r="G15" s="140"/>
-      <c r="H15" s="140"/>
-      <c r="I15" s="140"/>
-      <c r="J15" s="140"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="131"/>
-      <c r="M15" s="132"/>
+      <c r="G15" s="143"/>
+      <c r="H15" s="143"/>
+      <c r="I15" s="143"/>
+      <c r="J15" s="143"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="134"/>
+      <c r="M15" s="135"/>
     </row>
     <row r="16" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B16" s="144" t="s">
+      <c r="B16" s="147" t="s">
+        <v>276</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="D16" s="133" t="s">
+        <v>277</v>
+      </c>
+      <c r="E16" s="135"/>
+      <c r="F16" s="143" t="s">
+        <v>277</v>
+      </c>
+      <c r="G16" s="143"/>
+      <c r="H16" s="143"/>
+      <c r="I16" s="143"/>
+      <c r="J16" s="143"/>
+      <c r="K16" s="133" t="s">
         <v>280</v>
       </c>
-      <c r="C16" s="51" t="s">
-        <v>222</v>
-      </c>
-      <c r="D16" s="130" t="s">
-        <v>281</v>
-      </c>
-      <c r="E16" s="132"/>
-      <c r="F16" s="140" t="s">
-        <v>281</v>
-      </c>
-      <c r="G16" s="140"/>
-      <c r="H16" s="140"/>
-      <c r="I16" s="140"/>
-      <c r="J16" s="140"/>
-      <c r="K16" s="130" t="s">
-        <v>284</v>
-      </c>
-      <c r="L16" s="131"/>
-      <c r="M16" s="132"/>
+      <c r="L16" s="134"/>
+      <c r="M16" s="135"/>
     </row>
     <row r="17" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B17" s="146"/>
+      <c r="B17" s="149"/>
       <c r="C17" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="D17" s="130" t="s">
-        <v>282</v>
-      </c>
-      <c r="E17" s="132"/>
-      <c r="F17" s="140" t="s">
-        <v>282</v>
-      </c>
-      <c r="G17" s="140"/>
-      <c r="H17" s="140"/>
-      <c r="I17" s="140"/>
-      <c r="J17" s="140"/>
-      <c r="K17" s="130"/>
-      <c r="L17" s="131"/>
-      <c r="M17" s="132"/>
+        <v>220</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>278</v>
+      </c>
+      <c r="E17" s="135"/>
+      <c r="F17" s="143" t="s">
+        <v>278</v>
+      </c>
+      <c r="G17" s="143"/>
+      <c r="H17" s="143"/>
+      <c r="I17" s="143"/>
+      <c r="J17" s="143"/>
+      <c r="K17" s="133"/>
+      <c r="L17" s="134"/>
+      <c r="M17" s="135"/>
     </row>
     <row r="18" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B18" s="155" t="s">
-        <v>374</v>
+      <c r="B18" s="158" t="s">
+        <v>362</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>375</v>
-      </c>
-      <c r="D18" s="130" t="s">
-        <v>377</v>
-      </c>
-      <c r="E18" s="132"/>
-      <c r="F18" s="134" t="s">
-        <v>379</v>
-      </c>
-      <c r="G18" s="135"/>
-      <c r="H18" s="135"/>
-      <c r="I18" s="135"/>
-      <c r="J18" s="136"/>
-      <c r="K18" s="130" t="s">
-        <v>381</v>
-      </c>
-      <c r="L18" s="131"/>
-      <c r="M18" s="132"/>
+        <v>363</v>
+      </c>
+      <c r="D18" s="133" t="s">
+        <v>365</v>
+      </c>
+      <c r="E18" s="135"/>
+      <c r="F18" s="137" t="s">
+        <v>367</v>
+      </c>
+      <c r="G18" s="138"/>
+      <c r="H18" s="138"/>
+      <c r="I18" s="138"/>
+      <c r="J18" s="139"/>
+      <c r="K18" s="133" t="s">
+        <v>369</v>
+      </c>
+      <c r="L18" s="134"/>
+      <c r="M18" s="135"/>
     </row>
     <row r="19" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B19" s="156"/>
+      <c r="B19" s="159"/>
       <c r="C19" s="51" t="s">
-        <v>376</v>
-      </c>
-      <c r="D19" s="130" t="s">
-        <v>378</v>
-      </c>
-      <c r="E19" s="132"/>
-      <c r="F19" s="134" t="s">
-        <v>380</v>
-      </c>
-      <c r="G19" s="135"/>
-      <c r="H19" s="135"/>
-      <c r="I19" s="135"/>
-      <c r="J19" s="136"/>
+        <v>364</v>
+      </c>
+      <c r="D19" s="133" t="s">
+        <v>366</v>
+      </c>
+      <c r="E19" s="135"/>
+      <c r="F19" s="137" t="s">
+        <v>368</v>
+      </c>
+      <c r="G19" s="138"/>
+      <c r="H19" s="138"/>
+      <c r="I19" s="138"/>
+      <c r="J19" s="139"/>
       <c r="K19" s="63"/>
       <c r="L19" s="64"/>
       <c r="M19" s="65"/>
     </row>
     <row r="20" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B20" s="155" t="s">
-        <v>372</v>
+      <c r="B20" s="158" t="s">
+        <v>360</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>222</v>
-      </c>
-      <c r="D20" s="130" t="s">
-        <v>248</v>
-      </c>
-      <c r="E20" s="132"/>
-      <c r="F20" s="140" t="s">
-        <v>101</v>
-      </c>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="140"/>
-      <c r="J20" s="140"/>
-      <c r="K20" s="130" t="s">
-        <v>285</v>
-      </c>
-      <c r="L20" s="131"/>
-      <c r="M20" s="132"/>
+        <v>219</v>
+      </c>
+      <c r="D20" s="133" t="s">
+        <v>244</v>
+      </c>
+      <c r="E20" s="135"/>
+      <c r="F20" s="143" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="143"/>
+      <c r="H20" s="143"/>
+      <c r="I20" s="143"/>
+      <c r="J20" s="143"/>
+      <c r="K20" s="133" t="s">
+        <v>281</v>
+      </c>
+      <c r="L20" s="134"/>
+      <c r="M20" s="135"/>
     </row>
     <row r="21" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B21" s="156"/>
+      <c r="B21" s="159"/>
       <c r="C21" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="D21" s="130" t="s">
-        <v>249</v>
-      </c>
-      <c r="E21" s="132"/>
-      <c r="F21" s="140" t="s">
-        <v>80</v>
-      </c>
-      <c r="G21" s="140"/>
-      <c r="H21" s="140"/>
-      <c r="I21" s="140"/>
-      <c r="J21" s="140"/>
-      <c r="K21" s="130"/>
-      <c r="L21" s="131"/>
-      <c r="M21" s="132"/>
+        <v>220</v>
+      </c>
+      <c r="D21" s="133" t="s">
+        <v>245</v>
+      </c>
+      <c r="E21" s="135"/>
+      <c r="F21" s="143" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="143"/>
+      <c r="H21" s="143"/>
+      <c r="I21" s="143"/>
+      <c r="J21" s="143"/>
+      <c r="K21" s="133"/>
+      <c r="L21" s="134"/>
+      <c r="M21" s="135"/>
     </row>
   </sheetData>
   <mergeCells count="58">
@@ -8140,30 +8828,30 @@
         <v>0</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E2" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="H2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="14" t="s">
-        <v>313</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="H2" s="16" t="s">
+      <c r="I2" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="J2" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="15" t="s">
-        <v>315</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>45</v>
-      </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="B3" s="82" t="s">
-        <v>286</v>
+      <c r="B3" s="81" t="s">
+        <v>282</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>17</v>
@@ -8202,176 +8890,176 @@
       <c r="J4" s="36"/>
     </row>
     <row r="5" spans="2:13" ht="26.25" customHeight="1">
-      <c r="B5" s="71" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="72" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" s="137" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="138"/>
-      <c r="F5" s="148" t="s">
-        <v>84</v>
-      </c>
-      <c r="G5" s="148"/>
-      <c r="H5" s="148"/>
-      <c r="I5" s="148"/>
-      <c r="J5" s="148"/>
-      <c r="K5" s="137" t="s">
-        <v>103</v>
-      </c>
-      <c r="L5" s="139"/>
-      <c r="M5" s="138"/>
+      <c r="B5" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="140" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="141"/>
+      <c r="F5" s="151" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="151"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="151"/>
+      <c r="K5" s="140" t="s">
+        <v>100</v>
+      </c>
+      <c r="L5" s="142"/>
+      <c r="M5" s="141"/>
     </row>
     <row r="6" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B6" s="73">
+      <c r="B6" s="72">
         <v>0</v>
       </c>
-      <c r="C6" s="74" t="s">
+      <c r="C6" s="73" t="s">
+        <v>288</v>
+      </c>
+      <c r="D6" s="133" t="s">
+        <v>289</v>
+      </c>
+      <c r="E6" s="135"/>
+      <c r="F6" s="143"/>
+      <c r="G6" s="143"/>
+      <c r="H6" s="143"/>
+      <c r="I6" s="143"/>
+      <c r="J6" s="143"/>
+      <c r="K6" s="136" t="s">
+        <v>290</v>
+      </c>
+      <c r="L6" s="136"/>
+      <c r="M6" s="136"/>
+    </row>
+    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B7" s="150" t="s">
+        <v>291</v>
+      </c>
+      <c r="C7" s="51" t="s">
         <v>292</v>
       </c>
-      <c r="D6" s="130" t="s">
+      <c r="D7" s="133" t="s">
+        <v>295</v>
+      </c>
+      <c r="E7" s="135"/>
+      <c r="F7" s="143" t="s">
+        <v>296</v>
+      </c>
+      <c r="G7" s="143"/>
+      <c r="H7" s="143"/>
+      <c r="I7" s="143"/>
+      <c r="J7" s="143"/>
+      <c r="K7" s="133" t="s">
+        <v>299</v>
+      </c>
+      <c r="L7" s="134"/>
+      <c r="M7" s="135"/>
+    </row>
+    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B8" s="150"/>
+      <c r="C8" s="51" t="s">
         <v>293</v>
       </c>
-      <c r="E6" s="132"/>
-      <c r="F6" s="140"/>
-      <c r="G6" s="140"/>
-      <c r="H6" s="140"/>
-      <c r="I6" s="140"/>
-      <c r="J6" s="140"/>
-      <c r="K6" s="133" t="s">
-        <v>294</v>
-      </c>
-      <c r="L6" s="133"/>
-      <c r="M6" s="133"/>
-    </row>
-    <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="147" t="s">
-        <v>295</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>296</v>
-      </c>
-      <c r="D7" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="E7" s="132"/>
-      <c r="F7" s="140" t="s">
-        <v>300</v>
-      </c>
-      <c r="G7" s="140"/>
-      <c r="H7" s="140"/>
-      <c r="I7" s="140"/>
-      <c r="J7" s="140"/>
-      <c r="K7" s="130" t="s">
-        <v>303</v>
-      </c>
-      <c r="L7" s="131"/>
-      <c r="M7" s="132"/>
-    </row>
-    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="147"/>
-      <c r="C8" s="51" t="s">
+      <c r="D8" s="133" t="s">
+        <v>304</v>
+      </c>
+      <c r="E8" s="135"/>
+      <c r="F8" s="143" t="s">
         <v>297</v>
       </c>
-      <c r="D8" s="130" t="s">
-        <v>308</v>
-      </c>
-      <c r="E8" s="132"/>
-      <c r="F8" s="140" t="s">
-        <v>301</v>
-      </c>
-      <c r="G8" s="140"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="140"/>
-      <c r="J8" s="140"/>
+      <c r="G8" s="143"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="143"/>
+      <c r="J8" s="143"/>
       <c r="K8" s="63"/>
       <c r="L8" s="64"/>
       <c r="M8" s="65"/>
     </row>
     <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="147"/>
+      <c r="B9" s="150"/>
       <c r="C9" s="51" t="s">
+        <v>294</v>
+      </c>
+      <c r="D9" s="133" t="s">
+        <v>305</v>
+      </c>
+      <c r="E9" s="135"/>
+      <c r="F9" s="143" t="s">
         <v>298</v>
       </c>
-      <c r="D9" s="130" t="s">
-        <v>309</v>
-      </c>
-      <c r="E9" s="132"/>
-      <c r="F9" s="140" t="s">
+      <c r="G9" s="143"/>
+      <c r="H9" s="143"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="133"/>
+      <c r="L9" s="134"/>
+      <c r="M9" s="135"/>
+    </row>
+    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B10" s="158" t="s">
+        <v>437</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>300</v>
+      </c>
+      <c r="D10" s="133" t="s">
+        <v>303</v>
+      </c>
+      <c r="E10" s="135"/>
+      <c r="F10" s="143" t="s">
+        <v>308</v>
+      </c>
+      <c r="G10" s="143"/>
+      <c r="H10" s="143"/>
+      <c r="I10" s="143"/>
+      <c r="J10" s="143"/>
+      <c r="K10" s="133"/>
+      <c r="L10" s="134"/>
+      <c r="M10" s="135"/>
+    </row>
+    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B11" s="160"/>
+      <c r="C11" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="G9" s="140"/>
-      <c r="H9" s="140"/>
-      <c r="I9" s="140"/>
-      <c r="J9" s="140"/>
-      <c r="K9" s="130"/>
-      <c r="L9" s="131"/>
-      <c r="M9" s="132"/>
-    </row>
-    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B10" s="155" t="s">
-        <v>451</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>304</v>
-      </c>
-      <c r="D10" s="130" t="s">
-        <v>307</v>
-      </c>
-      <c r="E10" s="132"/>
-      <c r="F10" s="140" t="s">
-        <v>312</v>
-      </c>
-      <c r="G10" s="140"/>
-      <c r="H10" s="140"/>
-      <c r="I10" s="140"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="130"/>
-      <c r="L10" s="131"/>
-      <c r="M10" s="132"/>
-    </row>
-    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="157"/>
-      <c r="C11" s="51" t="s">
+      <c r="D11" s="133" t="s">
         <v>306</v>
       </c>
-      <c r="D11" s="130" t="s">
-        <v>310</v>
-      </c>
-      <c r="E11" s="132"/>
-      <c r="F11" s="140" t="s">
-        <v>312</v>
-      </c>
-      <c r="G11" s="140"/>
-      <c r="H11" s="140"/>
-      <c r="I11" s="140"/>
-      <c r="J11" s="140"/>
+      <c r="E11" s="135"/>
+      <c r="F11" s="143" t="s">
+        <v>308</v>
+      </c>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
       <c r="K11" s="63"/>
       <c r="L11" s="64"/>
       <c r="M11" s="65"/>
     </row>
     <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="156"/>
+      <c r="B12" s="159"/>
       <c r="C12" s="51" t="s">
-        <v>305</v>
-      </c>
-      <c r="D12" s="130" t="s">
-        <v>311</v>
-      </c>
-      <c r="E12" s="132"/>
-      <c r="F12" s="140" t="s">
-        <v>312</v>
-      </c>
-      <c r="G12" s="140"/>
-      <c r="H12" s="140"/>
-      <c r="I12" s="140"/>
-      <c r="J12" s="140"/>
-      <c r="K12" s="130"/>
-      <c r="L12" s="131"/>
-      <c r="M12" s="132"/>
+        <v>301</v>
+      </c>
+      <c r="D12" s="133" t="s">
+        <v>307</v>
+      </c>
+      <c r="E12" s="135"/>
+      <c r="F12" s="143" t="s">
+        <v>308</v>
+      </c>
+      <c r="G12" s="143"/>
+      <c r="H12" s="143"/>
+      <c r="I12" s="143"/>
+      <c r="J12" s="143"/>
+      <c r="K12" s="133"/>
+      <c r="L12" s="134"/>
+      <c r="M12" s="135"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -8410,7 +9098,7 @@
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="B1:K3"/>
+  <dimension ref="B1:K7"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
@@ -8419,43 +9107,85 @@
   <sheetData>
     <row r="1" spans="2:11" ht="6" customHeight="1"/>
     <row r="2" spans="2:11" ht="26.25" customHeight="1">
-      <c r="B2" s="137" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="138"/>
-      <c r="D2" s="148" t="s">
-        <v>84</v>
-      </c>
-      <c r="E2" s="148"/>
-      <c r="F2" s="148"/>
-      <c r="G2" s="148"/>
-      <c r="H2" s="148"/>
-      <c r="I2" s="137" t="s">
-        <v>103</v>
-      </c>
-      <c r="J2" s="139"/>
-      <c r="K2" s="138"/>
+      <c r="B2" s="140" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="141"/>
+      <c r="D2" s="151" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="140" t="s">
+        <v>100</v>
+      </c>
+      <c r="J2" s="142"/>
+      <c r="K2" s="141"/>
     </row>
     <row r="3" spans="2:11" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="130" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" s="132"/>
-      <c r="D3" s="140" t="s">
-        <v>352</v>
-      </c>
-      <c r="E3" s="140"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="140"/>
-      <c r="I3" s="133" t="s">
-        <v>353</v>
-      </c>
-      <c r="J3" s="133"/>
-      <c r="K3" s="133"/>
+      <c r="B3" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="135"/>
+      <c r="D3" s="143" t="s">
+        <v>343</v>
+      </c>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="143"/>
+      <c r="I3" s="136" t="s">
+        <v>344</v>
+      </c>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+    </row>
+    <row r="4" spans="2:11" ht="20.100000000000001" customHeight="1">
+      <c r="B4" s="176" t="s">
+        <v>487</v>
+      </c>
+      <c r="C4" s="177"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="143"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
+      <c r="K4" s="136"/>
+    </row>
+    <row r="5" spans="2:11" ht="20.100000000000001" customHeight="1">
+      <c r="B5" s="178"/>
+      <c r="C5" s="179"/>
+      <c r="D5" s="143"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="143"/>
+      <c r="G5" s="143"/>
+      <c r="H5" s="143"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="136"/>
+    </row>
+    <row r="6" spans="2:11" ht="20.100000000000001" customHeight="1">
+      <c r="B6" s="176" t="s">
+        <v>488</v>
+      </c>
+      <c r="C6" s="177"/>
+    </row>
+    <row r="7" spans="2:11" ht="20.100000000000001" customHeight="1">
+      <c r="B7" s="178"/>
+      <c r="C7" s="179"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="12">
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="B4:C5"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="I2:K2"/>
@@ -8473,7 +9203,7 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="B1:M12"/>
+  <dimension ref="B1:M13"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
@@ -8486,10 +9216,10 @@
         <v>14</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1">
@@ -8515,185 +9245,201 @@
       </c>
     </row>
     <row r="6" spans="2:13" ht="26.25" customHeight="1">
-      <c r="B6" s="71" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="72" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="137" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="138"/>
-      <c r="F6" s="148" t="s">
-        <v>84</v>
-      </c>
-      <c r="G6" s="148"/>
-      <c r="H6" s="148"/>
-      <c r="I6" s="148"/>
-      <c r="J6" s="148"/>
-      <c r="K6" s="137" t="s">
-        <v>103</v>
-      </c>
-      <c r="L6" s="139"/>
-      <c r="M6" s="138"/>
+      <c r="B6" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="140" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="141"/>
+      <c r="F6" s="151" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" s="151"/>
+      <c r="H6" s="151"/>
+      <c r="I6" s="151"/>
+      <c r="J6" s="151"/>
+      <c r="K6" s="140" t="s">
+        <v>100</v>
+      </c>
+      <c r="L6" s="142"/>
+      <c r="M6" s="141"/>
     </row>
     <row r="7" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B7" s="144" t="s">
+      <c r="B7" s="147" t="s">
+        <v>347</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>491</v>
+      </c>
+      <c r="D7" s="133" t="s">
+        <v>355</v>
+      </c>
+      <c r="E7" s="135"/>
+      <c r="F7" s="143" t="s">
         <v>356</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="G7" s="143"/>
+      <c r="H7" s="143"/>
+      <c r="I7" s="143"/>
+      <c r="J7" s="143"/>
+      <c r="K7" s="136" t="s">
+        <v>359</v>
+      </c>
+      <c r="L7" s="136"/>
+      <c r="M7" s="136"/>
+    </row>
+    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B8" s="148"/>
+      <c r="C8" s="180" t="s">
+        <v>493</v>
+      </c>
+      <c r="D8" s="121"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="124"/>
+      <c r="G8" s="124"/>
+      <c r="H8" s="124"/>
+      <c r="I8" s="124"/>
+      <c r="J8" s="124"/>
+      <c r="K8" s="121"/>
+      <c r="L8" s="122"/>
+      <c r="M8" s="123"/>
+    </row>
+    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B9" s="148"/>
+      <c r="C9" s="51" t="s">
+        <v>348</v>
+      </c>
+      <c r="D9" s="133" t="s">
+        <v>355</v>
+      </c>
+      <c r="E9" s="135"/>
+      <c r="F9" s="143" t="s">
         <v>357</v>
       </c>
-      <c r="D7" s="130" t="s">
-        <v>367</v>
-      </c>
-      <c r="E7" s="132"/>
-      <c r="F7" s="140" t="s">
-        <v>368</v>
-      </c>
-      <c r="G7" s="140"/>
-      <c r="H7" s="140"/>
-      <c r="I7" s="140"/>
-      <c r="J7" s="140"/>
-      <c r="K7" s="133" t="s">
-        <v>371</v>
-      </c>
-      <c r="L7" s="133"/>
-      <c r="M7" s="133"/>
-    </row>
-    <row r="8" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B8" s="145"/>
-      <c r="C8" s="51" t="s">
+      <c r="G9" s="143"/>
+      <c r="H9" s="143"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="64"/>
+      <c r="M9" s="65"/>
+    </row>
+    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B10" s="149"/>
+      <c r="C10" s="51" t="s">
+        <v>492</v>
+      </c>
+      <c r="D10" s="133" t="s">
+        <v>355</v>
+      </c>
+      <c r="E10" s="135"/>
+      <c r="F10" s="143" t="s">
         <v>358</v>
       </c>
-      <c r="D8" s="130" t="s">
-        <v>367</v>
-      </c>
-      <c r="E8" s="132"/>
-      <c r="F8" s="140" t="s">
-        <v>369</v>
-      </c>
-      <c r="G8" s="140"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="140"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="65"/>
-    </row>
-    <row r="9" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B9" s="146"/>
-      <c r="C9" s="51" t="s">
-        <v>359</v>
-      </c>
-      <c r="D9" s="130" t="s">
-        <v>367</v>
-      </c>
-      <c r="E9" s="132"/>
-      <c r="F9" s="140" t="s">
+      <c r="G10" s="143"/>
+      <c r="H10" s="143"/>
+      <c r="I10" s="143"/>
+      <c r="J10" s="143"/>
+      <c r="K10" s="133"/>
+      <c r="L10" s="134"/>
+      <c r="M10" s="135"/>
+    </row>
+    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B11" s="150" t="s">
+        <v>349</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>247</v>
+      </c>
+      <c r="D11" s="133" t="s">
+        <v>351</v>
+      </c>
+      <c r="E11" s="135"/>
+      <c r="F11" s="137" t="s">
+        <v>352</v>
+      </c>
+      <c r="G11" s="138"/>
+      <c r="H11" s="138"/>
+      <c r="I11" s="138"/>
+      <c r="J11" s="138"/>
+      <c r="K11" s="133" t="s">
+        <v>354</v>
+      </c>
+      <c r="L11" s="134"/>
+      <c r="M11" s="135"/>
+    </row>
+    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B12" s="150"/>
+      <c r="C12" s="181" t="s">
+        <v>350</v>
+      </c>
+      <c r="D12" s="182" t="s">
+        <v>353</v>
+      </c>
+      <c r="E12" s="183"/>
+      <c r="F12" s="184" t="s">
+        <v>494</v>
+      </c>
+      <c r="G12" s="185"/>
+      <c r="H12" s="185"/>
+      <c r="I12" s="185"/>
+      <c r="J12" s="185"/>
+      <c r="K12" s="133"/>
+      <c r="L12" s="134"/>
+      <c r="M12" s="135"/>
+    </row>
+    <row r="13" spans="2:13" ht="20.100000000000001" customHeight="1">
+      <c r="B13" s="186" t="s">
         <v>370</v>
       </c>
-      <c r="G9" s="140"/>
-      <c r="H9" s="140"/>
-      <c r="I9" s="140"/>
-      <c r="J9" s="140"/>
-      <c r="K9" s="130"/>
-      <c r="L9" s="131"/>
-      <c r="M9" s="132"/>
-    </row>
-    <row r="10" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B10" s="147" t="s">
-        <v>360</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="D10" s="130" t="s">
-        <v>362</v>
-      </c>
-      <c r="E10" s="132"/>
-      <c r="F10" s="134" t="s">
-        <v>363</v>
-      </c>
-      <c r="G10" s="135"/>
-      <c r="H10" s="135"/>
-      <c r="I10" s="135"/>
-      <c r="J10" s="135"/>
-      <c r="K10" s="130" t="s">
-        <v>366</v>
-      </c>
-      <c r="L10" s="131"/>
-      <c r="M10" s="132"/>
-    </row>
-    <row r="11" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B11" s="147"/>
-      <c r="C11" s="51" t="s">
-        <v>361</v>
-      </c>
-      <c r="D11" s="130" t="s">
-        <v>364</v>
-      </c>
-      <c r="E11" s="132"/>
-      <c r="F11" s="134" t="s">
-        <v>365</v>
-      </c>
-      <c r="G11" s="135"/>
-      <c r="H11" s="135"/>
-      <c r="I11" s="135"/>
-      <c r="J11" s="135"/>
-      <c r="K11" s="130"/>
-      <c r="L11" s="131"/>
-      <c r="M11" s="132"/>
-    </row>
-    <row r="12" spans="2:13" ht="20.100000000000001" customHeight="1">
-      <c r="B12" s="73" t="s">
-        <v>382</v>
-      </c>
-      <c r="C12" s="73" t="s">
-        <v>382</v>
-      </c>
-      <c r="D12" s="130" t="s">
-        <v>382</v>
-      </c>
-      <c r="E12" s="132"/>
-      <c r="F12" s="134" t="s">
-        <v>317</v>
-      </c>
-      <c r="G12" s="135"/>
-      <c r="H12" s="135"/>
-      <c r="I12" s="135"/>
-      <c r="J12" s="136"/>
-      <c r="K12" s="130" t="s">
-        <v>366</v>
-      </c>
-      <c r="L12" s="131"/>
-      <c r="M12" s="132"/>
+      <c r="C13" s="186" t="s">
+        <v>370</v>
+      </c>
+      <c r="D13" s="182" t="s">
+        <v>370</v>
+      </c>
+      <c r="E13" s="183"/>
+      <c r="F13" s="184" t="s">
+        <v>495</v>
+      </c>
+      <c r="G13" s="185"/>
+      <c r="H13" s="185"/>
+      <c r="I13" s="185"/>
+      <c r="J13" s="187"/>
+      <c r="K13" s="133" t="s">
+        <v>354</v>
+      </c>
+      <c r="L13" s="134"/>
+      <c r="M13" s="135"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="K11:M11"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="F12:J12"/>
     <mergeCell ref="K12:M12"/>
-    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="K7:M7"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="F10:J10"/>
     <mergeCell ref="K10:M10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="K7:M7"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="F9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:J8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
